--- a/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
+++ b/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
@@ -21196,4248 +21196,4281 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="72" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="88" t="str">
-        <x:v>Job Title</x:v>
-      </x:c>
-      <x:c r="B1" s="88" t="str">
-        <x:v>Salary Scale</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>Supplier Type</x:v>
-      </x:c>
-      <x:c r="D1" s="88" t="str">
-        <x:v>Scale</x:v>
-      </x:c>
-      <x:c r="E1" s="88" t="str">
-        <x:v>Minimum</x:v>
-      </x:c>
-      <x:c r="F1" s="88" t="str">
-        <x:v>Midpoint</x:v>
-      </x:c>
-      <x:c r="G1" s="88" t="str">
-        <x:v>Maximum</x:v>
-      </x:c>
-      <x:c r="I1" s="88" t="str">
-        <x:v>PIR from</x:v>
-      </x:c>
-      <x:c r="J1" s="88" t="str">
-        <x:v>Range Band</x:v>
-      </x:c>
-      <x:c r="K1" s="88" t="str">
-        <x:v>Merit 2026</x:v>
-      </x:c>
-      <x:c r="L1" s="88" t="str">
-        <x:v>Merit 2027</x:v>
-      </x:c>
-      <x:c r="N1" s="88" t="str">
-        <x:v>Assumption</x:v>
-      </x:c>
-      <x:c r="O1" s="88" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="90" t="str">
-        <x:v>Accountant - II - Finance &amp; Legal (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B2" s="90" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="E2" s="93" t="n">
-        <x:v>24300</x:v>
-      </x:c>
-      <x:c r="F2" s="93" t="n">
-        <x:v>33600</x:v>
-      </x:c>
-      <x:c r="G2" s="93" t="n">
-        <x:v>42300</x:v>
-      </x:c>
-      <x:c r="I2" s="94" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>Onder het minimum</x:v>
-      </x:c>
-      <x:c r="K2" s="95" t="n">
-        <x:v>0.048</x:v>
-      </x:c>
-      <x:c r="L2" s="95" t="n">
-        <x:v>0.0495</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>Month factor</x:v>
-      </x:c>
-      <x:c r="O2" s="96" t="n">
-        <x:v>13.32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="91" t="str">
-        <x:v>Accountant - III - Finance &amp; Legal (B Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B3" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E3" s="93" t="n">
-        <x:v>31400</x:v>
-      </x:c>
-      <x:c r="F3" s="93" t="n">
-        <x:v>42400</x:v>
-      </x:c>
-      <x:c r="G3" s="93" t="n">
-        <x:v>53400</x:v>
-      </x:c>
-      <x:c r="I3" s="94" t="n">
-        <x:v>0.741</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>1e derde deel</x:v>
-      </x:c>
-      <x:c r="K3" s="95" t="n">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="L3" s="95" t="n">
-        <x:v>0.041299999999999996</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
-        <x:v>Hour factor</x:v>
-      </x:c>
-      <x:c r="O3" s="96" t="n">
-        <x:v>173.93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="91" t="str">
-        <x:v>Administrative Assistant - II - Business Support (A) Admin/Finance/HR - B2</x:v>
-      </x:c>
-      <x:c r="B4" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E4" s="93" t="n">
-        <x:v>34400</x:v>
-      </x:c>
-      <x:c r="F4" s="93" t="n">
-        <x:v>46500</x:v>
-      </x:c>
-      <x:c r="G4" s="93" t="n">
-        <x:v>58600</x:v>
-      </x:c>
-      <x:c r="I4" s="94" t="n">
-        <x:v>0.914</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>2e derde deel</x:v>
-      </x:c>
-      <x:c r="K4" s="95" t="n">
-        <x:v>0.032</x:v>
-      </x:c>
-      <x:c r="L4" s="95" t="n">
-        <x:v>0.033</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
-        <x:v>GS markup factor</x:v>
-      </x:c>
-      <x:c r="O4" s="96" t="n">
-        <x:v>2.45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="91" t="str">
-        <x:v>Administrative Assistant - III - Business Support (A) Admin/Finance/HR - B3</x:v>
-      </x:c>
-      <x:c r="B5" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="E5" s="93" t="n">
-        <x:v>37800</x:v>
-      </x:c>
-      <x:c r="F5" s="93" t="n">
-        <x:v>51100</x:v>
-      </x:c>
-      <x:c r="G5" s="93" t="n">
-        <x:v>64400</x:v>
-      </x:c>
-      <x:c r="I5" s="94" t="n">
-        <x:v>1.086</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>3e derde deel</x:v>
-      </x:c>
-      <x:c r="K5" s="95" t="n">
-        <x:v>0.022400000000000003</x:v>
-      </x:c>
-      <x:c r="L5" s="95" t="n">
-        <x:v>0.0231</x:v>
-      </x:c>
-      <x:c r="N5" t="str">
-        <x:v>PS markup factor</x:v>
-      </x:c>
-      <x:c r="O5" s="96" t="n">
-        <x:v>2.55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="91" t="str">
-        <x:v>Analytical Chemist - I - LAB (B Support / Research) - R1</x:v>
-      </x:c>
-      <x:c r="B6" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="E6" s="93" t="n">
-        <x:v>41600</x:v>
-      </x:c>
-      <x:c r="F6" s="93" t="n">
-        <x:v>56100</x:v>
-      </x:c>
-      <x:c r="G6" s="93" t="n">
-        <x:v>70600</x:v>
-      </x:c>
-      <x:c r="I6" s="94" t="n">
-        <x:v>1.259</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>Boven het maximum</x:v>
-      </x:c>
-      <x:c r="K6" s="95" t="n">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="L6" s="95" t="n">
-        <x:v>0.0165</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="91" t="str">
-        <x:v>Assembler - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</x:v>
-      </x:c>
-      <x:c r="B7" s="91" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="E7" s="93" t="n">
-        <x:v>45800</x:v>
-      </x:c>
-      <x:c r="F7" s="93" t="n">
-        <x:v>61800</x:v>
-      </x:c>
-      <x:c r="G7" s="93" t="n">
-        <x:v>77800</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="91" t="str">
-        <x:v>Automation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B8" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="E8" s="93" t="n">
-        <x:v>50200</x:v>
-      </x:c>
-      <x:c r="F8" s="93" t="n">
-        <x:v>67800</x:v>
-      </x:c>
-      <x:c r="G8" s="93" t="n">
-        <x:v>85400</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="91" t="str">
-        <x:v>Biochemical Operator – ll - Production &amp; Operations Support (T): Industrial – O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B9" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="E9" s="93" t="n">
-        <x:v>55200</x:v>
-      </x:c>
-      <x:c r="F9" s="93" t="n">
-        <x:v>74600</x:v>
-      </x:c>
-      <x:c r="G9" s="93" t="n">
-        <x:v>93900</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="91" t="str">
-        <x:v>Biochemist - I - LAB (B Support / Research) - R1</x:v>
-      </x:c>
-      <x:c r="B10" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>I</x:v>
-      </x:c>
-      <x:c r="E10" s="93" t="n">
-        <x:v>60700</x:v>
-      </x:c>
-      <x:c r="F10" s="93" t="n">
-        <x:v>81900</x:v>
-      </x:c>
-      <x:c r="G10" s="93" t="n">
-        <x:v>103200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="91" t="str">
-        <x:v>Biologist - I - LAB (B Support / Research) - R1</x:v>
-      </x:c>
-      <x:c r="B11" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="E11" s="93" t="n">
-        <x:v>66800</x:v>
-      </x:c>
-      <x:c r="F11" s="93" t="n">
-        <x:v>90200</x:v>
-      </x:c>
-      <x:c r="G11" s="93" t="n">
-        <x:v>113600</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="91" t="str">
-        <x:v>Business Analyst - II - Information Communications Technology (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B12" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>K</x:v>
-      </x:c>
-      <x:c r="E12" s="93" t="n">
-        <x:v>73400</x:v>
-      </x:c>
-      <x:c r="F12" s="93" t="n">
-        <x:v>99000</x:v>
-      </x:c>
-      <x:c r="G12" s="93" t="n">
-        <x:v>124700</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="91" t="str">
-        <x:v>Business Analyst - III - Information Communications Technology (B Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B13" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="E13" s="93" t="n">
-        <x:v>80800</x:v>
-      </x:c>
-      <x:c r="F13" s="93" t="n">
-        <x:v>109000</x:v>
-      </x:c>
-      <x:c r="G13" s="93" t="n">
-        <x:v>137300</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="91" t="str">
-        <x:v>Business Analyst - IV - Information Communications Technology (B Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B14" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>M</x:v>
-      </x:c>
-      <x:c r="E14" s="93" t="n">
-        <x:v>88800</x:v>
-      </x:c>
-      <x:c r="F14" s="93" t="n">
-        <x:v>119900</x:v>
-      </x:c>
-      <x:c r="G14" s="93" t="n">
-        <x:v>150900</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="91" t="str">
-        <x:v>Business Consultant - IV - Information Communications Technology (B Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B15" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="91" t="str">
-        <x:v>Chemical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B16" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="91" t="str">
-        <x:v>Civil Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B17" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="91" t="str">
-        <x:v>Civil Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B18" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="91" t="str">
-        <x:v>Compliance Specialist - I - Administrative (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B19" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="91" t="str">
-        <x:v>Data Analyst - II - Information Communications Technology (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B20" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="91" t="str">
-        <x:v>Data Entry Clerk - III - Business Support (A) Admin/Finance/HR - B3</x:v>
-      </x:c>
-      <x:c r="B21" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="91" t="str">
-        <x:v>Documentation Specialist - I - Administrative (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B22" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="91" t="str">
-        <x:v>Documentation Specialist - III - Administrative (B Support / Professional) - B3</x:v>
-      </x:c>
-      <x:c r="B23" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="91" t="str">
-        <x:v>Electrical Engineer - I - Engineering (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B24" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="91" t="str">
-        <x:v>Electrical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B25" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="91" t="str">
-        <x:v>Environmental Monitoring Specialist II - Environment Health &amp; Safety P&amp;O Support / Professional P2</x:v>
-      </x:c>
-      <x:c r="B26" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="91" t="str">
-        <x:v>Executive Assistant - II - Business Support (A) Admin/Finance/HR - B2</x:v>
-      </x:c>
-      <x:c r="B27" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="91" t="str">
-        <x:v>Health/Safety Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B28" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="91" t="str">
-        <x:v>Health/Safety Specialist - III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B29" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C29" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="91" t="str">
-        <x:v>Health/Safety Specialist - IV - Environment Health &amp; Safety (P &amp; O Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B30" s="91" t="str">
-        <x:v>M</x:v>
-      </x:c>
-      <x:c r="C30" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="91" t="str">
-        <x:v>HR Analyst - I - Human Resources (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B31" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="91" t="str">
-        <x:v>HR Analyst - II - Human Resources (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B32" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="91" t="str">
-        <x:v>Industrial Hygienist - I - Environment Health  &amp; Safety P&amp;O Support / Professional - P1</x:v>
-      </x:c>
-      <x:c r="B33" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="91" t="str">
-        <x:v>Industrial Hygienist - II - Environment  Health &amp; Safety P&amp;O Support / Professional - P2</x:v>
-      </x:c>
-      <x:c r="B34" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="91" t="str">
-        <x:v>Inspector Operator - III - Industrial (P &amp; O Support / Professional) - O3</x:v>
-      </x:c>
-      <x:c r="B35" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C35" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="91" t="str">
-        <x:v>Lab Assistant - III - Business Support (T) Science/Medical/Clinical - B3</x:v>
-      </x:c>
-      <x:c r="B36" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C36" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="91" t="str">
-        <x:v>Lab Technician - Animal - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mi</x:v>
-      </x:c>
-      <x:c r="B37" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C37" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="91" t="str">
-        <x:v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (High)</x:v>
-      </x:c>
-      <x:c r="B38" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C38" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="91" t="str">
-        <x:v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B39" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C39" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="91" t="str">
-        <x:v>Lab Technician - III - Production &amp; Operations Support (T) Science/Medical/Clinical - O3</x:v>
-      </x:c>
-      <x:c r="B40" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C40" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="91" t="str">
-        <x:v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial - O2 (High)</x:v>
-      </x:c>
-      <x:c r="B41" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C41" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="91" t="str">
-        <x:v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O2 High – PS</x:v>
-      </x:c>
-      <x:c r="B42" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C42" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="91" t="str">
-        <x:v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O3 – PS</x:v>
-      </x:c>
-      <x:c r="B43" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C43" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="91" t="str">
-        <x:v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O4 – PS</x:v>
-      </x:c>
-      <x:c r="B44" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C44" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="91" t="str">
-        <x:v>Maintenance Technician - IV - Production &amp; Operations Support (T): Industrial - O4</x:v>
-      </x:c>
-      <x:c r="B45" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C45" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="91" t="str">
-        <x:v>Marketing Research Specialist - II - Creative (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B46" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C46" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="91" t="str">
-        <x:v>Mechanical Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B47" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C47" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="91" t="str">
-        <x:v>Mechanical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B48" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C48" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="91" t="str">
-        <x:v>Operations Manager - I - Industrial (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B49" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C49" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="91" t="str">
-        <x:v>Operations Manager - II - Industrial (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B50" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C50" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="91" t="str">
-        <x:v>Operations Manager - IV - Industrial (P &amp; O Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B51" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C51" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="91" t="str">
-        <x:v>Packaging Engineer - II - Industrial (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B52" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C52" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="91" t="str">
-        <x:v>Packaging Operator - I - Production &amp; Operations Support (T): Industrial - O1</x:v>
-      </x:c>
-      <x:c r="B53" s="91" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C53" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="91" t="str">
-        <x:v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</x:v>
-      </x:c>
-      <x:c r="B54" s="91" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C54" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="91" t="str">
-        <x:v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B55" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C55" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="91" t="str">
-        <x:v>Packaging Operator - III - Production &amp; Operations Support (T): Industrial - O3</x:v>
-      </x:c>
-      <x:c r="B56" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C56" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="91" t="str">
-        <x:v>Pharmaceutical Specialist - I - Engineering (P &amp; O  Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B57" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C57" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="91" t="str">
-        <x:v>Pharmaceutical Specialist - Ill - Engineering (P &amp; O  Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B58" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C58" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="91" t="str">
-        <x:v>Process Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B59" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C59" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="91" t="str">
-        <x:v>Process Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B60" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C60" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="91" t="str">
-        <x:v>Process Engineer - IV - Engineering (P &amp; O Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B61" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C61" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="91" t="str">
-        <x:v>Procurement Specialist - llI - Administrative (B Support /  Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B62" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C62" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="91" t="str">
-        <x:v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (High)</x:v>
-      </x:c>
-      <x:c r="B63" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C63" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="91" t="str">
-        <x:v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B64" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C64" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="91" t="str">
-        <x:v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (High)</x:v>
-      </x:c>
-      <x:c r="B65" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C65" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="91" t="str">
-        <x:v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B66" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C66" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="91" t="str">
-        <x:v>Project Coordinator - I - Administrative (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B67" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C67" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="91" t="str">
-        <x:v>Project Coordinator - II - Administrative (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B68" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C68" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="91" t="str">
-        <x:v>Project Manager - Il - Engineering (P &amp; O Support /  Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B69" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C69" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="91" t="str">
-        <x:v>Project Manager - Ill - Engineering (P &amp; O Support /  Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B70" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C70" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="91" t="str">
-        <x:v>Project Manager - IT - II - Information Communications Technology (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B71" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C71" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="91" t="str">
-        <x:v>Project Manager - IT - III - Information Communications Technology (B Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B72" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C72" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="91" t="str">
-        <x:v>Project Manager - IT - IV - Information Communications Technology (B Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B73" s="91" t="str">
-        <x:v>M</x:v>
-      </x:c>
-      <x:c r="C73" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="91" t="str">
-        <x:v>Project Manager - IV - Engineering (P &amp; O Support /  Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B74" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C74" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="91" t="str">
-        <x:v>Project Manager - Non IT - II - Administrative (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B75" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C75" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="91" t="str">
-        <x:v>Project Manager - Non IT - III - Administrative (B Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B76" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C76" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="91" t="str">
-        <x:v>Project Manager - Non IT - IV - Administrative (B Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B77" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C77" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="91" t="str">
-        <x:v>Qualified Person - III - Administrative (B Support /  Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B78" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C78" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="91" t="str">
-        <x:v>Quality Assurance - Packaging - I - Industrial (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B79" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C79" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="91" t="str">
-        <x:v>Quality Assurance - Packaging - II - Industrial (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B80" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C80" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="91" t="str">
-        <x:v>Quality Assurance - Packaging - IV - Industrial (P &amp; O Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B81" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C81" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="91" t="str">
-        <x:v>Quality Auditor - I - Administrative (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B82" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C82" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="91" t="str">
-        <x:v>Quality Auditor - II - Administrative (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B83" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C83" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="91" t="str">
-        <x:v>Quality Auditor - III - Administrative (B Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B84" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C84" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="91" t="str">
-        <x:v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (High)</x:v>
-      </x:c>
-      <x:c r="B85" s="91" t="str">
-        <x:v>D</x:v>
-      </x:c>
-      <x:c r="C85" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="91" t="str">
-        <x:v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B86" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C86" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="91" t="str">
-        <x:v>Quality Control Specialist - III - LAB (O Support / Research) - O3</x:v>
-      </x:c>
-      <x:c r="B87" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C87" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="91" t="str">
-        <x:v>Quality Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B88" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C88" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="91" t="str">
-        <x:v>Regulatory Affairs Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B89" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C89" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="91" t="str">
-        <x:v>Regulatory Affairs Specialist III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B90" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C90" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="91" t="str">
-        <x:v>Reliability Engineer - I - Engineering (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B91" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C91" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92" s="91" t="str">
-        <x:v>Reliability Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B92" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C92" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93" s="91" t="str">
-        <x:v>Reliability Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B93" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C93" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="91" t="str">
-        <x:v>Reliability Engineer - IV - Engineering (P &amp; O Support / Professional) - O4</x:v>
-      </x:c>
-      <x:c r="B94" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C94" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="91" t="str">
-        <x:v>Sales Assistant - I - Administrative (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B95" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C95" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="91" t="str">
-        <x:v>Scientific Technical Specialist - I - Engineering (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B96" s="91" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C96" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="91" t="str">
-        <x:v>Scientific Technical Specialist - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B97" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C97" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="91" t="str">
-        <x:v>Scientific Technical Specialist - III - Engineering (P &amp; O Support / Professional) - O3</x:v>
-      </x:c>
-      <x:c r="B98" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C98" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="91" t="str">
-        <x:v>Scientist - I - Science (P &amp; O / Research) - R1</x:v>
-      </x:c>
-      <x:c r="B99" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C99" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="91" t="str">
-        <x:v>Scientist - I - Science (P &amp; O / Research) - R1 - GS</x:v>
-      </x:c>
-      <x:c r="B100" s="91" t="str">
-        <x:v>E</x:v>
-      </x:c>
-      <x:c r="C100" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="91" t="str">
-        <x:v>Scientist - II - Science (P &amp; O / Research) - R2</x:v>
-      </x:c>
-      <x:c r="B101" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C101" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="91" t="str">
-        <x:v>Scientist - III - Science (P &amp; O / Research) - R3</x:v>
-      </x:c>
-      <x:c r="B102" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C102" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="91" t="str">
-        <x:v>Shipping/Receiving Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B103" s="91" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C103" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="91" t="str">
-        <x:v>Supply Chain Specialist - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B104" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C104" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="91" t="str">
-        <x:v>Supply Chain Specialist - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B105" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C105" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="91" t="str">
-        <x:v>Supply Chain Specialist - IV - Engineering (P &amp; O Support / Professional) - P4</x:v>
-      </x:c>
-      <x:c r="B106" s="91" t="str">
-        <x:v>L</x:v>
-      </x:c>
-      <x:c r="C106" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="91" t="str">
-        <x:v>Technical Support Analyst - I - Information Communications Tech (B Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B107" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C107" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="91" t="str">
-        <x:v>Technical Support Analyst - II - Information Communications Tech (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B108" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C108" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109">
-      <x:c r="A109" s="91" t="str">
-        <x:v>Technical Writer - II - Information Communications Technology (B Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B109" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C109" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="91" t="str">
-        <x:v>Validation Engineer - I - Engineering (P &amp; O Support / Professional) - P1</x:v>
-      </x:c>
-      <x:c r="B110" s="91" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C110" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="91" t="str">
-        <x:v>Validation Engineer - II - Engineering (P &amp; O Support / Professional) - P2</x:v>
-      </x:c>
-      <x:c r="B111" s="91" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C111" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112">
-      <x:c r="A112" s="91" t="str">
-        <x:v>Validation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</x:v>
-      </x:c>
-      <x:c r="B112" s="91" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C112" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113">
-      <x:c r="A113" s="92" t="str">
-        <x:v>Warehouse Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</x:v>
-      </x:c>
-      <x:c r="B113" s="92" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C113" t="str">
-        <x:v>GS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="92" t="str">
-        <x:v>CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)
-1 stap boven mid</x:v>
-      </x:c>
-      <x:c r="B114" s="92" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C114" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115">
-      <x:c r="A115" t="str">
-        <x:v>CQ engineer Site Engineering P1-F midpoint   (CQ=Commissioning&amp;Qualification)</x:v>
-      </x:c>
-      <x:c r="B115" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C115" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" t="str">
-        <x:v>CQ engineer Site Engineering P1-G Tussen midpoint en max.   (CQ=Commissioning&amp;Qualification)</x:v>
-      </x:c>
-      <x:c r="B116" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C116" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" t="str">
-        <x:v>SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.
-2 stappen boven mid 1 stap  onder max</x:v>
-      </x:c>
-      <x:c r="B117" t="str">
-        <x:v>J</x:v>
-      </x:c>
-      <x:c r="C117" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" t="str">
-        <x:v>Projectmanager Site Engineering P2-H Tussen midpoint en max.
-2 stappen boven mid 1 stap onder max</x:v>
-      </x:c>
-      <x:c r="B118" t="str">
-        <x:v>H</x:v>
-      </x:c>
-      <x:c r="C118" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119">
-      <x:c r="A119" t="str">
-        <x:v>Civil engineer Site Engineering P1-G midpoint 1 stap boven</x:v>
-      </x:c>
-      <x:c r="B119" t="str">
-        <x:v>G</x:v>
-      </x:c>
-      <x:c r="C119" t="str">
-        <x:v>PS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120">
-      <x:c r="A120"/>
-      <x:c r="B120"/>
-      <x:c r="C120"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="A121"/>
-      <x:c r="B121"/>
-      <x:c r="C121"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="A122"/>
-      <x:c r="B122"/>
-      <x:c r="C122"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="A123"/>
-      <x:c r="B123"/>
-      <x:c r="C123"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="A124"/>
-      <x:c r="B124"/>
-      <x:c r="C124"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="A125"/>
-      <x:c r="B125"/>
-      <x:c r="C125"/>
-    </x:row>
-    <x:row r="126">
-      <x:c r="A126"/>
-      <x:c r="B126"/>
-      <x:c r="C126"/>
-    </x:row>
-    <x:row r="127">
-      <x:c r="A127"/>
-      <x:c r="B127"/>
-      <x:c r="C127"/>
-    </x:row>
-    <x:row r="128">
-      <x:c r="A128"/>
-      <x:c r="B128"/>
-      <x:c r="C128"/>
-    </x:row>
-    <x:row r="129">
-      <x:c r="A129"/>
-      <x:c r="B129"/>
-      <x:c r="C129"/>
-    </x:row>
-    <x:row r="130">
-      <x:c r="A130"/>
-      <x:c r="B130"/>
-      <x:c r="C130"/>
-    </x:row>
-    <x:row r="131">
-      <x:c r="A131"/>
-      <x:c r="B131"/>
-      <x:c r="C131"/>
-    </x:row>
-    <x:row r="132">
-      <x:c r="A132"/>
-      <x:c r="B132"/>
-      <x:c r="C132"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="A133"/>
-      <x:c r="B133"/>
-      <x:c r="C133"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="A134"/>
-      <x:c r="B134"/>
-      <x:c r="C134"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135"/>
-      <x:c r="B135"/>
-      <x:c r="C135"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="A136"/>
-      <x:c r="B136"/>
-      <x:c r="C136"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="A137"/>
-      <x:c r="B137"/>
-      <x:c r="C137"/>
-    </x:row>
-    <x:row r="138">
-      <x:c r="A138"/>
-      <x:c r="B138"/>
-      <x:c r="C138"/>
-    </x:row>
-    <x:row r="139">
-      <x:c r="A139"/>
-      <x:c r="B139"/>
-      <x:c r="C139"/>
-    </x:row>
-    <x:row r="140">
-      <x:c r="A140"/>
-      <x:c r="B140"/>
-      <x:c r="C140"/>
-    </x:row>
-    <x:row r="141">
-      <x:c r="A141"/>
-      <x:c r="B141"/>
-      <x:c r="C141"/>
-    </x:row>
-    <x:row r="142">
-      <x:c r="A142"/>
-      <x:c r="B142"/>
-      <x:c r="C142"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="A143"/>
-      <x:c r="B143"/>
-      <x:c r="C143"/>
-    </x:row>
-    <x:row r="144">
-      <x:c r="A144"/>
-      <x:c r="B144"/>
-      <x:c r="C144"/>
-    </x:row>
-    <x:row r="145">
-      <x:c r="A145"/>
-      <x:c r="B145"/>
-      <x:c r="C145"/>
-    </x:row>
-    <x:row r="146">
-      <x:c r="A146"/>
-      <x:c r="B146"/>
-      <x:c r="C146"/>
-    </x:row>
-    <x:row r="147">
-      <x:c r="A147"/>
-      <x:c r="B147"/>
-      <x:c r="C147"/>
-    </x:row>
-    <x:row r="148">
-      <x:c r="A148"/>
-      <x:c r="B148"/>
-      <x:c r="C148"/>
-    </x:row>
-    <x:row r="149">
-      <x:c r="A149"/>
-      <x:c r="B149"/>
-      <x:c r="C149"/>
-    </x:row>
-    <x:row r="150">
-      <x:c r="A150"/>
-      <x:c r="B150"/>
-      <x:c r="C150"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151"/>
-      <x:c r="B151"/>
-      <x:c r="C151"/>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152"/>
-      <x:c r="B152"/>
-      <x:c r="C152"/>
-    </x:row>
-    <x:row r="153">
-      <x:c r="A153"/>
-      <x:c r="B153"/>
-      <x:c r="C153"/>
-    </x:row>
-    <x:row r="154">
-      <x:c r="A154"/>
-      <x:c r="B154"/>
-      <x:c r="C154"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155"/>
-      <x:c r="B155"/>
-      <x:c r="C155"/>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156"/>
-      <x:c r="B156"/>
-      <x:c r="C156"/>
-    </x:row>
-    <x:row r="157">
-      <x:c r="A157"/>
-      <x:c r="B157"/>
-      <x:c r="C157"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158"/>
-      <x:c r="B158"/>
-      <x:c r="C158"/>
-    </x:row>
-    <x:row r="159">
-      <x:c r="A159"/>
-      <x:c r="B159"/>
-      <x:c r="C159"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160"/>
-      <x:c r="B160"/>
-      <x:c r="C160"/>
-    </x:row>
-    <x:row r="161">
-      <x:c r="A161"/>
-      <x:c r="B161"/>
-      <x:c r="C161"/>
-    </x:row>
-    <x:row r="162">
-      <x:c r="A162"/>
-      <x:c r="B162"/>
-      <x:c r="C162"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163"/>
-      <x:c r="B163"/>
-      <x:c r="C163"/>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164"/>
-      <x:c r="B164"/>
-      <x:c r="C164"/>
-    </x:row>
-    <x:row r="165">
-      <x:c r="A165"/>
-      <x:c r="B165"/>
-      <x:c r="C165"/>
-    </x:row>
-    <x:row r="166">
-      <x:c r="A166"/>
-      <x:c r="B166"/>
-      <x:c r="C166"/>
-    </x:row>
-    <x:row r="167">
-      <x:c r="A167"/>
-      <x:c r="B167"/>
-      <x:c r="C167"/>
-    </x:row>
-    <x:row r="168">
-      <x:c r="A168"/>
-      <x:c r="B168"/>
-      <x:c r="C168"/>
-    </x:row>
-    <x:row r="169">
-      <x:c r="A169"/>
-      <x:c r="B169"/>
-      <x:c r="C169"/>
-    </x:row>
-    <x:row r="170">
-      <x:c r="A170"/>
-      <x:c r="B170"/>
-      <x:c r="C170"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171"/>
-      <x:c r="B171"/>
-      <x:c r="C171"/>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172"/>
-      <x:c r="B172"/>
-      <x:c r="C172"/>
-    </x:row>
-    <x:row r="173">
-      <x:c r="A173"/>
-      <x:c r="B173"/>
-      <x:c r="C173"/>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174"/>
-      <x:c r="B174"/>
-      <x:c r="C174"/>
-    </x:row>
-    <x:row r="175">
-      <x:c r="A175"/>
-      <x:c r="B175"/>
-      <x:c r="C175"/>
-    </x:row>
-    <x:row r="176">
-      <x:c r="A176"/>
-      <x:c r="B176"/>
-      <x:c r="C176"/>
-    </x:row>
-    <x:row r="177">
-      <x:c r="A177"/>
-      <x:c r="B177"/>
-      <x:c r="C177"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178"/>
-      <x:c r="B178"/>
-      <x:c r="C178"/>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179"/>
-      <x:c r="B179"/>
-      <x:c r="C179"/>
-    </x:row>
-    <x:row r="180">
-      <x:c r="A180"/>
-      <x:c r="B180"/>
-      <x:c r="C180"/>
-    </x:row>
-    <x:row r="181">
-      <x:c r="A181"/>
-      <x:c r="B181"/>
-      <x:c r="C181"/>
-    </x:row>
-    <x:row r="182">
-      <x:c r="A182"/>
-      <x:c r="B182"/>
-      <x:c r="C182"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183"/>
-      <x:c r="B183"/>
-      <x:c r="C183"/>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184"/>
-      <x:c r="B184"/>
-      <x:c r="C184"/>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185"/>
-      <x:c r="B185"/>
-      <x:c r="C185"/>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186"/>
-      <x:c r="B186"/>
-      <x:c r="C186"/>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187"/>
-      <x:c r="B187"/>
-      <x:c r="C187"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188"/>
-      <x:c r="B188"/>
-      <x:c r="C188"/>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189"/>
-      <x:c r="B189"/>
-      <x:c r="C189"/>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190"/>
-      <x:c r="B190"/>
-      <x:c r="C190"/>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191"/>
-      <x:c r="B191"/>
-      <x:c r="C191"/>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192"/>
-      <x:c r="B192"/>
-      <x:c r="C192"/>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193"/>
-      <x:c r="B193"/>
-      <x:c r="C193"/>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194"/>
-      <x:c r="B194"/>
-      <x:c r="C194"/>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195"/>
-      <x:c r="B195"/>
-      <x:c r="C195"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196"/>
-      <x:c r="B196"/>
-      <x:c r="C196"/>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197"/>
-      <x:c r="B197"/>
-      <x:c r="C197"/>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198"/>
-      <x:c r="B198"/>
-      <x:c r="C198"/>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199"/>
-      <x:c r="B199"/>
-      <x:c r="C199"/>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200"/>
-      <x:c r="B200"/>
-      <x:c r="C200"/>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201"/>
-      <x:c r="B201"/>
-      <x:c r="C201"/>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202"/>
-      <x:c r="B202"/>
-      <x:c r="C202"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203"/>
-      <x:c r="B203"/>
-      <x:c r="C203"/>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204"/>
-      <x:c r="B204"/>
-      <x:c r="C204"/>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A205"/>
-      <x:c r="B205"/>
-      <x:c r="C205"/>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A206"/>
-      <x:c r="B206"/>
-      <x:c r="C206"/>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A207"/>
-      <x:c r="B207"/>
-      <x:c r="C207"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208"/>
-      <x:c r="B208"/>
-      <x:c r="C208"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209"/>
-      <x:c r="B209"/>
-      <x:c r="C209"/>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A210"/>
-      <x:c r="B210"/>
-      <x:c r="C210"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211"/>
-      <x:c r="B211"/>
-      <x:c r="C211"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212"/>
-      <x:c r="B212"/>
-      <x:c r="C212"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213"/>
-      <x:c r="B213"/>
-      <x:c r="C213"/>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214"/>
-      <x:c r="B214"/>
-      <x:c r="C214"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A215"/>
-      <x:c r="B215"/>
-      <x:c r="C215"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A216"/>
-      <x:c r="B216"/>
-      <x:c r="C216"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A217"/>
-      <x:c r="B217"/>
-      <x:c r="C217"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="A218"/>
-      <x:c r="B218"/>
-      <x:c r="C218"/>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A219"/>
-      <x:c r="B219"/>
-      <x:c r="C219"/>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A220"/>
-      <x:c r="B220"/>
-      <x:c r="C220"/>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221"/>
-      <x:c r="B221"/>
-      <x:c r="C221"/>
-    </x:row>
-    <x:row r="222">
-      <x:c r="A222"/>
-      <x:c r="B222"/>
-      <x:c r="C222"/>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A223"/>
-      <x:c r="B223"/>
-      <x:c r="C223"/>
-    </x:row>
-    <x:row r="224">
-      <x:c r="A224"/>
-      <x:c r="B224"/>
-      <x:c r="C224"/>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A225"/>
-      <x:c r="B225"/>
-      <x:c r="C225"/>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A226"/>
-      <x:c r="B226"/>
-      <x:c r="C226"/>
-    </x:row>
-    <x:row r="227">
-      <x:c r="A227"/>
-      <x:c r="B227"/>
-      <x:c r="C227"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A228"/>
-      <x:c r="B228"/>
-      <x:c r="C228"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229"/>
-      <x:c r="B229"/>
-      <x:c r="C229"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A230"/>
-      <x:c r="B230"/>
-      <x:c r="C230"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A231"/>
-      <x:c r="B231"/>
-      <x:c r="C231"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A232"/>
-      <x:c r="B232"/>
-      <x:c r="C232"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A233"/>
-      <x:c r="B233"/>
-      <x:c r="C233"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A234"/>
-      <x:c r="B234"/>
-      <x:c r="C234"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A235"/>
-      <x:c r="B235"/>
-      <x:c r="C235"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A236"/>
-      <x:c r="B236"/>
-      <x:c r="C236"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A237"/>
-      <x:c r="B237"/>
-      <x:c r="C237"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A238"/>
-      <x:c r="B238"/>
-      <x:c r="C238"/>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A239"/>
-      <x:c r="B239"/>
-      <x:c r="C239"/>
-    </x:row>
-    <x:row r="240">
-      <x:c r="A240"/>
-      <x:c r="B240"/>
-      <x:c r="C240"/>
-    </x:row>
-    <x:row r="241">
-      <x:c r="A241"/>
-      <x:c r="B241"/>
-      <x:c r="C241"/>
-    </x:row>
-    <x:row r="242">
-      <x:c r="A242"/>
-      <x:c r="B242"/>
-      <x:c r="C242"/>
-    </x:row>
-    <x:row r="243">
-      <x:c r="A243"/>
-      <x:c r="B243"/>
-      <x:c r="C243"/>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A244"/>
-      <x:c r="B244"/>
-      <x:c r="C244"/>
-    </x:row>
-    <x:row r="245">
-      <x:c r="A245"/>
-      <x:c r="B245"/>
-      <x:c r="C245"/>
-    </x:row>
-    <x:row r="246">
-      <x:c r="A246"/>
-      <x:c r="B246"/>
-      <x:c r="C246"/>
-    </x:row>
-    <x:row r="247">
-      <x:c r="A247"/>
-      <x:c r="B247"/>
-      <x:c r="C247"/>
-    </x:row>
-    <x:row r="248">
-      <x:c r="A248"/>
-      <x:c r="B248"/>
-      <x:c r="C248"/>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A249"/>
-      <x:c r="B249"/>
-      <x:c r="C249"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250"/>
-      <x:c r="B250"/>
-      <x:c r="C250"/>
-    </x:row>
-    <x:row r="251">
-      <x:c r="A251"/>
-      <x:c r="B251"/>
-      <x:c r="C251"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252"/>
-      <x:c r="B252"/>
-      <x:c r="C252"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253"/>
-      <x:c r="B253"/>
-      <x:c r="C253"/>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254"/>
-      <x:c r="B254"/>
-      <x:c r="C254"/>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255"/>
-      <x:c r="B255"/>
-      <x:c r="C255"/>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256"/>
-      <x:c r="B256"/>
-      <x:c r="C256"/>
-    </x:row>
-    <x:row r="257">
-      <x:c r="A257"/>
-      <x:c r="B257"/>
-      <x:c r="C257"/>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A258"/>
-      <x:c r="B258"/>
-      <x:c r="C258"/>
-    </x:row>
-    <x:row r="259">
-      <x:c r="A259"/>
-      <x:c r="B259"/>
-      <x:c r="C259"/>
-    </x:row>
-    <x:row r="260">
-      <x:c r="A260"/>
-      <x:c r="B260"/>
-      <x:c r="C260"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A261"/>
-      <x:c r="B261"/>
-      <x:c r="C261"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262"/>
-      <x:c r="B262"/>
-      <x:c r="C262"/>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A263"/>
-      <x:c r="B263"/>
-      <x:c r="C263"/>
-    </x:row>
-    <x:row r="264">
-      <x:c r="A264"/>
-      <x:c r="B264"/>
-      <x:c r="C264"/>
-    </x:row>
-    <x:row r="265">
-      <x:c r="A265"/>
-      <x:c r="B265"/>
-      <x:c r="C265"/>
-    </x:row>
-    <x:row r="266">
-      <x:c r="A266"/>
-      <x:c r="B266"/>
-      <x:c r="C266"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A267"/>
-      <x:c r="B267"/>
-      <x:c r="C267"/>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A268"/>
-      <x:c r="B268"/>
-      <x:c r="C268"/>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A269"/>
-      <x:c r="B269"/>
-      <x:c r="C269"/>
-    </x:row>
-    <x:row r="270">
-      <x:c r="A270"/>
-      <x:c r="B270"/>
-      <x:c r="C270"/>
-    </x:row>
-    <x:row r="271">
-      <x:c r="A271"/>
-      <x:c r="B271"/>
-      <x:c r="C271"/>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A272"/>
-      <x:c r="B272"/>
-      <x:c r="C272"/>
-    </x:row>
-    <x:row r="273">
-      <x:c r="A273"/>
-      <x:c r="B273"/>
-      <x:c r="C273"/>
-    </x:row>
-    <x:row r="274">
-      <x:c r="A274"/>
-      <x:c r="B274"/>
-      <x:c r="C274"/>
-    </x:row>
-    <x:row r="275">
-      <x:c r="A275"/>
-      <x:c r="B275"/>
-      <x:c r="C275"/>
-    </x:row>
-    <x:row r="276">
-      <x:c r="A276"/>
-      <x:c r="B276"/>
-      <x:c r="C276"/>
-    </x:row>
-    <x:row r="277">
-      <x:c r="A277"/>
-      <x:c r="B277"/>
-      <x:c r="C277"/>
-    </x:row>
-    <x:row r="278">
-      <x:c r="A278"/>
-      <x:c r="B278"/>
-      <x:c r="C278"/>
-    </x:row>
-    <x:row r="279">
-      <x:c r="A279"/>
-      <x:c r="B279"/>
-      <x:c r="C279"/>
-    </x:row>
-    <x:row r="280">
-      <x:c r="A280"/>
-      <x:c r="B280"/>
-      <x:c r="C280"/>
-    </x:row>
-    <x:row r="281">
-      <x:c r="A281"/>
-      <x:c r="B281"/>
-      <x:c r="C281"/>
-    </x:row>
-    <x:row r="282">
-      <x:c r="A282"/>
-      <x:c r="B282"/>
-      <x:c r="C282"/>
-    </x:row>
-    <x:row r="283">
-      <x:c r="A283"/>
-      <x:c r="B283"/>
-      <x:c r="C283"/>
-    </x:row>
-    <x:row r="284">
-      <x:c r="A284"/>
-      <x:c r="B284"/>
-      <x:c r="C284"/>
-    </x:row>
-    <x:row r="285">
-      <x:c r="A285"/>
-      <x:c r="B285"/>
-      <x:c r="C285"/>
-    </x:row>
-    <x:row r="286">
-      <x:c r="A286"/>
-      <x:c r="B286"/>
-      <x:c r="C286"/>
-    </x:row>
-    <x:row r="287">
-      <x:c r="A287"/>
-      <x:c r="B287"/>
-      <x:c r="C287"/>
-    </x:row>
-    <x:row r="288">
-      <x:c r="A288"/>
-      <x:c r="B288"/>
-      <x:c r="C288"/>
-    </x:row>
-    <x:row r="289">
-      <x:c r="A289"/>
-      <x:c r="B289"/>
-      <x:c r="C289"/>
-    </x:row>
-    <x:row r="290">
-      <x:c r="A290"/>
-      <x:c r="B290"/>
-      <x:c r="C290"/>
-    </x:row>
-    <x:row r="291">
-      <x:c r="A291"/>
-      <x:c r="B291"/>
-      <x:c r="C291"/>
-    </x:row>
-    <x:row r="292">
-      <x:c r="A292"/>
-      <x:c r="B292"/>
-      <x:c r="C292"/>
-    </x:row>
-    <x:row r="293">
-      <x:c r="A293"/>
-      <x:c r="B293"/>
-      <x:c r="C293"/>
-    </x:row>
-    <x:row r="294">
-      <x:c r="A294"/>
-      <x:c r="B294"/>
-      <x:c r="C294"/>
-    </x:row>
-    <x:row r="295">
-      <x:c r="A295"/>
-      <x:c r="B295"/>
-      <x:c r="C295"/>
-    </x:row>
-    <x:row r="296">
-      <x:c r="A296"/>
-      <x:c r="B296"/>
-      <x:c r="C296"/>
-    </x:row>
-    <x:row r="297">
-      <x:c r="A297"/>
-      <x:c r="B297"/>
-      <x:c r="C297"/>
-    </x:row>
-    <x:row r="298">
-      <x:c r="A298"/>
-      <x:c r="B298"/>
-      <x:c r="C298"/>
-    </x:row>
-    <x:row r="299">
-      <x:c r="A299"/>
-      <x:c r="B299"/>
-      <x:c r="C299"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="A300"/>
-      <x:c r="B300"/>
-      <x:c r="C300"/>
-    </x:row>
-    <x:row r="301">
-      <x:c r="A301"/>
-      <x:c r="B301"/>
-      <x:c r="C301"/>
-    </x:row>
-    <x:row r="302">
-      <x:c r="A302"/>
-      <x:c r="B302"/>
-      <x:c r="C302"/>
-    </x:row>
-    <x:row r="303">
-      <x:c r="A303"/>
-      <x:c r="B303"/>
-      <x:c r="C303"/>
-    </x:row>
-    <x:row r="304">
-      <x:c r="A304"/>
-      <x:c r="B304"/>
-      <x:c r="C304"/>
-    </x:row>
-    <x:row r="305">
-      <x:c r="A305"/>
-      <x:c r="B305"/>
-      <x:c r="C305"/>
-    </x:row>
-    <x:row r="306">
-      <x:c r="A306"/>
-      <x:c r="B306"/>
-      <x:c r="C306"/>
-    </x:row>
-    <x:row r="307">
-      <x:c r="A307"/>
-      <x:c r="B307"/>
-      <x:c r="C307"/>
-    </x:row>
-    <x:row r="308">
-      <x:c r="A308"/>
-      <x:c r="B308"/>
-      <x:c r="C308"/>
-    </x:row>
-    <x:row r="309">
-      <x:c r="A309"/>
-      <x:c r="B309"/>
-      <x:c r="C309"/>
-    </x:row>
-    <x:row r="310">
-      <x:c r="A310"/>
-      <x:c r="B310"/>
-      <x:c r="C310"/>
-    </x:row>
-    <x:row r="311">
-      <x:c r="A311"/>
-      <x:c r="B311"/>
-      <x:c r="C311"/>
-    </x:row>
-    <x:row r="312">
-      <x:c r="A312"/>
-      <x:c r="B312"/>
-      <x:c r="C312"/>
-    </x:row>
-    <x:row r="313">
-      <x:c r="A313"/>
-      <x:c r="B313"/>
-      <x:c r="C313"/>
-    </x:row>
-    <x:row r="314">
-      <x:c r="A314"/>
-      <x:c r="B314"/>
-      <x:c r="C314"/>
-    </x:row>
-    <x:row r="315">
-      <x:c r="A315"/>
-      <x:c r="B315"/>
-      <x:c r="C315"/>
-    </x:row>
-    <x:row r="316">
-      <x:c r="A316"/>
-      <x:c r="B316"/>
-      <x:c r="C316"/>
-    </x:row>
-    <x:row r="317">
-      <x:c r="A317"/>
-      <x:c r="B317"/>
-      <x:c r="C317"/>
-    </x:row>
-    <x:row r="318">
-      <x:c r="A318"/>
-      <x:c r="B318"/>
-      <x:c r="C318"/>
-    </x:row>
-    <x:row r="319">
-      <x:c r="A319"/>
-      <x:c r="B319"/>
-      <x:c r="C319"/>
-    </x:row>
-    <x:row r="320">
-      <x:c r="A320"/>
-      <x:c r="B320"/>
-      <x:c r="C320"/>
-    </x:row>
-    <x:row r="321">
-      <x:c r="A321"/>
-      <x:c r="B321"/>
-      <x:c r="C321"/>
-    </x:row>
-    <x:row r="322">
-      <x:c r="A322"/>
-      <x:c r="B322"/>
-      <x:c r="C322"/>
-    </x:row>
-    <x:row r="323">
-      <x:c r="A323"/>
-      <x:c r="B323"/>
-      <x:c r="C323"/>
-    </x:row>
-    <x:row r="324">
-      <x:c r="A324"/>
-      <x:c r="B324"/>
-      <x:c r="C324"/>
-    </x:row>
-    <x:row r="325">
-      <x:c r="A325"/>
-      <x:c r="B325"/>
-      <x:c r="C325"/>
-    </x:row>
-    <x:row r="326">
-      <x:c r="A326"/>
-      <x:c r="B326"/>
-      <x:c r="C326"/>
-    </x:row>
-    <x:row r="327">
-      <x:c r="A327"/>
-      <x:c r="B327"/>
-      <x:c r="C327"/>
-    </x:row>
-    <x:row r="328">
-      <x:c r="A328"/>
-      <x:c r="B328"/>
-      <x:c r="C328"/>
-    </x:row>
-    <x:row r="329">
-      <x:c r="A329"/>
-      <x:c r="B329"/>
-      <x:c r="C329"/>
-    </x:row>
-    <x:row r="330">
-      <x:c r="A330"/>
-      <x:c r="B330"/>
-      <x:c r="C330"/>
-    </x:row>
-    <x:row r="331">
-      <x:c r="A331"/>
-      <x:c r="B331"/>
-      <x:c r="C331"/>
-    </x:row>
-    <x:row r="332">
-      <x:c r="A332"/>
-      <x:c r="B332"/>
-      <x:c r="C332"/>
-    </x:row>
-    <x:row r="333">
-      <x:c r="A333"/>
-      <x:c r="B333"/>
-      <x:c r="C333"/>
-    </x:row>
-    <x:row r="334">
-      <x:c r="A334"/>
-      <x:c r="B334"/>
-      <x:c r="C334"/>
-    </x:row>
-    <x:row r="335">
-      <x:c r="A335"/>
-      <x:c r="B335"/>
-      <x:c r="C335"/>
-    </x:row>
-    <x:row r="336">
-      <x:c r="A336"/>
-      <x:c r="B336"/>
-      <x:c r="C336"/>
-    </x:row>
-    <x:row r="337">
-      <x:c r="A337"/>
-      <x:c r="B337"/>
-      <x:c r="C337"/>
-    </x:row>
-    <x:row r="338">
-      <x:c r="A338"/>
-      <x:c r="B338"/>
-      <x:c r="C338"/>
-    </x:row>
-    <x:row r="339">
-      <x:c r="A339"/>
-      <x:c r="B339"/>
-      <x:c r="C339"/>
-    </x:row>
-    <x:row r="340">
-      <x:c r="A340"/>
-      <x:c r="B340"/>
-      <x:c r="C340"/>
-    </x:row>
-    <x:row r="341">
-      <x:c r="A341"/>
-      <x:c r="B341"/>
-      <x:c r="C341"/>
-    </x:row>
-    <x:row r="342">
-      <x:c r="A342"/>
-      <x:c r="B342"/>
-      <x:c r="C342"/>
-    </x:row>
-    <x:row r="343">
-      <x:c r="A343"/>
-      <x:c r="B343"/>
-      <x:c r="C343"/>
-    </x:row>
-    <x:row r="344">
-      <x:c r="A344"/>
-      <x:c r="B344"/>
-      <x:c r="C344"/>
-    </x:row>
-    <x:row r="345">
-      <x:c r="A345"/>
-      <x:c r="B345"/>
-      <x:c r="C345"/>
-    </x:row>
-    <x:row r="346">
-      <x:c r="A346"/>
-      <x:c r="B346"/>
-      <x:c r="C346"/>
-    </x:row>
-    <x:row r="347">
-      <x:c r="A347"/>
-      <x:c r="B347"/>
-      <x:c r="C347"/>
-    </x:row>
-    <x:row r="348">
-      <x:c r="A348"/>
-      <x:c r="B348"/>
-      <x:c r="C348"/>
-    </x:row>
-    <x:row r="349">
-      <x:c r="A349"/>
-      <x:c r="B349"/>
-      <x:c r="C349"/>
-    </x:row>
-    <x:row r="350">
-      <x:c r="A350"/>
-      <x:c r="B350"/>
-      <x:c r="C350"/>
-    </x:row>
-    <x:row r="351">
-      <x:c r="A351"/>
-      <x:c r="B351"/>
-      <x:c r="C351"/>
-    </x:row>
-    <x:row r="352">
-      <x:c r="A352"/>
-      <x:c r="B352"/>
-      <x:c r="C352"/>
-    </x:row>
-    <x:row r="353">
-      <x:c r="A353"/>
-      <x:c r="B353"/>
-      <x:c r="C353"/>
-    </x:row>
-    <x:row r="354">
-      <x:c r="A354"/>
-      <x:c r="B354"/>
-      <x:c r="C354"/>
-    </x:row>
-    <x:row r="355">
-      <x:c r="A355"/>
-      <x:c r="B355"/>
-      <x:c r="C355"/>
-    </x:row>
-    <x:row r="356">
-      <x:c r="A356"/>
-      <x:c r="B356"/>
-      <x:c r="C356"/>
-    </x:row>
-    <x:row r="357">
-      <x:c r="A357"/>
-      <x:c r="B357"/>
-      <x:c r="C357"/>
-    </x:row>
-    <x:row r="358">
-      <x:c r="A358"/>
-      <x:c r="B358"/>
-      <x:c r="C358"/>
-    </x:row>
-    <x:row r="359">
-      <x:c r="A359"/>
-      <x:c r="B359"/>
-      <x:c r="C359"/>
-    </x:row>
-    <x:row r="360">
-      <x:c r="A360"/>
-      <x:c r="B360"/>
-      <x:c r="C360"/>
-    </x:row>
-    <x:row r="361">
-      <x:c r="A361"/>
-      <x:c r="B361"/>
-      <x:c r="C361"/>
-    </x:row>
-    <x:row r="362">
-      <x:c r="A362"/>
-      <x:c r="B362"/>
-      <x:c r="C362"/>
-    </x:row>
-    <x:row r="363">
-      <x:c r="A363"/>
-      <x:c r="B363"/>
-      <x:c r="C363"/>
-    </x:row>
-    <x:row r="364">
-      <x:c r="A364"/>
-      <x:c r="B364"/>
-      <x:c r="C364"/>
-    </x:row>
-    <x:row r="365">
-      <x:c r="A365"/>
-      <x:c r="B365"/>
-      <x:c r="C365"/>
-    </x:row>
-    <x:row r="366">
-      <x:c r="A366"/>
-      <x:c r="B366"/>
-      <x:c r="C366"/>
-    </x:row>
-    <x:row r="367">
-      <x:c r="A367"/>
-      <x:c r="B367"/>
-      <x:c r="C367"/>
-    </x:row>
-    <x:row r="368">
-      <x:c r="A368"/>
-      <x:c r="B368"/>
-      <x:c r="C368"/>
-    </x:row>
-    <x:row r="369">
-      <x:c r="A369"/>
-      <x:c r="B369"/>
-      <x:c r="C369"/>
-    </x:row>
-    <x:row r="370">
-      <x:c r="A370"/>
-      <x:c r="B370"/>
-      <x:c r="C370"/>
-    </x:row>
-    <x:row r="371">
-      <x:c r="A371"/>
-      <x:c r="B371"/>
-      <x:c r="C371"/>
-    </x:row>
-    <x:row r="372">
-      <x:c r="A372"/>
-      <x:c r="B372"/>
-      <x:c r="C372"/>
-    </x:row>
-    <x:row r="373">
-      <x:c r="A373"/>
-      <x:c r="B373"/>
-      <x:c r="C373"/>
-    </x:row>
-    <x:row r="374">
-      <x:c r="A374"/>
-      <x:c r="B374"/>
-      <x:c r="C374"/>
-    </x:row>
-    <x:row r="375">
-      <x:c r="A375"/>
-      <x:c r="B375"/>
-      <x:c r="C375"/>
-    </x:row>
-    <x:row r="376">
-      <x:c r="A376"/>
-      <x:c r="B376"/>
-      <x:c r="C376"/>
-    </x:row>
-    <x:row r="377">
-      <x:c r="A377"/>
-      <x:c r="B377"/>
-      <x:c r="C377"/>
-    </x:row>
-    <x:row r="378">
-      <x:c r="A378"/>
-      <x:c r="B378"/>
-      <x:c r="C378"/>
-    </x:row>
-    <x:row r="379">
-      <x:c r="A379"/>
-      <x:c r="B379"/>
-      <x:c r="C379"/>
-    </x:row>
-    <x:row r="380">
-      <x:c r="A380"/>
-      <x:c r="B380"/>
-      <x:c r="C380"/>
-    </x:row>
-    <x:row r="381">
-      <x:c r="A381"/>
-      <x:c r="B381"/>
-      <x:c r="C381"/>
-    </x:row>
-    <x:row r="382">
-      <x:c r="A382"/>
-      <x:c r="B382"/>
-      <x:c r="C382"/>
-    </x:row>
-    <x:row r="383">
-      <x:c r="A383"/>
-      <x:c r="B383"/>
-      <x:c r="C383"/>
-    </x:row>
-    <x:row r="384">
-      <x:c r="A384"/>
-      <x:c r="B384"/>
-      <x:c r="C384"/>
-    </x:row>
-    <x:row r="385">
-      <x:c r="A385"/>
-      <x:c r="B385"/>
-      <x:c r="C385"/>
-    </x:row>
-    <x:row r="386">
-      <x:c r="A386"/>
-      <x:c r="B386"/>
-      <x:c r="C386"/>
-    </x:row>
-    <x:row r="387">
-      <x:c r="A387"/>
-      <x:c r="B387"/>
-      <x:c r="C387"/>
-    </x:row>
-    <x:row r="388">
-      <x:c r="A388"/>
-      <x:c r="B388"/>
-      <x:c r="C388"/>
-    </x:row>
-    <x:row r="389">
-      <x:c r="A389"/>
-      <x:c r="B389"/>
-      <x:c r="C389"/>
-    </x:row>
-    <x:row r="390">
-      <x:c r="A390"/>
-      <x:c r="B390"/>
-      <x:c r="C390"/>
-    </x:row>
-    <x:row r="391">
-      <x:c r="A391"/>
-      <x:c r="B391"/>
-      <x:c r="C391"/>
-    </x:row>
-    <x:row r="392">
-      <x:c r="A392"/>
-      <x:c r="B392"/>
-      <x:c r="C392"/>
-    </x:row>
-    <x:row r="393">
-      <x:c r="A393"/>
-      <x:c r="B393"/>
-      <x:c r="C393"/>
-    </x:row>
-    <x:row r="394">
-      <x:c r="A394"/>
-      <x:c r="B394"/>
-      <x:c r="C394"/>
-    </x:row>
-    <x:row r="395">
-      <x:c r="A395"/>
-      <x:c r="B395"/>
-      <x:c r="C395"/>
-    </x:row>
-    <x:row r="396">
-      <x:c r="A396"/>
-      <x:c r="B396"/>
-      <x:c r="C396"/>
-    </x:row>
-    <x:row r="397">
-      <x:c r="A397"/>
-      <x:c r="B397"/>
-      <x:c r="C397"/>
-    </x:row>
-    <x:row r="398">
-      <x:c r="A398"/>
-      <x:c r="B398"/>
-      <x:c r="C398"/>
-    </x:row>
-    <x:row r="399">
-      <x:c r="A399"/>
-      <x:c r="B399"/>
-      <x:c r="C399"/>
-    </x:row>
-    <x:row r="400">
-      <x:c r="A400"/>
-      <x:c r="B400"/>
-      <x:c r="C400"/>
-    </x:row>
-    <x:row r="401">
-      <x:c r="A401"/>
-      <x:c r="B401"/>
-      <x:c r="C401"/>
-    </x:row>
-    <x:row r="402">
-      <x:c r="A402"/>
-      <x:c r="B402"/>
-      <x:c r="C402"/>
-    </x:row>
-    <x:row r="403">
-      <x:c r="A403"/>
-      <x:c r="B403"/>
-      <x:c r="C403"/>
-    </x:row>
-    <x:row r="404">
-      <x:c r="A404"/>
-      <x:c r="B404"/>
-      <x:c r="C404"/>
-    </x:row>
-    <x:row r="405">
-      <x:c r="A405"/>
-      <x:c r="B405"/>
-      <x:c r="C405"/>
-    </x:row>
-    <x:row r="406">
-      <x:c r="A406"/>
-      <x:c r="B406"/>
-      <x:c r="C406"/>
-    </x:row>
-    <x:row r="407">
-      <x:c r="A407"/>
-      <x:c r="B407"/>
-      <x:c r="C407"/>
-    </x:row>
-    <x:row r="408">
-      <x:c r="A408"/>
-      <x:c r="B408"/>
-      <x:c r="C408"/>
-    </x:row>
-    <x:row r="409">
-      <x:c r="A409"/>
-      <x:c r="B409"/>
-      <x:c r="C409"/>
-    </x:row>
-    <x:row r="410">
-      <x:c r="A410"/>
-      <x:c r="B410"/>
-      <x:c r="C410"/>
-    </x:row>
-    <x:row r="411">
-      <x:c r="A411"/>
-      <x:c r="B411"/>
-      <x:c r="C411"/>
-    </x:row>
-    <x:row r="412">
-      <x:c r="A412"/>
-      <x:c r="B412"/>
-      <x:c r="C412"/>
-    </x:row>
-    <x:row r="413">
-      <x:c r="A413"/>
-      <x:c r="B413"/>
-      <x:c r="C413"/>
-    </x:row>
-    <x:row r="414">
-      <x:c r="A414"/>
-      <x:c r="B414"/>
-      <x:c r="C414"/>
-    </x:row>
-    <x:row r="415">
-      <x:c r="A415"/>
-      <x:c r="B415"/>
-      <x:c r="C415"/>
-    </x:row>
-    <x:row r="416">
-      <x:c r="A416"/>
-      <x:c r="B416"/>
-      <x:c r="C416"/>
-    </x:row>
-    <x:row r="417">
-      <x:c r="A417"/>
-      <x:c r="B417"/>
-      <x:c r="C417"/>
-    </x:row>
-    <x:row r="418">
-      <x:c r="A418"/>
-      <x:c r="B418"/>
-      <x:c r="C418"/>
-    </x:row>
-    <x:row r="419">
-      <x:c r="A419"/>
-      <x:c r="B419"/>
-      <x:c r="C419"/>
-    </x:row>
-    <x:row r="420">
-      <x:c r="A420"/>
-      <x:c r="B420"/>
-      <x:c r="C420"/>
-    </x:row>
-    <x:row r="421">
-      <x:c r="A421"/>
-      <x:c r="B421"/>
-      <x:c r="C421"/>
-    </x:row>
-    <x:row r="422">
-      <x:c r="A422"/>
-      <x:c r="B422"/>
-      <x:c r="C422"/>
-    </x:row>
-    <x:row r="423">
-      <x:c r="A423"/>
-      <x:c r="B423"/>
-      <x:c r="C423"/>
-    </x:row>
-    <x:row r="424">
-      <x:c r="A424"/>
-      <x:c r="B424"/>
-      <x:c r="C424"/>
-    </x:row>
-    <x:row r="425">
-      <x:c r="A425"/>
-      <x:c r="B425"/>
-      <x:c r="C425"/>
-    </x:row>
-    <x:row r="426">
-      <x:c r="A426"/>
-      <x:c r="B426"/>
-      <x:c r="C426"/>
-    </x:row>
-    <x:row r="427">
-      <x:c r="A427"/>
-      <x:c r="B427"/>
-      <x:c r="C427"/>
-    </x:row>
-    <x:row r="428">
-      <x:c r="A428"/>
-      <x:c r="B428"/>
-      <x:c r="C428"/>
-    </x:row>
-    <x:row r="429">
-      <x:c r="A429"/>
-      <x:c r="B429"/>
-      <x:c r="C429"/>
-    </x:row>
-    <x:row r="430">
-      <x:c r="A430"/>
-      <x:c r="B430"/>
-      <x:c r="C430"/>
-    </x:row>
-    <x:row r="431">
-      <x:c r="A431"/>
-      <x:c r="B431"/>
-      <x:c r="C431"/>
-    </x:row>
-    <x:row r="432">
-      <x:c r="A432"/>
-      <x:c r="B432"/>
-      <x:c r="C432"/>
-    </x:row>
-    <x:row r="433">
-      <x:c r="A433"/>
-      <x:c r="B433"/>
-      <x:c r="C433"/>
-    </x:row>
-    <x:row r="434">
-      <x:c r="A434"/>
-      <x:c r="B434"/>
-      <x:c r="C434"/>
-    </x:row>
-    <x:row r="435">
-      <x:c r="A435"/>
-      <x:c r="B435"/>
-      <x:c r="C435"/>
-    </x:row>
-    <x:row r="436">
-      <x:c r="A436"/>
-      <x:c r="B436"/>
-      <x:c r="C436"/>
-    </x:row>
-    <x:row r="437">
-      <x:c r="A437"/>
-      <x:c r="B437"/>
-      <x:c r="C437"/>
-    </x:row>
-    <x:row r="438">
-      <x:c r="A438"/>
-      <x:c r="B438"/>
-      <x:c r="C438"/>
-    </x:row>
-    <x:row r="439">
-      <x:c r="A439"/>
-      <x:c r="B439"/>
-      <x:c r="C439"/>
-    </x:row>
-    <x:row r="440">
-      <x:c r="A440"/>
-      <x:c r="B440"/>
-      <x:c r="C440"/>
-    </x:row>
-    <x:row r="441">
-      <x:c r="A441"/>
-      <x:c r="B441"/>
-      <x:c r="C441"/>
-    </x:row>
-    <x:row r="442">
-      <x:c r="A442"/>
-      <x:c r="B442"/>
-      <x:c r="C442"/>
-    </x:row>
-    <x:row r="443">
-      <x:c r="A443"/>
-      <x:c r="B443"/>
-      <x:c r="C443"/>
-    </x:row>
-    <x:row r="444">
-      <x:c r="A444"/>
-      <x:c r="B444"/>
-      <x:c r="C444"/>
-    </x:row>
-    <x:row r="445">
-      <x:c r="A445"/>
-      <x:c r="B445"/>
-      <x:c r="C445"/>
-    </x:row>
-    <x:row r="446">
-      <x:c r="A446"/>
-      <x:c r="B446"/>
-      <x:c r="C446"/>
-    </x:row>
-    <x:row r="447">
-      <x:c r="A447"/>
-      <x:c r="B447"/>
-      <x:c r="C447"/>
-    </x:row>
-    <x:row r="448">
-      <x:c r="A448"/>
-      <x:c r="B448"/>
-      <x:c r="C448"/>
-    </x:row>
-    <x:row r="449">
-      <x:c r="A449"/>
-      <x:c r="B449"/>
-      <x:c r="C449"/>
-    </x:row>
-    <x:row r="450">
-      <x:c r="A450"/>
-      <x:c r="B450"/>
-      <x:c r="C450"/>
-    </x:row>
-    <x:row r="451">
-      <x:c r="A451"/>
-      <x:c r="B451"/>
-      <x:c r="C451"/>
-    </x:row>
-    <x:row r="452">
-      <x:c r="A452"/>
-      <x:c r="B452"/>
-      <x:c r="C452"/>
-    </x:row>
-    <x:row r="453">
-      <x:c r="A453"/>
-      <x:c r="B453"/>
-      <x:c r="C453"/>
-    </x:row>
-    <x:row r="454">
-      <x:c r="A454"/>
-      <x:c r="B454"/>
-      <x:c r="C454"/>
-    </x:row>
-    <x:row r="455">
-      <x:c r="A455"/>
-      <x:c r="B455"/>
-      <x:c r="C455"/>
-    </x:row>
-    <x:row r="456">
-      <x:c r="A456"/>
-      <x:c r="B456"/>
-      <x:c r="C456"/>
-    </x:row>
-    <x:row r="457">
-      <x:c r="A457"/>
-      <x:c r="B457"/>
-      <x:c r="C457"/>
-    </x:row>
-    <x:row r="458">
-      <x:c r="A458"/>
-      <x:c r="B458"/>
-      <x:c r="C458"/>
-    </x:row>
-    <x:row r="459">
-      <x:c r="A459"/>
-      <x:c r="B459"/>
-      <x:c r="C459"/>
-    </x:row>
-    <x:row r="460">
-      <x:c r="A460"/>
-      <x:c r="B460"/>
-      <x:c r="C460"/>
-    </x:row>
-    <x:row r="461">
-      <x:c r="A461"/>
-      <x:c r="B461"/>
-      <x:c r="C461"/>
-    </x:row>
-    <x:row r="462">
-      <x:c r="A462"/>
-      <x:c r="B462"/>
-      <x:c r="C462"/>
-    </x:row>
-    <x:row r="463">
-      <x:c r="A463"/>
-      <x:c r="B463"/>
-      <x:c r="C463"/>
-    </x:row>
-    <x:row r="464">
-      <x:c r="A464"/>
-      <x:c r="B464"/>
-      <x:c r="C464"/>
-    </x:row>
-    <x:row r="465">
-      <x:c r="A465"/>
-      <x:c r="B465"/>
-      <x:c r="C465"/>
-    </x:row>
-    <x:row r="466">
-      <x:c r="A466"/>
-      <x:c r="B466"/>
-      <x:c r="C466"/>
-    </x:row>
-    <x:row r="467">
-      <x:c r="A467"/>
-      <x:c r="B467"/>
-      <x:c r="C467"/>
-    </x:row>
-    <x:row r="468">
-      <x:c r="A468"/>
-      <x:c r="B468"/>
-      <x:c r="C468"/>
-    </x:row>
-    <x:row r="469">
-      <x:c r="A469"/>
-      <x:c r="B469"/>
-      <x:c r="C469"/>
-    </x:row>
-    <x:row r="470">
-      <x:c r="A470"/>
-      <x:c r="B470"/>
-      <x:c r="C470"/>
-    </x:row>
-    <x:row r="471">
-      <x:c r="A471"/>
-      <x:c r="B471"/>
-      <x:c r="C471"/>
-    </x:row>
-    <x:row r="472">
-      <x:c r="A472"/>
-      <x:c r="B472"/>
-      <x:c r="C472"/>
-    </x:row>
-    <x:row r="473">
-      <x:c r="A473"/>
-      <x:c r="B473"/>
-      <x:c r="C473"/>
-    </x:row>
-    <x:row r="474">
-      <x:c r="A474"/>
-      <x:c r="B474"/>
-      <x:c r="C474"/>
-    </x:row>
-    <x:row r="475">
-      <x:c r="A475"/>
-      <x:c r="B475"/>
-      <x:c r="C475"/>
-    </x:row>
-    <x:row r="476">
-      <x:c r="A476"/>
-      <x:c r="B476"/>
-      <x:c r="C476"/>
-    </x:row>
-    <x:row r="477">
-      <x:c r="A477"/>
-      <x:c r="B477"/>
-      <x:c r="C477"/>
-    </x:row>
-    <x:row r="478">
-      <x:c r="A478"/>
-      <x:c r="B478"/>
-      <x:c r="C478"/>
-    </x:row>
-    <x:row r="479">
-      <x:c r="A479"/>
-      <x:c r="B479"/>
-      <x:c r="C479"/>
-    </x:row>
-    <x:row r="480">
-      <x:c r="A480"/>
-      <x:c r="B480"/>
-      <x:c r="C480"/>
-    </x:row>
-    <x:row r="481">
-      <x:c r="A481"/>
-      <x:c r="B481"/>
-      <x:c r="C481"/>
-    </x:row>
-    <x:row r="482">
-      <x:c r="A482"/>
-      <x:c r="B482"/>
-      <x:c r="C482"/>
-    </x:row>
-    <x:row r="483">
-      <x:c r="A483"/>
-      <x:c r="B483"/>
-      <x:c r="C483"/>
-    </x:row>
-    <x:row r="484">
-      <x:c r="A484"/>
-      <x:c r="B484"/>
-      <x:c r="C484"/>
-    </x:row>
-    <x:row r="485">
-      <x:c r="A485"/>
-      <x:c r="B485"/>
-      <x:c r="C485"/>
-    </x:row>
-    <x:row r="486">
-      <x:c r="A486"/>
-      <x:c r="B486"/>
-      <x:c r="C486"/>
-    </x:row>
-    <x:row r="487">
-      <x:c r="A487"/>
-      <x:c r="B487"/>
-      <x:c r="C487"/>
-    </x:row>
-    <x:row r="488">
-      <x:c r="A488"/>
-      <x:c r="B488"/>
-      <x:c r="C488"/>
-    </x:row>
-    <x:row r="489">
-      <x:c r="A489"/>
-      <x:c r="B489"/>
-      <x:c r="C489"/>
-    </x:row>
-    <x:row r="490">
-      <x:c r="A490"/>
-      <x:c r="B490"/>
-      <x:c r="C490"/>
-    </x:row>
-    <x:row r="491">
-      <x:c r="A491"/>
-      <x:c r="B491"/>
-      <x:c r="C491"/>
-    </x:row>
-    <x:row r="492">
-      <x:c r="A492"/>
-      <x:c r="B492"/>
-      <x:c r="C492"/>
-    </x:row>
-    <x:row r="493">
-      <x:c r="A493"/>
-      <x:c r="B493"/>
-      <x:c r="C493"/>
-    </x:row>
-    <x:row r="494">
-      <x:c r="A494"/>
-      <x:c r="B494"/>
-      <x:c r="C494"/>
-    </x:row>
-    <x:row r="495">
-      <x:c r="A495"/>
-      <x:c r="B495"/>
-      <x:c r="C495"/>
-    </x:row>
-    <x:row r="496">
-      <x:c r="A496"/>
-      <x:c r="B496"/>
-      <x:c r="C496"/>
-    </x:row>
-    <x:row r="497">
-      <x:c r="A497"/>
-      <x:c r="B497"/>
-      <x:c r="C497"/>
-    </x:row>
-    <x:row r="498">
-      <x:c r="A498"/>
-      <x:c r="B498"/>
-      <x:c r="C498"/>
-    </x:row>
-    <x:row r="499">
-      <x:c r="A499"/>
-      <x:c r="B499"/>
-      <x:c r="C499"/>
-    </x:row>
-    <x:row r="500">
-      <x:c r="A500"/>
-      <x:c r="B500"/>
-      <x:c r="C500"/>
-    </x:row>
-    <x:row r="501">
-      <x:c r="A501"/>
-      <x:c r="B501"/>
-      <x:c r="C501"/>
-    </x:row>
-    <x:row r="502">
-      <x:c r="A502"/>
-      <x:c r="B502"/>
-      <x:c r="C502"/>
-    </x:row>
-    <x:row r="503">
-      <x:c r="A503"/>
-      <x:c r="B503"/>
-      <x:c r="C503"/>
-    </x:row>
-    <x:row r="504">
-      <x:c r="A504"/>
-      <x:c r="B504"/>
-      <x:c r="C504"/>
-    </x:row>
-    <x:row r="505">
-      <x:c r="A505"/>
-      <x:c r="B505"/>
-      <x:c r="C505"/>
-    </x:row>
-    <x:row r="506">
-      <x:c r="A506"/>
-      <x:c r="B506"/>
-      <x:c r="C506"/>
-    </x:row>
-    <x:row r="507">
-      <x:c r="A507"/>
-      <x:c r="B507"/>
-      <x:c r="C507"/>
-    </x:row>
-    <x:row r="508">
-      <x:c r="A508"/>
-      <x:c r="B508"/>
-      <x:c r="C508"/>
-    </x:row>
-    <x:row r="509">
-      <x:c r="A509"/>
-      <x:c r="B509"/>
-      <x:c r="C509"/>
-    </x:row>
-    <x:row r="510">
-      <x:c r="A510"/>
-      <x:c r="B510"/>
-      <x:c r="C510"/>
-    </x:row>
-    <x:row r="511">
-      <x:c r="A511"/>
-      <x:c r="B511"/>
-      <x:c r="C511"/>
-    </x:row>
-    <x:row r="512">
-      <x:c r="A512"/>
-      <x:c r="B512"/>
-      <x:c r="C512"/>
-    </x:row>
-    <x:row r="513">
-      <x:c r="A513"/>
-      <x:c r="B513"/>
-      <x:c r="C513"/>
-    </x:row>
-    <x:row r="514">
-      <x:c r="A514"/>
-      <x:c r="B514"/>
-      <x:c r="C514"/>
-    </x:row>
-    <x:row r="515">
-      <x:c r="A515"/>
-      <x:c r="B515"/>
-      <x:c r="C515"/>
-    </x:row>
-    <x:row r="516">
-      <x:c r="A516"/>
-      <x:c r="B516"/>
-      <x:c r="C516"/>
-    </x:row>
-    <x:row r="517">
-      <x:c r="A517"/>
-      <x:c r="B517"/>
-      <x:c r="C517"/>
-    </x:row>
-    <x:row r="518">
-      <x:c r="A518"/>
-      <x:c r="B518"/>
-      <x:c r="C518"/>
-    </x:row>
-    <x:row r="519">
-      <x:c r="A519"/>
-      <x:c r="B519"/>
-      <x:c r="C519"/>
-    </x:row>
-    <x:row r="520">
-      <x:c r="A520"/>
-      <x:c r="B520"/>
-      <x:c r="C520"/>
-    </x:row>
-    <x:row r="521">
-      <x:c r="A521"/>
-      <x:c r="B521"/>
-      <x:c r="C521"/>
-    </x:row>
-    <x:row r="522">
-      <x:c r="A522"/>
-      <x:c r="B522"/>
-      <x:c r="C522"/>
-    </x:row>
-    <x:row r="523">
-      <x:c r="A523"/>
-      <x:c r="B523"/>
-      <x:c r="C523"/>
-    </x:row>
-    <x:row r="524">
-      <x:c r="A524"/>
-      <x:c r="B524"/>
-      <x:c r="C524"/>
-    </x:row>
-    <x:row r="525">
-      <x:c r="A525"/>
-      <x:c r="B525"/>
-      <x:c r="C525"/>
-    </x:row>
-    <x:row r="526">
-      <x:c r="A526"/>
-      <x:c r="B526"/>
-      <x:c r="C526"/>
-    </x:row>
-    <x:row r="527">
-      <x:c r="A527"/>
-      <x:c r="B527"/>
-      <x:c r="C527"/>
-    </x:row>
-    <x:row r="528">
-      <x:c r="A528"/>
-      <x:c r="B528"/>
-      <x:c r="C528"/>
-    </x:row>
-    <x:row r="529">
-      <x:c r="A529"/>
-      <x:c r="B529"/>
-      <x:c r="C529"/>
-    </x:row>
-    <x:row r="530">
-      <x:c r="A530"/>
-      <x:c r="B530"/>
-      <x:c r="C530"/>
-    </x:row>
-    <x:row r="531">
-      <x:c r="A531"/>
-      <x:c r="B531"/>
-      <x:c r="C531"/>
-    </x:row>
-    <x:row r="532">
-      <x:c r="A532"/>
-      <x:c r="B532"/>
-      <x:c r="C532"/>
-    </x:row>
-    <x:row r="533">
-      <x:c r="A533"/>
-      <x:c r="B533"/>
-      <x:c r="C533"/>
-    </x:row>
-    <x:row r="534">
-      <x:c r="A534"/>
-      <x:c r="B534"/>
-      <x:c r="C534"/>
-    </x:row>
-    <x:row r="535">
-      <x:c r="A535"/>
-      <x:c r="B535"/>
-      <x:c r="C535"/>
-    </x:row>
-    <x:row r="536">
-      <x:c r="A536"/>
-      <x:c r="B536"/>
-      <x:c r="C536"/>
-    </x:row>
-    <x:row r="537">
-      <x:c r="A537"/>
-      <x:c r="B537"/>
-      <x:c r="C537"/>
-    </x:row>
-    <x:row r="538">
-      <x:c r="A538"/>
-      <x:c r="B538"/>
-      <x:c r="C538"/>
-    </x:row>
-    <x:row r="539">
-      <x:c r="A539"/>
-      <x:c r="B539"/>
-      <x:c r="C539"/>
-    </x:row>
-    <x:row r="540">
-      <x:c r="A540"/>
-      <x:c r="B540"/>
-      <x:c r="C540"/>
-    </x:row>
-    <x:row r="541">
-      <x:c r="A541"/>
-      <x:c r="B541"/>
-      <x:c r="C541"/>
-    </x:row>
-    <x:row r="542">
-      <x:c r="A542"/>
-      <x:c r="B542"/>
-      <x:c r="C542"/>
-    </x:row>
-    <x:row r="543">
-      <x:c r="A543"/>
-      <x:c r="B543"/>
-      <x:c r="C543"/>
-    </x:row>
-    <x:row r="544">
-      <x:c r="A544"/>
-      <x:c r="B544"/>
-      <x:c r="C544"/>
-    </x:row>
-    <x:row r="545">
-      <x:c r="A545"/>
-      <x:c r="B545"/>
-      <x:c r="C545"/>
-    </x:row>
-    <x:row r="546">
-      <x:c r="A546"/>
-      <x:c r="B546"/>
-      <x:c r="C546"/>
-    </x:row>
-    <x:row r="547">
-      <x:c r="A547"/>
-      <x:c r="B547"/>
-      <x:c r="C547"/>
-    </x:row>
-    <x:row r="548">
-      <x:c r="A548"/>
-      <x:c r="B548"/>
-      <x:c r="C548"/>
-    </x:row>
-    <x:row r="549">
-      <x:c r="A549"/>
-      <x:c r="B549"/>
-      <x:c r="C549"/>
-    </x:row>
-    <x:row r="550">
-      <x:c r="A550"/>
-      <x:c r="B550"/>
-      <x:c r="C550"/>
-    </x:row>
-    <x:row r="551">
-      <x:c r="A551"/>
-      <x:c r="B551"/>
-      <x:c r="C551"/>
-    </x:row>
-    <x:row r="552">
-      <x:c r="A552"/>
-      <x:c r="B552"/>
-      <x:c r="C552"/>
-    </x:row>
-    <x:row r="553">
-      <x:c r="A553"/>
-      <x:c r="B553"/>
-      <x:c r="C553"/>
-    </x:row>
-    <x:row r="554">
-      <x:c r="A554"/>
-      <x:c r="B554"/>
-      <x:c r="C554"/>
-    </x:row>
-    <x:row r="555">
-      <x:c r="A555"/>
-      <x:c r="B555"/>
-      <x:c r="C555"/>
-    </x:row>
-    <x:row r="556">
-      <x:c r="A556"/>
-      <x:c r="B556"/>
-      <x:c r="C556"/>
-    </x:row>
-    <x:row r="557">
-      <x:c r="A557"/>
-      <x:c r="B557"/>
-      <x:c r="C557"/>
-    </x:row>
-    <x:row r="558">
-      <x:c r="A558"/>
-      <x:c r="B558"/>
-      <x:c r="C558"/>
-    </x:row>
-    <x:row r="559">
-      <x:c r="A559"/>
-      <x:c r="B559"/>
-      <x:c r="C559"/>
-    </x:row>
-    <x:row r="560">
-      <x:c r="A560"/>
-      <x:c r="B560"/>
-      <x:c r="C560"/>
-    </x:row>
-    <x:row r="561">
-      <x:c r="A561"/>
-      <x:c r="B561"/>
-      <x:c r="C561"/>
-    </x:row>
-    <x:row r="562">
-      <x:c r="A562"/>
-      <x:c r="B562"/>
-      <x:c r="C562"/>
-    </x:row>
-    <x:row r="563">
-      <x:c r="A563"/>
-      <x:c r="B563"/>
-      <x:c r="C563"/>
-    </x:row>
-    <x:row r="564">
-      <x:c r="A564"/>
-      <x:c r="B564"/>
-      <x:c r="C564"/>
-    </x:row>
-    <x:row r="565">
-      <x:c r="A565"/>
-      <x:c r="B565"/>
-      <x:c r="C565"/>
-    </x:row>
-    <x:row r="566">
-      <x:c r="A566"/>
-      <x:c r="B566"/>
-      <x:c r="C566"/>
-    </x:row>
-    <x:row r="567">
-      <x:c r="A567"/>
-      <x:c r="B567"/>
-      <x:c r="C567"/>
-    </x:row>
-    <x:row r="568">
-      <x:c r="A568"/>
-      <x:c r="B568"/>
-      <x:c r="C568"/>
-    </x:row>
-    <x:row r="569">
-      <x:c r="A569"/>
-      <x:c r="B569"/>
-      <x:c r="C569"/>
-    </x:row>
-    <x:row r="570">
-      <x:c r="A570"/>
-      <x:c r="B570"/>
-      <x:c r="C570"/>
-    </x:row>
-    <x:row r="571">
-      <x:c r="A571"/>
-      <x:c r="B571"/>
-      <x:c r="C571"/>
-    </x:row>
-    <x:row r="572">
-      <x:c r="A572"/>
-      <x:c r="B572"/>
-      <x:c r="C572"/>
-    </x:row>
-    <x:row r="573">
-      <x:c r="A573"/>
-      <x:c r="B573"/>
-      <x:c r="C573"/>
-    </x:row>
-    <x:row r="574">
-      <x:c r="A574"/>
-      <x:c r="B574"/>
-      <x:c r="C574"/>
-    </x:row>
-    <x:row r="575">
-      <x:c r="A575"/>
-      <x:c r="B575"/>
-      <x:c r="C575"/>
-    </x:row>
-    <x:row r="576">
-      <x:c r="A576"/>
-      <x:c r="B576"/>
-      <x:c r="C576"/>
-    </x:row>
-    <x:row r="577">
-      <x:c r="A577"/>
-      <x:c r="B577"/>
-      <x:c r="C577"/>
-    </x:row>
-    <x:row r="578">
-      <x:c r="A578"/>
-      <x:c r="B578"/>
-      <x:c r="C578"/>
-    </x:row>
-    <x:row r="579">
-      <x:c r="A579"/>
-      <x:c r="B579"/>
-      <x:c r="C579"/>
-    </x:row>
-    <x:row r="580">
-      <x:c r="A580"/>
-      <x:c r="B580"/>
-      <x:c r="C580"/>
-    </x:row>
-    <x:row r="581">
-      <x:c r="A581"/>
-      <x:c r="B581"/>
-      <x:c r="C581"/>
-    </x:row>
-    <x:row r="582">
-      <x:c r="A582"/>
-      <x:c r="B582"/>
-      <x:c r="C582"/>
-    </x:row>
-    <x:row r="583">
-      <x:c r="A583"/>
-      <x:c r="B583"/>
-      <x:c r="C583"/>
-    </x:row>
-    <x:row r="584">
-      <x:c r="A584"/>
-      <x:c r="B584"/>
-      <x:c r="C584"/>
-    </x:row>
-    <x:row r="585">
-      <x:c r="A585"/>
-      <x:c r="B585"/>
-      <x:c r="C585"/>
-    </x:row>
-    <x:row r="586">
-      <x:c r="A586"/>
-      <x:c r="B586"/>
-      <x:c r="C586"/>
-    </x:row>
-    <x:row r="587">
-      <x:c r="A587"/>
-      <x:c r="B587"/>
-      <x:c r="C587"/>
-    </x:row>
-    <x:row r="588">
-      <x:c r="A588"/>
-      <x:c r="B588"/>
-      <x:c r="C588"/>
-    </x:row>
-    <x:row r="589">
-      <x:c r="A589"/>
-      <x:c r="B589"/>
-      <x:c r="C589"/>
-    </x:row>
-    <x:row r="590">
-      <x:c r="A590"/>
-      <x:c r="B590"/>
-      <x:c r="C590"/>
-    </x:row>
-    <x:row r="591">
-      <x:c r="A591"/>
-      <x:c r="B591"/>
-      <x:c r="C591"/>
-    </x:row>
-    <x:row r="592">
-      <x:c r="A592"/>
-      <x:c r="B592"/>
-      <x:c r="C592"/>
-    </x:row>
-    <x:row r="593">
-      <x:c r="A593"/>
-      <x:c r="B593"/>
-      <x:c r="C593"/>
-    </x:row>
-    <x:row r="594">
-      <x:c r="A594"/>
-      <x:c r="B594"/>
-      <x:c r="C594"/>
-    </x:row>
-    <x:row r="595">
-      <x:c r="A595"/>
-      <x:c r="B595"/>
-      <x:c r="C595"/>
-    </x:row>
-    <x:row r="596">
-      <x:c r="A596"/>
-      <x:c r="B596"/>
-      <x:c r="C596"/>
-    </x:row>
-    <x:row r="597">
-      <x:c r="A597"/>
-      <x:c r="B597"/>
-      <x:c r="C597"/>
-    </x:row>
-    <x:row r="598">
-      <x:c r="A598"/>
-      <x:c r="B598"/>
-      <x:c r="C598"/>
-    </x:row>
-    <x:row r="599">
-      <x:c r="A599"/>
-      <x:c r="B599"/>
-      <x:c r="C599"/>
-    </x:row>
-    <x:row r="600">
-      <x:c r="A600"/>
-      <x:c r="B600"/>
-      <x:c r="C600"/>
-    </x:row>
-    <x:row r="601">
-      <x:c r="A601"/>
-      <x:c r="B601"/>
-      <x:c r="C601"/>
-    </x:row>
-    <x:row r="602">
-      <x:c r="A602"/>
-      <x:c r="B602"/>
-      <x:c r="C602"/>
-    </x:row>
-    <x:row r="603">
-      <x:c r="A603"/>
-      <x:c r="B603"/>
-      <x:c r="C603"/>
-    </x:row>
-    <x:row r="604">
-      <x:c r="A604"/>
-      <x:c r="B604"/>
-      <x:c r="C604"/>
-    </x:row>
-    <x:row r="605">
-      <x:c r="A605"/>
-      <x:c r="B605"/>
-      <x:c r="C605"/>
-    </x:row>
-    <x:row r="606">
-      <x:c r="A606"/>
-      <x:c r="B606"/>
-      <x:c r="C606"/>
-    </x:row>
-    <x:row r="607">
-      <x:c r="A607"/>
-      <x:c r="B607"/>
-      <x:c r="C607"/>
-    </x:row>
-    <x:row r="608">
-      <x:c r="A608"/>
-      <x:c r="B608"/>
-      <x:c r="C608"/>
-    </x:row>
-    <x:row r="609">
-      <x:c r="A609"/>
-      <x:c r="B609"/>
-      <x:c r="C609"/>
-    </x:row>
-    <x:row r="610">
-      <x:c r="A610"/>
-      <x:c r="B610"/>
-      <x:c r="C610"/>
-    </x:row>
-    <x:row r="611">
-      <x:c r="A611"/>
-      <x:c r="B611"/>
-      <x:c r="C611"/>
-    </x:row>
-    <x:row r="612">
-      <x:c r="A612"/>
-      <x:c r="B612"/>
-      <x:c r="C612"/>
-    </x:row>
-    <x:row r="613">
-      <x:c r="A613"/>
-      <x:c r="B613"/>
-      <x:c r="C613"/>
-    </x:row>
-    <x:row r="614">
-      <x:c r="A614"/>
-      <x:c r="B614"/>
-      <x:c r="C614"/>
-    </x:row>
-    <x:row r="615">
-      <x:c r="A615"/>
-      <x:c r="B615"/>
-      <x:c r="C615"/>
-    </x:row>
-    <x:row r="616">
-      <x:c r="A616"/>
-      <x:c r="B616"/>
-      <x:c r="C616"/>
-    </x:row>
-    <x:row r="617">
-      <x:c r="A617"/>
-      <x:c r="B617"/>
-      <x:c r="C617"/>
-    </x:row>
-    <x:row r="618">
-      <x:c r="A618"/>
-      <x:c r="B618"/>
-      <x:c r="C618"/>
-    </x:row>
-    <x:row r="619">
-      <x:c r="A619"/>
-      <x:c r="B619"/>
-      <x:c r="C619"/>
-    </x:row>
-    <x:row r="620">
-      <x:c r="A620"/>
-      <x:c r="B620"/>
-      <x:c r="C620"/>
-    </x:row>
-    <x:row r="621">
-      <x:c r="A621"/>
-      <x:c r="B621"/>
-      <x:c r="C621"/>
-    </x:row>
-    <x:row r="622">
-      <x:c r="A622"/>
-      <x:c r="B622"/>
-      <x:c r="C622"/>
-    </x:row>
-    <x:row r="623">
-      <x:c r="A623"/>
-      <x:c r="B623"/>
-      <x:c r="C623"/>
-    </x:row>
-    <x:row r="624">
-      <x:c r="A624"/>
-      <x:c r="B624"/>
-      <x:c r="C624"/>
-    </x:row>
-    <x:row r="625">
-      <x:c r="A625"/>
-      <x:c r="B625"/>
-      <x:c r="C625"/>
-    </x:row>
-    <x:row r="626">
-      <x:c r="A626"/>
-      <x:c r="B626"/>
-      <x:c r="C626"/>
-    </x:row>
-    <x:row r="627">
-      <x:c r="A627"/>
-      <x:c r="B627"/>
-      <x:c r="C627"/>
-    </x:row>
-    <x:row r="628">
-      <x:c r="A628"/>
-      <x:c r="B628"/>
-      <x:c r="C628"/>
-    </x:row>
-    <x:row r="629">
-      <x:c r="A629"/>
-      <x:c r="B629"/>
-      <x:c r="C629"/>
-    </x:row>
-    <x:row r="630">
-      <x:c r="A630"/>
-      <x:c r="B630"/>
-      <x:c r="C630"/>
-    </x:row>
-    <x:row r="631">
-      <x:c r="A631"/>
-      <x:c r="B631"/>
-      <x:c r="C631"/>
-    </x:row>
-    <x:row r="632">
-      <x:c r="A632"/>
-      <x:c r="B632"/>
-      <x:c r="C632"/>
-    </x:row>
-    <x:row r="633">
-      <x:c r="A633"/>
-      <x:c r="B633"/>
-      <x:c r="C633"/>
-    </x:row>
-    <x:row r="634">
-      <x:c r="A634"/>
-      <x:c r="B634"/>
-      <x:c r="C634"/>
-    </x:row>
-    <x:row r="635">
-      <x:c r="A635"/>
-      <x:c r="B635"/>
-      <x:c r="C635"/>
-    </x:row>
-    <x:row r="636">
-      <x:c r="A636"/>
-      <x:c r="B636"/>
-      <x:c r="C636"/>
-    </x:row>
-    <x:row r="637">
-      <x:c r="A637"/>
-      <x:c r="B637"/>
-      <x:c r="C637"/>
-    </x:row>
-    <x:row r="638">
-      <x:c r="A638"/>
-      <x:c r="B638"/>
-      <x:c r="C638"/>
-    </x:row>
-    <x:row r="639">
-      <x:c r="A639"/>
-      <x:c r="B639"/>
-      <x:c r="C639"/>
-    </x:row>
-    <x:row r="640">
-      <x:c r="A640"/>
-      <x:c r="B640"/>
-      <x:c r="C640"/>
-    </x:row>
-    <x:row r="641">
-      <x:c r="A641"/>
-      <x:c r="B641"/>
-      <x:c r="C641"/>
-    </x:row>
-    <x:row r="642">
-      <x:c r="A642"/>
-      <x:c r="B642"/>
-      <x:c r="C642"/>
-    </x:row>
-    <x:row r="643">
-      <x:c r="A643"/>
-      <x:c r="B643"/>
-      <x:c r="C643"/>
-    </x:row>
-    <x:row r="644">
-      <x:c r="A644"/>
-      <x:c r="B644"/>
-      <x:c r="C644"/>
-    </x:row>
-    <x:row r="645">
-      <x:c r="A645"/>
-      <x:c r="B645"/>
-      <x:c r="C645"/>
-      <x:c r="D645"/>
-      <x:c r="E645"/>
-      <x:c r="F645"/>
-      <x:c r="G645"/>
-      <x:c r="H645"/>
-      <x:c r="I645"/>
-      <x:c r="J645"/>
-      <x:c r="K645"/>
-      <x:c r="L645"/>
-      <x:c r="M645"/>
-      <x:c r="N645"/>
-      <x:c r="O645"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="88" t="str">
+        <v>Job Title</v>
+      </c>
+      <c r="B1" s="88" t="str">
+        <v>Salary Scale</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Supplier Type</v>
+      </c>
+      <c r="D1" s="88" t="str">
+        <v>Scale</v>
+      </c>
+      <c r="E1" s="88" t="str">
+        <v>Minimum</v>
+      </c>
+      <c r="F1" s="88" t="str">
+        <v>Midpoint</v>
+      </c>
+      <c r="G1" s="88" t="str">
+        <v>Maximum</v>
+      </c>
+      <c r="I1" s="88" t="str">
+        <v>PIR from</v>
+      </c>
+      <c r="J1" s="88" t="str">
+        <v>Range Band</v>
+      </c>
+      <c r="K1" s="88" t="str">
+        <v>Merit 2026</v>
+      </c>
+      <c r="L1" s="88" t="str">
+        <v>Merit 2027</v>
+      </c>
+      <c r="N1" s="88" t="str">
+        <v>Assumption</v>
+      </c>
+      <c r="O1" s="88" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="90" t="str">
+        <v>Accountant - II - Finance &amp; Legal (B Support / Professional) - P2</v>
+      </c>
+      <c r="B2" s="90" t="str">
+        <v>H</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D2" t="str">
+        <v>A</v>
+      </c>
+      <c r="E2" s="93" t="n">
+        <v>24300</v>
+      </c>
+      <c r="F2" s="93" t="n">
+        <v>33600</v>
+      </c>
+      <c r="G2" s="93" t="n">
+        <v>42300</v>
+      </c>
+      <c r="I2" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Onder het minimum</v>
+      </c>
+      <c r="K2" s="95" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L2" s="95" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Month factor</v>
+      </c>
+      <c r="O2" s="96" t="n">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="91" t="str">
+        <v>Accountant - III - Finance &amp; Legal (B Support / Professional) - P3</v>
+      </c>
+      <c r="B3" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D3" t="str">
+        <v>B</v>
+      </c>
+      <c r="E3" s="93" t="n">
+        <v>31400</v>
+      </c>
+      <c r="F3" s="93" t="n">
+        <v>42400</v>
+      </c>
+      <c r="G3" s="93" t="n">
+        <v>53400</v>
+      </c>
+      <c r="I3" s="94" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="J3" t="str">
+        <v>1e derde deel</v>
+      </c>
+      <c r="K3" s="95" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L3" s="95" t="n">
+        <v>0.041299999999999996</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Hour factor</v>
+      </c>
+      <c r="O3" s="96" t="n">
+        <v>173.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="91" t="str">
+        <v>Administrative Assistant - II - Business Support (A) Admin/Finance/HR - B2</v>
+      </c>
+      <c r="B4" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C4" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D4" t="str">
+        <v>C</v>
+      </c>
+      <c r="E4" s="93" t="n">
+        <v>34400</v>
+      </c>
+      <c r="F4" s="93" t="n">
+        <v>46500</v>
+      </c>
+      <c r="G4" s="93" t="n">
+        <v>58600</v>
+      </c>
+      <c r="I4" s="94" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2e derde deel</v>
+      </c>
+      <c r="K4" s="95" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="L4" s="95" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="N4" t="str">
+        <v>GS markup factor</v>
+      </c>
+      <c r="O4" s="96" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="str">
+        <v>Administrative Assistant - III - Business Support (A) Admin/Finance/HR - B3</v>
+      </c>
+      <c r="B5" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C5" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D5" t="str">
+        <v>D</v>
+      </c>
+      <c r="E5" s="93" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F5" s="93" t="n">
+        <v>51100</v>
+      </c>
+      <c r="G5" s="93" t="n">
+        <v>64400</v>
+      </c>
+      <c r="I5" s="94" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="J5" t="str">
+        <v>3e derde deel</v>
+      </c>
+      <c r="K5" s="95" t="n">
+        <v>0.022400000000000003</v>
+      </c>
+      <c r="L5" s="95" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="N5" t="str">
+        <v>PS markup factor</v>
+      </c>
+      <c r="O5" s="96" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="str">
+        <v>Analytical Chemist - I - LAB (B Support / Research) - R1</v>
+      </c>
+      <c r="B6" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C6" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D6" t="str">
+        <v>E</v>
+      </c>
+      <c r="E6" s="93" t="n">
+        <v>41600</v>
+      </c>
+      <c r="F6" s="93" t="n">
+        <v>56100</v>
+      </c>
+      <c r="G6" s="93" t="n">
+        <v>70600</v>
+      </c>
+      <c r="I6" s="94" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Boven het maximum</v>
+      </c>
+      <c r="K6" s="95" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L6" s="95" t="n">
+        <v>0.0165</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="91" t="str">
+        <v>Assembler - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</v>
+      </c>
+      <c r="B7" s="91" t="str">
+        <v>B</v>
+      </c>
+      <c r="C7" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D7" t="str">
+        <v>F</v>
+      </c>
+      <c r="E7" s="93" t="n">
+        <v>45800</v>
+      </c>
+      <c r="F7" s="93" t="n">
+        <v>61800</v>
+      </c>
+      <c r="G7" s="93" t="n">
+        <v>77800</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="91" t="str">
+        <v>Automation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B8" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C8" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D8" t="str">
+        <v>G</v>
+      </c>
+      <c r="E8" s="93" t="n">
+        <v>50200</v>
+      </c>
+      <c r="F8" s="93" t="n">
+        <v>67800</v>
+      </c>
+      <c r="G8" s="93" t="n">
+        <v>85400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="91" t="str">
+        <v>Biochemical Operator – ll - Production &amp; Operations Support (T): Industrial – O2 (Mid)</v>
+      </c>
+      <c r="B9" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C9" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D9" t="str">
+        <v>H</v>
+      </c>
+      <c r="E9" s="93" t="n">
+        <v>55200</v>
+      </c>
+      <c r="F9" s="93" t="n">
+        <v>74600</v>
+      </c>
+      <c r="G9" s="93" t="n">
+        <v>93900</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="91" t="str">
+        <v>Biochemist - I - LAB (B Support / Research) - R1</v>
+      </c>
+      <c r="B10" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C10" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>I</v>
+      </c>
+      <c r="E10" s="93" t="n">
+        <v>60700</v>
+      </c>
+      <c r="F10" s="93" t="n">
+        <v>81900</v>
+      </c>
+      <c r="G10" s="93" t="n">
+        <v>103200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="91" t="str">
+        <v>Biologist - I - LAB (B Support / Research) - R1</v>
+      </c>
+      <c r="B11" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C11" t="str">
+        <v>GS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>J</v>
+      </c>
+      <c r="E11" s="93" t="n">
+        <v>66800</v>
+      </c>
+      <c r="F11" s="93" t="n">
+        <v>90200</v>
+      </c>
+      <c r="G11" s="93" t="n">
+        <v>113600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="91" t="str">
+        <v>Business Analyst - II - Information Communications Technology (B Support / Professional) - P2</v>
+      </c>
+      <c r="B12" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C12" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D12" t="str">
+        <v>K</v>
+      </c>
+      <c r="E12" s="93" t="n">
+        <v>73400</v>
+      </c>
+      <c r="F12" s="93" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G12" s="93" t="n">
+        <v>124700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="str">
+        <v>Business Analyst - III - Information Communications Technology (B Support / Professional) - P3</v>
+      </c>
+      <c r="B13" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C13" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>L</v>
+      </c>
+      <c r="E13" s="93" t="n">
+        <v>80800</v>
+      </c>
+      <c r="F13" s="93" t="n">
+        <v>109000</v>
+      </c>
+      <c r="G13" s="93" t="n">
+        <v>137300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="91" t="str">
+        <v>Business Analyst - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      </c>
+      <c r="B14" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C14" t="str">
+        <v>PS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>M</v>
+      </c>
+      <c r="E14" s="93" t="n">
+        <v>88800</v>
+      </c>
+      <c r="F14" s="93" t="n">
+        <v>119900</v>
+      </c>
+      <c r="G14" s="93" t="n">
+        <v>150900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="str">
+        <v>Business Consultant - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      </c>
+      <c r="B15" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C15" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="91" t="str">
+        <v>Chemical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B16" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="91" t="str">
+        <v>Civil Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B17" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="str">
+        <v>Civil Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B18" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C18" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="91" t="str">
+        <v>Compliance Specialist - I - Administrative (B Support / Professional) - P1</v>
+      </c>
+      <c r="B19" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C19" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="str">
+        <v>Data Analyst - II - Information Communications Technology (B Support / Professional) - P2</v>
+      </c>
+      <c r="B20" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C20" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="91" t="str">
+        <v>Data Entry Clerk - III - Business Support (A) Admin/Finance/HR - B3</v>
+      </c>
+      <c r="B21" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C21" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="91" t="str">
+        <v>Documentation Specialist - I - Administrative (B Support / Professional) - P1</v>
+      </c>
+      <c r="B22" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C22" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="91" t="str">
+        <v>Documentation Specialist - III - Administrative (B Support / Professional) - B3</v>
+      </c>
+      <c r="B23" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C23" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="91" t="str">
+        <v>Electrical Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B24" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C24" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="91" t="str">
+        <v>Electrical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B25" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C25" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="91" t="str">
+        <v>Environmental Monitoring Specialist II - Environment Health &amp; Safety P&amp;O Support / Professional P2</v>
+      </c>
+      <c r="B26" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C26" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="91" t="str">
+        <v>Executive Assistant - II - Business Support (A) Admin/Finance/HR - B2</v>
+      </c>
+      <c r="B27" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C27" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="str">
+        <v>Health/Safety Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B28" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C28" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="91" t="str">
+        <v>Health/Safety Specialist - III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B29" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C29" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="91" t="str">
+        <v>Health/Safety Specialist - IV - Environment Health &amp; Safety (P &amp; O Support / Professional) - P4</v>
+      </c>
+      <c r="B30" s="91" t="str">
+        <v>M</v>
+      </c>
+      <c r="C30" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="91" t="str">
+        <v>HR Analyst - I - Human Resources (B Support / Professional) - P1</v>
+      </c>
+      <c r="B31" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C31" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="91" t="str">
+        <v>HR Analyst - II - Human Resources (B Support / Professional) - P2</v>
+      </c>
+      <c r="B32" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="91" t="str">
+        <v>Industrial Hygienist - I - Environment Health  &amp; Safety P&amp;O Support / Professional - P1</v>
+      </c>
+      <c r="B33" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="str">
+        <v>Industrial Hygienist - II - Environment  Health &amp; Safety P&amp;O Support / Professional - P2</v>
+      </c>
+      <c r="B34" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="str">
+        <v>Inspector Operator - III - Industrial (P &amp; O Support / Professional) - O3</v>
+      </c>
+      <c r="B35" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C35" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="str">
+        <v>Lab Assistant - III - Business Support (T) Science/Medical/Clinical - B3</v>
+      </c>
+      <c r="B36" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C36" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="str">
+        <v>Lab Technician - Animal - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mi</v>
+      </c>
+      <c r="B37" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C37" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="91" t="str">
+        <v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (High)</v>
+      </c>
+      <c r="B38" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C38" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="91" t="str">
+        <v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mid)</v>
+      </c>
+      <c r="B39" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C39" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="91" t="str">
+        <v>Lab Technician - III - Production &amp; Operations Support (T) Science/Medical/Clinical - O3</v>
+      </c>
+      <c r="B40" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C40" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="91" t="str">
+        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      </c>
+      <c r="B41" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C41" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="91" t="str">
+        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O2 High – PS</v>
+      </c>
+      <c r="B42" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C42" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="91" t="str">
+        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O3 – PS</v>
+      </c>
+      <c r="B43" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C43" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="91" t="str">
+        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O4 – PS</v>
+      </c>
+      <c r="B44" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C44" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="91" t="str">
+        <v>Maintenance Technician - IV - Production &amp; Operations Support (T): Industrial - O4</v>
+      </c>
+      <c r="B45" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C45" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="91" t="str">
+        <v>Marketing Research Specialist - II - Creative (B Support / Professional) - P2</v>
+      </c>
+      <c r="B46" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C46" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="91" t="str">
+        <v>Mechanical Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B47" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C47" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="91" t="str">
+        <v>Mechanical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B48" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C48" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="91" t="str">
+        <v>Operations Manager - I - Industrial (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B49" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C49" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="91" t="str">
+        <v>Operations Manager - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B50" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C50" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="91" t="str">
+        <v>Operations Manager - IV - Industrial (P &amp; O Support / Professional) - P4</v>
+      </c>
+      <c r="B51" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C51" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="91" t="str">
+        <v>Packaging Engineer - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B52" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C52" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="91" t="str">
+        <v>Packaging Operator - I - Production &amp; Operations Support (T): Industrial - O1</v>
+      </c>
+      <c r="B53" s="91" t="str">
+        <v>B</v>
+      </c>
+      <c r="C53" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="91" t="str">
+        <v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</v>
+      </c>
+      <c r="B54" s="91" t="str">
+        <v>B</v>
+      </c>
+      <c r="C54" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="91" t="str">
+        <v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      </c>
+      <c r="B55" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C55" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="91" t="str">
+        <v>Packaging Operator - III - Production &amp; Operations Support (T): Industrial - O3</v>
+      </c>
+      <c r="B56" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C56" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="91" t="str">
+        <v>Pharmaceutical Specialist - I - Engineering (P &amp; O  Support / Professional) - P1</v>
+      </c>
+      <c r="B57" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C57" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="91" t="str">
+        <v>Pharmaceutical Specialist - Ill - Engineering (P &amp; O  Support / Professional) - P3</v>
+      </c>
+      <c r="B58" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C58" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="91" t="str">
+        <v>Process Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B59" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C59" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="91" t="str">
+        <v>Process Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B60" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C60" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="91" t="str">
+        <v>Process Engineer - IV - Engineering (P &amp; O Support / Professional) - P4</v>
+      </c>
+      <c r="B61" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C61" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="91" t="str">
+        <v>Procurement Specialist - llI - Administrative (B Support /  Professional) - P3</v>
+      </c>
+      <c r="B62" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C62" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="91" t="str">
+        <v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      </c>
+      <c r="B63" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C63" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="91" t="str">
+        <v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      </c>
+      <c r="B64" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C64" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="91" t="str">
+        <v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      </c>
+      <c r="B65" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C65" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="91" t="str">
+        <v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      </c>
+      <c r="B66" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C66" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="91" t="str">
+        <v>Project Coordinator - I - Administrative (B Support / Professional) - P1</v>
+      </c>
+      <c r="B67" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C67" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="91" t="str">
+        <v>Project Coordinator - II - Administrative (B Support / Professional) - P2</v>
+      </c>
+      <c r="B68" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C68" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="91" t="str">
+        <v>Project Manager - Il - Engineering (P &amp; O Support /  Professional) - P2</v>
+      </c>
+      <c r="B69" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C69" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="91" t="str">
+        <v>Project Manager - Ill - Engineering (P &amp; O Support /  Professional) - P3</v>
+      </c>
+      <c r="B70" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C70" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="91" t="str">
+        <v>Project Manager - IT - II - Information Communications Technology (B Support / Professional) - P2</v>
+      </c>
+      <c r="B71" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C71" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="91" t="str">
+        <v>Project Manager - IT - III - Information Communications Technology (B Support / Professional) - P3</v>
+      </c>
+      <c r="B72" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C72" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="91" t="str">
+        <v>Project Manager - IT - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      </c>
+      <c r="B73" s="91" t="str">
+        <v>M</v>
+      </c>
+      <c r="C73" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="91" t="str">
+        <v>Project Manager - IV - Engineering (P &amp; O Support /  Professional) - P4</v>
+      </c>
+      <c r="B74" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C74" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="91" t="str">
+        <v>Project Manager - Non IT - II - Administrative (B Support / Professional) - P2</v>
+      </c>
+      <c r="B75" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C75" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="91" t="str">
+        <v>Project Manager - Non IT - III - Administrative (B Support / Professional) - P3</v>
+      </c>
+      <c r="B76" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C76" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="91" t="str">
+        <v>Project Manager - Non IT - IV - Administrative (B Support / Professional) - P4</v>
+      </c>
+      <c r="B77" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C77" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="91" t="str">
+        <v>Qualified Person - III - Administrative (B Support /  Professional) - P3</v>
+      </c>
+      <c r="B78" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C78" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="91" t="str">
+        <v>Quality Assurance - Packaging - I - Industrial (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B79" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C79" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="91" t="str">
+        <v>Quality Assurance - Packaging - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B80" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C80" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="91" t="str">
+        <v>Quality Assurance - Packaging - IV - Industrial (P &amp; O Support / Professional) - P4</v>
+      </c>
+      <c r="B81" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C81" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="91" t="str">
+        <v>Quality Auditor - I - Administrative (B Support / Professional) - P1</v>
+      </c>
+      <c r="B82" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C82" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="91" t="str">
+        <v>Quality Auditor - II - Administrative (B Support / Professional) - P2</v>
+      </c>
+      <c r="B83" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C83" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="91" t="str">
+        <v>Quality Auditor - III - Administrative (B Support / Professional) - P3</v>
+      </c>
+      <c r="B84" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C84" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="91" t="str">
+        <v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (High)</v>
+      </c>
+      <c r="B85" s="91" t="str">
+        <v>D</v>
+      </c>
+      <c r="C85" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="91" t="str">
+        <v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (Mid)</v>
+      </c>
+      <c r="B86" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C86" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="91" t="str">
+        <v>Quality Control Specialist - III - LAB (O Support / Research) - O3</v>
+      </c>
+      <c r="B87" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C87" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="91" t="str">
+        <v>Quality Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B88" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C88" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="91" t="str">
+        <v>Regulatory Affairs Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B89" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C89" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="91" t="str">
+        <v>Regulatory Affairs Specialist III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B90" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C90" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="91" t="str">
+        <v>Reliability Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B91" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C91" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="91" t="str">
+        <v>Reliability Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B92" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C92" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="91" t="str">
+        <v>Reliability Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B93" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C93" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="91" t="str">
+        <v>Reliability Engineer - IV - Engineering (P &amp; O Support / Professional) - O4</v>
+      </c>
+      <c r="B94" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C94" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="91" t="str">
+        <v>Sales Assistant - I - Administrative (B Support / Professional) - P1</v>
+      </c>
+      <c r="B95" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C95" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="91" t="str">
+        <v>Scientific Technical Specialist - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B96" s="91" t="str">
+        <v>F</v>
+      </c>
+      <c r="C96" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="91" t="str">
+        <v>Scientific Technical Specialist - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B97" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C97" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="91" t="str">
+        <v>Scientific Technical Specialist - III - Engineering (P &amp; O Support / Professional) - O3</v>
+      </c>
+      <c r="B98" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C98" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="91" t="str">
+        <v>Scientist - I - Science (P &amp; O / Research) - R1</v>
+      </c>
+      <c r="B99" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C99" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="91" t="str">
+        <v>Scientist - I - Science (P &amp; O / Research) - R1 - GS</v>
+      </c>
+      <c r="B100" s="91" t="str">
+        <v>E</v>
+      </c>
+      <c r="C100" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="91" t="str">
+        <v>Scientist - II - Science (P &amp; O / Research) - R2</v>
+      </c>
+      <c r="B101" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C101" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="91" t="str">
+        <v>Scientist - III - Science (P &amp; O / Research) - R3</v>
+      </c>
+      <c r="B102" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C102" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="91" t="str">
+        <v>Shipping/Receiving Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      </c>
+      <c r="B103" s="91" t="str">
+        <v>C</v>
+      </c>
+      <c r="C103" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="91" t="str">
+        <v>Supply Chain Specialist - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B104" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C104" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="91" t="str">
+        <v>Supply Chain Specialist - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B105" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C105" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="91" t="str">
+        <v>Supply Chain Specialist - IV - Engineering (P &amp; O Support / Professional) - P4</v>
+      </c>
+      <c r="B106" s="91" t="str">
+        <v>L</v>
+      </c>
+      <c r="C106" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="91" t="str">
+        <v>Technical Support Analyst - I - Information Communications Tech (B Support / Professional) - P1</v>
+      </c>
+      <c r="B107" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C107" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="91" t="str">
+        <v>Technical Support Analyst - II - Information Communications Tech (B Support / Professional) - P2</v>
+      </c>
+      <c r="B108" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C108" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="91" t="str">
+        <v>Technical Writer - II - Information Communications Technology (B Support / Professional) - P2</v>
+      </c>
+      <c r="B109" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C109" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="91" t="str">
+        <v>Validation Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      </c>
+      <c r="B110" s="91" t="str">
+        <v>G</v>
+      </c>
+      <c r="C110" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="91" t="str">
+        <v>Validation Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      </c>
+      <c r="B111" s="91" t="str">
+        <v>H</v>
+      </c>
+      <c r="C111" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="91" t="str">
+        <v>Validation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      </c>
+      <c r="B112" s="91" t="str">
+        <v>J</v>
+      </c>
+      <c r="C112" t="str">
+        <v>PS</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="92" t="str">
+        <v>Warehouse Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      </c>
+      <c r="B113" s="92" t="str">
+        <v>C</v>
+      </c>
+      <c r="C113" t="str">
+        <v>GS</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="92" t="inlineStr">
+        <is>
+          <t>CQ engineer Site Engineering P1-G midpoint (CQ=Commissioning&amp;Qualification)</t>
+        </is>
+      </c>
+      <c r="B114" s="92" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CQ engineer Site Engineering P1-F midpoint (CQ=Commissioning&amp;Qualification)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CQ engineer Site Engineering P1-G Tussen midpoint en max. (CQ=Commissioning&amp;Qualification)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SPOC=Programma-manager Site Engineering P3-J Tussen midpoint en max.</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Projectmanager Site Engineering P2-H Tussen midpoint en max.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Civil engineer Site Engineering P1-G midpoint 1 stap boven</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+    </row>
+    <row r="121">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+    </row>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+    </row>
+    <row r="123">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+    </row>
+    <row r="124">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+    </row>
+    <row r="125">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+    </row>
+    <row r="126">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+    </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+    </row>
+    <row r="128">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+    </row>
+    <row r="129">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+    </row>
+    <row r="130">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+    </row>
+    <row r="131">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+    </row>
+    <row r="132">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+    </row>
+    <row r="133">
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+    </row>
+    <row r="134">
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+    </row>
+    <row r="135">
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+    </row>
+    <row r="136">
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+    </row>
+    <row r="137">
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+    </row>
+    <row r="138">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+    </row>
+    <row r="139">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+    </row>
+    <row r="140">
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+    </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+    </row>
+    <row r="142">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+    </row>
+    <row r="143">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+    </row>
+    <row r="144">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+    </row>
+    <row r="145">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+    </row>
+    <row r="147">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+    </row>
+    <row r="148">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+    </row>
+    <row r="150">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+    </row>
+    <row r="151">
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+    </row>
+    <row r="152">
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+    </row>
+    <row r="153">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+    </row>
+    <row r="154">
+      <c r="A154"/>
+      <c r="B154"/>
+      <c r="C154"/>
+    </row>
+    <row r="155">
+      <c r="A155"/>
+      <c r="B155"/>
+      <c r="C155"/>
+    </row>
+    <row r="156">
+      <c r="A156"/>
+      <c r="B156"/>
+      <c r="C156"/>
+    </row>
+    <row r="157">
+      <c r="A157"/>
+      <c r="B157"/>
+      <c r="C157"/>
+    </row>
+    <row r="158">
+      <c r="A158"/>
+      <c r="B158"/>
+      <c r="C158"/>
+    </row>
+    <row r="159">
+      <c r="A159"/>
+      <c r="B159"/>
+      <c r="C159"/>
+    </row>
+    <row r="160">
+      <c r="A160"/>
+      <c r="B160"/>
+      <c r="C160"/>
+    </row>
+    <row r="161">
+      <c r="A161"/>
+      <c r="B161"/>
+      <c r="C161"/>
+    </row>
+    <row r="162">
+      <c r="A162"/>
+      <c r="B162"/>
+      <c r="C162"/>
+    </row>
+    <row r="163">
+      <c r="A163"/>
+      <c r="B163"/>
+      <c r="C163"/>
+    </row>
+    <row r="164">
+      <c r="A164"/>
+      <c r="B164"/>
+      <c r="C164"/>
+    </row>
+    <row r="165">
+      <c r="A165"/>
+      <c r="B165"/>
+      <c r="C165"/>
+    </row>
+    <row r="166">
+      <c r="A166"/>
+      <c r="B166"/>
+      <c r="C166"/>
+    </row>
+    <row r="167">
+      <c r="A167"/>
+      <c r="B167"/>
+      <c r="C167"/>
+    </row>
+    <row r="168">
+      <c r="A168"/>
+      <c r="B168"/>
+      <c r="C168"/>
+    </row>
+    <row r="169">
+      <c r="A169"/>
+      <c r="B169"/>
+      <c r="C169"/>
+    </row>
+    <row r="170">
+      <c r="A170"/>
+      <c r="B170"/>
+      <c r="C170"/>
+    </row>
+    <row r="171">
+      <c r="A171"/>
+      <c r="B171"/>
+      <c r="C171"/>
+    </row>
+    <row r="172">
+      <c r="A172"/>
+      <c r="B172"/>
+      <c r="C172"/>
+    </row>
+    <row r="173">
+      <c r="A173"/>
+      <c r="B173"/>
+      <c r="C173"/>
+    </row>
+    <row r="174">
+      <c r="A174"/>
+      <c r="B174"/>
+      <c r="C174"/>
+    </row>
+    <row r="175">
+      <c r="A175"/>
+      <c r="B175"/>
+      <c r="C175"/>
+    </row>
+    <row r="176">
+      <c r="A176"/>
+      <c r="B176"/>
+      <c r="C176"/>
+    </row>
+    <row r="177">
+      <c r="A177"/>
+      <c r="B177"/>
+      <c r="C177"/>
+    </row>
+    <row r="178">
+      <c r="A178"/>
+      <c r="B178"/>
+      <c r="C178"/>
+    </row>
+    <row r="179">
+      <c r="A179"/>
+      <c r="B179"/>
+      <c r="C179"/>
+    </row>
+    <row r="180">
+      <c r="A180"/>
+      <c r="B180"/>
+      <c r="C180"/>
+    </row>
+    <row r="181">
+      <c r="A181"/>
+      <c r="B181"/>
+      <c r="C181"/>
+    </row>
+    <row r="182">
+      <c r="A182"/>
+      <c r="B182"/>
+      <c r="C182"/>
+    </row>
+    <row r="183">
+      <c r="A183"/>
+      <c r="B183"/>
+      <c r="C183"/>
+    </row>
+    <row r="184">
+      <c r="A184"/>
+      <c r="B184"/>
+      <c r="C184"/>
+    </row>
+    <row r="185">
+      <c r="A185"/>
+      <c r="B185"/>
+      <c r="C185"/>
+    </row>
+    <row r="186">
+      <c r="A186"/>
+      <c r="B186"/>
+      <c r="C186"/>
+    </row>
+    <row r="187">
+      <c r="A187"/>
+      <c r="B187"/>
+      <c r="C187"/>
+    </row>
+    <row r="188">
+      <c r="A188"/>
+      <c r="B188"/>
+      <c r="C188"/>
+    </row>
+    <row r="189">
+      <c r="A189"/>
+      <c r="B189"/>
+      <c r="C189"/>
+    </row>
+    <row r="190">
+      <c r="A190"/>
+      <c r="B190"/>
+      <c r="C190"/>
+    </row>
+    <row r="191">
+      <c r="A191"/>
+      <c r="B191"/>
+      <c r="C191"/>
+    </row>
+    <row r="192">
+      <c r="A192"/>
+      <c r="B192"/>
+      <c r="C192"/>
+    </row>
+    <row r="193">
+      <c r="A193"/>
+      <c r="B193"/>
+      <c r="C193"/>
+    </row>
+    <row r="194">
+      <c r="A194"/>
+      <c r="B194"/>
+      <c r="C194"/>
+    </row>
+    <row r="195">
+      <c r="A195"/>
+      <c r="B195"/>
+      <c r="C195"/>
+    </row>
+    <row r="196">
+      <c r="A196"/>
+      <c r="B196"/>
+      <c r="C196"/>
+    </row>
+    <row r="197">
+      <c r="A197"/>
+      <c r="B197"/>
+      <c r="C197"/>
+    </row>
+    <row r="198">
+      <c r="A198"/>
+      <c r="B198"/>
+      <c r="C198"/>
+    </row>
+    <row r="199">
+      <c r="A199"/>
+      <c r="B199"/>
+      <c r="C199"/>
+    </row>
+    <row r="200">
+      <c r="A200"/>
+      <c r="B200"/>
+      <c r="C200"/>
+    </row>
+    <row r="201">
+      <c r="A201"/>
+      <c r="B201"/>
+      <c r="C201"/>
+    </row>
+    <row r="202">
+      <c r="A202"/>
+      <c r="B202"/>
+      <c r="C202"/>
+    </row>
+    <row r="203">
+      <c r="A203"/>
+      <c r="B203"/>
+      <c r="C203"/>
+    </row>
+    <row r="204">
+      <c r="A204"/>
+      <c r="B204"/>
+      <c r="C204"/>
+    </row>
+    <row r="205">
+      <c r="A205"/>
+      <c r="B205"/>
+      <c r="C205"/>
+    </row>
+    <row r="206">
+      <c r="A206"/>
+      <c r="B206"/>
+      <c r="C206"/>
+    </row>
+    <row r="207">
+      <c r="A207"/>
+      <c r="B207"/>
+      <c r="C207"/>
+    </row>
+    <row r="208">
+      <c r="A208"/>
+      <c r="B208"/>
+      <c r="C208"/>
+    </row>
+    <row r="209">
+      <c r="A209"/>
+      <c r="B209"/>
+      <c r="C209"/>
+    </row>
+    <row r="210">
+      <c r="A210"/>
+      <c r="B210"/>
+      <c r="C210"/>
+    </row>
+    <row r="211">
+      <c r="A211"/>
+      <c r="B211"/>
+      <c r="C211"/>
+    </row>
+    <row r="212">
+      <c r="A212"/>
+      <c r="B212"/>
+      <c r="C212"/>
+    </row>
+    <row r="213">
+      <c r="A213"/>
+      <c r="B213"/>
+      <c r="C213"/>
+    </row>
+    <row r="214">
+      <c r="A214"/>
+      <c r="B214"/>
+      <c r="C214"/>
+    </row>
+    <row r="215">
+      <c r="A215"/>
+      <c r="B215"/>
+      <c r="C215"/>
+    </row>
+    <row r="216">
+      <c r="A216"/>
+      <c r="B216"/>
+      <c r="C216"/>
+    </row>
+    <row r="217">
+      <c r="A217"/>
+      <c r="B217"/>
+      <c r="C217"/>
+    </row>
+    <row r="218">
+      <c r="A218"/>
+      <c r="B218"/>
+      <c r="C218"/>
+    </row>
+    <row r="219">
+      <c r="A219"/>
+      <c r="B219"/>
+      <c r="C219"/>
+    </row>
+    <row r="220">
+      <c r="A220"/>
+      <c r="B220"/>
+      <c r="C220"/>
+    </row>
+    <row r="221">
+      <c r="A221"/>
+      <c r="B221"/>
+      <c r="C221"/>
+    </row>
+    <row r="222">
+      <c r="A222"/>
+      <c r="B222"/>
+      <c r="C222"/>
+    </row>
+    <row r="223">
+      <c r="A223"/>
+      <c r="B223"/>
+      <c r="C223"/>
+    </row>
+    <row r="224">
+      <c r="A224"/>
+      <c r="B224"/>
+      <c r="C224"/>
+    </row>
+    <row r="225">
+      <c r="A225"/>
+      <c r="B225"/>
+      <c r="C225"/>
+    </row>
+    <row r="226">
+      <c r="A226"/>
+      <c r="B226"/>
+      <c r="C226"/>
+    </row>
+    <row r="227">
+      <c r="A227"/>
+      <c r="B227"/>
+      <c r="C227"/>
+    </row>
+    <row r="228">
+      <c r="A228"/>
+      <c r="B228"/>
+      <c r="C228"/>
+    </row>
+    <row r="229">
+      <c r="A229"/>
+      <c r="B229"/>
+      <c r="C229"/>
+    </row>
+    <row r="230">
+      <c r="A230"/>
+      <c r="B230"/>
+      <c r="C230"/>
+    </row>
+    <row r="231">
+      <c r="A231"/>
+      <c r="B231"/>
+      <c r="C231"/>
+    </row>
+    <row r="232">
+      <c r="A232"/>
+      <c r="B232"/>
+      <c r="C232"/>
+    </row>
+    <row r="233">
+      <c r="A233"/>
+      <c r="B233"/>
+      <c r="C233"/>
+    </row>
+    <row r="234">
+      <c r="A234"/>
+      <c r="B234"/>
+      <c r="C234"/>
+    </row>
+    <row r="235">
+      <c r="A235"/>
+      <c r="B235"/>
+      <c r="C235"/>
+    </row>
+    <row r="236">
+      <c r="A236"/>
+      <c r="B236"/>
+      <c r="C236"/>
+    </row>
+    <row r="237">
+      <c r="A237"/>
+      <c r="B237"/>
+      <c r="C237"/>
+    </row>
+    <row r="238">
+      <c r="A238"/>
+      <c r="B238"/>
+      <c r="C238"/>
+    </row>
+    <row r="239">
+      <c r="A239"/>
+      <c r="B239"/>
+      <c r="C239"/>
+    </row>
+    <row r="240">
+      <c r="A240"/>
+      <c r="B240"/>
+      <c r="C240"/>
+    </row>
+    <row r="241">
+      <c r="A241"/>
+      <c r="B241"/>
+      <c r="C241"/>
+    </row>
+    <row r="242">
+      <c r="A242"/>
+      <c r="B242"/>
+      <c r="C242"/>
+    </row>
+    <row r="243">
+      <c r="A243"/>
+      <c r="B243"/>
+      <c r="C243"/>
+    </row>
+    <row r="244">
+      <c r="A244"/>
+      <c r="B244"/>
+      <c r="C244"/>
+    </row>
+    <row r="245">
+      <c r="A245"/>
+      <c r="B245"/>
+      <c r="C245"/>
+    </row>
+    <row r="246">
+      <c r="A246"/>
+      <c r="B246"/>
+      <c r="C246"/>
+    </row>
+    <row r="247">
+      <c r="A247"/>
+      <c r="B247"/>
+      <c r="C247"/>
+    </row>
+    <row r="248">
+      <c r="A248"/>
+      <c r="B248"/>
+      <c r="C248"/>
+    </row>
+    <row r="249">
+      <c r="A249"/>
+      <c r="B249"/>
+      <c r="C249"/>
+    </row>
+    <row r="250">
+      <c r="A250"/>
+      <c r="B250"/>
+      <c r="C250"/>
+    </row>
+    <row r="251">
+      <c r="A251"/>
+      <c r="B251"/>
+      <c r="C251"/>
+    </row>
+    <row r="252">
+      <c r="A252"/>
+      <c r="B252"/>
+      <c r="C252"/>
+    </row>
+    <row r="253">
+      <c r="A253"/>
+      <c r="B253"/>
+      <c r="C253"/>
+    </row>
+    <row r="254">
+      <c r="A254"/>
+      <c r="B254"/>
+      <c r="C254"/>
+    </row>
+    <row r="255">
+      <c r="A255"/>
+      <c r="B255"/>
+      <c r="C255"/>
+    </row>
+    <row r="256">
+      <c r="A256"/>
+      <c r="B256"/>
+      <c r="C256"/>
+    </row>
+    <row r="257">
+      <c r="A257"/>
+      <c r="B257"/>
+      <c r="C257"/>
+    </row>
+    <row r="258">
+      <c r="A258"/>
+      <c r="B258"/>
+      <c r="C258"/>
+    </row>
+    <row r="259">
+      <c r="A259"/>
+      <c r="B259"/>
+      <c r="C259"/>
+    </row>
+    <row r="260">
+      <c r="A260"/>
+      <c r="B260"/>
+      <c r="C260"/>
+    </row>
+    <row r="261">
+      <c r="A261"/>
+      <c r="B261"/>
+      <c r="C261"/>
+    </row>
+    <row r="262">
+      <c r="A262"/>
+      <c r="B262"/>
+      <c r="C262"/>
+    </row>
+    <row r="263">
+      <c r="A263"/>
+      <c r="B263"/>
+      <c r="C263"/>
+    </row>
+    <row r="264">
+      <c r="A264"/>
+      <c r="B264"/>
+      <c r="C264"/>
+    </row>
+    <row r="265">
+      <c r="A265"/>
+      <c r="B265"/>
+      <c r="C265"/>
+    </row>
+    <row r="266">
+      <c r="A266"/>
+      <c r="B266"/>
+      <c r="C266"/>
+    </row>
+    <row r="267">
+      <c r="A267"/>
+      <c r="B267"/>
+      <c r="C267"/>
+    </row>
+    <row r="268">
+      <c r="A268"/>
+      <c r="B268"/>
+      <c r="C268"/>
+    </row>
+    <row r="269">
+      <c r="A269"/>
+      <c r="B269"/>
+      <c r="C269"/>
+    </row>
+    <row r="270">
+      <c r="A270"/>
+      <c r="B270"/>
+      <c r="C270"/>
+    </row>
+    <row r="271">
+      <c r="A271"/>
+      <c r="B271"/>
+      <c r="C271"/>
+    </row>
+    <row r="272">
+      <c r="A272"/>
+      <c r="B272"/>
+      <c r="C272"/>
+    </row>
+    <row r="273">
+      <c r="A273"/>
+      <c r="B273"/>
+      <c r="C273"/>
+    </row>
+    <row r="274">
+      <c r="A274"/>
+      <c r="B274"/>
+      <c r="C274"/>
+    </row>
+    <row r="275">
+      <c r="A275"/>
+      <c r="B275"/>
+      <c r="C275"/>
+    </row>
+    <row r="276">
+      <c r="A276"/>
+      <c r="B276"/>
+      <c r="C276"/>
+    </row>
+    <row r="277">
+      <c r="A277"/>
+      <c r="B277"/>
+      <c r="C277"/>
+    </row>
+    <row r="278">
+      <c r="A278"/>
+      <c r="B278"/>
+      <c r="C278"/>
+    </row>
+    <row r="279">
+      <c r="A279"/>
+      <c r="B279"/>
+      <c r="C279"/>
+    </row>
+    <row r="280">
+      <c r="A280"/>
+      <c r="B280"/>
+      <c r="C280"/>
+    </row>
+    <row r="281">
+      <c r="A281"/>
+      <c r="B281"/>
+      <c r="C281"/>
+    </row>
+    <row r="282">
+      <c r="A282"/>
+      <c r="B282"/>
+      <c r="C282"/>
+    </row>
+    <row r="283">
+      <c r="A283"/>
+      <c r="B283"/>
+      <c r="C283"/>
+    </row>
+    <row r="284">
+      <c r="A284"/>
+      <c r="B284"/>
+      <c r="C284"/>
+    </row>
+    <row r="285">
+      <c r="A285"/>
+      <c r="B285"/>
+      <c r="C285"/>
+    </row>
+    <row r="286">
+      <c r="A286"/>
+      <c r="B286"/>
+      <c r="C286"/>
+    </row>
+    <row r="287">
+      <c r="A287"/>
+      <c r="B287"/>
+      <c r="C287"/>
+    </row>
+    <row r="288">
+      <c r="A288"/>
+      <c r="B288"/>
+      <c r="C288"/>
+    </row>
+    <row r="289">
+      <c r="A289"/>
+      <c r="B289"/>
+      <c r="C289"/>
+    </row>
+    <row r="290">
+      <c r="A290"/>
+      <c r="B290"/>
+      <c r="C290"/>
+    </row>
+    <row r="291">
+      <c r="A291"/>
+      <c r="B291"/>
+      <c r="C291"/>
+    </row>
+    <row r="292">
+      <c r="A292"/>
+      <c r="B292"/>
+      <c r="C292"/>
+    </row>
+    <row r="293">
+      <c r="A293"/>
+      <c r="B293"/>
+      <c r="C293"/>
+    </row>
+    <row r="294">
+      <c r="A294"/>
+      <c r="B294"/>
+      <c r="C294"/>
+    </row>
+    <row r="295">
+      <c r="A295"/>
+      <c r="B295"/>
+      <c r="C295"/>
+    </row>
+    <row r="296">
+      <c r="A296"/>
+      <c r="B296"/>
+      <c r="C296"/>
+    </row>
+    <row r="297">
+      <c r="A297"/>
+      <c r="B297"/>
+      <c r="C297"/>
+    </row>
+    <row r="298">
+      <c r="A298"/>
+      <c r="B298"/>
+      <c r="C298"/>
+    </row>
+    <row r="299">
+      <c r="A299"/>
+      <c r="B299"/>
+      <c r="C299"/>
+    </row>
+    <row r="300">
+      <c r="A300"/>
+      <c r="B300"/>
+      <c r="C300"/>
+    </row>
+    <row r="301">
+      <c r="A301"/>
+      <c r="B301"/>
+      <c r="C301"/>
+    </row>
+    <row r="302">
+      <c r="A302"/>
+      <c r="B302"/>
+      <c r="C302"/>
+    </row>
+    <row r="303">
+      <c r="A303"/>
+      <c r="B303"/>
+      <c r="C303"/>
+    </row>
+    <row r="304">
+      <c r="A304"/>
+      <c r="B304"/>
+      <c r="C304"/>
+    </row>
+    <row r="305">
+      <c r="A305"/>
+      <c r="B305"/>
+      <c r="C305"/>
+    </row>
+    <row r="306">
+      <c r="A306"/>
+      <c r="B306"/>
+      <c r="C306"/>
+    </row>
+    <row r="307">
+      <c r="A307"/>
+      <c r="B307"/>
+      <c r="C307"/>
+    </row>
+    <row r="308">
+      <c r="A308"/>
+      <c r="B308"/>
+      <c r="C308"/>
+    </row>
+    <row r="309">
+      <c r="A309"/>
+      <c r="B309"/>
+      <c r="C309"/>
+    </row>
+    <row r="310">
+      <c r="A310"/>
+      <c r="B310"/>
+      <c r="C310"/>
+    </row>
+    <row r="311">
+      <c r="A311"/>
+      <c r="B311"/>
+      <c r="C311"/>
+    </row>
+    <row r="312">
+      <c r="A312"/>
+      <c r="B312"/>
+      <c r="C312"/>
+    </row>
+    <row r="313">
+      <c r="A313"/>
+      <c r="B313"/>
+      <c r="C313"/>
+    </row>
+    <row r="314">
+      <c r="A314"/>
+      <c r="B314"/>
+      <c r="C314"/>
+    </row>
+    <row r="315">
+      <c r="A315"/>
+      <c r="B315"/>
+      <c r="C315"/>
+    </row>
+    <row r="316">
+      <c r="A316"/>
+      <c r="B316"/>
+      <c r="C316"/>
+    </row>
+    <row r="317">
+      <c r="A317"/>
+      <c r="B317"/>
+      <c r="C317"/>
+    </row>
+    <row r="318">
+      <c r="A318"/>
+      <c r="B318"/>
+      <c r="C318"/>
+    </row>
+    <row r="319">
+      <c r="A319"/>
+      <c r="B319"/>
+      <c r="C319"/>
+    </row>
+    <row r="320">
+      <c r="A320"/>
+      <c r="B320"/>
+      <c r="C320"/>
+    </row>
+    <row r="321">
+      <c r="A321"/>
+      <c r="B321"/>
+      <c r="C321"/>
+    </row>
+    <row r="322">
+      <c r="A322"/>
+      <c r="B322"/>
+      <c r="C322"/>
+    </row>
+    <row r="323">
+      <c r="A323"/>
+      <c r="B323"/>
+      <c r="C323"/>
+    </row>
+    <row r="324">
+      <c r="A324"/>
+      <c r="B324"/>
+      <c r="C324"/>
+    </row>
+    <row r="325">
+      <c r="A325"/>
+      <c r="B325"/>
+      <c r="C325"/>
+    </row>
+    <row r="326">
+      <c r="A326"/>
+      <c r="B326"/>
+      <c r="C326"/>
+    </row>
+    <row r="327">
+      <c r="A327"/>
+      <c r="B327"/>
+      <c r="C327"/>
+    </row>
+    <row r="328">
+      <c r="A328"/>
+      <c r="B328"/>
+      <c r="C328"/>
+    </row>
+    <row r="329">
+      <c r="A329"/>
+      <c r="B329"/>
+      <c r="C329"/>
+    </row>
+    <row r="330">
+      <c r="A330"/>
+      <c r="B330"/>
+      <c r="C330"/>
+    </row>
+    <row r="331">
+      <c r="A331"/>
+      <c r="B331"/>
+      <c r="C331"/>
+    </row>
+    <row r="332">
+      <c r="A332"/>
+      <c r="B332"/>
+      <c r="C332"/>
+    </row>
+    <row r="333">
+      <c r="A333"/>
+      <c r="B333"/>
+      <c r="C333"/>
+    </row>
+    <row r="334">
+      <c r="A334"/>
+      <c r="B334"/>
+      <c r="C334"/>
+    </row>
+    <row r="335">
+      <c r="A335"/>
+      <c r="B335"/>
+      <c r="C335"/>
+    </row>
+    <row r="336">
+      <c r="A336"/>
+      <c r="B336"/>
+      <c r="C336"/>
+    </row>
+    <row r="337">
+      <c r="A337"/>
+      <c r="B337"/>
+      <c r="C337"/>
+    </row>
+    <row r="338">
+      <c r="A338"/>
+      <c r="B338"/>
+      <c r="C338"/>
+    </row>
+    <row r="339">
+      <c r="A339"/>
+      <c r="B339"/>
+      <c r="C339"/>
+    </row>
+    <row r="340">
+      <c r="A340"/>
+      <c r="B340"/>
+      <c r="C340"/>
+    </row>
+    <row r="341">
+      <c r="A341"/>
+      <c r="B341"/>
+      <c r="C341"/>
+    </row>
+    <row r="342">
+      <c r="A342"/>
+      <c r="B342"/>
+      <c r="C342"/>
+    </row>
+    <row r="343">
+      <c r="A343"/>
+      <c r="B343"/>
+      <c r="C343"/>
+    </row>
+    <row r="344">
+      <c r="A344"/>
+      <c r="B344"/>
+      <c r="C344"/>
+    </row>
+    <row r="345">
+      <c r="A345"/>
+      <c r="B345"/>
+      <c r="C345"/>
+    </row>
+    <row r="346">
+      <c r="A346"/>
+      <c r="B346"/>
+      <c r="C346"/>
+    </row>
+    <row r="347">
+      <c r="A347"/>
+      <c r="B347"/>
+      <c r="C347"/>
+    </row>
+    <row r="348">
+      <c r="A348"/>
+      <c r="B348"/>
+      <c r="C348"/>
+    </row>
+    <row r="349">
+      <c r="A349"/>
+      <c r="B349"/>
+      <c r="C349"/>
+    </row>
+    <row r="350">
+      <c r="A350"/>
+      <c r="B350"/>
+      <c r="C350"/>
+    </row>
+    <row r="351">
+      <c r="A351"/>
+      <c r="B351"/>
+      <c r="C351"/>
+    </row>
+    <row r="352">
+      <c r="A352"/>
+      <c r="B352"/>
+      <c r="C352"/>
+    </row>
+    <row r="353">
+      <c r="A353"/>
+      <c r="B353"/>
+      <c r="C353"/>
+    </row>
+    <row r="354">
+      <c r="A354"/>
+      <c r="B354"/>
+      <c r="C354"/>
+    </row>
+    <row r="355">
+      <c r="A355"/>
+      <c r="B355"/>
+      <c r="C355"/>
+    </row>
+    <row r="356">
+      <c r="A356"/>
+      <c r="B356"/>
+      <c r="C356"/>
+    </row>
+    <row r="357">
+      <c r="A357"/>
+      <c r="B357"/>
+      <c r="C357"/>
+    </row>
+    <row r="358">
+      <c r="A358"/>
+      <c r="B358"/>
+      <c r="C358"/>
+    </row>
+    <row r="359">
+      <c r="A359"/>
+      <c r="B359"/>
+      <c r="C359"/>
+    </row>
+    <row r="360">
+      <c r="A360"/>
+      <c r="B360"/>
+      <c r="C360"/>
+    </row>
+    <row r="361">
+      <c r="A361"/>
+      <c r="B361"/>
+      <c r="C361"/>
+    </row>
+    <row r="362">
+      <c r="A362"/>
+      <c r="B362"/>
+      <c r="C362"/>
+    </row>
+    <row r="363">
+      <c r="A363"/>
+      <c r="B363"/>
+      <c r="C363"/>
+    </row>
+    <row r="364">
+      <c r="A364"/>
+      <c r="B364"/>
+      <c r="C364"/>
+    </row>
+    <row r="365">
+      <c r="A365"/>
+      <c r="B365"/>
+      <c r="C365"/>
+    </row>
+    <row r="366">
+      <c r="A366"/>
+      <c r="B366"/>
+      <c r="C366"/>
+    </row>
+    <row r="367">
+      <c r="A367"/>
+      <c r="B367"/>
+      <c r="C367"/>
+    </row>
+    <row r="368">
+      <c r="A368"/>
+      <c r="B368"/>
+      <c r="C368"/>
+    </row>
+    <row r="369">
+      <c r="A369"/>
+      <c r="B369"/>
+      <c r="C369"/>
+    </row>
+    <row r="370">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+    </row>
+    <row r="371">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+    </row>
+    <row r="372">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+    </row>
+    <row r="373">
+      <c r="A373"/>
+      <c r="B373"/>
+      <c r="C373"/>
+    </row>
+    <row r="374">
+      <c r="A374"/>
+      <c r="B374"/>
+      <c r="C374"/>
+    </row>
+    <row r="375">
+      <c r="A375"/>
+      <c r="B375"/>
+      <c r="C375"/>
+    </row>
+    <row r="376">
+      <c r="A376"/>
+      <c r="B376"/>
+      <c r="C376"/>
+    </row>
+    <row r="377">
+      <c r="A377"/>
+      <c r="B377"/>
+      <c r="C377"/>
+    </row>
+    <row r="378">
+      <c r="A378"/>
+      <c r="B378"/>
+      <c r="C378"/>
+    </row>
+    <row r="379">
+      <c r="A379"/>
+      <c r="B379"/>
+      <c r="C379"/>
+    </row>
+    <row r="380">
+      <c r="A380"/>
+      <c r="B380"/>
+      <c r="C380"/>
+    </row>
+    <row r="381">
+      <c r="A381"/>
+      <c r="B381"/>
+      <c r="C381"/>
+    </row>
+    <row r="382">
+      <c r="A382"/>
+      <c r="B382"/>
+      <c r="C382"/>
+    </row>
+    <row r="383">
+      <c r="A383"/>
+      <c r="B383"/>
+      <c r="C383"/>
+    </row>
+    <row r="384">
+      <c r="A384"/>
+      <c r="B384"/>
+      <c r="C384"/>
+    </row>
+    <row r="385">
+      <c r="A385"/>
+      <c r="B385"/>
+      <c r="C385"/>
+    </row>
+    <row r="386">
+      <c r="A386"/>
+      <c r="B386"/>
+      <c r="C386"/>
+    </row>
+    <row r="387">
+      <c r="A387"/>
+      <c r="B387"/>
+      <c r="C387"/>
+    </row>
+    <row r="388">
+      <c r="A388"/>
+      <c r="B388"/>
+      <c r="C388"/>
+    </row>
+    <row r="389">
+      <c r="A389"/>
+      <c r="B389"/>
+      <c r="C389"/>
+    </row>
+    <row r="390">
+      <c r="A390"/>
+      <c r="B390"/>
+      <c r="C390"/>
+    </row>
+    <row r="391">
+      <c r="A391"/>
+      <c r="B391"/>
+      <c r="C391"/>
+    </row>
+    <row r="392">
+      <c r="A392"/>
+      <c r="B392"/>
+      <c r="C392"/>
+    </row>
+    <row r="393">
+      <c r="A393"/>
+      <c r="B393"/>
+      <c r="C393"/>
+    </row>
+    <row r="394">
+      <c r="A394"/>
+      <c r="B394"/>
+      <c r="C394"/>
+    </row>
+    <row r="395">
+      <c r="A395"/>
+      <c r="B395"/>
+      <c r="C395"/>
+    </row>
+    <row r="396">
+      <c r="A396"/>
+      <c r="B396"/>
+      <c r="C396"/>
+    </row>
+    <row r="397">
+      <c r="A397"/>
+      <c r="B397"/>
+      <c r="C397"/>
+    </row>
+    <row r="398">
+      <c r="A398"/>
+      <c r="B398"/>
+      <c r="C398"/>
+    </row>
+    <row r="399">
+      <c r="A399"/>
+      <c r="B399"/>
+      <c r="C399"/>
+    </row>
+    <row r="400">
+      <c r="A400"/>
+      <c r="B400"/>
+      <c r="C400"/>
+    </row>
+    <row r="401">
+      <c r="A401"/>
+      <c r="B401"/>
+      <c r="C401"/>
+    </row>
+    <row r="402">
+      <c r="A402"/>
+      <c r="B402"/>
+      <c r="C402"/>
+    </row>
+    <row r="403">
+      <c r="A403"/>
+      <c r="B403"/>
+      <c r="C403"/>
+    </row>
+    <row r="404">
+      <c r="A404"/>
+      <c r="B404"/>
+      <c r="C404"/>
+    </row>
+    <row r="405">
+      <c r="A405"/>
+      <c r="B405"/>
+      <c r="C405"/>
+    </row>
+    <row r="406">
+      <c r="A406"/>
+      <c r="B406"/>
+      <c r="C406"/>
+    </row>
+    <row r="407">
+      <c r="A407"/>
+      <c r="B407"/>
+      <c r="C407"/>
+    </row>
+    <row r="408">
+      <c r="A408"/>
+      <c r="B408"/>
+      <c r="C408"/>
+    </row>
+    <row r="409">
+      <c r="A409"/>
+      <c r="B409"/>
+      <c r="C409"/>
+    </row>
+    <row r="410">
+      <c r="A410"/>
+      <c r="B410"/>
+      <c r="C410"/>
+    </row>
+    <row r="411">
+      <c r="A411"/>
+      <c r="B411"/>
+      <c r="C411"/>
+    </row>
+    <row r="412">
+      <c r="A412"/>
+      <c r="B412"/>
+      <c r="C412"/>
+    </row>
+    <row r="413">
+      <c r="A413"/>
+      <c r="B413"/>
+      <c r="C413"/>
+    </row>
+    <row r="414">
+      <c r="A414"/>
+      <c r="B414"/>
+      <c r="C414"/>
+    </row>
+    <row r="415">
+      <c r="A415"/>
+      <c r="B415"/>
+      <c r="C415"/>
+    </row>
+    <row r="416">
+      <c r="A416"/>
+      <c r="B416"/>
+      <c r="C416"/>
+    </row>
+    <row r="417">
+      <c r="A417"/>
+      <c r="B417"/>
+      <c r="C417"/>
+    </row>
+    <row r="418">
+      <c r="A418"/>
+      <c r="B418"/>
+      <c r="C418"/>
+    </row>
+    <row r="419">
+      <c r="A419"/>
+      <c r="B419"/>
+      <c r="C419"/>
+    </row>
+    <row r="420">
+      <c r="A420"/>
+      <c r="B420"/>
+      <c r="C420"/>
+    </row>
+    <row r="421">
+      <c r="A421"/>
+      <c r="B421"/>
+      <c r="C421"/>
+    </row>
+    <row r="422">
+      <c r="A422"/>
+      <c r="B422"/>
+      <c r="C422"/>
+    </row>
+    <row r="423">
+      <c r="A423"/>
+      <c r="B423"/>
+      <c r="C423"/>
+    </row>
+    <row r="424">
+      <c r="A424"/>
+      <c r="B424"/>
+      <c r="C424"/>
+    </row>
+    <row r="425">
+      <c r="A425"/>
+      <c r="B425"/>
+      <c r="C425"/>
+    </row>
+    <row r="426">
+      <c r="A426"/>
+      <c r="B426"/>
+      <c r="C426"/>
+    </row>
+    <row r="427">
+      <c r="A427"/>
+      <c r="B427"/>
+      <c r="C427"/>
+    </row>
+    <row r="428">
+      <c r="A428"/>
+      <c r="B428"/>
+      <c r="C428"/>
+    </row>
+    <row r="429">
+      <c r="A429"/>
+      <c r="B429"/>
+      <c r="C429"/>
+    </row>
+    <row r="430">
+      <c r="A430"/>
+      <c r="B430"/>
+      <c r="C430"/>
+    </row>
+    <row r="431">
+      <c r="A431"/>
+      <c r="B431"/>
+      <c r="C431"/>
+    </row>
+    <row r="432">
+      <c r="A432"/>
+      <c r="B432"/>
+      <c r="C432"/>
+    </row>
+    <row r="433">
+      <c r="A433"/>
+      <c r="B433"/>
+      <c r="C433"/>
+    </row>
+    <row r="434">
+      <c r="A434"/>
+      <c r="B434"/>
+      <c r="C434"/>
+    </row>
+    <row r="435">
+      <c r="A435"/>
+      <c r="B435"/>
+      <c r="C435"/>
+    </row>
+    <row r="436">
+      <c r="A436"/>
+      <c r="B436"/>
+      <c r="C436"/>
+    </row>
+    <row r="437">
+      <c r="A437"/>
+      <c r="B437"/>
+      <c r="C437"/>
+    </row>
+    <row r="438">
+      <c r="A438"/>
+      <c r="B438"/>
+      <c r="C438"/>
+    </row>
+    <row r="439">
+      <c r="A439"/>
+      <c r="B439"/>
+      <c r="C439"/>
+    </row>
+    <row r="440">
+      <c r="A440"/>
+      <c r="B440"/>
+      <c r="C440"/>
+    </row>
+    <row r="441">
+      <c r="A441"/>
+      <c r="B441"/>
+      <c r="C441"/>
+    </row>
+    <row r="442">
+      <c r="A442"/>
+      <c r="B442"/>
+      <c r="C442"/>
+    </row>
+    <row r="443">
+      <c r="A443"/>
+      <c r="B443"/>
+      <c r="C443"/>
+    </row>
+    <row r="444">
+      <c r="A444"/>
+      <c r="B444"/>
+      <c r="C444"/>
+    </row>
+    <row r="445">
+      <c r="A445"/>
+      <c r="B445"/>
+      <c r="C445"/>
+    </row>
+    <row r="446">
+      <c r="A446"/>
+      <c r="B446"/>
+      <c r="C446"/>
+    </row>
+    <row r="447">
+      <c r="A447"/>
+      <c r="B447"/>
+      <c r="C447"/>
+    </row>
+    <row r="448">
+      <c r="A448"/>
+      <c r="B448"/>
+      <c r="C448"/>
+    </row>
+    <row r="449">
+      <c r="A449"/>
+      <c r="B449"/>
+      <c r="C449"/>
+    </row>
+    <row r="450">
+      <c r="A450"/>
+      <c r="B450"/>
+      <c r="C450"/>
+    </row>
+    <row r="451">
+      <c r="A451"/>
+      <c r="B451"/>
+      <c r="C451"/>
+    </row>
+    <row r="452">
+      <c r="A452"/>
+      <c r="B452"/>
+      <c r="C452"/>
+    </row>
+    <row r="453">
+      <c r="A453"/>
+      <c r="B453"/>
+      <c r="C453"/>
+    </row>
+    <row r="454">
+      <c r="A454"/>
+      <c r="B454"/>
+      <c r="C454"/>
+    </row>
+    <row r="455">
+      <c r="A455"/>
+      <c r="B455"/>
+      <c r="C455"/>
+    </row>
+    <row r="456">
+      <c r="A456"/>
+      <c r="B456"/>
+      <c r="C456"/>
+    </row>
+    <row r="457">
+      <c r="A457"/>
+      <c r="B457"/>
+      <c r="C457"/>
+    </row>
+    <row r="458">
+      <c r="A458"/>
+      <c r="B458"/>
+      <c r="C458"/>
+    </row>
+    <row r="459">
+      <c r="A459"/>
+      <c r="B459"/>
+      <c r="C459"/>
+    </row>
+    <row r="460">
+      <c r="A460"/>
+      <c r="B460"/>
+      <c r="C460"/>
+    </row>
+    <row r="461">
+      <c r="A461"/>
+      <c r="B461"/>
+      <c r="C461"/>
+    </row>
+    <row r="462">
+      <c r="A462"/>
+      <c r="B462"/>
+      <c r="C462"/>
+    </row>
+    <row r="463">
+      <c r="A463"/>
+      <c r="B463"/>
+      <c r="C463"/>
+    </row>
+    <row r="464">
+      <c r="A464"/>
+      <c r="B464"/>
+      <c r="C464"/>
+    </row>
+    <row r="465">
+      <c r="A465"/>
+      <c r="B465"/>
+      <c r="C465"/>
+    </row>
+    <row r="466">
+      <c r="A466"/>
+      <c r="B466"/>
+      <c r="C466"/>
+    </row>
+    <row r="467">
+      <c r="A467"/>
+      <c r="B467"/>
+      <c r="C467"/>
+    </row>
+    <row r="468">
+      <c r="A468"/>
+      <c r="B468"/>
+      <c r="C468"/>
+    </row>
+    <row r="469">
+      <c r="A469"/>
+      <c r="B469"/>
+      <c r="C469"/>
+    </row>
+    <row r="470">
+      <c r="A470"/>
+      <c r="B470"/>
+      <c r="C470"/>
+    </row>
+    <row r="471">
+      <c r="A471"/>
+      <c r="B471"/>
+      <c r="C471"/>
+    </row>
+    <row r="472">
+      <c r="A472"/>
+      <c r="B472"/>
+      <c r="C472"/>
+    </row>
+    <row r="473">
+      <c r="A473"/>
+      <c r="B473"/>
+      <c r="C473"/>
+    </row>
+    <row r="474">
+      <c r="A474"/>
+      <c r="B474"/>
+      <c r="C474"/>
+    </row>
+    <row r="475">
+      <c r="A475"/>
+      <c r="B475"/>
+      <c r="C475"/>
+    </row>
+    <row r="476">
+      <c r="A476"/>
+      <c r="B476"/>
+      <c r="C476"/>
+    </row>
+    <row r="477">
+      <c r="A477"/>
+      <c r="B477"/>
+      <c r="C477"/>
+    </row>
+    <row r="478">
+      <c r="A478"/>
+      <c r="B478"/>
+      <c r="C478"/>
+    </row>
+    <row r="479">
+      <c r="A479"/>
+      <c r="B479"/>
+      <c r="C479"/>
+    </row>
+    <row r="480">
+      <c r="A480"/>
+      <c r="B480"/>
+      <c r="C480"/>
+    </row>
+    <row r="481">
+      <c r="A481"/>
+      <c r="B481"/>
+      <c r="C481"/>
+    </row>
+    <row r="482">
+      <c r="A482"/>
+      <c r="B482"/>
+      <c r="C482"/>
+    </row>
+    <row r="483">
+      <c r="A483"/>
+      <c r="B483"/>
+      <c r="C483"/>
+    </row>
+    <row r="484">
+      <c r="A484"/>
+      <c r="B484"/>
+      <c r="C484"/>
+    </row>
+    <row r="485">
+      <c r="A485"/>
+      <c r="B485"/>
+      <c r="C485"/>
+    </row>
+    <row r="486">
+      <c r="A486"/>
+      <c r="B486"/>
+      <c r="C486"/>
+    </row>
+    <row r="487">
+      <c r="A487"/>
+      <c r="B487"/>
+      <c r="C487"/>
+    </row>
+    <row r="488">
+      <c r="A488"/>
+      <c r="B488"/>
+      <c r="C488"/>
+    </row>
+    <row r="489">
+      <c r="A489"/>
+      <c r="B489"/>
+      <c r="C489"/>
+    </row>
+    <row r="490">
+      <c r="A490"/>
+      <c r="B490"/>
+      <c r="C490"/>
+    </row>
+    <row r="491">
+      <c r="A491"/>
+      <c r="B491"/>
+      <c r="C491"/>
+    </row>
+    <row r="492">
+      <c r="A492"/>
+      <c r="B492"/>
+      <c r="C492"/>
+    </row>
+    <row r="493">
+      <c r="A493"/>
+      <c r="B493"/>
+      <c r="C493"/>
+    </row>
+    <row r="494">
+      <c r="A494"/>
+      <c r="B494"/>
+      <c r="C494"/>
+    </row>
+    <row r="495">
+      <c r="A495"/>
+      <c r="B495"/>
+      <c r="C495"/>
+    </row>
+    <row r="496">
+      <c r="A496"/>
+      <c r="B496"/>
+      <c r="C496"/>
+    </row>
+    <row r="497">
+      <c r="A497"/>
+      <c r="B497"/>
+      <c r="C497"/>
+    </row>
+    <row r="498">
+      <c r="A498"/>
+      <c r="B498"/>
+      <c r="C498"/>
+    </row>
+    <row r="499">
+      <c r="A499"/>
+      <c r="B499"/>
+      <c r="C499"/>
+    </row>
+    <row r="500">
+      <c r="A500"/>
+      <c r="B500"/>
+      <c r="C500"/>
+    </row>
+    <row r="501">
+      <c r="A501"/>
+      <c r="B501"/>
+      <c r="C501"/>
+    </row>
+    <row r="502">
+      <c r="A502"/>
+      <c r="B502"/>
+      <c r="C502"/>
+    </row>
+    <row r="503">
+      <c r="A503"/>
+      <c r="B503"/>
+      <c r="C503"/>
+    </row>
+    <row r="504">
+      <c r="A504"/>
+      <c r="B504"/>
+      <c r="C504"/>
+    </row>
+    <row r="505">
+      <c r="A505"/>
+      <c r="B505"/>
+      <c r="C505"/>
+    </row>
+    <row r="506">
+      <c r="A506"/>
+      <c r="B506"/>
+      <c r="C506"/>
+    </row>
+    <row r="507">
+      <c r="A507"/>
+      <c r="B507"/>
+      <c r="C507"/>
+    </row>
+    <row r="508">
+      <c r="A508"/>
+      <c r="B508"/>
+      <c r="C508"/>
+    </row>
+    <row r="509">
+      <c r="A509"/>
+      <c r="B509"/>
+      <c r="C509"/>
+    </row>
+    <row r="510">
+      <c r="A510"/>
+      <c r="B510"/>
+      <c r="C510"/>
+    </row>
+    <row r="511">
+      <c r="A511"/>
+      <c r="B511"/>
+      <c r="C511"/>
+    </row>
+    <row r="512">
+      <c r="A512"/>
+      <c r="B512"/>
+      <c r="C512"/>
+    </row>
+    <row r="513">
+      <c r="A513"/>
+      <c r="B513"/>
+      <c r="C513"/>
+    </row>
+    <row r="514">
+      <c r="A514"/>
+      <c r="B514"/>
+      <c r="C514"/>
+    </row>
+    <row r="515">
+      <c r="A515"/>
+      <c r="B515"/>
+      <c r="C515"/>
+    </row>
+    <row r="516">
+      <c r="A516"/>
+      <c r="B516"/>
+      <c r="C516"/>
+    </row>
+    <row r="517">
+      <c r="A517"/>
+      <c r="B517"/>
+      <c r="C517"/>
+    </row>
+    <row r="518">
+      <c r="A518"/>
+      <c r="B518"/>
+      <c r="C518"/>
+    </row>
+    <row r="519">
+      <c r="A519"/>
+      <c r="B519"/>
+      <c r="C519"/>
+    </row>
+    <row r="520">
+      <c r="A520"/>
+      <c r="B520"/>
+      <c r="C520"/>
+    </row>
+    <row r="521">
+      <c r="A521"/>
+      <c r="B521"/>
+      <c r="C521"/>
+    </row>
+    <row r="522">
+      <c r="A522"/>
+      <c r="B522"/>
+      <c r="C522"/>
+    </row>
+    <row r="523">
+      <c r="A523"/>
+      <c r="B523"/>
+      <c r="C523"/>
+    </row>
+    <row r="524">
+      <c r="A524"/>
+      <c r="B524"/>
+      <c r="C524"/>
+    </row>
+    <row r="525">
+      <c r="A525"/>
+      <c r="B525"/>
+      <c r="C525"/>
+    </row>
+    <row r="526">
+      <c r="A526"/>
+      <c r="B526"/>
+      <c r="C526"/>
+    </row>
+    <row r="527">
+      <c r="A527"/>
+      <c r="B527"/>
+      <c r="C527"/>
+    </row>
+    <row r="528">
+      <c r="A528"/>
+      <c r="B528"/>
+      <c r="C528"/>
+    </row>
+    <row r="529">
+      <c r="A529"/>
+      <c r="B529"/>
+      <c r="C529"/>
+    </row>
+    <row r="530">
+      <c r="A530"/>
+      <c r="B530"/>
+      <c r="C530"/>
+    </row>
+    <row r="531">
+      <c r="A531"/>
+      <c r="B531"/>
+      <c r="C531"/>
+    </row>
+    <row r="532">
+      <c r="A532"/>
+      <c r="B532"/>
+      <c r="C532"/>
+    </row>
+    <row r="533">
+      <c r="A533"/>
+      <c r="B533"/>
+      <c r="C533"/>
+    </row>
+    <row r="534">
+      <c r="A534"/>
+      <c r="B534"/>
+      <c r="C534"/>
+    </row>
+    <row r="535">
+      <c r="A535"/>
+      <c r="B535"/>
+      <c r="C535"/>
+    </row>
+    <row r="536">
+      <c r="A536"/>
+      <c r="B536"/>
+      <c r="C536"/>
+    </row>
+    <row r="537">
+      <c r="A537"/>
+      <c r="B537"/>
+      <c r="C537"/>
+    </row>
+    <row r="538">
+      <c r="A538"/>
+      <c r="B538"/>
+      <c r="C538"/>
+    </row>
+    <row r="539">
+      <c r="A539"/>
+      <c r="B539"/>
+      <c r="C539"/>
+    </row>
+    <row r="540">
+      <c r="A540"/>
+      <c r="B540"/>
+      <c r="C540"/>
+    </row>
+    <row r="541">
+      <c r="A541"/>
+      <c r="B541"/>
+      <c r="C541"/>
+    </row>
+    <row r="542">
+      <c r="A542"/>
+      <c r="B542"/>
+      <c r="C542"/>
+    </row>
+    <row r="543">
+      <c r="A543"/>
+      <c r="B543"/>
+      <c r="C543"/>
+    </row>
+    <row r="544">
+      <c r="A544"/>
+      <c r="B544"/>
+      <c r="C544"/>
+    </row>
+    <row r="545">
+      <c r="A545"/>
+      <c r="B545"/>
+      <c r="C545"/>
+    </row>
+    <row r="546">
+      <c r="A546"/>
+      <c r="B546"/>
+      <c r="C546"/>
+    </row>
+    <row r="547">
+      <c r="A547"/>
+      <c r="B547"/>
+      <c r="C547"/>
+    </row>
+    <row r="548">
+      <c r="A548"/>
+      <c r="B548"/>
+      <c r="C548"/>
+    </row>
+    <row r="549">
+      <c r="A549"/>
+      <c r="B549"/>
+      <c r="C549"/>
+    </row>
+    <row r="550">
+      <c r="A550"/>
+      <c r="B550"/>
+      <c r="C550"/>
+    </row>
+    <row r="551">
+      <c r="A551"/>
+      <c r="B551"/>
+      <c r="C551"/>
+    </row>
+    <row r="552">
+      <c r="A552"/>
+      <c r="B552"/>
+      <c r="C552"/>
+    </row>
+    <row r="553">
+      <c r="A553"/>
+      <c r="B553"/>
+      <c r="C553"/>
+    </row>
+    <row r="554">
+      <c r="A554"/>
+      <c r="B554"/>
+      <c r="C554"/>
+    </row>
+    <row r="555">
+      <c r="A555"/>
+      <c r="B555"/>
+      <c r="C555"/>
+    </row>
+    <row r="556">
+      <c r="A556"/>
+      <c r="B556"/>
+      <c r="C556"/>
+    </row>
+    <row r="557">
+      <c r="A557"/>
+      <c r="B557"/>
+      <c r="C557"/>
+    </row>
+    <row r="558">
+      <c r="A558"/>
+      <c r="B558"/>
+      <c r="C558"/>
+    </row>
+    <row r="559">
+      <c r="A559"/>
+      <c r="B559"/>
+      <c r="C559"/>
+    </row>
+    <row r="560">
+      <c r="A560"/>
+      <c r="B560"/>
+      <c r="C560"/>
+    </row>
+    <row r="561">
+      <c r="A561"/>
+      <c r="B561"/>
+      <c r="C561"/>
+    </row>
+    <row r="562">
+      <c r="A562"/>
+      <c r="B562"/>
+      <c r="C562"/>
+    </row>
+    <row r="563">
+      <c r="A563"/>
+      <c r="B563"/>
+      <c r="C563"/>
+    </row>
+    <row r="564">
+      <c r="A564"/>
+      <c r="B564"/>
+      <c r="C564"/>
+    </row>
+    <row r="565">
+      <c r="A565"/>
+      <c r="B565"/>
+      <c r="C565"/>
+    </row>
+    <row r="566">
+      <c r="A566"/>
+      <c r="B566"/>
+      <c r="C566"/>
+    </row>
+    <row r="567">
+      <c r="A567"/>
+      <c r="B567"/>
+      <c r="C567"/>
+    </row>
+    <row r="568">
+      <c r="A568"/>
+      <c r="B568"/>
+      <c r="C568"/>
+    </row>
+    <row r="569">
+      <c r="A569"/>
+      <c r="B569"/>
+      <c r="C569"/>
+    </row>
+    <row r="570">
+      <c r="A570"/>
+      <c r="B570"/>
+      <c r="C570"/>
+    </row>
+    <row r="571">
+      <c r="A571"/>
+      <c r="B571"/>
+      <c r="C571"/>
+    </row>
+    <row r="572">
+      <c r="A572"/>
+      <c r="B572"/>
+      <c r="C572"/>
+    </row>
+    <row r="573">
+      <c r="A573"/>
+      <c r="B573"/>
+      <c r="C573"/>
+    </row>
+    <row r="574">
+      <c r="A574"/>
+      <c r="B574"/>
+      <c r="C574"/>
+    </row>
+    <row r="575">
+      <c r="A575"/>
+      <c r="B575"/>
+      <c r="C575"/>
+    </row>
+    <row r="576">
+      <c r="A576"/>
+      <c r="B576"/>
+      <c r="C576"/>
+    </row>
+    <row r="577">
+      <c r="A577"/>
+      <c r="B577"/>
+      <c r="C577"/>
+    </row>
+    <row r="578">
+      <c r="A578"/>
+      <c r="B578"/>
+      <c r="C578"/>
+    </row>
+    <row r="579">
+      <c r="A579"/>
+      <c r="B579"/>
+      <c r="C579"/>
+    </row>
+    <row r="580">
+      <c r="A580"/>
+      <c r="B580"/>
+      <c r="C580"/>
+    </row>
+    <row r="581">
+      <c r="A581"/>
+      <c r="B581"/>
+      <c r="C581"/>
+    </row>
+    <row r="582">
+      <c r="A582"/>
+      <c r="B582"/>
+      <c r="C582"/>
+    </row>
+    <row r="583">
+      <c r="A583"/>
+      <c r="B583"/>
+      <c r="C583"/>
+    </row>
+    <row r="584">
+      <c r="A584"/>
+      <c r="B584"/>
+      <c r="C584"/>
+    </row>
+    <row r="585">
+      <c r="A585"/>
+      <c r="B585"/>
+      <c r="C585"/>
+    </row>
+    <row r="586">
+      <c r="A586"/>
+      <c r="B586"/>
+      <c r="C586"/>
+    </row>
+    <row r="587">
+      <c r="A587"/>
+      <c r="B587"/>
+      <c r="C587"/>
+    </row>
+    <row r="588">
+      <c r="A588"/>
+      <c r="B588"/>
+      <c r="C588"/>
+    </row>
+    <row r="589">
+      <c r="A589"/>
+      <c r="B589"/>
+      <c r="C589"/>
+    </row>
+    <row r="590">
+      <c r="A590"/>
+      <c r="B590"/>
+      <c r="C590"/>
+    </row>
+    <row r="591">
+      <c r="A591"/>
+      <c r="B591"/>
+      <c r="C591"/>
+    </row>
+    <row r="592">
+      <c r="A592"/>
+      <c r="B592"/>
+      <c r="C592"/>
+    </row>
+    <row r="593">
+      <c r="A593"/>
+      <c r="B593"/>
+      <c r="C593"/>
+    </row>
+    <row r="594">
+      <c r="A594"/>
+      <c r="B594"/>
+      <c r="C594"/>
+    </row>
+    <row r="595">
+      <c r="A595"/>
+      <c r="B595"/>
+      <c r="C595"/>
+    </row>
+    <row r="596">
+      <c r="A596"/>
+      <c r="B596"/>
+      <c r="C596"/>
+    </row>
+    <row r="597">
+      <c r="A597"/>
+      <c r="B597"/>
+      <c r="C597"/>
+    </row>
+    <row r="598">
+      <c r="A598"/>
+      <c r="B598"/>
+      <c r="C598"/>
+    </row>
+    <row r="599">
+      <c r="A599"/>
+      <c r="B599"/>
+      <c r="C599"/>
+    </row>
+    <row r="600">
+      <c r="A600"/>
+      <c r="B600"/>
+      <c r="C600"/>
+    </row>
+    <row r="601">
+      <c r="A601"/>
+      <c r="B601"/>
+      <c r="C601"/>
+    </row>
+    <row r="602">
+      <c r="A602"/>
+      <c r="B602"/>
+      <c r="C602"/>
+    </row>
+    <row r="603">
+      <c r="A603"/>
+      <c r="B603"/>
+      <c r="C603"/>
+    </row>
+    <row r="604">
+      <c r="A604"/>
+      <c r="B604"/>
+      <c r="C604"/>
+    </row>
+    <row r="605">
+      <c r="A605"/>
+      <c r="B605"/>
+      <c r="C605"/>
+    </row>
+    <row r="606">
+      <c r="A606"/>
+      <c r="B606"/>
+      <c r="C606"/>
+    </row>
+    <row r="607">
+      <c r="A607"/>
+      <c r="B607"/>
+      <c r="C607"/>
+    </row>
+    <row r="608">
+      <c r="A608"/>
+      <c r="B608"/>
+      <c r="C608"/>
+    </row>
+    <row r="609">
+      <c r="A609"/>
+      <c r="B609"/>
+      <c r="C609"/>
+    </row>
+    <row r="610">
+      <c r="A610"/>
+      <c r="B610"/>
+      <c r="C610"/>
+    </row>
+    <row r="611">
+      <c r="A611"/>
+      <c r="B611"/>
+      <c r="C611"/>
+    </row>
+    <row r="612">
+      <c r="A612"/>
+      <c r="B612"/>
+      <c r="C612"/>
+    </row>
+    <row r="613">
+      <c r="A613"/>
+      <c r="B613"/>
+      <c r="C613"/>
+    </row>
+    <row r="614">
+      <c r="A614"/>
+      <c r="B614"/>
+      <c r="C614"/>
+    </row>
+    <row r="615">
+      <c r="A615"/>
+      <c r="B615"/>
+      <c r="C615"/>
+    </row>
+    <row r="616">
+      <c r="A616"/>
+      <c r="B616"/>
+      <c r="C616"/>
+    </row>
+    <row r="617">
+      <c r="A617"/>
+      <c r="B617"/>
+      <c r="C617"/>
+    </row>
+    <row r="618">
+      <c r="A618"/>
+      <c r="B618"/>
+      <c r="C618"/>
+    </row>
+    <row r="619">
+      <c r="A619"/>
+      <c r="B619"/>
+      <c r="C619"/>
+    </row>
+    <row r="620">
+      <c r="A620"/>
+      <c r="B620"/>
+      <c r="C620"/>
+    </row>
+    <row r="621">
+      <c r="A621"/>
+      <c r="B621"/>
+      <c r="C621"/>
+    </row>
+    <row r="622">
+      <c r="A622"/>
+      <c r="B622"/>
+      <c r="C622"/>
+    </row>
+    <row r="623">
+      <c r="A623"/>
+      <c r="B623"/>
+      <c r="C623"/>
+    </row>
+    <row r="624">
+      <c r="A624"/>
+      <c r="B624"/>
+      <c r="C624"/>
+    </row>
+    <row r="625">
+      <c r="A625"/>
+      <c r="B625"/>
+      <c r="C625"/>
+    </row>
+    <row r="626">
+      <c r="A626"/>
+      <c r="B626"/>
+      <c r="C626"/>
+    </row>
+    <row r="627">
+      <c r="A627"/>
+      <c r="B627"/>
+      <c r="C627"/>
+    </row>
+    <row r="628">
+      <c r="A628"/>
+      <c r="B628"/>
+      <c r="C628"/>
+    </row>
+    <row r="629">
+      <c r="A629"/>
+      <c r="B629"/>
+      <c r="C629"/>
+    </row>
+    <row r="630">
+      <c r="A630"/>
+      <c r="B630"/>
+      <c r="C630"/>
+    </row>
+    <row r="631">
+      <c r="A631"/>
+      <c r="B631"/>
+      <c r="C631"/>
+    </row>
+    <row r="632">
+      <c r="A632"/>
+      <c r="B632"/>
+      <c r="C632"/>
+    </row>
+    <row r="633">
+      <c r="A633"/>
+      <c r="B633"/>
+      <c r="C633"/>
+    </row>
+    <row r="634">
+      <c r="A634"/>
+      <c r="B634"/>
+      <c r="C634"/>
+    </row>
+    <row r="635">
+      <c r="A635"/>
+      <c r="B635"/>
+      <c r="C635"/>
+    </row>
+    <row r="636">
+      <c r="A636"/>
+      <c r="B636"/>
+      <c r="C636"/>
+    </row>
+    <row r="637">
+      <c r="A637"/>
+      <c r="B637"/>
+      <c r="C637"/>
+    </row>
+    <row r="638">
+      <c r="A638"/>
+      <c r="B638"/>
+      <c r="C638"/>
+    </row>
+    <row r="639">
+      <c r="A639"/>
+      <c r="B639"/>
+      <c r="C639"/>
+    </row>
+    <row r="640">
+      <c r="A640"/>
+      <c r="B640"/>
+      <c r="C640"/>
+    </row>
+    <row r="641">
+      <c r="A641"/>
+      <c r="B641"/>
+      <c r="C641"/>
+    </row>
+    <row r="642">
+      <c r="A642"/>
+      <c r="B642"/>
+      <c r="C642"/>
+    </row>
+    <row r="643">
+      <c r="A643"/>
+      <c r="B643"/>
+      <c r="C643"/>
+    </row>
+    <row r="644">
+      <c r="A644"/>
+      <c r="B644"/>
+      <c r="C644"/>
+    </row>
+    <row r="645">
+      <c r="A645"/>
+      <c r="B645"/>
+      <c r="C645"/>
+      <c r="D645"/>
+      <c r="E645"/>
+      <c r="F645"/>
+      <c r="G645"/>
+      <c r="H645"/>
+      <c r="I645"/>
+      <c r="J645"/>
+      <c r="K645"/>
+      <c r="L645"/>
+      <c r="M645"/>
+      <c r="N645"/>
+      <c r="O645"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
+++ b/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
@@ -22729,7 +22729,7 @@
     <row r="114">
       <c r="A114" s="92" t="inlineStr">
         <is>
-          <t>CQ engineer Site Engineering P1-G midpoint (CQ=Commissioning&amp;Qualification)</t>
+          <t xml:space="preserve">CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)</t>
         </is>
       </c>
       <c r="B114" s="92" t="inlineStr">
@@ -22746,7 +22746,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CQ engineer Site Engineering P1-F midpoint (CQ=Commissioning&amp;Qualification)</t>
+          <t xml:space="preserve">CQ engineer Site Engineering P1-F midpoint   (CQ=Commissioning&amp;Qualification)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -22763,7 +22763,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CQ engineer Site Engineering P1-G Tussen midpoint en max. (CQ=Commissioning&amp;Qualification)</t>
+          <t xml:space="preserve">CQ engineer Site Engineering P1-G Tussen midpoint en max.   (CQ=Commissioning&amp;Qualification)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SPOC=Programma-manager Site Engineering P3-J Tussen midpoint en max.</t>
+          <t xml:space="preserve">SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">

--- a/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
+++ b/downloads/Merit_2026_Employee_Bulk_Calculator_350_exact.xlsx
@@ -1,11 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employee Merit 2026" sheetId="1" r:id="R98c536f9c52848a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="R471b6d2a701c4dd7"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Employee Merit 2026" sheetId="1" ns1:id="R98c536f9c52848a3"/>
+    <sheet name="Data" sheetId="2" ns1:id="R471b6d2a701c4dd7"/>
+  </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1197,10 +1198,10 @@
         <f>IF($L5="","",$C5*$L5)</f>
       </c>
       <c r="N5" s="106" t="str">
-        <f>IF($M5="","",ROUNDDOWN($C5+$M5,2))</f>
+        <f>IF($M5="","",ROUNDUP($C5+$M5,2))</f>
       </c>
       <c r="O5" s="107" t="str">
-        <f>IF($N5="","",ROUNDDOWN(ROUNDDOWN($N5,2)*$E5,3))</f>
+        <f>IF($N5="","",ROUNDUP(ROUNDUP($N5,2)*$E5,3))</f>
       </c>
       <c r="P5" s="108" t="str">
         <f>IF($L5="","",$I5*$L5)</f>
@@ -1253,10 +1254,10 @@
         <f>IF($L6="","",$C6*$L6)</f>
       </c>
       <c r="N6" s="119" t="str">
-        <f>IF($M6="","",ROUNDDOWN($C6+$M6,2))</f>
+        <f>IF($M6="","",ROUNDUP($C6+$M6,2))</f>
       </c>
       <c r="O6" s="120" t="str">
-        <f>IF($N6="","",ROUNDDOWN(ROUNDDOWN($N6,2)*$E6,3))</f>
+        <f>IF($N6="","",ROUNDUP(ROUNDUP($N6,2)*$E6,3))</f>
       </c>
       <c r="P6" s="121" t="str">
         <f>IF($L6="","",$I6*$L6)</f>
@@ -1309,10 +1310,10 @@
         <f>IF($L7="","",$C7*$L7)</f>
       </c>
       <c r="N7" s="119" t="str">
-        <f>IF($M7="","",ROUNDDOWN($C7+$M7,2))</f>
+        <f>IF($M7="","",ROUNDUP($C7+$M7,2))</f>
       </c>
       <c r="O7" s="120" t="str">
-        <f>IF($N7="","",ROUNDDOWN(ROUNDDOWN($N7,2)*$E7,3))</f>
+        <f>IF($N7="","",ROUNDUP(ROUNDUP($N7,2)*$E7,3))</f>
       </c>
       <c r="P7" s="121" t="str">
         <f>IF($L7="","",$I7*$L7)</f>
@@ -1365,10 +1366,10 @@
         <f>IF($L8="","",$C8*$L8)</f>
       </c>
       <c r="N8" s="119" t="str">
-        <f>IF($M8="","",ROUNDDOWN($C8+$M8,2))</f>
+        <f>IF($M8="","",ROUNDUP($C8+$M8,2))</f>
       </c>
       <c r="O8" s="120" t="str">
-        <f>IF($N8="","",ROUNDDOWN(ROUNDDOWN($N8,2)*$E8,3))</f>
+        <f>IF($N8="","",ROUNDUP(ROUNDUP($N8,2)*$E8,3))</f>
       </c>
       <c r="P8" s="121" t="str">
         <f>IF($L8="","",$I8*$L8)</f>
@@ -1421,10 +1422,10 @@
         <f>IF($L9="","",$C9*$L9)</f>
       </c>
       <c r="N9" s="119" t="str">
-        <f>IF($M9="","",ROUNDDOWN($C9+$M9,2))</f>
+        <f>IF($M9="","",ROUNDUP($C9+$M9,2))</f>
       </c>
       <c r="O9" s="120" t="str">
-        <f>IF($N9="","",ROUNDDOWN(ROUNDDOWN($N9,2)*$E9,3))</f>
+        <f>IF($N9="","",ROUNDUP(ROUNDUP($N9,2)*$E9,3))</f>
       </c>
       <c r="P9" s="121" t="str">
         <f>IF($L9="","",$I9*$L9)</f>
@@ -1477,10 +1478,10 @@
         <f>IF($L10="","",$C10*$L10)</f>
       </c>
       <c r="N10" s="119" t="str">
-        <f>IF($M10="","",ROUNDDOWN($C10+$M10,2))</f>
+        <f>IF($M10="","",ROUNDUP($C10+$M10,2))</f>
       </c>
       <c r="O10" s="120" t="str">
-        <f>IF($N10="","",ROUNDDOWN(ROUNDDOWN($N10,2)*$E10,3))</f>
+        <f>IF($N10="","",ROUNDUP(ROUNDUP($N10,2)*$E10,3))</f>
       </c>
       <c r="P10" s="121" t="str">
         <f>IF($L10="","",$I10*$L10)</f>
@@ -1533,10 +1534,10 @@
         <f>IF($L11="","",$C11*$L11)</f>
       </c>
       <c r="N11" s="119" t="str">
-        <f>IF($M11="","",ROUNDDOWN($C11+$M11,2))</f>
+        <f>IF($M11="","",ROUNDUP($C11+$M11,2))</f>
       </c>
       <c r="O11" s="120" t="str">
-        <f>IF($N11="","",ROUNDDOWN(ROUNDDOWN($N11,2)*$E11,3))</f>
+        <f>IF($N11="","",ROUNDUP(ROUNDUP($N11,2)*$E11,3))</f>
       </c>
       <c r="P11" s="121" t="str">
         <f>IF($L11="","",$I11*$L11)</f>
@@ -1589,10 +1590,10 @@
         <f>IF($L12="","",$C12*$L12)</f>
       </c>
       <c r="N12" s="119" t="str">
-        <f>IF($M12="","",ROUNDDOWN($C12+$M12,2))</f>
+        <f>IF($M12="","",ROUNDUP($C12+$M12,2))</f>
       </c>
       <c r="O12" s="120" t="str">
-        <f>IF($N12="","",ROUNDDOWN(ROUNDDOWN($N12,2)*$E12,3))</f>
+        <f>IF($N12="","",ROUNDUP(ROUNDUP($N12,2)*$E12,3))</f>
       </c>
       <c r="P12" s="121" t="str">
         <f>IF($L12="","",$I12*$L12)</f>
@@ -1645,10 +1646,10 @@
         <f>IF($L13="","",$C13*$L13)</f>
       </c>
       <c r="N13" s="119" t="str">
-        <f>IF($M13="","",ROUNDDOWN($C13+$M13,2))</f>
+        <f>IF($M13="","",ROUNDUP($C13+$M13,2))</f>
       </c>
       <c r="O13" s="120" t="str">
-        <f>IF($N13="","",ROUNDDOWN(ROUNDDOWN($N13,2)*$E13,3))</f>
+        <f>IF($N13="","",ROUNDUP(ROUNDUP($N13,2)*$E13,3))</f>
       </c>
       <c r="P13" s="121" t="str">
         <f>IF($L13="","",$I13*$L13)</f>
@@ -1701,10 +1702,10 @@
         <f>IF($L14="","",$C14*$L14)</f>
       </c>
       <c r="N14" s="119" t="str">
-        <f>IF($M14="","",ROUNDDOWN($C14+$M14,2))</f>
+        <f>IF($M14="","",ROUNDUP($C14+$M14,2))</f>
       </c>
       <c r="O14" s="120" t="str">
-        <f>IF($N14="","",ROUNDDOWN(ROUNDDOWN($N14,2)*$E14,3))</f>
+        <f>IF($N14="","",ROUNDUP(ROUNDUP($N14,2)*$E14,3))</f>
       </c>
       <c r="P14" s="121" t="str">
         <f>IF($L14="","",$I14*$L14)</f>
@@ -1757,10 +1758,10 @@
         <f>IF($L15="","",$C15*$L15)</f>
       </c>
       <c r="N15" s="119" t="str">
-        <f>IF($M15="","",ROUNDDOWN($C15+$M15,2))</f>
+        <f>IF($M15="","",ROUNDUP($C15+$M15,2))</f>
       </c>
       <c r="O15" s="120" t="str">
-        <f>IF($N15="","",ROUNDDOWN(ROUNDDOWN($N15,2)*$E15,3))</f>
+        <f>IF($N15="","",ROUNDUP(ROUNDUP($N15,2)*$E15,3))</f>
       </c>
       <c r="P15" s="121" t="str">
         <f>IF($L15="","",$I15*$L15)</f>
@@ -1813,10 +1814,10 @@
         <f>IF($L16="","",$C16*$L16)</f>
       </c>
       <c r="N16" s="119" t="str">
-        <f>IF($M16="","",ROUNDDOWN($C16+$M16,2))</f>
+        <f>IF($M16="","",ROUNDUP($C16+$M16,2))</f>
       </c>
       <c r="O16" s="120" t="str">
-        <f>IF($N16="","",ROUNDDOWN(ROUNDDOWN($N16,2)*$E16,3))</f>
+        <f>IF($N16="","",ROUNDUP(ROUNDUP($N16,2)*$E16,3))</f>
       </c>
       <c r="P16" s="121" t="str">
         <f>IF($L16="","",$I16*$L16)</f>
@@ -1869,10 +1870,10 @@
         <f>IF($L17="","",$C17*$L17)</f>
       </c>
       <c r="N17" s="119" t="str">
-        <f>IF($M17="","",ROUNDDOWN($C17+$M17,2))</f>
+        <f>IF($M17="","",ROUNDUP($C17+$M17,2))</f>
       </c>
       <c r="O17" s="120" t="str">
-        <f>IF($N17="","",ROUNDDOWN(ROUNDDOWN($N17,2)*$E17,3))</f>
+        <f>IF($N17="","",ROUNDUP(ROUNDUP($N17,2)*$E17,3))</f>
       </c>
       <c r="P17" s="121" t="str">
         <f>IF($L17="","",$I17*$L17)</f>
@@ -1925,10 +1926,10 @@
         <f>IF($L18="","",$C18*$L18)</f>
       </c>
       <c r="N18" s="119" t="str">
-        <f>IF($M18="","",ROUNDDOWN($C18+$M18,2))</f>
+        <f>IF($M18="","",ROUNDUP($C18+$M18,2))</f>
       </c>
       <c r="O18" s="120" t="str">
-        <f>IF($N18="","",ROUNDDOWN(ROUNDDOWN($N18,2)*$E18,3))</f>
+        <f>IF($N18="","",ROUNDUP(ROUNDUP($N18,2)*$E18,3))</f>
       </c>
       <c r="P18" s="121" t="str">
         <f>IF($L18="","",$I18*$L18)</f>
@@ -1981,10 +1982,10 @@
         <f>IF($L19="","",$C19*$L19)</f>
       </c>
       <c r="N19" s="119" t="str">
-        <f>IF($M19="","",ROUNDDOWN($C19+$M19,2))</f>
+        <f>IF($M19="","",ROUNDUP($C19+$M19,2))</f>
       </c>
       <c r="O19" s="120" t="str">
-        <f>IF($N19="","",ROUNDDOWN(ROUNDDOWN($N19,2)*$E19,3))</f>
+        <f>IF($N19="","",ROUNDUP(ROUNDUP($N19,2)*$E19,3))</f>
       </c>
       <c r="P19" s="121" t="str">
         <f>IF($L19="","",$I19*$L19)</f>
@@ -2037,10 +2038,10 @@
         <f>IF($L20="","",$C20*$L20)</f>
       </c>
       <c r="N20" s="119" t="str">
-        <f>IF($M20="","",ROUNDDOWN($C20+$M20,2))</f>
+        <f>IF($M20="","",ROUNDUP($C20+$M20,2))</f>
       </c>
       <c r="O20" s="120" t="str">
-        <f>IF($N20="","",ROUNDDOWN(ROUNDDOWN($N20,2)*$E20,3))</f>
+        <f>IF($N20="","",ROUNDUP(ROUNDUP($N20,2)*$E20,3))</f>
       </c>
       <c r="P20" s="121" t="str">
         <f>IF($L20="","",$I20*$L20)</f>
@@ -2093,10 +2094,10 @@
         <f>IF($L21="","",$C21*$L21)</f>
       </c>
       <c r="N21" s="119" t="str">
-        <f>IF($M21="","",ROUNDDOWN($C21+$M21,2))</f>
+        <f>IF($M21="","",ROUNDUP($C21+$M21,2))</f>
       </c>
       <c r="O21" s="120" t="str">
-        <f>IF($N21="","",ROUNDDOWN(ROUNDDOWN($N21,2)*$E21,3))</f>
+        <f>IF($N21="","",ROUNDUP(ROUNDUP($N21,2)*$E21,3))</f>
       </c>
       <c r="P21" s="121" t="str">
         <f>IF($L21="","",$I21*$L21)</f>
@@ -2149,10 +2150,10 @@
         <f>IF($L22="","",$C22*$L22)</f>
       </c>
       <c r="N22" s="119" t="str">
-        <f>IF($M22="","",ROUNDDOWN($C22+$M22,2))</f>
+        <f>IF($M22="","",ROUNDUP($C22+$M22,2))</f>
       </c>
       <c r="O22" s="120" t="str">
-        <f>IF($N22="","",ROUNDDOWN(ROUNDDOWN($N22,2)*$E22,3))</f>
+        <f>IF($N22="","",ROUNDUP(ROUNDUP($N22,2)*$E22,3))</f>
       </c>
       <c r="P22" s="121" t="str">
         <f>IF($L22="","",$I22*$L22)</f>
@@ -2205,10 +2206,10 @@
         <f>IF($L23="","",$C23*$L23)</f>
       </c>
       <c r="N23" s="119" t="str">
-        <f>IF($M23="","",ROUNDDOWN($C23+$M23,2))</f>
+        <f>IF($M23="","",ROUNDUP($C23+$M23,2))</f>
       </c>
       <c r="O23" s="120" t="str">
-        <f>IF($N23="","",ROUNDDOWN(ROUNDDOWN($N23,2)*$E23,3))</f>
+        <f>IF($N23="","",ROUNDUP(ROUNDUP($N23,2)*$E23,3))</f>
       </c>
       <c r="P23" s="121" t="str">
         <f>IF($L23="","",$I23*$L23)</f>
@@ -2261,10 +2262,10 @@
         <f>IF($L24="","",$C24*$L24)</f>
       </c>
       <c r="N24" s="119" t="str">
-        <f>IF($M24="","",ROUNDDOWN($C24+$M24,2))</f>
+        <f>IF($M24="","",ROUNDUP($C24+$M24,2))</f>
       </c>
       <c r="O24" s="120" t="str">
-        <f>IF($N24="","",ROUNDDOWN(ROUNDDOWN($N24,2)*$E24,3))</f>
+        <f>IF($N24="","",ROUNDUP(ROUNDUP($N24,2)*$E24,3))</f>
       </c>
       <c r="P24" s="121" t="str">
         <f>IF($L24="","",$I24*$L24)</f>
@@ -2317,10 +2318,10 @@
         <f>IF($L25="","",$C25*$L25)</f>
       </c>
       <c r="N25" s="119" t="str">
-        <f>IF($M25="","",ROUNDDOWN($C25+$M25,2))</f>
+        <f>IF($M25="","",ROUNDUP($C25+$M25,2))</f>
       </c>
       <c r="O25" s="120" t="str">
-        <f>IF($N25="","",ROUNDDOWN(ROUNDDOWN($N25,2)*$E25,3))</f>
+        <f>IF($N25="","",ROUNDUP(ROUNDUP($N25,2)*$E25,3))</f>
       </c>
       <c r="P25" s="121" t="str">
         <f>IF($L25="","",$I25*$L25)</f>
@@ -2373,10 +2374,10 @@
         <f>IF($L26="","",$C26*$L26)</f>
       </c>
       <c r="N26" s="119" t="str">
-        <f>IF($M26="","",ROUNDDOWN($C26+$M26,2))</f>
+        <f>IF($M26="","",ROUNDUP($C26+$M26,2))</f>
       </c>
       <c r="O26" s="120" t="str">
-        <f>IF($N26="","",ROUNDDOWN(ROUNDDOWN($N26,2)*$E26,3))</f>
+        <f>IF($N26="","",ROUNDUP(ROUNDUP($N26,2)*$E26,3))</f>
       </c>
       <c r="P26" s="121" t="str">
         <f>IF($L26="","",$I26*$L26)</f>
@@ -2429,10 +2430,10 @@
         <f>IF($L27="","",$C27*$L27)</f>
       </c>
       <c r="N27" s="119" t="str">
-        <f>IF($M27="","",ROUNDDOWN($C27+$M27,2))</f>
+        <f>IF($M27="","",ROUNDUP($C27+$M27,2))</f>
       </c>
       <c r="O27" s="120" t="str">
-        <f>IF($N27="","",ROUNDDOWN(ROUNDDOWN($N27,2)*$E27,3))</f>
+        <f>IF($N27="","",ROUNDUP(ROUNDUP($N27,2)*$E27,3))</f>
       </c>
       <c r="P27" s="121" t="str">
         <f>IF($L27="","",$I27*$L27)</f>
@@ -2485,10 +2486,10 @@
         <f>IF($L28="","",$C28*$L28)</f>
       </c>
       <c r="N28" s="119" t="str">
-        <f>IF($M28="","",ROUNDDOWN($C28+$M28,2))</f>
+        <f>IF($M28="","",ROUNDUP($C28+$M28,2))</f>
       </c>
       <c r="O28" s="120" t="str">
-        <f>IF($N28="","",ROUNDDOWN(ROUNDDOWN($N28,2)*$E28,3))</f>
+        <f>IF($N28="","",ROUNDUP(ROUNDUP($N28,2)*$E28,3))</f>
       </c>
       <c r="P28" s="121" t="str">
         <f>IF($L28="","",$I28*$L28)</f>
@@ -2541,10 +2542,10 @@
         <f>IF($L29="","",$C29*$L29)</f>
       </c>
       <c r="N29" s="119" t="str">
-        <f>IF($M29="","",ROUNDDOWN($C29+$M29,2))</f>
+        <f>IF($M29="","",ROUNDUP($C29+$M29,2))</f>
       </c>
       <c r="O29" s="120" t="str">
-        <f>IF($N29="","",ROUNDDOWN(ROUNDDOWN($N29,2)*$E29,3))</f>
+        <f>IF($N29="","",ROUNDUP(ROUNDUP($N29,2)*$E29,3))</f>
       </c>
       <c r="P29" s="121" t="str">
         <f>IF($L29="","",$I29*$L29)</f>
@@ -2597,10 +2598,10 @@
         <f>IF($L30="","",$C30*$L30)</f>
       </c>
       <c r="N30" s="119" t="str">
-        <f>IF($M30="","",ROUNDDOWN($C30+$M30,2))</f>
+        <f>IF($M30="","",ROUNDUP($C30+$M30,2))</f>
       </c>
       <c r="O30" s="120" t="str">
-        <f>IF($N30="","",ROUNDDOWN(ROUNDDOWN($N30,2)*$E30,3))</f>
+        <f>IF($N30="","",ROUNDUP(ROUNDUP($N30,2)*$E30,3))</f>
       </c>
       <c r="P30" s="121" t="str">
         <f>IF($L30="","",$I30*$L30)</f>
@@ -2653,10 +2654,10 @@
         <f>IF($L31="","",$C31*$L31)</f>
       </c>
       <c r="N31" s="119" t="str">
-        <f>IF($M31="","",ROUNDDOWN($C31+$M31,2))</f>
+        <f>IF($M31="","",ROUNDUP($C31+$M31,2))</f>
       </c>
       <c r="O31" s="120" t="str">
-        <f>IF($N31="","",ROUNDDOWN(ROUNDDOWN($N31,2)*$E31,3))</f>
+        <f>IF($N31="","",ROUNDUP(ROUNDUP($N31,2)*$E31,3))</f>
       </c>
       <c r="P31" s="121" t="str">
         <f>IF($L31="","",$I31*$L31)</f>
@@ -2709,10 +2710,10 @@
         <f>IF($L32="","",$C32*$L32)</f>
       </c>
       <c r="N32" s="119" t="str">
-        <f>IF($M32="","",ROUNDDOWN($C32+$M32,2))</f>
+        <f>IF($M32="","",ROUNDUP($C32+$M32,2))</f>
       </c>
       <c r="O32" s="120" t="str">
-        <f>IF($N32="","",ROUNDDOWN(ROUNDDOWN($N32,2)*$E32,3))</f>
+        <f>IF($N32="","",ROUNDUP(ROUNDUP($N32,2)*$E32,3))</f>
       </c>
       <c r="P32" s="121" t="str">
         <f>IF($L32="","",$I32*$L32)</f>
@@ -2765,10 +2766,10 @@
         <f>IF($L33="","",$C33*$L33)</f>
       </c>
       <c r="N33" s="119" t="str">
-        <f>IF($M33="","",ROUNDDOWN($C33+$M33,2))</f>
+        <f>IF($M33="","",ROUNDUP($C33+$M33,2))</f>
       </c>
       <c r="O33" s="120" t="str">
-        <f>IF($N33="","",ROUNDDOWN(ROUNDDOWN($N33,2)*$E33,3))</f>
+        <f>IF($N33="","",ROUNDUP(ROUNDUP($N33,2)*$E33,3))</f>
       </c>
       <c r="P33" s="121" t="str">
         <f>IF($L33="","",$I33*$L33)</f>
@@ -2821,10 +2822,10 @@
         <f>IF($L34="","",$C34*$L34)</f>
       </c>
       <c r="N34" s="119" t="str">
-        <f>IF($M34="","",ROUNDDOWN($C34+$M34,2))</f>
+        <f>IF($M34="","",ROUNDUP($C34+$M34,2))</f>
       </c>
       <c r="O34" s="120" t="str">
-        <f>IF($N34="","",ROUNDDOWN(ROUNDDOWN($N34,2)*$E34,3))</f>
+        <f>IF($N34="","",ROUNDUP(ROUNDUP($N34,2)*$E34,3))</f>
       </c>
       <c r="P34" s="121" t="str">
         <f>IF($L34="","",$I34*$L34)</f>
@@ -2877,10 +2878,10 @@
         <f>IF($L35="","",$C35*$L35)</f>
       </c>
       <c r="N35" s="119" t="str">
-        <f>IF($M35="","",ROUNDDOWN($C35+$M35,2))</f>
+        <f>IF($M35="","",ROUNDUP($C35+$M35,2))</f>
       </c>
       <c r="O35" s="120" t="str">
-        <f>IF($N35="","",ROUNDDOWN(ROUNDDOWN($N35,2)*$E35,3))</f>
+        <f>IF($N35="","",ROUNDUP(ROUNDUP($N35,2)*$E35,3))</f>
       </c>
       <c r="P35" s="121" t="str">
         <f>IF($L35="","",$I35*$L35)</f>
@@ -2933,10 +2934,10 @@
         <f>IF($L36="","",$C36*$L36)</f>
       </c>
       <c r="N36" s="119" t="str">
-        <f>IF($M36="","",ROUNDDOWN($C36+$M36,2))</f>
+        <f>IF($M36="","",ROUNDUP($C36+$M36,2))</f>
       </c>
       <c r="O36" s="120" t="str">
-        <f>IF($N36="","",ROUNDDOWN(ROUNDDOWN($N36,2)*$E36,3))</f>
+        <f>IF($N36="","",ROUNDUP(ROUNDUP($N36,2)*$E36,3))</f>
       </c>
       <c r="P36" s="121" t="str">
         <f>IF($L36="","",$I36*$L36)</f>
@@ -2989,10 +2990,10 @@
         <f>IF($L37="","",$C37*$L37)</f>
       </c>
       <c r="N37" s="119" t="str">
-        <f>IF($M37="","",ROUNDDOWN($C37+$M37,2))</f>
+        <f>IF($M37="","",ROUNDUP($C37+$M37,2))</f>
       </c>
       <c r="O37" s="120" t="str">
-        <f>IF($N37="","",ROUNDDOWN(ROUNDDOWN($N37,2)*$E37,3))</f>
+        <f>IF($N37="","",ROUNDUP(ROUNDUP($N37,2)*$E37,3))</f>
       </c>
       <c r="P37" s="121" t="str">
         <f>IF($L37="","",$I37*$L37)</f>
@@ -3045,10 +3046,10 @@
         <f>IF($L38="","",$C38*$L38)</f>
       </c>
       <c r="N38" s="119" t="str">
-        <f>IF($M38="","",ROUNDDOWN($C38+$M38,2))</f>
+        <f>IF($M38="","",ROUNDUP($C38+$M38,2))</f>
       </c>
       <c r="O38" s="120" t="str">
-        <f>IF($N38="","",ROUNDDOWN(ROUNDDOWN($N38,2)*$E38,3))</f>
+        <f>IF($N38="","",ROUNDUP(ROUNDUP($N38,2)*$E38,3))</f>
       </c>
       <c r="P38" s="121" t="str">
         <f>IF($L38="","",$I38*$L38)</f>
@@ -3101,10 +3102,10 @@
         <f>IF($L39="","",$C39*$L39)</f>
       </c>
       <c r="N39" s="119" t="str">
-        <f>IF($M39="","",ROUNDDOWN($C39+$M39,2))</f>
+        <f>IF($M39="","",ROUNDUP($C39+$M39,2))</f>
       </c>
       <c r="O39" s="120" t="str">
-        <f>IF($N39="","",ROUNDDOWN(ROUNDDOWN($N39,2)*$E39,3))</f>
+        <f>IF($N39="","",ROUNDUP(ROUNDUP($N39,2)*$E39,3))</f>
       </c>
       <c r="P39" s="121" t="str">
         <f>IF($L39="","",$I39*$L39)</f>
@@ -3157,10 +3158,10 @@
         <f>IF($L40="","",$C40*$L40)</f>
       </c>
       <c r="N40" s="119" t="str">
-        <f>IF($M40="","",ROUNDDOWN($C40+$M40,2))</f>
+        <f>IF($M40="","",ROUNDUP($C40+$M40,2))</f>
       </c>
       <c r="O40" s="120" t="str">
-        <f>IF($N40="","",ROUNDDOWN(ROUNDDOWN($N40,2)*$E40,3))</f>
+        <f>IF($N40="","",ROUNDUP(ROUNDUP($N40,2)*$E40,3))</f>
       </c>
       <c r="P40" s="121" t="str">
         <f>IF($L40="","",$I40*$L40)</f>
@@ -3213,10 +3214,10 @@
         <f>IF($L41="","",$C41*$L41)</f>
       </c>
       <c r="N41" s="119" t="str">
-        <f>IF($M41="","",ROUNDDOWN($C41+$M41,2))</f>
+        <f>IF($M41="","",ROUNDUP($C41+$M41,2))</f>
       </c>
       <c r="O41" s="120" t="str">
-        <f>IF($N41="","",ROUNDDOWN(ROUNDDOWN($N41,2)*$E41,3))</f>
+        <f>IF($N41="","",ROUNDUP(ROUNDUP($N41,2)*$E41,3))</f>
       </c>
       <c r="P41" s="121" t="str">
         <f>IF($L41="","",$I41*$L41)</f>
@@ -3269,10 +3270,10 @@
         <f>IF($L42="","",$C42*$L42)</f>
       </c>
       <c r="N42" s="119" t="str">
-        <f>IF($M42="","",ROUNDDOWN($C42+$M42,2))</f>
+        <f>IF($M42="","",ROUNDUP($C42+$M42,2))</f>
       </c>
       <c r="O42" s="120" t="str">
-        <f>IF($N42="","",ROUNDDOWN(ROUNDDOWN($N42,2)*$E42,3))</f>
+        <f>IF($N42="","",ROUNDUP(ROUNDUP($N42,2)*$E42,3))</f>
       </c>
       <c r="P42" s="121" t="str">
         <f>IF($L42="","",$I42*$L42)</f>
@@ -3325,10 +3326,10 @@
         <f>IF($L43="","",$C43*$L43)</f>
       </c>
       <c r="N43" s="119" t="str">
-        <f>IF($M43="","",ROUNDDOWN($C43+$M43,2))</f>
+        <f>IF($M43="","",ROUNDUP($C43+$M43,2))</f>
       </c>
       <c r="O43" s="120" t="str">
-        <f>IF($N43="","",ROUNDDOWN(ROUNDDOWN($N43,2)*$E43,3))</f>
+        <f>IF($N43="","",ROUNDUP(ROUNDUP($N43,2)*$E43,3))</f>
       </c>
       <c r="P43" s="121" t="str">
         <f>IF($L43="","",$I43*$L43)</f>
@@ -3381,10 +3382,10 @@
         <f>IF($L44="","",$C44*$L44)</f>
       </c>
       <c r="N44" s="119" t="str">
-        <f>IF($M44="","",ROUNDDOWN($C44+$M44,2))</f>
+        <f>IF($M44="","",ROUNDUP($C44+$M44,2))</f>
       </c>
       <c r="O44" s="120" t="str">
-        <f>IF($N44="","",ROUNDDOWN(ROUNDDOWN($N44,2)*$E44,3))</f>
+        <f>IF($N44="","",ROUNDUP(ROUNDUP($N44,2)*$E44,3))</f>
       </c>
       <c r="P44" s="121" t="str">
         <f>IF($L44="","",$I44*$L44)</f>
@@ -3437,10 +3438,10 @@
         <f>IF($L45="","",$C45*$L45)</f>
       </c>
       <c r="N45" s="119" t="str">
-        <f>IF($M45="","",ROUNDDOWN($C45+$M45,2))</f>
+        <f>IF($M45="","",ROUNDUP($C45+$M45,2))</f>
       </c>
       <c r="O45" s="120" t="str">
-        <f>IF($N45="","",ROUNDDOWN(ROUNDDOWN($N45,2)*$E45,3))</f>
+        <f>IF($N45="","",ROUNDUP(ROUNDUP($N45,2)*$E45,3))</f>
       </c>
       <c r="P45" s="121" t="str">
         <f>IF($L45="","",$I45*$L45)</f>
@@ -3493,10 +3494,10 @@
         <f>IF($L46="","",$C46*$L46)</f>
       </c>
       <c r="N46" s="119" t="str">
-        <f>IF($M46="","",ROUNDDOWN($C46+$M46,2))</f>
+        <f>IF($M46="","",ROUNDUP($C46+$M46,2))</f>
       </c>
       <c r="O46" s="120" t="str">
-        <f>IF($N46="","",ROUNDDOWN(ROUNDDOWN($N46,2)*$E46,3))</f>
+        <f>IF($N46="","",ROUNDUP(ROUNDUP($N46,2)*$E46,3))</f>
       </c>
       <c r="P46" s="121" t="str">
         <f>IF($L46="","",$I46*$L46)</f>
@@ -3549,10 +3550,10 @@
         <f>IF($L47="","",$C47*$L47)</f>
       </c>
       <c r="N47" s="119" t="str">
-        <f>IF($M47="","",ROUNDDOWN($C47+$M47,2))</f>
+        <f>IF($M47="","",ROUNDUP($C47+$M47,2))</f>
       </c>
       <c r="O47" s="120" t="str">
-        <f>IF($N47="","",ROUNDDOWN(ROUNDDOWN($N47,2)*$E47,3))</f>
+        <f>IF($N47="","",ROUNDUP(ROUNDUP($N47,2)*$E47,3))</f>
       </c>
       <c r="P47" s="121" t="str">
         <f>IF($L47="","",$I47*$L47)</f>
@@ -3605,10 +3606,10 @@
         <f>IF($L48="","",$C48*$L48)</f>
       </c>
       <c r="N48" s="119" t="str">
-        <f>IF($M48="","",ROUNDDOWN($C48+$M48,2))</f>
+        <f>IF($M48="","",ROUNDUP($C48+$M48,2))</f>
       </c>
       <c r="O48" s="120" t="str">
-        <f>IF($N48="","",ROUNDDOWN(ROUNDDOWN($N48,2)*$E48,3))</f>
+        <f>IF($N48="","",ROUNDUP(ROUNDUP($N48,2)*$E48,3))</f>
       </c>
       <c r="P48" s="121" t="str">
         <f>IF($L48="","",$I48*$L48)</f>
@@ -3661,10 +3662,10 @@
         <f>IF($L49="","",$C49*$L49)</f>
       </c>
       <c r="N49" s="119" t="str">
-        <f>IF($M49="","",ROUNDDOWN($C49+$M49,2))</f>
+        <f>IF($M49="","",ROUNDUP($C49+$M49,2))</f>
       </c>
       <c r="O49" s="120" t="str">
-        <f>IF($N49="","",ROUNDDOWN(ROUNDDOWN($N49,2)*$E49,3))</f>
+        <f>IF($N49="","",ROUNDUP(ROUNDUP($N49,2)*$E49,3))</f>
       </c>
       <c r="P49" s="121" t="str">
         <f>IF($L49="","",$I49*$L49)</f>
@@ -3717,10 +3718,10 @@
         <f>IF($L50="","",$C50*$L50)</f>
       </c>
       <c r="N50" s="119" t="str">
-        <f>IF($M50="","",ROUNDDOWN($C50+$M50,2))</f>
+        <f>IF($M50="","",ROUNDUP($C50+$M50,2))</f>
       </c>
       <c r="O50" s="120" t="str">
-        <f>IF($N50="","",ROUNDDOWN(ROUNDDOWN($N50,2)*$E50,3))</f>
+        <f>IF($N50="","",ROUNDUP(ROUNDUP($N50,2)*$E50,3))</f>
       </c>
       <c r="P50" s="121" t="str">
         <f>IF($L50="","",$I50*$L50)</f>
@@ -3773,10 +3774,10 @@
         <f>IF($L51="","",$C51*$L51)</f>
       </c>
       <c r="N51" s="119" t="str">
-        <f>IF($M51="","",ROUNDDOWN($C51+$M51,2))</f>
+        <f>IF($M51="","",ROUNDUP($C51+$M51,2))</f>
       </c>
       <c r="O51" s="120" t="str">
-        <f>IF($N51="","",ROUNDDOWN(ROUNDDOWN($N51,2)*$E51,3))</f>
+        <f>IF($N51="","",ROUNDUP(ROUNDUP($N51,2)*$E51,3))</f>
       </c>
       <c r="P51" s="121" t="str">
         <f>IF($L51="","",$I51*$L51)</f>
@@ -3829,10 +3830,10 @@
         <f>IF($L52="","",$C52*$L52)</f>
       </c>
       <c r="N52" s="119" t="str">
-        <f>IF($M52="","",ROUNDDOWN($C52+$M52,2))</f>
+        <f>IF($M52="","",ROUNDUP($C52+$M52,2))</f>
       </c>
       <c r="O52" s="120" t="str">
-        <f>IF($N52="","",ROUNDDOWN(ROUNDDOWN($N52,2)*$E52,3))</f>
+        <f>IF($N52="","",ROUNDUP(ROUNDUP($N52,2)*$E52,3))</f>
       </c>
       <c r="P52" s="121" t="str">
         <f>IF($L52="","",$I52*$L52)</f>
@@ -3885,10 +3886,10 @@
         <f>IF($L53="","",$C53*$L53)</f>
       </c>
       <c r="N53" s="119" t="str">
-        <f>IF($M53="","",ROUNDDOWN($C53+$M53,2))</f>
+        <f>IF($M53="","",ROUNDUP($C53+$M53,2))</f>
       </c>
       <c r="O53" s="120" t="str">
-        <f>IF($N53="","",ROUNDDOWN(ROUNDDOWN($N53,2)*$E53,3))</f>
+        <f>IF($N53="","",ROUNDUP(ROUNDUP($N53,2)*$E53,3))</f>
       </c>
       <c r="P53" s="121" t="str">
         <f>IF($L53="","",$I53*$L53)</f>
@@ -3941,10 +3942,10 @@
         <f>IF($L54="","",$C54*$L54)</f>
       </c>
       <c r="N54" s="119" t="str">
-        <f>IF($M54="","",ROUNDDOWN($C54+$M54,2))</f>
+        <f>IF($M54="","",ROUNDUP($C54+$M54,2))</f>
       </c>
       <c r="O54" s="120" t="str">
-        <f>IF($N54="","",ROUNDDOWN(ROUNDDOWN($N54,2)*$E54,3))</f>
+        <f>IF($N54="","",ROUNDUP(ROUNDUP($N54,2)*$E54,3))</f>
       </c>
       <c r="P54" s="121" t="str">
         <f>IF($L54="","",$I54*$L54)</f>
@@ -3997,10 +3998,10 @@
         <f>IF($L55="","",$C55*$L55)</f>
       </c>
       <c r="N55" s="119" t="str">
-        <f>IF($M55="","",ROUNDDOWN($C55+$M55,2))</f>
+        <f>IF($M55="","",ROUNDUP($C55+$M55,2))</f>
       </c>
       <c r="O55" s="120" t="str">
-        <f>IF($N55="","",ROUNDDOWN(ROUNDDOWN($N55,2)*$E55,3))</f>
+        <f>IF($N55="","",ROUNDUP(ROUNDUP($N55,2)*$E55,3))</f>
       </c>
       <c r="P55" s="121" t="str">
         <f>IF($L55="","",$I55*$L55)</f>
@@ -4053,10 +4054,10 @@
         <f>IF($L56="","",$C56*$L56)</f>
       </c>
       <c r="N56" s="119" t="str">
-        <f>IF($M56="","",ROUNDDOWN($C56+$M56,2))</f>
+        <f>IF($M56="","",ROUNDUP($C56+$M56,2))</f>
       </c>
       <c r="O56" s="120" t="str">
-        <f>IF($N56="","",ROUNDDOWN(ROUNDDOWN($N56,2)*$E56,3))</f>
+        <f>IF($N56="","",ROUNDUP(ROUNDUP($N56,2)*$E56,3))</f>
       </c>
       <c r="P56" s="121" t="str">
         <f>IF($L56="","",$I56*$L56)</f>
@@ -4109,10 +4110,10 @@
         <f>IF($L57="","",$C57*$L57)</f>
       </c>
       <c r="N57" s="119" t="str">
-        <f>IF($M57="","",ROUNDDOWN($C57+$M57,2))</f>
+        <f>IF($M57="","",ROUNDUP($C57+$M57,2))</f>
       </c>
       <c r="O57" s="120" t="str">
-        <f>IF($N57="","",ROUNDDOWN(ROUNDDOWN($N57,2)*$E57,3))</f>
+        <f>IF($N57="","",ROUNDUP(ROUNDUP($N57,2)*$E57,3))</f>
       </c>
       <c r="P57" s="121" t="str">
         <f>IF($L57="","",$I57*$L57)</f>
@@ -4165,10 +4166,10 @@
         <f>IF($L58="","",$C58*$L58)</f>
       </c>
       <c r="N58" s="119" t="str">
-        <f>IF($M58="","",ROUNDDOWN($C58+$M58,2))</f>
+        <f>IF($M58="","",ROUNDUP($C58+$M58,2))</f>
       </c>
       <c r="O58" s="120" t="str">
-        <f>IF($N58="","",ROUNDDOWN(ROUNDDOWN($N58,2)*$E58,3))</f>
+        <f>IF($N58="","",ROUNDUP(ROUNDUP($N58,2)*$E58,3))</f>
       </c>
       <c r="P58" s="121" t="str">
         <f>IF($L58="","",$I58*$L58)</f>
@@ -4221,10 +4222,10 @@
         <f>IF($L59="","",$C59*$L59)</f>
       </c>
       <c r="N59" s="119" t="str">
-        <f>IF($M59="","",ROUNDDOWN($C59+$M59,2))</f>
+        <f>IF($M59="","",ROUNDUP($C59+$M59,2))</f>
       </c>
       <c r="O59" s="120" t="str">
-        <f>IF($N59="","",ROUNDDOWN(ROUNDDOWN($N59,2)*$E59,3))</f>
+        <f>IF($N59="","",ROUNDUP(ROUNDUP($N59,2)*$E59,3))</f>
       </c>
       <c r="P59" s="121" t="str">
         <f>IF($L59="","",$I59*$L59)</f>
@@ -4277,10 +4278,10 @@
         <f>IF($L60="","",$C60*$L60)</f>
       </c>
       <c r="N60" s="119" t="str">
-        <f>IF($M60="","",ROUNDDOWN($C60+$M60,2))</f>
+        <f>IF($M60="","",ROUNDUP($C60+$M60,2))</f>
       </c>
       <c r="O60" s="120" t="str">
-        <f>IF($N60="","",ROUNDDOWN(ROUNDDOWN($N60,2)*$E60,3))</f>
+        <f>IF($N60="","",ROUNDUP(ROUNDUP($N60,2)*$E60,3))</f>
       </c>
       <c r="P60" s="121" t="str">
         <f>IF($L60="","",$I60*$L60)</f>
@@ -4333,10 +4334,10 @@
         <f>IF($L61="","",$C61*$L61)</f>
       </c>
       <c r="N61" s="119" t="str">
-        <f>IF($M61="","",ROUNDDOWN($C61+$M61,2))</f>
+        <f>IF($M61="","",ROUNDUP($C61+$M61,2))</f>
       </c>
       <c r="O61" s="120" t="str">
-        <f>IF($N61="","",ROUNDDOWN(ROUNDDOWN($N61,2)*$E61,3))</f>
+        <f>IF($N61="","",ROUNDUP(ROUNDUP($N61,2)*$E61,3))</f>
       </c>
       <c r="P61" s="121" t="str">
         <f>IF($L61="","",$I61*$L61)</f>
@@ -4389,10 +4390,10 @@
         <f>IF($L62="","",$C62*$L62)</f>
       </c>
       <c r="N62" s="119" t="str">
-        <f>IF($M62="","",ROUNDDOWN($C62+$M62,2))</f>
+        <f>IF($M62="","",ROUNDUP($C62+$M62,2))</f>
       </c>
       <c r="O62" s="120" t="str">
-        <f>IF($N62="","",ROUNDDOWN(ROUNDDOWN($N62,2)*$E62,3))</f>
+        <f>IF($N62="","",ROUNDUP(ROUNDUP($N62,2)*$E62,3))</f>
       </c>
       <c r="P62" s="121" t="str">
         <f>IF($L62="","",$I62*$L62)</f>
@@ -4445,10 +4446,10 @@
         <f>IF($L63="","",$C63*$L63)</f>
       </c>
       <c r="N63" s="119" t="str">
-        <f>IF($M63="","",ROUNDDOWN($C63+$M63,2))</f>
+        <f>IF($M63="","",ROUNDUP($C63+$M63,2))</f>
       </c>
       <c r="O63" s="120" t="str">
-        <f>IF($N63="","",ROUNDDOWN(ROUNDDOWN($N63,2)*$E63,3))</f>
+        <f>IF($N63="","",ROUNDUP(ROUNDUP($N63,2)*$E63,3))</f>
       </c>
       <c r="P63" s="121" t="str">
         <f>IF($L63="","",$I63*$L63)</f>
@@ -4501,10 +4502,10 @@
         <f>IF($L64="","",$C64*$L64)</f>
       </c>
       <c r="N64" s="119" t="str">
-        <f>IF($M64="","",ROUNDDOWN($C64+$M64,2))</f>
+        <f>IF($M64="","",ROUNDUP($C64+$M64,2))</f>
       </c>
       <c r="O64" s="120" t="str">
-        <f>IF($N64="","",ROUNDDOWN(ROUNDDOWN($N64,2)*$E64,3))</f>
+        <f>IF($N64="","",ROUNDUP(ROUNDUP($N64,2)*$E64,3))</f>
       </c>
       <c r="P64" s="121" t="str">
         <f>IF($L64="","",$I64*$L64)</f>
@@ -4557,10 +4558,10 @@
         <f>IF($L65="","",$C65*$L65)</f>
       </c>
       <c r="N65" s="119" t="str">
-        <f>IF($M65="","",ROUNDDOWN($C65+$M65,2))</f>
+        <f>IF($M65="","",ROUNDUP($C65+$M65,2))</f>
       </c>
       <c r="O65" s="120" t="str">
-        <f>IF($N65="","",ROUNDDOWN(ROUNDDOWN($N65,2)*$E65,3))</f>
+        <f>IF($N65="","",ROUNDUP(ROUNDUP($N65,2)*$E65,3))</f>
       </c>
       <c r="P65" s="121" t="str">
         <f>IF($L65="","",$I65*$L65)</f>
@@ -4613,10 +4614,10 @@
         <f>IF($L66="","",$C66*$L66)</f>
       </c>
       <c r="N66" s="119" t="str">
-        <f>IF($M66="","",ROUNDDOWN($C66+$M66,2))</f>
+        <f>IF($M66="","",ROUNDUP($C66+$M66,2))</f>
       </c>
       <c r="O66" s="120" t="str">
-        <f>IF($N66="","",ROUNDDOWN(ROUNDDOWN($N66,2)*$E66,3))</f>
+        <f>IF($N66="","",ROUNDUP(ROUNDUP($N66,2)*$E66,3))</f>
       </c>
       <c r="P66" s="121" t="str">
         <f>IF($L66="","",$I66*$L66)</f>
@@ -4669,10 +4670,10 @@
         <f>IF($L67="","",$C67*$L67)</f>
       </c>
       <c r="N67" s="119" t="str">
-        <f>IF($M67="","",ROUNDDOWN($C67+$M67,2))</f>
+        <f>IF($M67="","",ROUNDUP($C67+$M67,2))</f>
       </c>
       <c r="O67" s="120" t="str">
-        <f>IF($N67="","",ROUNDDOWN(ROUNDDOWN($N67,2)*$E67,3))</f>
+        <f>IF($N67="","",ROUNDUP(ROUNDUP($N67,2)*$E67,3))</f>
       </c>
       <c r="P67" s="121" t="str">
         <f>IF($L67="","",$I67*$L67)</f>
@@ -4725,10 +4726,10 @@
         <f>IF($L68="","",$C68*$L68)</f>
       </c>
       <c r="N68" s="119" t="str">
-        <f>IF($M68="","",ROUNDDOWN($C68+$M68,2))</f>
+        <f>IF($M68="","",ROUNDUP($C68+$M68,2))</f>
       </c>
       <c r="O68" s="120" t="str">
-        <f>IF($N68="","",ROUNDDOWN(ROUNDDOWN($N68,2)*$E68,3))</f>
+        <f>IF($N68="","",ROUNDUP(ROUNDUP($N68,2)*$E68,3))</f>
       </c>
       <c r="P68" s="121" t="str">
         <f>IF($L68="","",$I68*$L68)</f>
@@ -4781,10 +4782,10 @@
         <f>IF($L69="","",$C69*$L69)</f>
       </c>
       <c r="N69" s="119" t="str">
-        <f>IF($M69="","",ROUNDDOWN($C69+$M69,2))</f>
+        <f>IF($M69="","",ROUNDUP($C69+$M69,2))</f>
       </c>
       <c r="O69" s="120" t="str">
-        <f>IF($N69="","",ROUNDDOWN(ROUNDDOWN($N69,2)*$E69,3))</f>
+        <f>IF($N69="","",ROUNDUP(ROUNDUP($N69,2)*$E69,3))</f>
       </c>
       <c r="P69" s="121" t="str">
         <f>IF($L69="","",$I69*$L69)</f>
@@ -4837,10 +4838,10 @@
         <f>IF($L70="","",$C70*$L70)</f>
       </c>
       <c r="N70" s="119" t="str">
-        <f>IF($M70="","",ROUNDDOWN($C70+$M70,2))</f>
+        <f>IF($M70="","",ROUNDUP($C70+$M70,2))</f>
       </c>
       <c r="O70" s="120" t="str">
-        <f>IF($N70="","",ROUNDDOWN(ROUNDDOWN($N70,2)*$E70,3))</f>
+        <f>IF($N70="","",ROUNDUP(ROUNDUP($N70,2)*$E70,3))</f>
       </c>
       <c r="P70" s="121" t="str">
         <f>IF($L70="","",$I70*$L70)</f>
@@ -4893,10 +4894,10 @@
         <f>IF($L71="","",$C71*$L71)</f>
       </c>
       <c r="N71" s="119" t="str">
-        <f>IF($M71="","",ROUNDDOWN($C71+$M71,2))</f>
+        <f>IF($M71="","",ROUNDUP($C71+$M71,2))</f>
       </c>
       <c r="O71" s="120" t="str">
-        <f>IF($N71="","",ROUNDDOWN(ROUNDDOWN($N71,2)*$E71,3))</f>
+        <f>IF($N71="","",ROUNDUP(ROUNDUP($N71,2)*$E71,3))</f>
       </c>
       <c r="P71" s="121" t="str">
         <f>IF($L71="","",$I71*$L71)</f>
@@ -4949,10 +4950,10 @@
         <f>IF($L72="","",$C72*$L72)</f>
       </c>
       <c r="N72" s="119" t="str">
-        <f>IF($M72="","",ROUNDDOWN($C72+$M72,2))</f>
+        <f>IF($M72="","",ROUNDUP($C72+$M72,2))</f>
       </c>
       <c r="O72" s="120" t="str">
-        <f>IF($N72="","",ROUNDDOWN(ROUNDDOWN($N72,2)*$E72,3))</f>
+        <f>IF($N72="","",ROUNDUP(ROUNDUP($N72,2)*$E72,3))</f>
       </c>
       <c r="P72" s="121" t="str">
         <f>IF($L72="","",$I72*$L72)</f>
@@ -5005,10 +5006,10 @@
         <f>IF($L73="","",$C73*$L73)</f>
       </c>
       <c r="N73" s="119" t="str">
-        <f>IF($M73="","",ROUNDDOWN($C73+$M73,2))</f>
+        <f>IF($M73="","",ROUNDUP($C73+$M73,2))</f>
       </c>
       <c r="O73" s="120" t="str">
-        <f>IF($N73="","",ROUNDDOWN(ROUNDDOWN($N73,2)*$E73,3))</f>
+        <f>IF($N73="","",ROUNDUP(ROUNDUP($N73,2)*$E73,3))</f>
       </c>
       <c r="P73" s="121" t="str">
         <f>IF($L73="","",$I73*$L73)</f>
@@ -5061,10 +5062,10 @@
         <f>IF($L74="","",$C74*$L74)</f>
       </c>
       <c r="N74" s="119" t="str">
-        <f>IF($M74="","",ROUNDDOWN($C74+$M74,2))</f>
+        <f>IF($M74="","",ROUNDUP($C74+$M74,2))</f>
       </c>
       <c r="O74" s="120" t="str">
-        <f>IF($N74="","",ROUNDDOWN(ROUNDDOWN($N74,2)*$E74,3))</f>
+        <f>IF($N74="","",ROUNDUP(ROUNDUP($N74,2)*$E74,3))</f>
       </c>
       <c r="P74" s="121" t="str">
         <f>IF($L74="","",$I74*$L74)</f>
@@ -5117,10 +5118,10 @@
         <f>IF($L75="","",$C75*$L75)</f>
       </c>
       <c r="N75" s="119" t="str">
-        <f>IF($M75="","",ROUNDDOWN($C75+$M75,2))</f>
+        <f>IF($M75="","",ROUNDUP($C75+$M75,2))</f>
       </c>
       <c r="O75" s="120" t="str">
-        <f>IF($N75="","",ROUNDDOWN(ROUNDDOWN($N75,2)*$E75,3))</f>
+        <f>IF($N75="","",ROUNDUP(ROUNDUP($N75,2)*$E75,3))</f>
       </c>
       <c r="P75" s="121" t="str">
         <f>IF($L75="","",$I75*$L75)</f>
@@ -5173,10 +5174,10 @@
         <f>IF($L76="","",$C76*$L76)</f>
       </c>
       <c r="N76" s="119" t="str">
-        <f>IF($M76="","",ROUNDDOWN($C76+$M76,2))</f>
+        <f>IF($M76="","",ROUNDUP($C76+$M76,2))</f>
       </c>
       <c r="O76" s="120" t="str">
-        <f>IF($N76="","",ROUNDDOWN(ROUNDDOWN($N76,2)*$E76,3))</f>
+        <f>IF($N76="","",ROUNDUP(ROUNDUP($N76,2)*$E76,3))</f>
       </c>
       <c r="P76" s="121" t="str">
         <f>IF($L76="","",$I76*$L76)</f>
@@ -5229,10 +5230,10 @@
         <f>IF($L77="","",$C77*$L77)</f>
       </c>
       <c r="N77" s="119" t="str">
-        <f>IF($M77="","",ROUNDDOWN($C77+$M77,2))</f>
+        <f>IF($M77="","",ROUNDUP($C77+$M77,2))</f>
       </c>
       <c r="O77" s="120" t="str">
-        <f>IF($N77="","",ROUNDDOWN(ROUNDDOWN($N77,2)*$E77,3))</f>
+        <f>IF($N77="","",ROUNDUP(ROUNDUP($N77,2)*$E77,3))</f>
       </c>
       <c r="P77" s="121" t="str">
         <f>IF($L77="","",$I77*$L77)</f>
@@ -5285,10 +5286,10 @@
         <f>IF($L78="","",$C78*$L78)</f>
       </c>
       <c r="N78" s="119" t="str">
-        <f>IF($M78="","",ROUNDDOWN($C78+$M78,2))</f>
+        <f>IF($M78="","",ROUNDUP($C78+$M78,2))</f>
       </c>
       <c r="O78" s="120" t="str">
-        <f>IF($N78="","",ROUNDDOWN(ROUNDDOWN($N78,2)*$E78,3))</f>
+        <f>IF($N78="","",ROUNDUP(ROUNDUP($N78,2)*$E78,3))</f>
       </c>
       <c r="P78" s="121" t="str">
         <f>IF($L78="","",$I78*$L78)</f>
@@ -5341,10 +5342,10 @@
         <f>IF($L79="","",$C79*$L79)</f>
       </c>
       <c r="N79" s="119" t="str">
-        <f>IF($M79="","",ROUNDDOWN($C79+$M79,2))</f>
+        <f>IF($M79="","",ROUNDUP($C79+$M79,2))</f>
       </c>
       <c r="O79" s="120" t="str">
-        <f>IF($N79="","",ROUNDDOWN(ROUNDDOWN($N79,2)*$E79,3))</f>
+        <f>IF($N79="","",ROUNDUP(ROUNDUP($N79,2)*$E79,3))</f>
       </c>
       <c r="P79" s="121" t="str">
         <f>IF($L79="","",$I79*$L79)</f>
@@ -5397,10 +5398,10 @@
         <f>IF($L80="","",$C80*$L80)</f>
       </c>
       <c r="N80" s="119" t="str">
-        <f>IF($M80="","",ROUNDDOWN($C80+$M80,2))</f>
+        <f>IF($M80="","",ROUNDUP($C80+$M80,2))</f>
       </c>
       <c r="O80" s="120" t="str">
-        <f>IF($N80="","",ROUNDDOWN(ROUNDDOWN($N80,2)*$E80,3))</f>
+        <f>IF($N80="","",ROUNDUP(ROUNDUP($N80,2)*$E80,3))</f>
       </c>
       <c r="P80" s="121" t="str">
         <f>IF($L80="","",$I80*$L80)</f>
@@ -5453,10 +5454,10 @@
         <f>IF($L81="","",$C81*$L81)</f>
       </c>
       <c r="N81" s="119" t="str">
-        <f>IF($M81="","",ROUNDDOWN($C81+$M81,2))</f>
+        <f>IF($M81="","",ROUNDUP($C81+$M81,2))</f>
       </c>
       <c r="O81" s="120" t="str">
-        <f>IF($N81="","",ROUNDDOWN(ROUNDDOWN($N81,2)*$E81,3))</f>
+        <f>IF($N81="","",ROUNDUP(ROUNDUP($N81,2)*$E81,3))</f>
       </c>
       <c r="P81" s="121" t="str">
         <f>IF($L81="","",$I81*$L81)</f>
@@ -5509,10 +5510,10 @@
         <f>IF($L82="","",$C82*$L82)</f>
       </c>
       <c r="N82" s="119" t="str">
-        <f>IF($M82="","",ROUNDDOWN($C82+$M82,2))</f>
+        <f>IF($M82="","",ROUNDUP($C82+$M82,2))</f>
       </c>
       <c r="O82" s="120" t="str">
-        <f>IF($N82="","",ROUNDDOWN(ROUNDDOWN($N82,2)*$E82,3))</f>
+        <f>IF($N82="","",ROUNDUP(ROUNDUP($N82,2)*$E82,3))</f>
       </c>
       <c r="P82" s="121" t="str">
         <f>IF($L82="","",$I82*$L82)</f>
@@ -5565,10 +5566,10 @@
         <f>IF($L83="","",$C83*$L83)</f>
       </c>
       <c r="N83" s="119" t="str">
-        <f>IF($M83="","",ROUNDDOWN($C83+$M83,2))</f>
+        <f>IF($M83="","",ROUNDUP($C83+$M83,2))</f>
       </c>
       <c r="O83" s="120" t="str">
-        <f>IF($N83="","",ROUNDDOWN(ROUNDDOWN($N83,2)*$E83,3))</f>
+        <f>IF($N83="","",ROUNDUP(ROUNDUP($N83,2)*$E83,3))</f>
       </c>
       <c r="P83" s="121" t="str">
         <f>IF($L83="","",$I83*$L83)</f>
@@ -5621,10 +5622,10 @@
         <f>IF($L84="","",$C84*$L84)</f>
       </c>
       <c r="N84" s="119" t="str">
-        <f>IF($M84="","",ROUNDDOWN($C84+$M84,2))</f>
+        <f>IF($M84="","",ROUNDUP($C84+$M84,2))</f>
       </c>
       <c r="O84" s="120" t="str">
-        <f>IF($N84="","",ROUNDDOWN(ROUNDDOWN($N84,2)*$E84,3))</f>
+        <f>IF($N84="","",ROUNDUP(ROUNDUP($N84,2)*$E84,3))</f>
       </c>
       <c r="P84" s="121" t="str">
         <f>IF($L84="","",$I84*$L84)</f>
@@ -5677,10 +5678,10 @@
         <f>IF($L85="","",$C85*$L85)</f>
       </c>
       <c r="N85" s="119" t="str">
-        <f>IF($M85="","",ROUNDDOWN($C85+$M85,2))</f>
+        <f>IF($M85="","",ROUNDUP($C85+$M85,2))</f>
       </c>
       <c r="O85" s="120" t="str">
-        <f>IF($N85="","",ROUNDDOWN(ROUNDDOWN($N85,2)*$E85,3))</f>
+        <f>IF($N85="","",ROUNDUP(ROUNDUP($N85,2)*$E85,3))</f>
       </c>
       <c r="P85" s="121" t="str">
         <f>IF($L85="","",$I85*$L85)</f>
@@ -5733,10 +5734,10 @@
         <f>IF($L86="","",$C86*$L86)</f>
       </c>
       <c r="N86" s="119" t="str">
-        <f>IF($M86="","",ROUNDDOWN($C86+$M86,2))</f>
+        <f>IF($M86="","",ROUNDUP($C86+$M86,2))</f>
       </c>
       <c r="O86" s="120" t="str">
-        <f>IF($N86="","",ROUNDDOWN(ROUNDDOWN($N86,2)*$E86,3))</f>
+        <f>IF($N86="","",ROUNDUP(ROUNDUP($N86,2)*$E86,3))</f>
       </c>
       <c r="P86" s="121" t="str">
         <f>IF($L86="","",$I86*$L86)</f>
@@ -5789,10 +5790,10 @@
         <f>IF($L87="","",$C87*$L87)</f>
       </c>
       <c r="N87" s="119" t="str">
-        <f>IF($M87="","",ROUNDDOWN($C87+$M87,2))</f>
+        <f>IF($M87="","",ROUNDUP($C87+$M87,2))</f>
       </c>
       <c r="O87" s="120" t="str">
-        <f>IF($N87="","",ROUNDDOWN(ROUNDDOWN($N87,2)*$E87,3))</f>
+        <f>IF($N87="","",ROUNDUP(ROUNDUP($N87,2)*$E87,3))</f>
       </c>
       <c r="P87" s="121" t="str">
         <f>IF($L87="","",$I87*$L87)</f>
@@ -5845,10 +5846,10 @@
         <f>IF($L88="","",$C88*$L88)</f>
       </c>
       <c r="N88" s="119" t="str">
-        <f>IF($M88="","",ROUNDDOWN($C88+$M88,2))</f>
+        <f>IF($M88="","",ROUNDUP($C88+$M88,2))</f>
       </c>
       <c r="O88" s="120" t="str">
-        <f>IF($N88="","",ROUNDDOWN(ROUNDDOWN($N88,2)*$E88,3))</f>
+        <f>IF($N88="","",ROUNDUP(ROUNDUP($N88,2)*$E88,3))</f>
       </c>
       <c r="P88" s="121" t="str">
         <f>IF($L88="","",$I88*$L88)</f>
@@ -5901,10 +5902,10 @@
         <f>IF($L89="","",$C89*$L89)</f>
       </c>
       <c r="N89" s="119" t="str">
-        <f>IF($M89="","",ROUNDDOWN($C89+$M89,2))</f>
+        <f>IF($M89="","",ROUNDUP($C89+$M89,2))</f>
       </c>
       <c r="O89" s="120" t="str">
-        <f>IF($N89="","",ROUNDDOWN(ROUNDDOWN($N89,2)*$E89,3))</f>
+        <f>IF($N89="","",ROUNDUP(ROUNDUP($N89,2)*$E89,3))</f>
       </c>
       <c r="P89" s="121" t="str">
         <f>IF($L89="","",$I89*$L89)</f>
@@ -5957,10 +5958,10 @@
         <f>IF($L90="","",$C90*$L90)</f>
       </c>
       <c r="N90" s="119" t="str">
-        <f>IF($M90="","",ROUNDDOWN($C90+$M90,2))</f>
+        <f>IF($M90="","",ROUNDUP($C90+$M90,2))</f>
       </c>
       <c r="O90" s="120" t="str">
-        <f>IF($N90="","",ROUNDDOWN(ROUNDDOWN($N90,2)*$E90,3))</f>
+        <f>IF($N90="","",ROUNDUP(ROUNDUP($N90,2)*$E90,3))</f>
       </c>
       <c r="P90" s="121" t="str">
         <f>IF($L90="","",$I90*$L90)</f>
@@ -6013,10 +6014,10 @@
         <f>IF($L91="","",$C91*$L91)</f>
       </c>
       <c r="N91" s="119" t="str">
-        <f>IF($M91="","",ROUNDDOWN($C91+$M91,2))</f>
+        <f>IF($M91="","",ROUNDUP($C91+$M91,2))</f>
       </c>
       <c r="O91" s="120" t="str">
-        <f>IF($N91="","",ROUNDDOWN(ROUNDDOWN($N91,2)*$E91,3))</f>
+        <f>IF($N91="","",ROUNDUP(ROUNDUP($N91,2)*$E91,3))</f>
       </c>
       <c r="P91" s="121" t="str">
         <f>IF($L91="","",$I91*$L91)</f>
@@ -6069,10 +6070,10 @@
         <f>IF($L92="","",$C92*$L92)</f>
       </c>
       <c r="N92" s="119" t="str">
-        <f>IF($M92="","",ROUNDDOWN($C92+$M92,2))</f>
+        <f>IF($M92="","",ROUNDUP($C92+$M92,2))</f>
       </c>
       <c r="O92" s="120" t="str">
-        <f>IF($N92="","",ROUNDDOWN(ROUNDDOWN($N92,2)*$E92,3))</f>
+        <f>IF($N92="","",ROUNDUP(ROUNDUP($N92,2)*$E92,3))</f>
       </c>
       <c r="P92" s="121" t="str">
         <f>IF($L92="","",$I92*$L92)</f>
@@ -6125,10 +6126,10 @@
         <f>IF($L93="","",$C93*$L93)</f>
       </c>
       <c r="N93" s="119" t="str">
-        <f>IF($M93="","",ROUNDDOWN($C93+$M93,2))</f>
+        <f>IF($M93="","",ROUNDUP($C93+$M93,2))</f>
       </c>
       <c r="O93" s="120" t="str">
-        <f>IF($N93="","",ROUNDDOWN(ROUNDDOWN($N93,2)*$E93,3))</f>
+        <f>IF($N93="","",ROUNDUP(ROUNDUP($N93,2)*$E93,3))</f>
       </c>
       <c r="P93" s="121" t="str">
         <f>IF($L93="","",$I93*$L93)</f>
@@ -6181,10 +6182,10 @@
         <f>IF($L94="","",$C94*$L94)</f>
       </c>
       <c r="N94" s="119" t="str">
-        <f>IF($M94="","",ROUNDDOWN($C94+$M94,2))</f>
+        <f>IF($M94="","",ROUNDUP($C94+$M94,2))</f>
       </c>
       <c r="O94" s="120" t="str">
-        <f>IF($N94="","",ROUNDDOWN(ROUNDDOWN($N94,2)*$E94,3))</f>
+        <f>IF($N94="","",ROUNDUP(ROUNDUP($N94,2)*$E94,3))</f>
       </c>
       <c r="P94" s="121" t="str">
         <f>IF($L94="","",$I94*$L94)</f>
@@ -6237,10 +6238,10 @@
         <f>IF($L95="","",$C95*$L95)</f>
       </c>
       <c r="N95" s="119" t="str">
-        <f>IF($M95="","",ROUNDDOWN($C95+$M95,2))</f>
+        <f>IF($M95="","",ROUNDUP($C95+$M95,2))</f>
       </c>
       <c r="O95" s="120" t="str">
-        <f>IF($N95="","",ROUNDDOWN(ROUNDDOWN($N95,2)*$E95,3))</f>
+        <f>IF($N95="","",ROUNDUP(ROUNDUP($N95,2)*$E95,3))</f>
       </c>
       <c r="P95" s="121" t="str">
         <f>IF($L95="","",$I95*$L95)</f>
@@ -6293,10 +6294,10 @@
         <f>IF($L96="","",$C96*$L96)</f>
       </c>
       <c r="N96" s="119" t="str">
-        <f>IF($M96="","",ROUNDDOWN($C96+$M96,2))</f>
+        <f>IF($M96="","",ROUNDUP($C96+$M96,2))</f>
       </c>
       <c r="O96" s="120" t="str">
-        <f>IF($N96="","",ROUNDDOWN(ROUNDDOWN($N96,2)*$E96,3))</f>
+        <f>IF($N96="","",ROUNDUP(ROUNDUP($N96,2)*$E96,3))</f>
       </c>
       <c r="P96" s="121" t="str">
         <f>IF($L96="","",$I96*$L96)</f>
@@ -6349,10 +6350,10 @@
         <f>IF($L97="","",$C97*$L97)</f>
       </c>
       <c r="N97" s="119" t="str">
-        <f>IF($M97="","",ROUNDDOWN($C97+$M97,2))</f>
+        <f>IF($M97="","",ROUNDUP($C97+$M97,2))</f>
       </c>
       <c r="O97" s="120" t="str">
-        <f>IF($N97="","",ROUNDDOWN(ROUNDDOWN($N97,2)*$E97,3))</f>
+        <f>IF($N97="","",ROUNDUP(ROUNDUP($N97,2)*$E97,3))</f>
       </c>
       <c r="P97" s="121" t="str">
         <f>IF($L97="","",$I97*$L97)</f>
@@ -6405,10 +6406,10 @@
         <f>IF($L98="","",$C98*$L98)</f>
       </c>
       <c r="N98" s="119" t="str">
-        <f>IF($M98="","",ROUNDDOWN($C98+$M98,2))</f>
+        <f>IF($M98="","",ROUNDUP($C98+$M98,2))</f>
       </c>
       <c r="O98" s="120" t="str">
-        <f>IF($N98="","",ROUNDDOWN(ROUNDDOWN($N98,2)*$E98,3))</f>
+        <f>IF($N98="","",ROUNDUP(ROUNDUP($N98,2)*$E98,3))</f>
       </c>
       <c r="P98" s="121" t="str">
         <f>IF($L98="","",$I98*$L98)</f>
@@ -6461,10 +6462,10 @@
         <f>IF($L99="","",$C99*$L99)</f>
       </c>
       <c r="N99" s="119" t="str">
-        <f>IF($M99="","",ROUNDDOWN($C99+$M99,2))</f>
+        <f>IF($M99="","",ROUNDUP($C99+$M99,2))</f>
       </c>
       <c r="O99" s="120" t="str">
-        <f>IF($N99="","",ROUNDDOWN(ROUNDDOWN($N99,2)*$E99,3))</f>
+        <f>IF($N99="","",ROUNDUP(ROUNDUP($N99,2)*$E99,3))</f>
       </c>
       <c r="P99" s="121" t="str">
         <f>IF($L99="","",$I99*$L99)</f>
@@ -6517,10 +6518,10 @@
         <f>IF($L100="","",$C100*$L100)</f>
       </c>
       <c r="N100" s="119" t="str">
-        <f>IF($M100="","",ROUNDDOWN($C100+$M100,2))</f>
+        <f>IF($M100="","",ROUNDUP($C100+$M100,2))</f>
       </c>
       <c r="O100" s="120" t="str">
-        <f>IF($N100="","",ROUNDDOWN(ROUNDDOWN($N100,2)*$E100,3))</f>
+        <f>IF($N100="","",ROUNDUP(ROUNDUP($N100,2)*$E100,3))</f>
       </c>
       <c r="P100" s="121" t="str">
         <f>IF($L100="","",$I100*$L100)</f>
@@ -6573,10 +6574,10 @@
         <f>IF($L101="","",$C101*$L101)</f>
       </c>
       <c r="N101" s="119" t="str">
-        <f>IF($M101="","",ROUNDDOWN($C101+$M101,2))</f>
+        <f>IF($M101="","",ROUNDUP($C101+$M101,2))</f>
       </c>
       <c r="O101" s="120" t="str">
-        <f>IF($N101="","",ROUNDDOWN(ROUNDDOWN($N101,2)*$E101,3))</f>
+        <f>IF($N101="","",ROUNDUP(ROUNDUP($N101,2)*$E101,3))</f>
       </c>
       <c r="P101" s="121" t="str">
         <f>IF($L101="","",$I101*$L101)</f>
@@ -6629,10 +6630,10 @@
         <f>IF($L102="","",$C102*$L102)</f>
       </c>
       <c r="N102" s="119" t="str">
-        <f>IF($M102="","",ROUNDDOWN($C102+$M102,2))</f>
+        <f>IF($M102="","",ROUNDUP($C102+$M102,2))</f>
       </c>
       <c r="O102" s="120" t="str">
-        <f>IF($N102="","",ROUNDDOWN(ROUNDDOWN($N102,2)*$E102,3))</f>
+        <f>IF($N102="","",ROUNDUP(ROUNDUP($N102,2)*$E102,3))</f>
       </c>
       <c r="P102" s="121" t="str">
         <f>IF($L102="","",$I102*$L102)</f>
@@ -6685,10 +6686,10 @@
         <f>IF($L103="","",$C103*$L103)</f>
       </c>
       <c r="N103" s="119" t="str">
-        <f>IF($M103="","",ROUNDDOWN($C103+$M103,2))</f>
+        <f>IF($M103="","",ROUNDUP($C103+$M103,2))</f>
       </c>
       <c r="O103" s="120" t="str">
-        <f>IF($N103="","",ROUNDDOWN(ROUNDDOWN($N103,2)*$E103,3))</f>
+        <f>IF($N103="","",ROUNDUP(ROUNDUP($N103,2)*$E103,3))</f>
       </c>
       <c r="P103" s="121" t="str">
         <f>IF($L103="","",$I103*$L103)</f>
@@ -6741,10 +6742,10 @@
         <f>IF($L104="","",$C104*$L104)</f>
       </c>
       <c r="N104" s="119" t="str">
-        <f>IF($M104="","",ROUNDDOWN($C104+$M104,2))</f>
+        <f>IF($M104="","",ROUNDUP($C104+$M104,2))</f>
       </c>
       <c r="O104" s="120" t="str">
-        <f>IF($N104="","",ROUNDDOWN(ROUNDDOWN($N104,2)*$E104,3))</f>
+        <f>IF($N104="","",ROUNDUP(ROUNDUP($N104,2)*$E104,3))</f>
       </c>
       <c r="P104" s="121" t="str">
         <f>IF($L104="","",$I104*$L104)</f>
@@ -6797,10 +6798,10 @@
         <f>IF($L105="","",$C105*$L105)</f>
       </c>
       <c r="N105" s="119" t="str">
-        <f>IF($M105="","",ROUNDDOWN($C105+$M105,2))</f>
+        <f>IF($M105="","",ROUNDUP($C105+$M105,2))</f>
       </c>
       <c r="O105" s="120" t="str">
-        <f>IF($N105="","",ROUNDDOWN(ROUNDDOWN($N105,2)*$E105,3))</f>
+        <f>IF($N105="","",ROUNDUP(ROUNDUP($N105,2)*$E105,3))</f>
       </c>
       <c r="P105" s="121" t="str">
         <f>IF($L105="","",$I105*$L105)</f>
@@ -6853,10 +6854,10 @@
         <f>IF($L106="","",$C106*$L106)</f>
       </c>
       <c r="N106" s="119" t="str">
-        <f>IF($M106="","",ROUNDDOWN($C106+$M106,2))</f>
+        <f>IF($M106="","",ROUNDUP($C106+$M106,2))</f>
       </c>
       <c r="O106" s="120" t="str">
-        <f>IF($N106="","",ROUNDDOWN(ROUNDDOWN($N106,2)*$E106,3))</f>
+        <f>IF($N106="","",ROUNDUP(ROUNDUP($N106,2)*$E106,3))</f>
       </c>
       <c r="P106" s="121" t="str">
         <f>IF($L106="","",$I106*$L106)</f>
@@ -6909,10 +6910,10 @@
         <f>IF($L107="","",$C107*$L107)</f>
       </c>
       <c r="N107" s="119" t="str">
-        <f>IF($M107="","",ROUNDDOWN($C107+$M107,2))</f>
+        <f>IF($M107="","",ROUNDUP($C107+$M107,2))</f>
       </c>
       <c r="O107" s="120" t="str">
-        <f>IF($N107="","",ROUNDDOWN(ROUNDDOWN($N107,2)*$E107,3))</f>
+        <f>IF($N107="","",ROUNDUP(ROUNDUP($N107,2)*$E107,3))</f>
       </c>
       <c r="P107" s="121" t="str">
         <f>IF($L107="","",$I107*$L107)</f>
@@ -6965,10 +6966,10 @@
         <f>IF($L108="","",$C108*$L108)</f>
       </c>
       <c r="N108" s="119" t="str">
-        <f>IF($M108="","",ROUNDDOWN($C108+$M108,2))</f>
+        <f>IF($M108="","",ROUNDUP($C108+$M108,2))</f>
       </c>
       <c r="O108" s="120" t="str">
-        <f>IF($N108="","",ROUNDDOWN(ROUNDDOWN($N108,2)*$E108,3))</f>
+        <f>IF($N108="","",ROUNDUP(ROUNDUP($N108,2)*$E108,3))</f>
       </c>
       <c r="P108" s="121" t="str">
         <f>IF($L108="","",$I108*$L108)</f>
@@ -7021,10 +7022,10 @@
         <f>IF($L109="","",$C109*$L109)</f>
       </c>
       <c r="N109" s="119" t="str">
-        <f>IF($M109="","",ROUNDDOWN($C109+$M109,2))</f>
+        <f>IF($M109="","",ROUNDUP($C109+$M109,2))</f>
       </c>
       <c r="O109" s="120" t="str">
-        <f>IF($N109="","",ROUNDDOWN(ROUNDDOWN($N109,2)*$E109,3))</f>
+        <f>IF($N109="","",ROUNDUP(ROUNDUP($N109,2)*$E109,3))</f>
       </c>
       <c r="P109" s="121" t="str">
         <f>IF($L109="","",$I109*$L109)</f>
@@ -7077,10 +7078,10 @@
         <f>IF($L110="","",$C110*$L110)</f>
       </c>
       <c r="N110" s="119" t="str">
-        <f>IF($M110="","",ROUNDDOWN($C110+$M110,2))</f>
+        <f>IF($M110="","",ROUNDUP($C110+$M110,2))</f>
       </c>
       <c r="O110" s="120" t="str">
-        <f>IF($N110="","",ROUNDDOWN(ROUNDDOWN($N110,2)*$E110,3))</f>
+        <f>IF($N110="","",ROUNDUP(ROUNDUP($N110,2)*$E110,3))</f>
       </c>
       <c r="P110" s="121" t="str">
         <f>IF($L110="","",$I110*$L110)</f>
@@ -7133,10 +7134,10 @@
         <f>IF($L111="","",$C111*$L111)</f>
       </c>
       <c r="N111" s="119" t="str">
-        <f>IF($M111="","",ROUNDDOWN($C111+$M111,2))</f>
+        <f>IF($M111="","",ROUNDUP($C111+$M111,2))</f>
       </c>
       <c r="O111" s="120" t="str">
-        <f>IF($N111="","",ROUNDDOWN(ROUNDDOWN($N111,2)*$E111,3))</f>
+        <f>IF($N111="","",ROUNDUP(ROUNDUP($N111,2)*$E111,3))</f>
       </c>
       <c r="P111" s="121" t="str">
         <f>IF($L111="","",$I111*$L111)</f>
@@ -7189,10 +7190,10 @@
         <f>IF($L112="","",$C112*$L112)</f>
       </c>
       <c r="N112" s="119" t="str">
-        <f>IF($M112="","",ROUNDDOWN($C112+$M112,2))</f>
+        <f>IF($M112="","",ROUNDUP($C112+$M112,2))</f>
       </c>
       <c r="O112" s="120" t="str">
-        <f>IF($N112="","",ROUNDDOWN(ROUNDDOWN($N112,2)*$E112,3))</f>
+        <f>IF($N112="","",ROUNDUP(ROUNDUP($N112,2)*$E112,3))</f>
       </c>
       <c r="P112" s="121" t="str">
         <f>IF($L112="","",$I112*$L112)</f>
@@ -7245,10 +7246,10 @@
         <f>IF($L113="","",$C113*$L113)</f>
       </c>
       <c r="N113" s="119" t="str">
-        <f>IF($M113="","",ROUNDDOWN($C113+$M113,2))</f>
+        <f>IF($M113="","",ROUNDUP($C113+$M113,2))</f>
       </c>
       <c r="O113" s="120" t="str">
-        <f>IF($N113="","",ROUNDDOWN(ROUNDDOWN($N113,2)*$E113,3))</f>
+        <f>IF($N113="","",ROUNDUP(ROUNDUP($N113,2)*$E113,3))</f>
       </c>
       <c r="P113" s="121" t="str">
         <f>IF($L113="","",$I113*$L113)</f>
@@ -7301,10 +7302,10 @@
         <f>IF($L114="","",$C114*$L114)</f>
       </c>
       <c r="N114" s="119" t="str">
-        <f>IF($M114="","",ROUNDDOWN($C114+$M114,2))</f>
+        <f>IF($M114="","",ROUNDUP($C114+$M114,2))</f>
       </c>
       <c r="O114" s="120" t="str">
-        <f>IF($N114="","",ROUNDDOWN(ROUNDDOWN($N114,2)*$E114,3))</f>
+        <f>IF($N114="","",ROUNDUP(ROUNDUP($N114,2)*$E114,3))</f>
       </c>
       <c r="P114" s="121" t="str">
         <f>IF($L114="","",$I114*$L114)</f>
@@ -7358,10 +7359,10 @@
         <f>IF($L115="","",$C115*$L115)</f>
       </c>
       <c r="N115" s="119" t="str">
-        <f>IF($M115="","",ROUNDDOWN($C115+$M115,2))</f>
+        <f>IF($M115="","",ROUNDUP($C115+$M115,2))</f>
       </c>
       <c r="O115" s="120" t="str">
-        <f>IF($N115="","",ROUNDDOWN(ROUNDDOWN($N115,2)*$E115,3))</f>
+        <f>IF($N115="","",ROUNDUP(ROUNDUP($N115,2)*$E115,3))</f>
       </c>
       <c r="P115" s="121" t="str">
         <f>IF($L115="","",$I115*$L115)</f>
@@ -7414,10 +7415,10 @@
         <f>IF($L116="","",$C116*$L116)</f>
       </c>
       <c r="N116" s="119" t="str">
-        <f>IF($M116="","",ROUNDDOWN($C116+$M116,2))</f>
+        <f>IF($M116="","",ROUNDUP($C116+$M116,2))</f>
       </c>
       <c r="O116" s="120" t="str">
-        <f>IF($N116="","",ROUNDDOWN(ROUNDDOWN($N116,2)*$E116,3))</f>
+        <f>IF($N116="","",ROUNDUP(ROUNDUP($N116,2)*$E116,3))</f>
       </c>
       <c r="P116" s="121" t="str">
         <f>IF($L116="","",$I116*$L116)</f>
@@ -7470,10 +7471,10 @@
         <f>IF($L117="","",$C117*$L117)</f>
       </c>
       <c r="N117" s="119" t="str">
-        <f>IF($M117="","",ROUNDDOWN($C117+$M117,2))</f>
+        <f>IF($M117="","",ROUNDUP($C117+$M117,2))</f>
       </c>
       <c r="O117" s="120" t="str">
-        <f>IF($N117="","",ROUNDDOWN(ROUNDDOWN($N117,2)*$E117,3))</f>
+        <f>IF($N117="","",ROUNDUP(ROUNDUP($N117,2)*$E117,3))</f>
       </c>
       <c r="P117" s="121" t="str">
         <f>IF($L117="","",$I117*$L117)</f>
@@ -7527,10 +7528,10 @@
         <f>IF($L118="","",$C118*$L118)</f>
       </c>
       <c r="N118" s="119" t="str">
-        <f>IF($M118="","",ROUNDDOWN($C118+$M118,2))</f>
+        <f>IF($M118="","",ROUNDUP($C118+$M118,2))</f>
       </c>
       <c r="O118" s="120" t="str">
-        <f>IF($N118="","",ROUNDDOWN(ROUNDDOWN($N118,2)*$E118,3))</f>
+        <f>IF($N118="","",ROUNDUP(ROUNDUP($N118,2)*$E118,3))</f>
       </c>
       <c r="P118" s="121" t="str">
         <f>IF($L118="","",$I118*$L118)</f>
@@ -7584,10 +7585,10 @@
         <f>IF($L119="","",$C119*$L119)</f>
       </c>
       <c r="N119" s="119" t="str">
-        <f>IF($M119="","",ROUNDDOWN($C119+$M119,2))</f>
+        <f>IF($M119="","",ROUNDUP($C119+$M119,2))</f>
       </c>
       <c r="O119" s="120" t="str">
-        <f>IF($N119="","",ROUNDDOWN(ROUNDDOWN($N119,2)*$E119,3))</f>
+        <f>IF($N119="","",ROUNDUP(ROUNDUP($N119,2)*$E119,3))</f>
       </c>
       <c r="P119" s="121" t="str">
         <f>IF($L119="","",$I119*$L119)</f>
@@ -7640,10 +7641,10 @@
         <f>IF($L120="","",$C120*$L120)</f>
       </c>
       <c r="N120" s="119" t="str">
-        <f>IF($M120="","",ROUNDDOWN($C120+$M120,2))</f>
+        <f>IF($M120="","",ROUNDUP($C120+$M120,2))</f>
       </c>
       <c r="O120" s="120" t="str">
-        <f>IF($N120="","",ROUNDDOWN(ROUNDDOWN($N120,2)*$E120,3))</f>
+        <f>IF($N120="","",ROUNDUP(ROUNDUP($N120,2)*$E120,3))</f>
       </c>
       <c r="P120" s="121" t="str">
         <f>IF($L120="","",$I120*$L120)</f>
@@ -7694,10 +7695,10 @@
         <f>IF($L121="","",$C121*$L121)</f>
       </c>
       <c r="N121" s="119" t="str">
-        <f>IF($M121="","",ROUNDDOWN($C121+$M121,2))</f>
+        <f>IF($M121="","",ROUNDUP($C121+$M121,2))</f>
       </c>
       <c r="O121" s="120" t="str">
-        <f>IF($N121="","",ROUNDDOWN(ROUNDDOWN($N121,2)*$E121,3))</f>
+        <f>IF($N121="","",ROUNDUP(ROUNDUP($N121,2)*$E121,3))</f>
       </c>
       <c r="P121" s="121" t="str">
         <f>IF($L121="","",$I121*$L121)</f>
@@ -7748,10 +7749,10 @@
         <f>IF($L122="","",$C122*$L122)</f>
       </c>
       <c r="N122" s="119" t="str">
-        <f>IF($M122="","",ROUNDDOWN($C122+$M122,2))</f>
+        <f>IF($M122="","",ROUNDUP($C122+$M122,2))</f>
       </c>
       <c r="O122" s="120" t="str">
-        <f>IF($N122="","",ROUNDDOWN(ROUNDDOWN($N122,2)*$E122,3))</f>
+        <f>IF($N122="","",ROUNDUP(ROUNDUP($N122,2)*$E122,3))</f>
       </c>
       <c r="P122" s="121" t="str">
         <f>IF($L122="","",$I122*$L122)</f>
@@ -7802,10 +7803,10 @@
         <f>IF($L123="","",$C123*$L123)</f>
       </c>
       <c r="N123" s="119" t="str">
-        <f>IF($M123="","",ROUNDDOWN($C123+$M123,2))</f>
+        <f>IF($M123="","",ROUNDUP($C123+$M123,2))</f>
       </c>
       <c r="O123" s="120" t="str">
-        <f>IF($N123="","",ROUNDDOWN(ROUNDDOWN($N123,2)*$E123,3))</f>
+        <f>IF($N123="","",ROUNDUP(ROUNDUP($N123,2)*$E123,3))</f>
       </c>
       <c r="P123" s="121" t="str">
         <f>IF($L123="","",$I123*$L123)</f>
@@ -7856,10 +7857,10 @@
         <f>IF($L124="","",$C124*$L124)</f>
       </c>
       <c r="N124" s="119" t="str">
-        <f>IF($M124="","",ROUNDDOWN($C124+$M124,2))</f>
+        <f>IF($M124="","",ROUNDUP($C124+$M124,2))</f>
       </c>
       <c r="O124" s="120" t="str">
-        <f>IF($N124="","",ROUNDDOWN(ROUNDDOWN($N124,2)*$E124,3))</f>
+        <f>IF($N124="","",ROUNDUP(ROUNDUP($N124,2)*$E124,3))</f>
       </c>
       <c r="P124" s="121" t="str">
         <f>IF($L124="","",$I124*$L124)</f>
@@ -7910,10 +7911,10 @@
         <f>IF($L125="","",$C125*$L125)</f>
       </c>
       <c r="N125" s="119" t="str">
-        <f>IF($M125="","",ROUNDDOWN($C125+$M125,2))</f>
+        <f>IF($M125="","",ROUNDUP($C125+$M125,2))</f>
       </c>
       <c r="O125" s="120" t="str">
-        <f>IF($N125="","",ROUNDDOWN(ROUNDDOWN($N125,2)*$E125,3))</f>
+        <f>IF($N125="","",ROUNDUP(ROUNDUP($N125,2)*$E125,3))</f>
       </c>
       <c r="P125" s="121" t="str">
         <f>IF($L125="","",$I125*$L125)</f>
@@ -7964,10 +7965,10 @@
         <f>IF($L126="","",$C126*$L126)</f>
       </c>
       <c r="N126" s="119" t="str">
-        <f>IF($M126="","",ROUNDDOWN($C126+$M126,2))</f>
+        <f>IF($M126="","",ROUNDUP($C126+$M126,2))</f>
       </c>
       <c r="O126" s="120" t="str">
-        <f>IF($N126="","",ROUNDDOWN(ROUNDDOWN($N126,2)*$E126,3))</f>
+        <f>IF($N126="","",ROUNDUP(ROUNDUP($N126,2)*$E126,3))</f>
       </c>
       <c r="P126" s="121" t="str">
         <f>IF($L126="","",$I126*$L126)</f>
@@ -8018,10 +8019,10 @@
         <f>IF($L127="","",$C127*$L127)</f>
       </c>
       <c r="N127" s="119" t="str">
-        <f>IF($M127="","",ROUNDDOWN($C127+$M127,2))</f>
+        <f>IF($M127="","",ROUNDUP($C127+$M127,2))</f>
       </c>
       <c r="O127" s="120" t="str">
-        <f>IF($N127="","",ROUNDDOWN(ROUNDDOWN($N127,2)*$E127,3))</f>
+        <f>IF($N127="","",ROUNDUP(ROUNDUP($N127,2)*$E127,3))</f>
       </c>
       <c r="P127" s="121" t="str">
         <f>IF($L127="","",$I127*$L127)</f>
@@ -8072,10 +8073,10 @@
         <f>IF($L128="","",$C128*$L128)</f>
       </c>
       <c r="N128" s="119" t="str">
-        <f>IF($M128="","",ROUNDDOWN($C128+$M128,2))</f>
+        <f>IF($M128="","",ROUNDUP($C128+$M128,2))</f>
       </c>
       <c r="O128" s="120" t="str">
-        <f>IF($N128="","",ROUNDDOWN(ROUNDDOWN($N128,2)*$E128,3))</f>
+        <f>IF($N128="","",ROUNDUP(ROUNDUP($N128,2)*$E128,3))</f>
       </c>
       <c r="P128" s="121" t="str">
         <f>IF($L128="","",$I128*$L128)</f>
@@ -8126,10 +8127,10 @@
         <f>IF($L129="","",$C129*$L129)</f>
       </c>
       <c r="N129" s="119" t="str">
-        <f>IF($M129="","",ROUNDDOWN($C129+$M129,2))</f>
+        <f>IF($M129="","",ROUNDUP($C129+$M129,2))</f>
       </c>
       <c r="O129" s="120" t="str">
-        <f>IF($N129="","",ROUNDDOWN(ROUNDDOWN($N129,2)*$E129,3))</f>
+        <f>IF($N129="","",ROUNDUP(ROUNDUP($N129,2)*$E129,3))</f>
       </c>
       <c r="P129" s="121" t="str">
         <f>IF($L129="","",$I129*$L129)</f>
@@ -8180,10 +8181,10 @@
         <f>IF($L130="","",$C130*$L130)</f>
       </c>
       <c r="N130" s="119" t="str">
-        <f>IF($M130="","",ROUNDDOWN($C130+$M130,2))</f>
+        <f>IF($M130="","",ROUNDUP($C130+$M130,2))</f>
       </c>
       <c r="O130" s="120" t="str">
-        <f>IF($N130="","",ROUNDDOWN(ROUNDDOWN($N130,2)*$E130,3))</f>
+        <f>IF($N130="","",ROUNDUP(ROUNDUP($N130,2)*$E130,3))</f>
       </c>
       <c r="P130" s="121" t="str">
         <f>IF($L130="","",$I130*$L130)</f>
@@ -8234,10 +8235,10 @@
         <f>IF($L131="","",$C131*$L131)</f>
       </c>
       <c r="N131" s="119" t="str">
-        <f>IF($M131="","",ROUNDDOWN($C131+$M131,2))</f>
+        <f>IF($M131="","",ROUNDUP($C131+$M131,2))</f>
       </c>
       <c r="O131" s="120" t="str">
-        <f>IF($N131="","",ROUNDDOWN(ROUNDDOWN($N131,2)*$E131,3))</f>
+        <f>IF($N131="","",ROUNDUP(ROUNDUP($N131,2)*$E131,3))</f>
       </c>
       <c r="P131" s="121" t="str">
         <f>IF($L131="","",$I131*$L131)</f>
@@ -8288,10 +8289,10 @@
         <f>IF($L132="","",$C132*$L132)</f>
       </c>
       <c r="N132" s="119" t="str">
-        <f>IF($M132="","",ROUNDDOWN($C132+$M132,2))</f>
+        <f>IF($M132="","",ROUNDUP($C132+$M132,2))</f>
       </c>
       <c r="O132" s="120" t="str">
-        <f>IF($N132="","",ROUNDDOWN(ROUNDDOWN($N132,2)*$E132,3))</f>
+        <f>IF($N132="","",ROUNDUP(ROUNDUP($N132,2)*$E132,3))</f>
       </c>
       <c r="P132" s="121" t="str">
         <f>IF($L132="","",$I132*$L132)</f>
@@ -8342,10 +8343,10 @@
         <f>IF($L133="","",$C133*$L133)</f>
       </c>
       <c r="N133" s="119" t="str">
-        <f>IF($M133="","",ROUNDDOWN($C133+$M133,2))</f>
+        <f>IF($M133="","",ROUNDUP($C133+$M133,2))</f>
       </c>
       <c r="O133" s="120" t="str">
-        <f>IF($N133="","",ROUNDDOWN(ROUNDDOWN($N133,2)*$E133,3))</f>
+        <f>IF($N133="","",ROUNDUP(ROUNDUP($N133,2)*$E133,3))</f>
       </c>
       <c r="P133" s="121" t="str">
         <f>IF($L133="","",$I133*$L133)</f>
@@ -8396,10 +8397,10 @@
         <f>IF($L134="","",$C134*$L134)</f>
       </c>
       <c r="N134" s="119" t="str">
-        <f>IF($M134="","",ROUNDDOWN($C134+$M134,2))</f>
+        <f>IF($M134="","",ROUNDUP($C134+$M134,2))</f>
       </c>
       <c r="O134" s="120" t="str">
-        <f>IF($N134="","",ROUNDDOWN(ROUNDDOWN($N134,2)*$E134,3))</f>
+        <f>IF($N134="","",ROUNDUP(ROUNDUP($N134,2)*$E134,3))</f>
       </c>
       <c r="P134" s="121" t="str">
         <f>IF($L134="","",$I134*$L134)</f>
@@ -8450,10 +8451,10 @@
         <f>IF($L135="","",$C135*$L135)</f>
       </c>
       <c r="N135" s="119" t="str">
-        <f>IF($M135="","",ROUNDDOWN($C135+$M135,2))</f>
+        <f>IF($M135="","",ROUNDUP($C135+$M135,2))</f>
       </c>
       <c r="O135" s="120" t="str">
-        <f>IF($N135="","",ROUNDDOWN(ROUNDDOWN($N135,2)*$E135,3))</f>
+        <f>IF($N135="","",ROUNDUP(ROUNDUP($N135,2)*$E135,3))</f>
       </c>
       <c r="P135" s="121" t="str">
         <f>IF($L135="","",$I135*$L135)</f>
@@ -8504,10 +8505,10 @@
         <f>IF($L136="","",$C136*$L136)</f>
       </c>
       <c r="N136" s="119" t="str">
-        <f>IF($M136="","",ROUNDDOWN($C136+$M136,2))</f>
+        <f>IF($M136="","",ROUNDUP($C136+$M136,2))</f>
       </c>
       <c r="O136" s="120" t="str">
-        <f>IF($N136="","",ROUNDDOWN(ROUNDDOWN($N136,2)*$E136,3))</f>
+        <f>IF($N136="","",ROUNDUP(ROUNDUP($N136,2)*$E136,3))</f>
       </c>
       <c r="P136" s="121" t="str">
         <f>IF($L136="","",$I136*$L136)</f>
@@ -8558,10 +8559,10 @@
         <f>IF($L137="","",$C137*$L137)</f>
       </c>
       <c r="N137" s="119" t="str">
-        <f>IF($M137="","",ROUNDDOWN($C137+$M137,2))</f>
+        <f>IF($M137="","",ROUNDUP($C137+$M137,2))</f>
       </c>
       <c r="O137" s="120" t="str">
-        <f>IF($N137="","",ROUNDDOWN(ROUNDDOWN($N137,2)*$E137,3))</f>
+        <f>IF($N137="","",ROUNDUP(ROUNDUP($N137,2)*$E137,3))</f>
       </c>
       <c r="P137" s="121" t="str">
         <f>IF($L137="","",$I137*$L137)</f>
@@ -8612,10 +8613,10 @@
         <f>IF($L138="","",$C138*$L138)</f>
       </c>
       <c r="N138" s="119" t="str">
-        <f>IF($M138="","",ROUNDDOWN($C138+$M138,2))</f>
+        <f>IF($M138="","",ROUNDUP($C138+$M138,2))</f>
       </c>
       <c r="O138" s="120" t="str">
-        <f>IF($N138="","",ROUNDDOWN(ROUNDDOWN($N138,2)*$E138,3))</f>
+        <f>IF($N138="","",ROUNDUP(ROUNDUP($N138,2)*$E138,3))</f>
       </c>
       <c r="P138" s="121" t="str">
         <f>IF($L138="","",$I138*$L138)</f>
@@ -8666,10 +8667,10 @@
         <f>IF($L139="","",$C139*$L139)</f>
       </c>
       <c r="N139" s="119" t="str">
-        <f>IF($M139="","",ROUNDDOWN($C139+$M139,2))</f>
+        <f>IF($M139="","",ROUNDUP($C139+$M139,2))</f>
       </c>
       <c r="O139" s="120" t="str">
-        <f>IF($N139="","",ROUNDDOWN(ROUNDDOWN($N139,2)*$E139,3))</f>
+        <f>IF($N139="","",ROUNDUP(ROUNDUP($N139,2)*$E139,3))</f>
       </c>
       <c r="P139" s="121" t="str">
         <f>IF($L139="","",$I139*$L139)</f>
@@ -8720,10 +8721,10 @@
         <f>IF($L140="","",$C140*$L140)</f>
       </c>
       <c r="N140" s="119" t="str">
-        <f>IF($M140="","",ROUNDDOWN($C140+$M140,2))</f>
+        <f>IF($M140="","",ROUNDUP($C140+$M140,2))</f>
       </c>
       <c r="O140" s="120" t="str">
-        <f>IF($N140="","",ROUNDDOWN(ROUNDDOWN($N140,2)*$E140,3))</f>
+        <f>IF($N140="","",ROUNDUP(ROUNDUP($N140,2)*$E140,3))</f>
       </c>
       <c r="P140" s="121" t="str">
         <f>IF($L140="","",$I140*$L140)</f>
@@ -8774,10 +8775,10 @@
         <f>IF($L141="","",$C141*$L141)</f>
       </c>
       <c r="N141" s="119" t="str">
-        <f>IF($M141="","",ROUNDDOWN($C141+$M141,2))</f>
+        <f>IF($M141="","",ROUNDUP($C141+$M141,2))</f>
       </c>
       <c r="O141" s="120" t="str">
-        <f>IF($N141="","",ROUNDDOWN(ROUNDDOWN($N141,2)*$E141,3))</f>
+        <f>IF($N141="","",ROUNDUP(ROUNDUP($N141,2)*$E141,3))</f>
       </c>
       <c r="P141" s="121" t="str">
         <f>IF($L141="","",$I141*$L141)</f>
@@ -8828,10 +8829,10 @@
         <f>IF($L142="","",$C142*$L142)</f>
       </c>
       <c r="N142" s="119" t="str">
-        <f>IF($M142="","",ROUNDDOWN($C142+$M142,2))</f>
+        <f>IF($M142="","",ROUNDUP($C142+$M142,2))</f>
       </c>
       <c r="O142" s="120" t="str">
-        <f>IF($N142="","",ROUNDDOWN(ROUNDDOWN($N142,2)*$E142,3))</f>
+        <f>IF($N142="","",ROUNDUP(ROUNDUP($N142,2)*$E142,3))</f>
       </c>
       <c r="P142" s="121" t="str">
         <f>IF($L142="","",$I142*$L142)</f>
@@ -8882,10 +8883,10 @@
         <f>IF($L143="","",$C143*$L143)</f>
       </c>
       <c r="N143" s="119" t="str">
-        <f>IF($M143="","",ROUNDDOWN($C143+$M143,2))</f>
+        <f>IF($M143="","",ROUNDUP($C143+$M143,2))</f>
       </c>
       <c r="O143" s="120" t="str">
-        <f>IF($N143="","",ROUNDDOWN(ROUNDDOWN($N143,2)*$E143,3))</f>
+        <f>IF($N143="","",ROUNDUP(ROUNDUP($N143,2)*$E143,3))</f>
       </c>
       <c r="P143" s="121" t="str">
         <f>IF($L143="","",$I143*$L143)</f>
@@ -8936,10 +8937,10 @@
         <f>IF($L144="","",$C144*$L144)</f>
       </c>
       <c r="N144" s="119" t="str">
-        <f>IF($M144="","",ROUNDDOWN($C144+$M144,2))</f>
+        <f>IF($M144="","",ROUNDUP($C144+$M144,2))</f>
       </c>
       <c r="O144" s="120" t="str">
-        <f>IF($N144="","",ROUNDDOWN(ROUNDDOWN($N144,2)*$E144,3))</f>
+        <f>IF($N144="","",ROUNDUP(ROUNDUP($N144,2)*$E144,3))</f>
       </c>
       <c r="P144" s="121" t="str">
         <f>IF($L144="","",$I144*$L144)</f>
@@ -8990,10 +8991,10 @@
         <f>IF($L145="","",$C145*$L145)</f>
       </c>
       <c r="N145" s="119" t="str">
-        <f>IF($M145="","",ROUNDDOWN($C145+$M145,2))</f>
+        <f>IF($M145="","",ROUNDUP($C145+$M145,2))</f>
       </c>
       <c r="O145" s="120" t="str">
-        <f>IF($N145="","",ROUNDDOWN(ROUNDDOWN($N145,2)*$E145,3))</f>
+        <f>IF($N145="","",ROUNDUP(ROUNDUP($N145,2)*$E145,3))</f>
       </c>
       <c r="P145" s="121" t="str">
         <f>IF($L145="","",$I145*$L145)</f>
@@ -9044,10 +9045,10 @@
         <f>IF($L146="","",$C146*$L146)</f>
       </c>
       <c r="N146" s="119" t="str">
-        <f>IF($M146="","",ROUNDDOWN($C146+$M146,2))</f>
+        <f>IF($M146="","",ROUNDUP($C146+$M146,2))</f>
       </c>
       <c r="O146" s="120" t="str">
-        <f>IF($N146="","",ROUNDDOWN(ROUNDDOWN($N146,2)*$E146,3))</f>
+        <f>IF($N146="","",ROUNDUP(ROUNDUP($N146,2)*$E146,3))</f>
       </c>
       <c r="P146" s="121" t="str">
         <f>IF($L146="","",$I146*$L146)</f>
@@ -9098,10 +9099,10 @@
         <f>IF($L147="","",$C147*$L147)</f>
       </c>
       <c r="N147" s="119" t="str">
-        <f>IF($M147="","",ROUNDDOWN($C147+$M147,2))</f>
+        <f>IF($M147="","",ROUNDUP($C147+$M147,2))</f>
       </c>
       <c r="O147" s="120" t="str">
-        <f>IF($N147="","",ROUNDDOWN(ROUNDDOWN($N147,2)*$E147,3))</f>
+        <f>IF($N147="","",ROUNDUP(ROUNDUP($N147,2)*$E147,3))</f>
       </c>
       <c r="P147" s="121" t="str">
         <f>IF($L147="","",$I147*$L147)</f>
@@ -9152,10 +9153,10 @@
         <f>IF($L148="","",$C148*$L148)</f>
       </c>
       <c r="N148" s="119" t="str">
-        <f>IF($M148="","",ROUNDDOWN($C148+$M148,2))</f>
+        <f>IF($M148="","",ROUNDUP($C148+$M148,2))</f>
       </c>
       <c r="O148" s="120" t="str">
-        <f>IF($N148="","",ROUNDDOWN(ROUNDDOWN($N148,2)*$E148,3))</f>
+        <f>IF($N148="","",ROUNDUP(ROUNDUP($N148,2)*$E148,3))</f>
       </c>
       <c r="P148" s="121" t="str">
         <f>IF($L148="","",$I148*$L148)</f>
@@ -9206,10 +9207,10 @@
         <f>IF($L149="","",$C149*$L149)</f>
       </c>
       <c r="N149" s="119" t="str">
-        <f>IF($M149="","",ROUNDDOWN($C149+$M149,2))</f>
+        <f>IF($M149="","",ROUNDUP($C149+$M149,2))</f>
       </c>
       <c r="O149" s="120" t="str">
-        <f>IF($N149="","",ROUNDDOWN(ROUNDDOWN($N149,2)*$E149,3))</f>
+        <f>IF($N149="","",ROUNDUP(ROUNDUP($N149,2)*$E149,3))</f>
       </c>
       <c r="P149" s="121" t="str">
         <f>IF($L149="","",$I149*$L149)</f>
@@ -9260,10 +9261,10 @@
         <f>IF($L150="","",$C150*$L150)</f>
       </c>
       <c r="N150" s="119" t="str">
-        <f>IF($M150="","",ROUNDDOWN($C150+$M150,2))</f>
+        <f>IF($M150="","",ROUNDUP($C150+$M150,2))</f>
       </c>
       <c r="O150" s="120" t="str">
-        <f>IF($N150="","",ROUNDDOWN(ROUNDDOWN($N150,2)*$E150,3))</f>
+        <f>IF($N150="","",ROUNDUP(ROUNDUP($N150,2)*$E150,3))</f>
       </c>
       <c r="P150" s="121" t="str">
         <f>IF($L150="","",$I150*$L150)</f>
@@ -9314,10 +9315,10 @@
         <f>IF($L151="","",$C151*$L151)</f>
       </c>
       <c r="N151" s="119" t="str">
-        <f>IF($M151="","",ROUNDDOWN($C151+$M151,2))</f>
+        <f>IF($M151="","",ROUNDUP($C151+$M151,2))</f>
       </c>
       <c r="O151" s="120" t="str">
-        <f>IF($N151="","",ROUNDDOWN(ROUNDDOWN($N151,2)*$E151,3))</f>
+        <f>IF($N151="","",ROUNDUP(ROUNDUP($N151,2)*$E151,3))</f>
       </c>
       <c r="P151" s="121" t="str">
         <f>IF($L151="","",$I151*$L151)</f>
@@ -9368,10 +9369,10 @@
         <f>IF($L152="","",$C152*$L152)</f>
       </c>
       <c r="N152" s="119" t="str">
-        <f>IF($M152="","",ROUNDDOWN($C152+$M152,2))</f>
+        <f>IF($M152="","",ROUNDUP($C152+$M152,2))</f>
       </c>
       <c r="O152" s="120" t="str">
-        <f>IF($N152="","",ROUNDDOWN(ROUNDDOWN($N152,2)*$E152,3))</f>
+        <f>IF($N152="","",ROUNDUP(ROUNDUP($N152,2)*$E152,3))</f>
       </c>
       <c r="P152" s="121" t="str">
         <f>IF($L152="","",$I152*$L152)</f>
@@ -9422,10 +9423,10 @@
         <f>IF($L153="","",$C153*$L153)</f>
       </c>
       <c r="N153" s="119" t="str">
-        <f>IF($M153="","",ROUNDDOWN($C153+$M153,2))</f>
+        <f>IF($M153="","",ROUNDUP($C153+$M153,2))</f>
       </c>
       <c r="O153" s="120" t="str">
-        <f>IF($N153="","",ROUNDDOWN(ROUNDDOWN($N153,2)*$E153,3))</f>
+        <f>IF($N153="","",ROUNDUP(ROUNDUP($N153,2)*$E153,3))</f>
       </c>
       <c r="P153" s="121" t="str">
         <f>IF($L153="","",$I153*$L153)</f>
@@ -9476,10 +9477,10 @@
         <f>IF($L154="","",$C154*$L154)</f>
       </c>
       <c r="N154" s="119" t="str">
-        <f>IF($M154="","",ROUNDDOWN($C154+$M154,2))</f>
+        <f>IF($M154="","",ROUNDUP($C154+$M154,2))</f>
       </c>
       <c r="O154" s="120" t="str">
-        <f>IF($N154="","",ROUNDDOWN(ROUNDDOWN($N154,2)*$E154,3))</f>
+        <f>IF($N154="","",ROUNDUP(ROUNDUP($N154,2)*$E154,3))</f>
       </c>
       <c r="P154" s="121" t="str">
         <f>IF($L154="","",$I154*$L154)</f>
@@ -9530,10 +9531,10 @@
         <f>IF($L155="","",$C155*$L155)</f>
       </c>
       <c r="N155" s="119" t="str">
-        <f>IF($M155="","",ROUNDDOWN($C155+$M155,2))</f>
+        <f>IF($M155="","",ROUNDUP($C155+$M155,2))</f>
       </c>
       <c r="O155" s="120" t="str">
-        <f>IF($N155="","",ROUNDDOWN(ROUNDDOWN($N155,2)*$E155,3))</f>
+        <f>IF($N155="","",ROUNDUP(ROUNDUP($N155,2)*$E155,3))</f>
       </c>
       <c r="P155" s="121" t="str">
         <f>IF($L155="","",$I155*$L155)</f>
@@ -9584,10 +9585,10 @@
         <f>IF($L156="","",$C156*$L156)</f>
       </c>
       <c r="N156" s="119" t="str">
-        <f>IF($M156="","",ROUNDDOWN($C156+$M156,2))</f>
+        <f>IF($M156="","",ROUNDUP($C156+$M156,2))</f>
       </c>
       <c r="O156" s="120" t="str">
-        <f>IF($N156="","",ROUNDDOWN(ROUNDDOWN($N156,2)*$E156,3))</f>
+        <f>IF($N156="","",ROUNDUP(ROUNDUP($N156,2)*$E156,3))</f>
       </c>
       <c r="P156" s="121" t="str">
         <f>IF($L156="","",$I156*$L156)</f>
@@ -9638,10 +9639,10 @@
         <f>IF($L157="","",$C157*$L157)</f>
       </c>
       <c r="N157" s="119" t="str">
-        <f>IF($M157="","",ROUNDDOWN($C157+$M157,2))</f>
+        <f>IF($M157="","",ROUNDUP($C157+$M157,2))</f>
       </c>
       <c r="O157" s="120" t="str">
-        <f>IF($N157="","",ROUNDDOWN(ROUNDDOWN($N157,2)*$E157,3))</f>
+        <f>IF($N157="","",ROUNDUP(ROUNDUP($N157,2)*$E157,3))</f>
       </c>
       <c r="P157" s="121" t="str">
         <f>IF($L157="","",$I157*$L157)</f>
@@ -9692,10 +9693,10 @@
         <f>IF($L158="","",$C158*$L158)</f>
       </c>
       <c r="N158" s="119" t="str">
-        <f>IF($M158="","",ROUNDDOWN($C158+$M158,2))</f>
+        <f>IF($M158="","",ROUNDUP($C158+$M158,2))</f>
       </c>
       <c r="O158" s="120" t="str">
-        <f>IF($N158="","",ROUNDDOWN(ROUNDDOWN($N158,2)*$E158,3))</f>
+        <f>IF($N158="","",ROUNDUP(ROUNDUP($N158,2)*$E158,3))</f>
       </c>
       <c r="P158" s="121" t="str">
         <f>IF($L158="","",$I158*$L158)</f>
@@ -9746,10 +9747,10 @@
         <f>IF($L159="","",$C159*$L159)</f>
       </c>
       <c r="N159" s="119" t="str">
-        <f>IF($M159="","",ROUNDDOWN($C159+$M159,2))</f>
+        <f>IF($M159="","",ROUNDUP($C159+$M159,2))</f>
       </c>
       <c r="O159" s="120" t="str">
-        <f>IF($N159="","",ROUNDDOWN(ROUNDDOWN($N159,2)*$E159,3))</f>
+        <f>IF($N159="","",ROUNDUP(ROUNDUP($N159,2)*$E159,3))</f>
       </c>
       <c r="P159" s="121" t="str">
         <f>IF($L159="","",$I159*$L159)</f>
@@ -9800,10 +9801,10 @@
         <f>IF($L160="","",$C160*$L160)</f>
       </c>
       <c r="N160" s="119" t="str">
-        <f>IF($M160="","",ROUNDDOWN($C160+$M160,2))</f>
+        <f>IF($M160="","",ROUNDUP($C160+$M160,2))</f>
       </c>
       <c r="O160" s="120" t="str">
-        <f>IF($N160="","",ROUNDDOWN(ROUNDDOWN($N160,2)*$E160,3))</f>
+        <f>IF($N160="","",ROUNDUP(ROUNDUP($N160,2)*$E160,3))</f>
       </c>
       <c r="P160" s="121" t="str">
         <f>IF($L160="","",$I160*$L160)</f>
@@ -9854,10 +9855,10 @@
         <f>IF($L161="","",$C161*$L161)</f>
       </c>
       <c r="N161" s="119" t="str">
-        <f>IF($M161="","",ROUNDDOWN($C161+$M161,2))</f>
+        <f>IF($M161="","",ROUNDUP($C161+$M161,2))</f>
       </c>
       <c r="O161" s="120" t="str">
-        <f>IF($N161="","",ROUNDDOWN(ROUNDDOWN($N161,2)*$E161,3))</f>
+        <f>IF($N161="","",ROUNDUP(ROUNDUP($N161,2)*$E161,3))</f>
       </c>
       <c r="P161" s="121" t="str">
         <f>IF($L161="","",$I161*$L161)</f>
@@ -9908,10 +9909,10 @@
         <f>IF($L162="","",$C162*$L162)</f>
       </c>
       <c r="N162" s="119" t="str">
-        <f>IF($M162="","",ROUNDDOWN($C162+$M162,2))</f>
+        <f>IF($M162="","",ROUNDUP($C162+$M162,2))</f>
       </c>
       <c r="O162" s="120" t="str">
-        <f>IF($N162="","",ROUNDDOWN(ROUNDDOWN($N162,2)*$E162,3))</f>
+        <f>IF($N162="","",ROUNDUP(ROUNDUP($N162,2)*$E162,3))</f>
       </c>
       <c r="P162" s="121" t="str">
         <f>IF($L162="","",$I162*$L162)</f>
@@ -9962,10 +9963,10 @@
         <f>IF($L163="","",$C163*$L163)</f>
       </c>
       <c r="N163" s="119" t="str">
-        <f>IF($M163="","",ROUNDDOWN($C163+$M163,2))</f>
+        <f>IF($M163="","",ROUNDUP($C163+$M163,2))</f>
       </c>
       <c r="O163" s="120" t="str">
-        <f>IF($N163="","",ROUNDDOWN(ROUNDDOWN($N163,2)*$E163,3))</f>
+        <f>IF($N163="","",ROUNDUP(ROUNDUP($N163,2)*$E163,3))</f>
       </c>
       <c r="P163" s="121" t="str">
         <f>IF($L163="","",$I163*$L163)</f>
@@ -10016,10 +10017,10 @@
         <f>IF($L164="","",$C164*$L164)</f>
       </c>
       <c r="N164" s="119" t="str">
-        <f>IF($M164="","",ROUNDDOWN($C164+$M164,2))</f>
+        <f>IF($M164="","",ROUNDUP($C164+$M164,2))</f>
       </c>
       <c r="O164" s="120" t="str">
-        <f>IF($N164="","",ROUNDDOWN(ROUNDDOWN($N164,2)*$E164,3))</f>
+        <f>IF($N164="","",ROUNDUP(ROUNDUP($N164,2)*$E164,3))</f>
       </c>
       <c r="P164" s="121" t="str">
         <f>IF($L164="","",$I164*$L164)</f>
@@ -10070,10 +10071,10 @@
         <f>IF($L165="","",$C165*$L165)</f>
       </c>
       <c r="N165" s="119" t="str">
-        <f>IF($M165="","",ROUNDDOWN($C165+$M165,2))</f>
+        <f>IF($M165="","",ROUNDUP($C165+$M165,2))</f>
       </c>
       <c r="O165" s="120" t="str">
-        <f>IF($N165="","",ROUNDDOWN(ROUNDDOWN($N165,2)*$E165,3))</f>
+        <f>IF($N165="","",ROUNDUP(ROUNDUP($N165,2)*$E165,3))</f>
       </c>
       <c r="P165" s="121" t="str">
         <f>IF($L165="","",$I165*$L165)</f>
@@ -10124,10 +10125,10 @@
         <f>IF($L166="","",$C166*$L166)</f>
       </c>
       <c r="N166" s="119" t="str">
-        <f>IF($M166="","",ROUNDDOWN($C166+$M166,2))</f>
+        <f>IF($M166="","",ROUNDUP($C166+$M166,2))</f>
       </c>
       <c r="O166" s="120" t="str">
-        <f>IF($N166="","",ROUNDDOWN(ROUNDDOWN($N166,2)*$E166,3))</f>
+        <f>IF($N166="","",ROUNDUP(ROUNDUP($N166,2)*$E166,3))</f>
       </c>
       <c r="P166" s="121" t="str">
         <f>IF($L166="","",$I166*$L166)</f>
@@ -10178,10 +10179,10 @@
         <f>IF($L167="","",$C167*$L167)</f>
       </c>
       <c r="N167" s="119" t="str">
-        <f>IF($M167="","",ROUNDDOWN($C167+$M167,2))</f>
+        <f>IF($M167="","",ROUNDUP($C167+$M167,2))</f>
       </c>
       <c r="O167" s="120" t="str">
-        <f>IF($N167="","",ROUNDDOWN(ROUNDDOWN($N167,2)*$E167,3))</f>
+        <f>IF($N167="","",ROUNDUP(ROUNDUP($N167,2)*$E167,3))</f>
       </c>
       <c r="P167" s="121" t="str">
         <f>IF($L167="","",$I167*$L167)</f>
@@ -10232,10 +10233,10 @@
         <f>IF($L168="","",$C168*$L168)</f>
       </c>
       <c r="N168" s="119" t="str">
-        <f>IF($M168="","",ROUNDDOWN($C168+$M168,2))</f>
+        <f>IF($M168="","",ROUNDUP($C168+$M168,2))</f>
       </c>
       <c r="O168" s="120" t="str">
-        <f>IF($N168="","",ROUNDDOWN(ROUNDDOWN($N168,2)*$E168,3))</f>
+        <f>IF($N168="","",ROUNDUP(ROUNDUP($N168,2)*$E168,3))</f>
       </c>
       <c r="P168" s="121" t="str">
         <f>IF($L168="","",$I168*$L168)</f>
@@ -10286,10 +10287,10 @@
         <f>IF($L169="","",$C169*$L169)</f>
       </c>
       <c r="N169" s="119" t="str">
-        <f>IF($M169="","",ROUNDDOWN($C169+$M169,2))</f>
+        <f>IF($M169="","",ROUNDUP($C169+$M169,2))</f>
       </c>
       <c r="O169" s="120" t="str">
-        <f>IF($N169="","",ROUNDDOWN(ROUNDDOWN($N169,2)*$E169,3))</f>
+        <f>IF($N169="","",ROUNDUP(ROUNDUP($N169,2)*$E169,3))</f>
       </c>
       <c r="P169" s="121" t="str">
         <f>IF($L169="","",$I169*$L169)</f>
@@ -10340,10 +10341,10 @@
         <f>IF($L170="","",$C170*$L170)</f>
       </c>
       <c r="N170" s="119" t="str">
-        <f>IF($M170="","",ROUNDDOWN($C170+$M170,2))</f>
+        <f>IF($M170="","",ROUNDUP($C170+$M170,2))</f>
       </c>
       <c r="O170" s="120" t="str">
-        <f>IF($N170="","",ROUNDDOWN(ROUNDDOWN($N170,2)*$E170,3))</f>
+        <f>IF($N170="","",ROUNDUP(ROUNDUP($N170,2)*$E170,3))</f>
       </c>
       <c r="P170" s="121" t="str">
         <f>IF($L170="","",$I170*$L170)</f>
@@ -10394,10 +10395,10 @@
         <f>IF($L171="","",$C171*$L171)</f>
       </c>
       <c r="N171" s="119" t="str">
-        <f>IF($M171="","",ROUNDDOWN($C171+$M171,2))</f>
+        <f>IF($M171="","",ROUNDUP($C171+$M171,2))</f>
       </c>
       <c r="O171" s="120" t="str">
-        <f>IF($N171="","",ROUNDDOWN(ROUNDDOWN($N171,2)*$E171,3))</f>
+        <f>IF($N171="","",ROUNDUP(ROUNDUP($N171,2)*$E171,3))</f>
       </c>
       <c r="P171" s="121" t="str">
         <f>IF($L171="","",$I171*$L171)</f>
@@ -10448,10 +10449,10 @@
         <f>IF($L172="","",$C172*$L172)</f>
       </c>
       <c r="N172" s="119" t="str">
-        <f>IF($M172="","",ROUNDDOWN($C172+$M172,2))</f>
+        <f>IF($M172="","",ROUNDUP($C172+$M172,2))</f>
       </c>
       <c r="O172" s="120" t="str">
-        <f>IF($N172="","",ROUNDDOWN(ROUNDDOWN($N172,2)*$E172,3))</f>
+        <f>IF($N172="","",ROUNDUP(ROUNDUP($N172,2)*$E172,3))</f>
       </c>
       <c r="P172" s="121" t="str">
         <f>IF($L172="","",$I172*$L172)</f>
@@ -10502,10 +10503,10 @@
         <f>IF($L173="","",$C173*$L173)</f>
       </c>
       <c r="N173" s="119" t="str">
-        <f>IF($M173="","",ROUNDDOWN($C173+$M173,2))</f>
+        <f>IF($M173="","",ROUNDUP($C173+$M173,2))</f>
       </c>
       <c r="O173" s="120" t="str">
-        <f>IF($N173="","",ROUNDDOWN(ROUNDDOWN($N173,2)*$E173,3))</f>
+        <f>IF($N173="","",ROUNDUP(ROUNDUP($N173,2)*$E173,3))</f>
       </c>
       <c r="P173" s="121" t="str">
         <f>IF($L173="","",$I173*$L173)</f>
@@ -10556,10 +10557,10 @@
         <f>IF($L174="","",$C174*$L174)</f>
       </c>
       <c r="N174" s="119" t="str">
-        <f>IF($M174="","",ROUNDDOWN($C174+$M174,2))</f>
+        <f>IF($M174="","",ROUNDUP($C174+$M174,2))</f>
       </c>
       <c r="O174" s="120" t="str">
-        <f>IF($N174="","",ROUNDDOWN(ROUNDDOWN($N174,2)*$E174,3))</f>
+        <f>IF($N174="","",ROUNDUP(ROUNDUP($N174,2)*$E174,3))</f>
       </c>
       <c r="P174" s="121" t="str">
         <f>IF($L174="","",$I174*$L174)</f>
@@ -10610,10 +10611,10 @@
         <f>IF($L175="","",$C175*$L175)</f>
       </c>
       <c r="N175" s="119" t="str">
-        <f>IF($M175="","",ROUNDDOWN($C175+$M175,2))</f>
+        <f>IF($M175="","",ROUNDUP($C175+$M175,2))</f>
       </c>
       <c r="O175" s="120" t="str">
-        <f>IF($N175="","",ROUNDDOWN(ROUNDDOWN($N175,2)*$E175,3))</f>
+        <f>IF($N175="","",ROUNDUP(ROUNDUP($N175,2)*$E175,3))</f>
       </c>
       <c r="P175" s="121" t="str">
         <f>IF($L175="","",$I175*$L175)</f>
@@ -10664,10 +10665,10 @@
         <f>IF($L176="","",$C176*$L176)</f>
       </c>
       <c r="N176" s="119" t="str">
-        <f>IF($M176="","",ROUNDDOWN($C176+$M176,2))</f>
+        <f>IF($M176="","",ROUNDUP($C176+$M176,2))</f>
       </c>
       <c r="O176" s="120" t="str">
-        <f>IF($N176="","",ROUNDDOWN(ROUNDDOWN($N176,2)*$E176,3))</f>
+        <f>IF($N176="","",ROUNDUP(ROUNDUP($N176,2)*$E176,3))</f>
       </c>
       <c r="P176" s="121" t="str">
         <f>IF($L176="","",$I176*$L176)</f>
@@ -10718,10 +10719,10 @@
         <f>IF($L177="","",$C177*$L177)</f>
       </c>
       <c r="N177" s="119" t="str">
-        <f>IF($M177="","",ROUNDDOWN($C177+$M177,2))</f>
+        <f>IF($M177="","",ROUNDUP($C177+$M177,2))</f>
       </c>
       <c r="O177" s="120" t="str">
-        <f>IF($N177="","",ROUNDDOWN(ROUNDDOWN($N177,2)*$E177,3))</f>
+        <f>IF($N177="","",ROUNDUP(ROUNDUP($N177,2)*$E177,3))</f>
       </c>
       <c r="P177" s="121" t="str">
         <f>IF($L177="","",$I177*$L177)</f>
@@ -10772,10 +10773,10 @@
         <f>IF($L178="","",$C178*$L178)</f>
       </c>
       <c r="N178" s="119" t="str">
-        <f>IF($M178="","",ROUNDDOWN($C178+$M178,2))</f>
+        <f>IF($M178="","",ROUNDUP($C178+$M178,2))</f>
       </c>
       <c r="O178" s="120" t="str">
-        <f>IF($N178="","",ROUNDDOWN(ROUNDDOWN($N178,2)*$E178,3))</f>
+        <f>IF($N178="","",ROUNDUP(ROUNDUP($N178,2)*$E178,3))</f>
       </c>
       <c r="P178" s="121" t="str">
         <f>IF($L178="","",$I178*$L178)</f>
@@ -10826,10 +10827,10 @@
         <f>IF($L179="","",$C179*$L179)</f>
       </c>
       <c r="N179" s="119" t="str">
-        <f>IF($M179="","",ROUNDDOWN($C179+$M179,2))</f>
+        <f>IF($M179="","",ROUNDUP($C179+$M179,2))</f>
       </c>
       <c r="O179" s="120" t="str">
-        <f>IF($N179="","",ROUNDDOWN(ROUNDDOWN($N179,2)*$E179,3))</f>
+        <f>IF($N179="","",ROUNDUP(ROUNDUP($N179,2)*$E179,3))</f>
       </c>
       <c r="P179" s="121" t="str">
         <f>IF($L179="","",$I179*$L179)</f>
@@ -10880,10 +10881,10 @@
         <f>IF($L180="","",$C180*$L180)</f>
       </c>
       <c r="N180" s="119" t="str">
-        <f>IF($M180="","",ROUNDDOWN($C180+$M180,2))</f>
+        <f>IF($M180="","",ROUNDUP($C180+$M180,2))</f>
       </c>
       <c r="O180" s="120" t="str">
-        <f>IF($N180="","",ROUNDDOWN(ROUNDDOWN($N180,2)*$E180,3))</f>
+        <f>IF($N180="","",ROUNDUP(ROUNDUP($N180,2)*$E180,3))</f>
       </c>
       <c r="P180" s="121" t="str">
         <f>IF($L180="","",$I180*$L180)</f>
@@ -10934,10 +10935,10 @@
         <f>IF($L181="","",$C181*$L181)</f>
       </c>
       <c r="N181" s="119" t="str">
-        <f>IF($M181="","",ROUNDDOWN($C181+$M181,2))</f>
+        <f>IF($M181="","",ROUNDUP($C181+$M181,2))</f>
       </c>
       <c r="O181" s="120" t="str">
-        <f>IF($N181="","",ROUNDDOWN(ROUNDDOWN($N181,2)*$E181,3))</f>
+        <f>IF($N181="","",ROUNDUP(ROUNDUP($N181,2)*$E181,3))</f>
       </c>
       <c r="P181" s="121" t="str">
         <f>IF($L181="","",$I181*$L181)</f>
@@ -10988,10 +10989,10 @@
         <f>IF($L182="","",$C182*$L182)</f>
       </c>
       <c r="N182" s="119" t="str">
-        <f>IF($M182="","",ROUNDDOWN($C182+$M182,2))</f>
+        <f>IF($M182="","",ROUNDUP($C182+$M182,2))</f>
       </c>
       <c r="O182" s="120" t="str">
-        <f>IF($N182="","",ROUNDDOWN(ROUNDDOWN($N182,2)*$E182,3))</f>
+        <f>IF($N182="","",ROUNDUP(ROUNDUP($N182,2)*$E182,3))</f>
       </c>
       <c r="P182" s="121" t="str">
         <f>IF($L182="","",$I182*$L182)</f>
@@ -11042,10 +11043,10 @@
         <f>IF($L183="","",$C183*$L183)</f>
       </c>
       <c r="N183" s="119" t="str">
-        <f>IF($M183="","",ROUNDDOWN($C183+$M183,2))</f>
+        <f>IF($M183="","",ROUNDUP($C183+$M183,2))</f>
       </c>
       <c r="O183" s="120" t="str">
-        <f>IF($N183="","",ROUNDDOWN(ROUNDDOWN($N183,2)*$E183,3))</f>
+        <f>IF($N183="","",ROUNDUP(ROUNDUP($N183,2)*$E183,3))</f>
       </c>
       <c r="P183" s="121" t="str">
         <f>IF($L183="","",$I183*$L183)</f>
@@ -11096,10 +11097,10 @@
         <f>IF($L184="","",$C184*$L184)</f>
       </c>
       <c r="N184" s="119" t="str">
-        <f>IF($M184="","",ROUNDDOWN($C184+$M184,2))</f>
+        <f>IF($M184="","",ROUNDUP($C184+$M184,2))</f>
       </c>
       <c r="O184" s="120" t="str">
-        <f>IF($N184="","",ROUNDDOWN(ROUNDDOWN($N184,2)*$E184,3))</f>
+        <f>IF($N184="","",ROUNDUP(ROUNDUP($N184,2)*$E184,3))</f>
       </c>
       <c r="P184" s="121" t="str">
         <f>IF($L184="","",$I184*$L184)</f>
@@ -11150,10 +11151,10 @@
         <f>IF($L185="","",$C185*$L185)</f>
       </c>
       <c r="N185" s="119" t="str">
-        <f>IF($M185="","",ROUNDDOWN($C185+$M185,2))</f>
+        <f>IF($M185="","",ROUNDUP($C185+$M185,2))</f>
       </c>
       <c r="O185" s="120" t="str">
-        <f>IF($N185="","",ROUNDDOWN(ROUNDDOWN($N185,2)*$E185,3))</f>
+        <f>IF($N185="","",ROUNDUP(ROUNDUP($N185,2)*$E185,3))</f>
       </c>
       <c r="P185" s="121" t="str">
         <f>IF($L185="","",$I185*$L185)</f>
@@ -11204,10 +11205,10 @@
         <f>IF($L186="","",$C186*$L186)</f>
       </c>
       <c r="N186" s="119" t="str">
-        <f>IF($M186="","",ROUNDDOWN($C186+$M186,2))</f>
+        <f>IF($M186="","",ROUNDUP($C186+$M186,2))</f>
       </c>
       <c r="O186" s="120" t="str">
-        <f>IF($N186="","",ROUNDDOWN(ROUNDDOWN($N186,2)*$E186,3))</f>
+        <f>IF($N186="","",ROUNDUP(ROUNDUP($N186,2)*$E186,3))</f>
       </c>
       <c r="P186" s="121" t="str">
         <f>IF($L186="","",$I186*$L186)</f>
@@ -11258,10 +11259,10 @@
         <f>IF($L187="","",$C187*$L187)</f>
       </c>
       <c r="N187" s="119" t="str">
-        <f>IF($M187="","",ROUNDDOWN($C187+$M187,2))</f>
+        <f>IF($M187="","",ROUNDUP($C187+$M187,2))</f>
       </c>
       <c r="O187" s="120" t="str">
-        <f>IF($N187="","",ROUNDDOWN(ROUNDDOWN($N187,2)*$E187,3))</f>
+        <f>IF($N187="","",ROUNDUP(ROUNDUP($N187,2)*$E187,3))</f>
       </c>
       <c r="P187" s="121" t="str">
         <f>IF($L187="","",$I187*$L187)</f>
@@ -11312,10 +11313,10 @@
         <f>IF($L188="","",$C188*$L188)</f>
       </c>
       <c r="N188" s="119" t="str">
-        <f>IF($M188="","",ROUNDDOWN($C188+$M188,2))</f>
+        <f>IF($M188="","",ROUNDUP($C188+$M188,2))</f>
       </c>
       <c r="O188" s="120" t="str">
-        <f>IF($N188="","",ROUNDDOWN(ROUNDDOWN($N188,2)*$E188,3))</f>
+        <f>IF($N188="","",ROUNDUP(ROUNDUP($N188,2)*$E188,3))</f>
       </c>
       <c r="P188" s="121" t="str">
         <f>IF($L188="","",$I188*$L188)</f>
@@ -11366,10 +11367,10 @@
         <f>IF($L189="","",$C189*$L189)</f>
       </c>
       <c r="N189" s="119" t="str">
-        <f>IF($M189="","",ROUNDDOWN($C189+$M189,2))</f>
+        <f>IF($M189="","",ROUNDUP($C189+$M189,2))</f>
       </c>
       <c r="O189" s="120" t="str">
-        <f>IF($N189="","",ROUNDDOWN(ROUNDDOWN($N189,2)*$E189,3))</f>
+        <f>IF($N189="","",ROUNDUP(ROUNDUP($N189,2)*$E189,3))</f>
       </c>
       <c r="P189" s="121" t="str">
         <f>IF($L189="","",$I189*$L189)</f>
@@ -11420,10 +11421,10 @@
         <f>IF($L190="","",$C190*$L190)</f>
       </c>
       <c r="N190" s="119" t="str">
-        <f>IF($M190="","",ROUNDDOWN($C190+$M190,2))</f>
+        <f>IF($M190="","",ROUNDUP($C190+$M190,2))</f>
       </c>
       <c r="O190" s="120" t="str">
-        <f>IF($N190="","",ROUNDDOWN(ROUNDDOWN($N190,2)*$E190,3))</f>
+        <f>IF($N190="","",ROUNDUP(ROUNDUP($N190,2)*$E190,3))</f>
       </c>
       <c r="P190" s="121" t="str">
         <f>IF($L190="","",$I190*$L190)</f>
@@ -11474,10 +11475,10 @@
         <f>IF($L191="","",$C191*$L191)</f>
       </c>
       <c r="N191" s="119" t="str">
-        <f>IF($M191="","",ROUNDDOWN($C191+$M191,2))</f>
+        <f>IF($M191="","",ROUNDUP($C191+$M191,2))</f>
       </c>
       <c r="O191" s="120" t="str">
-        <f>IF($N191="","",ROUNDDOWN(ROUNDDOWN($N191,2)*$E191,3))</f>
+        <f>IF($N191="","",ROUNDUP(ROUNDUP($N191,2)*$E191,3))</f>
       </c>
       <c r="P191" s="121" t="str">
         <f>IF($L191="","",$I191*$L191)</f>
@@ -11528,10 +11529,10 @@
         <f>IF($L192="","",$C192*$L192)</f>
       </c>
       <c r="N192" s="119" t="str">
-        <f>IF($M192="","",ROUNDDOWN($C192+$M192,2))</f>
+        <f>IF($M192="","",ROUNDUP($C192+$M192,2))</f>
       </c>
       <c r="O192" s="120" t="str">
-        <f>IF($N192="","",ROUNDDOWN(ROUNDDOWN($N192,2)*$E192,3))</f>
+        <f>IF($N192="","",ROUNDUP(ROUNDUP($N192,2)*$E192,3))</f>
       </c>
       <c r="P192" s="121" t="str">
         <f>IF($L192="","",$I192*$L192)</f>
@@ -11582,10 +11583,10 @@
         <f>IF($L193="","",$C193*$L193)</f>
       </c>
       <c r="N193" s="119" t="str">
-        <f>IF($M193="","",ROUNDDOWN($C193+$M193,2))</f>
+        <f>IF($M193="","",ROUNDUP($C193+$M193,2))</f>
       </c>
       <c r="O193" s="120" t="str">
-        <f>IF($N193="","",ROUNDDOWN(ROUNDDOWN($N193,2)*$E193,3))</f>
+        <f>IF($N193="","",ROUNDUP(ROUNDUP($N193,2)*$E193,3))</f>
       </c>
       <c r="P193" s="121" t="str">
         <f>IF($L193="","",$I193*$L193)</f>
@@ -11636,10 +11637,10 @@
         <f>IF($L194="","",$C194*$L194)</f>
       </c>
       <c r="N194" s="119" t="str">
-        <f>IF($M194="","",ROUNDDOWN($C194+$M194,2))</f>
+        <f>IF($M194="","",ROUNDUP($C194+$M194,2))</f>
       </c>
       <c r="O194" s="120" t="str">
-        <f>IF($N194="","",ROUNDDOWN(ROUNDDOWN($N194,2)*$E194,3))</f>
+        <f>IF($N194="","",ROUNDUP(ROUNDUP($N194,2)*$E194,3))</f>
       </c>
       <c r="P194" s="121" t="str">
         <f>IF($L194="","",$I194*$L194)</f>
@@ -11690,10 +11691,10 @@
         <f>IF($L195="","",$C195*$L195)</f>
       </c>
       <c r="N195" s="119" t="str">
-        <f>IF($M195="","",ROUNDDOWN($C195+$M195,2))</f>
+        <f>IF($M195="","",ROUNDUP($C195+$M195,2))</f>
       </c>
       <c r="O195" s="120" t="str">
-        <f>IF($N195="","",ROUNDDOWN(ROUNDDOWN($N195,2)*$E195,3))</f>
+        <f>IF($N195="","",ROUNDUP(ROUNDUP($N195,2)*$E195,3))</f>
       </c>
       <c r="P195" s="121" t="str">
         <f>IF($L195="","",$I195*$L195)</f>
@@ -11744,10 +11745,10 @@
         <f>IF($L196="","",$C196*$L196)</f>
       </c>
       <c r="N196" s="119" t="str">
-        <f>IF($M196="","",ROUNDDOWN($C196+$M196,2))</f>
+        <f>IF($M196="","",ROUNDUP($C196+$M196,2))</f>
       </c>
       <c r="O196" s="120" t="str">
-        <f>IF($N196="","",ROUNDDOWN(ROUNDDOWN($N196,2)*$E196,3))</f>
+        <f>IF($N196="","",ROUNDUP(ROUNDUP($N196,2)*$E196,3))</f>
       </c>
       <c r="P196" s="121" t="str">
         <f>IF($L196="","",$I196*$L196)</f>
@@ -11798,10 +11799,10 @@
         <f>IF($L197="","",$C197*$L197)</f>
       </c>
       <c r="N197" s="119" t="str">
-        <f>IF($M197="","",ROUNDDOWN($C197+$M197,2))</f>
+        <f>IF($M197="","",ROUNDUP($C197+$M197,2))</f>
       </c>
       <c r="O197" s="120" t="str">
-        <f>IF($N197="","",ROUNDDOWN(ROUNDDOWN($N197,2)*$E197,3))</f>
+        <f>IF($N197="","",ROUNDUP(ROUNDUP($N197,2)*$E197,3))</f>
       </c>
       <c r="P197" s="121" t="str">
         <f>IF($L197="","",$I197*$L197)</f>
@@ -11852,10 +11853,10 @@
         <f>IF($L198="","",$C198*$L198)</f>
       </c>
       <c r="N198" s="119" t="str">
-        <f>IF($M198="","",ROUNDDOWN($C198+$M198,2))</f>
+        <f>IF($M198="","",ROUNDUP($C198+$M198,2))</f>
       </c>
       <c r="O198" s="120" t="str">
-        <f>IF($N198="","",ROUNDDOWN(ROUNDDOWN($N198,2)*$E198,3))</f>
+        <f>IF($N198="","",ROUNDUP(ROUNDUP($N198,2)*$E198,3))</f>
       </c>
       <c r="P198" s="121" t="str">
         <f>IF($L198="","",$I198*$L198)</f>
@@ -11906,10 +11907,10 @@
         <f>IF($L199="","",$C199*$L199)</f>
       </c>
       <c r="N199" s="119" t="str">
-        <f>IF($M199="","",ROUNDDOWN($C199+$M199,2))</f>
+        <f>IF($M199="","",ROUNDUP($C199+$M199,2))</f>
       </c>
       <c r="O199" s="120" t="str">
-        <f>IF($N199="","",ROUNDDOWN(ROUNDDOWN($N199,2)*$E199,3))</f>
+        <f>IF($N199="","",ROUNDUP(ROUNDUP($N199,2)*$E199,3))</f>
       </c>
       <c r="P199" s="121" t="str">
         <f>IF($L199="","",$I199*$L199)</f>
@@ -11960,10 +11961,10 @@
         <f>IF($L200="","",$C200*$L200)</f>
       </c>
       <c r="N200" s="119" t="str">
-        <f>IF($M200="","",ROUNDDOWN($C200+$M200,2))</f>
+        <f>IF($M200="","",ROUNDUP($C200+$M200,2))</f>
       </c>
       <c r="O200" s="120" t="str">
-        <f>IF($N200="","",ROUNDDOWN(ROUNDDOWN($N200,2)*$E200,3))</f>
+        <f>IF($N200="","",ROUNDUP(ROUNDUP($N200,2)*$E200,3))</f>
       </c>
       <c r="P200" s="121" t="str">
         <f>IF($L200="","",$I200*$L200)</f>
@@ -12014,10 +12015,10 @@
         <f>IF($L201="","",$C201*$L201)</f>
       </c>
       <c r="N201" s="119" t="str">
-        <f>IF($M201="","",ROUNDDOWN($C201+$M201,2))</f>
+        <f>IF($M201="","",ROUNDUP($C201+$M201,2))</f>
       </c>
       <c r="O201" s="120" t="str">
-        <f>IF($N201="","",ROUNDDOWN(ROUNDDOWN($N201,2)*$E201,3))</f>
+        <f>IF($N201="","",ROUNDUP(ROUNDUP($N201,2)*$E201,3))</f>
       </c>
       <c r="P201" s="121" t="str">
         <f>IF($L201="","",$I201*$L201)</f>
@@ -12068,10 +12069,10 @@
         <f>IF($L202="","",$C202*$L202)</f>
       </c>
       <c r="N202" s="119" t="str">
-        <f>IF($M202="","",ROUNDDOWN($C202+$M202,2))</f>
+        <f>IF($M202="","",ROUNDUP($C202+$M202,2))</f>
       </c>
       <c r="O202" s="120" t="str">
-        <f>IF($N202="","",ROUNDDOWN(ROUNDDOWN($N202,2)*$E202,3))</f>
+        <f>IF($N202="","",ROUNDUP(ROUNDUP($N202,2)*$E202,3))</f>
       </c>
       <c r="P202" s="121" t="str">
         <f>IF($L202="","",$I202*$L202)</f>
@@ -12122,10 +12123,10 @@
         <f>IF($L203="","",$C203*$L203)</f>
       </c>
       <c r="N203" s="119" t="str">
-        <f>IF($M203="","",ROUNDDOWN($C203+$M203,2))</f>
+        <f>IF($M203="","",ROUNDUP($C203+$M203,2))</f>
       </c>
       <c r="O203" s="120" t="str">
-        <f>IF($N203="","",ROUNDDOWN(ROUNDDOWN($N203,2)*$E203,3))</f>
+        <f>IF($N203="","",ROUNDUP(ROUNDUP($N203,2)*$E203,3))</f>
       </c>
       <c r="P203" s="121" t="str">
         <f>IF($L203="","",$I203*$L203)</f>
@@ -12176,10 +12177,10 @@
         <f>IF($L204="","",$C204*$L204)</f>
       </c>
       <c r="N204" s="119" t="str">
-        <f>IF($M204="","",ROUNDDOWN($C204+$M204,2))</f>
+        <f>IF($M204="","",ROUNDUP($C204+$M204,2))</f>
       </c>
       <c r="O204" s="120" t="str">
-        <f>IF($N204="","",ROUNDDOWN(ROUNDDOWN($N204,2)*$E204,3))</f>
+        <f>IF($N204="","",ROUNDUP(ROUNDUP($N204,2)*$E204,3))</f>
       </c>
       <c r="P204" s="121" t="str">
         <f>IF($L204="","",$I204*$L204)</f>
@@ -12230,10 +12231,10 @@
         <f>IF($L205="","",$C205*$L205)</f>
       </c>
       <c r="N205" s="119" t="str">
-        <f>IF($M205="","",ROUNDDOWN($C205+$M205,2))</f>
+        <f>IF($M205="","",ROUNDUP($C205+$M205,2))</f>
       </c>
       <c r="O205" s="120" t="str">
-        <f>IF($N205="","",ROUNDDOWN(ROUNDDOWN($N205,2)*$E205,3))</f>
+        <f>IF($N205="","",ROUNDUP(ROUNDUP($N205,2)*$E205,3))</f>
       </c>
       <c r="P205" s="121" t="str">
         <f>IF($L205="","",$I205*$L205)</f>
@@ -12284,10 +12285,10 @@
         <f>IF($L206="","",$C206*$L206)</f>
       </c>
       <c r="N206" s="119" t="str">
-        <f>IF($M206="","",ROUNDDOWN($C206+$M206,2))</f>
+        <f>IF($M206="","",ROUNDUP($C206+$M206,2))</f>
       </c>
       <c r="O206" s="120" t="str">
-        <f>IF($N206="","",ROUNDDOWN(ROUNDDOWN($N206,2)*$E206,3))</f>
+        <f>IF($N206="","",ROUNDUP(ROUNDUP($N206,2)*$E206,3))</f>
       </c>
       <c r="P206" s="121" t="str">
         <f>IF($L206="","",$I206*$L206)</f>
@@ -12338,10 +12339,10 @@
         <f>IF($L207="","",$C207*$L207)</f>
       </c>
       <c r="N207" s="119" t="str">
-        <f>IF($M207="","",ROUNDDOWN($C207+$M207,2))</f>
+        <f>IF($M207="","",ROUNDUP($C207+$M207,2))</f>
       </c>
       <c r="O207" s="120" t="str">
-        <f>IF($N207="","",ROUNDDOWN(ROUNDDOWN($N207,2)*$E207,3))</f>
+        <f>IF($N207="","",ROUNDUP(ROUNDUP($N207,2)*$E207,3))</f>
       </c>
       <c r="P207" s="121" t="str">
         <f>IF($L207="","",$I207*$L207)</f>
@@ -12392,10 +12393,10 @@
         <f>IF($L208="","",$C208*$L208)</f>
       </c>
       <c r="N208" s="119" t="str">
-        <f>IF($M208="","",ROUNDDOWN($C208+$M208,2))</f>
+        <f>IF($M208="","",ROUNDUP($C208+$M208,2))</f>
       </c>
       <c r="O208" s="120" t="str">
-        <f>IF($N208="","",ROUNDDOWN(ROUNDDOWN($N208,2)*$E208,3))</f>
+        <f>IF($N208="","",ROUNDUP(ROUNDUP($N208,2)*$E208,3))</f>
       </c>
       <c r="P208" s="121" t="str">
         <f>IF($L208="","",$I208*$L208)</f>
@@ -12446,10 +12447,10 @@
         <f>IF($L209="","",$C209*$L209)</f>
       </c>
       <c r="N209" s="119" t="str">
-        <f>IF($M209="","",ROUNDDOWN($C209+$M209,2))</f>
+        <f>IF($M209="","",ROUNDUP($C209+$M209,2))</f>
       </c>
       <c r="O209" s="120" t="str">
-        <f>IF($N209="","",ROUNDDOWN(ROUNDDOWN($N209,2)*$E209,3))</f>
+        <f>IF($N209="","",ROUNDUP(ROUNDUP($N209,2)*$E209,3))</f>
       </c>
       <c r="P209" s="121" t="str">
         <f>IF($L209="","",$I209*$L209)</f>
@@ -12500,10 +12501,10 @@
         <f>IF($L210="","",$C210*$L210)</f>
       </c>
       <c r="N210" s="119" t="str">
-        <f>IF($M210="","",ROUNDDOWN($C210+$M210,2))</f>
+        <f>IF($M210="","",ROUNDUP($C210+$M210,2))</f>
       </c>
       <c r="O210" s="120" t="str">
-        <f>IF($N210="","",ROUNDDOWN(ROUNDDOWN($N210,2)*$E210,3))</f>
+        <f>IF($N210="","",ROUNDUP(ROUNDUP($N210,2)*$E210,3))</f>
       </c>
       <c r="P210" s="121" t="str">
         <f>IF($L210="","",$I210*$L210)</f>
@@ -12554,10 +12555,10 @@
         <f>IF($L211="","",$C211*$L211)</f>
       </c>
       <c r="N211" s="119" t="str">
-        <f>IF($M211="","",ROUNDDOWN($C211+$M211,2))</f>
+        <f>IF($M211="","",ROUNDUP($C211+$M211,2))</f>
       </c>
       <c r="O211" s="120" t="str">
-        <f>IF($N211="","",ROUNDDOWN(ROUNDDOWN($N211,2)*$E211,3))</f>
+        <f>IF($N211="","",ROUNDUP(ROUNDUP($N211,2)*$E211,3))</f>
       </c>
       <c r="P211" s="121" t="str">
         <f>IF($L211="","",$I211*$L211)</f>
@@ -12608,10 +12609,10 @@
         <f>IF($L212="","",$C212*$L212)</f>
       </c>
       <c r="N212" s="119" t="str">
-        <f>IF($M212="","",ROUNDDOWN($C212+$M212,2))</f>
+        <f>IF($M212="","",ROUNDUP($C212+$M212,2))</f>
       </c>
       <c r="O212" s="120" t="str">
-        <f>IF($N212="","",ROUNDDOWN(ROUNDDOWN($N212,2)*$E212,3))</f>
+        <f>IF($N212="","",ROUNDUP(ROUNDUP($N212,2)*$E212,3))</f>
       </c>
       <c r="P212" s="121" t="str">
         <f>IF($L212="","",$I212*$L212)</f>
@@ -12662,10 +12663,10 @@
         <f>IF($L213="","",$C213*$L213)</f>
       </c>
       <c r="N213" s="119" t="str">
-        <f>IF($M213="","",ROUNDDOWN($C213+$M213,2))</f>
+        <f>IF($M213="","",ROUNDUP($C213+$M213,2))</f>
       </c>
       <c r="O213" s="120" t="str">
-        <f>IF($N213="","",ROUNDDOWN(ROUNDDOWN($N213,2)*$E213,3))</f>
+        <f>IF($N213="","",ROUNDUP(ROUNDUP($N213,2)*$E213,3))</f>
       </c>
       <c r="P213" s="121" t="str">
         <f>IF($L213="","",$I213*$L213)</f>
@@ -12716,10 +12717,10 @@
         <f>IF($L214="","",$C214*$L214)</f>
       </c>
       <c r="N214" s="119" t="str">
-        <f>IF($M214="","",ROUNDDOWN($C214+$M214,2))</f>
+        <f>IF($M214="","",ROUNDUP($C214+$M214,2))</f>
       </c>
       <c r="O214" s="120" t="str">
-        <f>IF($N214="","",ROUNDDOWN(ROUNDDOWN($N214,2)*$E214,3))</f>
+        <f>IF($N214="","",ROUNDUP(ROUNDUP($N214,2)*$E214,3))</f>
       </c>
       <c r="P214" s="121" t="str">
         <f>IF($L214="","",$I214*$L214)</f>
@@ -12770,10 +12771,10 @@
         <f>IF($L215="","",$C215*$L215)</f>
       </c>
       <c r="N215" s="119" t="str">
-        <f>IF($M215="","",ROUNDDOWN($C215+$M215,2))</f>
+        <f>IF($M215="","",ROUNDUP($C215+$M215,2))</f>
       </c>
       <c r="O215" s="120" t="str">
-        <f>IF($N215="","",ROUNDDOWN(ROUNDDOWN($N215,2)*$E215,3))</f>
+        <f>IF($N215="","",ROUNDUP(ROUNDUP($N215,2)*$E215,3))</f>
       </c>
       <c r="P215" s="121" t="str">
         <f>IF($L215="","",$I215*$L215)</f>
@@ -12824,10 +12825,10 @@
         <f>IF($L216="","",$C216*$L216)</f>
       </c>
       <c r="N216" s="119" t="str">
-        <f>IF($M216="","",ROUNDDOWN($C216+$M216,2))</f>
+        <f>IF($M216="","",ROUNDUP($C216+$M216,2))</f>
       </c>
       <c r="O216" s="120" t="str">
-        <f>IF($N216="","",ROUNDDOWN(ROUNDDOWN($N216,2)*$E216,3))</f>
+        <f>IF($N216="","",ROUNDUP(ROUNDUP($N216,2)*$E216,3))</f>
       </c>
       <c r="P216" s="121" t="str">
         <f>IF($L216="","",$I216*$L216)</f>
@@ -12878,10 +12879,10 @@
         <f>IF($L217="","",$C217*$L217)</f>
       </c>
       <c r="N217" s="119" t="str">
-        <f>IF($M217="","",ROUNDDOWN($C217+$M217,2))</f>
+        <f>IF($M217="","",ROUNDUP($C217+$M217,2))</f>
       </c>
       <c r="O217" s="120" t="str">
-        <f>IF($N217="","",ROUNDDOWN(ROUNDDOWN($N217,2)*$E217,3))</f>
+        <f>IF($N217="","",ROUNDUP(ROUNDUP($N217,2)*$E217,3))</f>
       </c>
       <c r="P217" s="121" t="str">
         <f>IF($L217="","",$I217*$L217)</f>
@@ -12932,10 +12933,10 @@
         <f>IF($L218="","",$C218*$L218)</f>
       </c>
       <c r="N218" s="119" t="str">
-        <f>IF($M218="","",ROUNDDOWN($C218+$M218,2))</f>
+        <f>IF($M218="","",ROUNDUP($C218+$M218,2))</f>
       </c>
       <c r="O218" s="120" t="str">
-        <f>IF($N218="","",ROUNDDOWN(ROUNDDOWN($N218,2)*$E218,3))</f>
+        <f>IF($N218="","",ROUNDUP(ROUNDUP($N218,2)*$E218,3))</f>
       </c>
       <c r="P218" s="121" t="str">
         <f>IF($L218="","",$I218*$L218)</f>
@@ -12986,10 +12987,10 @@
         <f>IF($L219="","",$C219*$L219)</f>
       </c>
       <c r="N219" s="119" t="str">
-        <f>IF($M219="","",ROUNDDOWN($C219+$M219,2))</f>
+        <f>IF($M219="","",ROUNDUP($C219+$M219,2))</f>
       </c>
       <c r="O219" s="120" t="str">
-        <f>IF($N219="","",ROUNDDOWN(ROUNDDOWN($N219,2)*$E219,3))</f>
+        <f>IF($N219="","",ROUNDUP(ROUNDUP($N219,2)*$E219,3))</f>
       </c>
       <c r="P219" s="121" t="str">
         <f>IF($L219="","",$I219*$L219)</f>
@@ -13040,10 +13041,10 @@
         <f>IF($L220="","",$C220*$L220)</f>
       </c>
       <c r="N220" s="119" t="str">
-        <f>IF($M220="","",ROUNDDOWN($C220+$M220,2))</f>
+        <f>IF($M220="","",ROUNDUP($C220+$M220,2))</f>
       </c>
       <c r="O220" s="120" t="str">
-        <f>IF($N220="","",ROUNDDOWN(ROUNDDOWN($N220,2)*$E220,3))</f>
+        <f>IF($N220="","",ROUNDUP(ROUNDUP($N220,2)*$E220,3))</f>
       </c>
       <c r="P220" s="121" t="str">
         <f>IF($L220="","",$I220*$L220)</f>
@@ -13094,10 +13095,10 @@
         <f>IF($L221="","",$C221*$L221)</f>
       </c>
       <c r="N221" s="119" t="str">
-        <f>IF($M221="","",ROUNDDOWN($C221+$M221,2))</f>
+        <f>IF($M221="","",ROUNDUP($C221+$M221,2))</f>
       </c>
       <c r="O221" s="120" t="str">
-        <f>IF($N221="","",ROUNDDOWN(ROUNDDOWN($N221,2)*$E221,3))</f>
+        <f>IF($N221="","",ROUNDUP(ROUNDUP($N221,2)*$E221,3))</f>
       </c>
       <c r="P221" s="121" t="str">
         <f>IF($L221="","",$I221*$L221)</f>
@@ -13148,10 +13149,10 @@
         <f>IF($L222="","",$C222*$L222)</f>
       </c>
       <c r="N222" s="119" t="str">
-        <f>IF($M222="","",ROUNDDOWN($C222+$M222,2))</f>
+        <f>IF($M222="","",ROUNDUP($C222+$M222,2))</f>
       </c>
       <c r="O222" s="120" t="str">
-        <f>IF($N222="","",ROUNDDOWN(ROUNDDOWN($N222,2)*$E222,3))</f>
+        <f>IF($N222="","",ROUNDUP(ROUNDUP($N222,2)*$E222,3))</f>
       </c>
       <c r="P222" s="121" t="str">
         <f>IF($L222="","",$I222*$L222)</f>
@@ -13202,10 +13203,10 @@
         <f>IF($L223="","",$C223*$L223)</f>
       </c>
       <c r="N223" s="119" t="str">
-        <f>IF($M223="","",ROUNDDOWN($C223+$M223,2))</f>
+        <f>IF($M223="","",ROUNDUP($C223+$M223,2))</f>
       </c>
       <c r="O223" s="120" t="str">
-        <f>IF($N223="","",ROUNDDOWN(ROUNDDOWN($N223,2)*$E223,3))</f>
+        <f>IF($N223="","",ROUNDUP(ROUNDUP($N223,2)*$E223,3))</f>
       </c>
       <c r="P223" s="121" t="str">
         <f>IF($L223="","",$I223*$L223)</f>
@@ -13256,10 +13257,10 @@
         <f>IF($L224="","",$C224*$L224)</f>
       </c>
       <c r="N224" s="119" t="str">
-        <f>IF($M224="","",ROUNDDOWN($C224+$M224,2))</f>
+        <f>IF($M224="","",ROUNDUP($C224+$M224,2))</f>
       </c>
       <c r="O224" s="120" t="str">
-        <f>IF($N224="","",ROUNDDOWN(ROUNDDOWN($N224,2)*$E224,3))</f>
+        <f>IF($N224="","",ROUNDUP(ROUNDUP($N224,2)*$E224,3))</f>
       </c>
       <c r="P224" s="121" t="str">
         <f>IF($L224="","",$I224*$L224)</f>
@@ -13310,10 +13311,10 @@
         <f>IF($L225="","",$C225*$L225)</f>
       </c>
       <c r="N225" s="119" t="str">
-        <f>IF($M225="","",ROUNDDOWN($C225+$M225,2))</f>
+        <f>IF($M225="","",ROUNDUP($C225+$M225,2))</f>
       </c>
       <c r="O225" s="120" t="str">
-        <f>IF($N225="","",ROUNDDOWN(ROUNDDOWN($N225,2)*$E225,3))</f>
+        <f>IF($N225="","",ROUNDUP(ROUNDUP($N225,2)*$E225,3))</f>
       </c>
       <c r="P225" s="121" t="str">
         <f>IF($L225="","",$I225*$L225)</f>
@@ -13364,10 +13365,10 @@
         <f>IF($L226="","",$C226*$L226)</f>
       </c>
       <c r="N226" s="119" t="str">
-        <f>IF($M226="","",ROUNDDOWN($C226+$M226,2))</f>
+        <f>IF($M226="","",ROUNDUP($C226+$M226,2))</f>
       </c>
       <c r="O226" s="120" t="str">
-        <f>IF($N226="","",ROUNDDOWN(ROUNDDOWN($N226,2)*$E226,3))</f>
+        <f>IF($N226="","",ROUNDUP(ROUNDUP($N226,2)*$E226,3))</f>
       </c>
       <c r="P226" s="121" t="str">
         <f>IF($L226="","",$I226*$L226)</f>
@@ -13418,10 +13419,10 @@
         <f>IF($L227="","",$C227*$L227)</f>
       </c>
       <c r="N227" s="119" t="str">
-        <f>IF($M227="","",ROUNDDOWN($C227+$M227,2))</f>
+        <f>IF($M227="","",ROUNDUP($C227+$M227,2))</f>
       </c>
       <c r="O227" s="120" t="str">
-        <f>IF($N227="","",ROUNDDOWN(ROUNDDOWN($N227,2)*$E227,3))</f>
+        <f>IF($N227="","",ROUNDUP(ROUNDUP($N227,2)*$E227,3))</f>
       </c>
       <c r="P227" s="121" t="str">
         <f>IF($L227="","",$I227*$L227)</f>
@@ -13472,10 +13473,10 @@
         <f>IF($L228="","",$C228*$L228)</f>
       </c>
       <c r="N228" s="119" t="str">
-        <f>IF($M228="","",ROUNDDOWN($C228+$M228,2))</f>
+        <f>IF($M228="","",ROUNDUP($C228+$M228,2))</f>
       </c>
       <c r="O228" s="120" t="str">
-        <f>IF($N228="","",ROUNDDOWN(ROUNDDOWN($N228,2)*$E228,3))</f>
+        <f>IF($N228="","",ROUNDUP(ROUNDUP($N228,2)*$E228,3))</f>
       </c>
       <c r="P228" s="121" t="str">
         <f>IF($L228="","",$I228*$L228)</f>
@@ -13526,10 +13527,10 @@
         <f>IF($L229="","",$C229*$L229)</f>
       </c>
       <c r="N229" s="119" t="str">
-        <f>IF($M229="","",ROUNDDOWN($C229+$M229,2))</f>
+        <f>IF($M229="","",ROUNDUP($C229+$M229,2))</f>
       </c>
       <c r="O229" s="120" t="str">
-        <f>IF($N229="","",ROUNDDOWN(ROUNDDOWN($N229,2)*$E229,3))</f>
+        <f>IF($N229="","",ROUNDUP(ROUNDUP($N229,2)*$E229,3))</f>
       </c>
       <c r="P229" s="121" t="str">
         <f>IF($L229="","",$I229*$L229)</f>
@@ -13580,10 +13581,10 @@
         <f>IF($L230="","",$C230*$L230)</f>
       </c>
       <c r="N230" s="119" t="str">
-        <f>IF($M230="","",ROUNDDOWN($C230+$M230,2))</f>
+        <f>IF($M230="","",ROUNDUP($C230+$M230,2))</f>
       </c>
       <c r="O230" s="120" t="str">
-        <f>IF($N230="","",ROUNDDOWN(ROUNDDOWN($N230,2)*$E230,3))</f>
+        <f>IF($N230="","",ROUNDUP(ROUNDUP($N230,2)*$E230,3))</f>
       </c>
       <c r="P230" s="121" t="str">
         <f>IF($L230="","",$I230*$L230)</f>
@@ -13634,10 +13635,10 @@
         <f>IF($L231="","",$C231*$L231)</f>
       </c>
       <c r="N231" s="119" t="str">
-        <f>IF($M231="","",ROUNDDOWN($C231+$M231,2))</f>
+        <f>IF($M231="","",ROUNDUP($C231+$M231,2))</f>
       </c>
       <c r="O231" s="120" t="str">
-        <f>IF($N231="","",ROUNDDOWN(ROUNDDOWN($N231,2)*$E231,3))</f>
+        <f>IF($N231="","",ROUNDUP(ROUNDUP($N231,2)*$E231,3))</f>
       </c>
       <c r="P231" s="121" t="str">
         <f>IF($L231="","",$I231*$L231)</f>
@@ -13688,10 +13689,10 @@
         <f>IF($L232="","",$C232*$L232)</f>
       </c>
       <c r="N232" s="119" t="str">
-        <f>IF($M232="","",ROUNDDOWN($C232+$M232,2))</f>
+        <f>IF($M232="","",ROUNDUP($C232+$M232,2))</f>
       </c>
       <c r="O232" s="120" t="str">
-        <f>IF($N232="","",ROUNDDOWN(ROUNDDOWN($N232,2)*$E232,3))</f>
+        <f>IF($N232="","",ROUNDUP(ROUNDUP($N232,2)*$E232,3))</f>
       </c>
       <c r="P232" s="121" t="str">
         <f>IF($L232="","",$I232*$L232)</f>
@@ -13742,10 +13743,10 @@
         <f>IF($L233="","",$C233*$L233)</f>
       </c>
       <c r="N233" s="119" t="str">
-        <f>IF($M233="","",ROUNDDOWN($C233+$M233,2))</f>
+        <f>IF($M233="","",ROUNDUP($C233+$M233,2))</f>
       </c>
       <c r="O233" s="120" t="str">
-        <f>IF($N233="","",ROUNDDOWN(ROUNDDOWN($N233,2)*$E233,3))</f>
+        <f>IF($N233="","",ROUNDUP(ROUNDUP($N233,2)*$E233,3))</f>
       </c>
       <c r="P233" s="121" t="str">
         <f>IF($L233="","",$I233*$L233)</f>
@@ -13796,10 +13797,10 @@
         <f>IF($L234="","",$C234*$L234)</f>
       </c>
       <c r="N234" s="119" t="str">
-        <f>IF($M234="","",ROUNDDOWN($C234+$M234,2))</f>
+        <f>IF($M234="","",ROUNDUP($C234+$M234,2))</f>
       </c>
       <c r="O234" s="120" t="str">
-        <f>IF($N234="","",ROUNDDOWN(ROUNDDOWN($N234,2)*$E234,3))</f>
+        <f>IF($N234="","",ROUNDUP(ROUNDUP($N234,2)*$E234,3))</f>
       </c>
       <c r="P234" s="121" t="str">
         <f>IF($L234="","",$I234*$L234)</f>
@@ -13850,10 +13851,10 @@
         <f>IF($L235="","",$C235*$L235)</f>
       </c>
       <c r="N235" s="119" t="str">
-        <f>IF($M235="","",ROUNDDOWN($C235+$M235,2))</f>
+        <f>IF($M235="","",ROUNDUP($C235+$M235,2))</f>
       </c>
       <c r="O235" s="120" t="str">
-        <f>IF($N235="","",ROUNDDOWN(ROUNDDOWN($N235,2)*$E235,3))</f>
+        <f>IF($N235="","",ROUNDUP(ROUNDUP($N235,2)*$E235,3))</f>
       </c>
       <c r="P235" s="121" t="str">
         <f>IF($L235="","",$I235*$L235)</f>
@@ -13904,10 +13905,10 @@
         <f>IF($L236="","",$C236*$L236)</f>
       </c>
       <c r="N236" s="119" t="str">
-        <f>IF($M236="","",ROUNDDOWN($C236+$M236,2))</f>
+        <f>IF($M236="","",ROUNDUP($C236+$M236,2))</f>
       </c>
       <c r="O236" s="120" t="str">
-        <f>IF($N236="","",ROUNDDOWN(ROUNDDOWN($N236,2)*$E236,3))</f>
+        <f>IF($N236="","",ROUNDUP(ROUNDUP($N236,2)*$E236,3))</f>
       </c>
       <c r="P236" s="121" t="str">
         <f>IF($L236="","",$I236*$L236)</f>
@@ -13958,10 +13959,10 @@
         <f>IF($L237="","",$C237*$L237)</f>
       </c>
       <c r="N237" s="119" t="str">
-        <f>IF($M237="","",ROUNDDOWN($C237+$M237,2))</f>
+        <f>IF($M237="","",ROUNDUP($C237+$M237,2))</f>
       </c>
       <c r="O237" s="120" t="str">
-        <f>IF($N237="","",ROUNDDOWN(ROUNDDOWN($N237,2)*$E237,3))</f>
+        <f>IF($N237="","",ROUNDUP(ROUNDUP($N237,2)*$E237,3))</f>
       </c>
       <c r="P237" s="121" t="str">
         <f>IF($L237="","",$I237*$L237)</f>
@@ -14012,10 +14013,10 @@
         <f>IF($L238="","",$C238*$L238)</f>
       </c>
       <c r="N238" s="119" t="str">
-        <f>IF($M238="","",ROUNDDOWN($C238+$M238,2))</f>
+        <f>IF($M238="","",ROUNDUP($C238+$M238,2))</f>
       </c>
       <c r="O238" s="120" t="str">
-        <f>IF($N238="","",ROUNDDOWN(ROUNDDOWN($N238,2)*$E238,3))</f>
+        <f>IF($N238="","",ROUNDUP(ROUNDUP($N238,2)*$E238,3))</f>
       </c>
       <c r="P238" s="121" t="str">
         <f>IF($L238="","",$I238*$L238)</f>
@@ -14066,10 +14067,10 @@
         <f>IF($L239="","",$C239*$L239)</f>
       </c>
       <c r="N239" s="119" t="str">
-        <f>IF($M239="","",ROUNDDOWN($C239+$M239,2))</f>
+        <f>IF($M239="","",ROUNDUP($C239+$M239,2))</f>
       </c>
       <c r="O239" s="120" t="str">
-        <f>IF($N239="","",ROUNDDOWN(ROUNDDOWN($N239,2)*$E239,3))</f>
+        <f>IF($N239="","",ROUNDUP(ROUNDUP($N239,2)*$E239,3))</f>
       </c>
       <c r="P239" s="121" t="str">
         <f>IF($L239="","",$I239*$L239)</f>
@@ -14120,10 +14121,10 @@
         <f>IF($L240="","",$C240*$L240)</f>
       </c>
       <c r="N240" s="119" t="str">
-        <f>IF($M240="","",ROUNDDOWN($C240+$M240,2))</f>
+        <f>IF($M240="","",ROUNDUP($C240+$M240,2))</f>
       </c>
       <c r="O240" s="120" t="str">
-        <f>IF($N240="","",ROUNDDOWN(ROUNDDOWN($N240,2)*$E240,3))</f>
+        <f>IF($N240="","",ROUNDUP(ROUNDUP($N240,2)*$E240,3))</f>
       </c>
       <c r="P240" s="121" t="str">
         <f>IF($L240="","",$I240*$L240)</f>
@@ -14174,10 +14175,10 @@
         <f>IF($L241="","",$C241*$L241)</f>
       </c>
       <c r="N241" s="119" t="str">
-        <f>IF($M241="","",ROUNDDOWN($C241+$M241,2))</f>
+        <f>IF($M241="","",ROUNDUP($C241+$M241,2))</f>
       </c>
       <c r="O241" s="120" t="str">
-        <f>IF($N241="","",ROUNDDOWN(ROUNDDOWN($N241,2)*$E241,3))</f>
+        <f>IF($N241="","",ROUNDUP(ROUNDUP($N241,2)*$E241,3))</f>
       </c>
       <c r="P241" s="121" t="str">
         <f>IF($L241="","",$I241*$L241)</f>
@@ -14228,10 +14229,10 @@
         <f>IF($L242="","",$C242*$L242)</f>
       </c>
       <c r="N242" s="119" t="str">
-        <f>IF($M242="","",ROUNDDOWN($C242+$M242,2))</f>
+        <f>IF($M242="","",ROUNDUP($C242+$M242,2))</f>
       </c>
       <c r="O242" s="120" t="str">
-        <f>IF($N242="","",ROUNDDOWN(ROUNDDOWN($N242,2)*$E242,3))</f>
+        <f>IF($N242="","",ROUNDUP(ROUNDUP($N242,2)*$E242,3))</f>
       </c>
       <c r="P242" s="121" t="str">
         <f>IF($L242="","",$I242*$L242)</f>
@@ -14282,10 +14283,10 @@
         <f>IF($L243="","",$C243*$L243)</f>
       </c>
       <c r="N243" s="119" t="str">
-        <f>IF($M243="","",ROUNDDOWN($C243+$M243,2))</f>
+        <f>IF($M243="","",ROUNDUP($C243+$M243,2))</f>
       </c>
       <c r="O243" s="120" t="str">
-        <f>IF($N243="","",ROUNDDOWN(ROUNDDOWN($N243,2)*$E243,3))</f>
+        <f>IF($N243="","",ROUNDUP(ROUNDUP($N243,2)*$E243,3))</f>
       </c>
       <c r="P243" s="121" t="str">
         <f>IF($L243="","",$I243*$L243)</f>
@@ -14336,10 +14337,10 @@
         <f>IF($L244="","",$C244*$L244)</f>
       </c>
       <c r="N244" s="119" t="str">
-        <f>IF($M244="","",ROUNDDOWN($C244+$M244,2))</f>
+        <f>IF($M244="","",ROUNDUP($C244+$M244,2))</f>
       </c>
       <c r="O244" s="120" t="str">
-        <f>IF($N244="","",ROUNDDOWN(ROUNDDOWN($N244,2)*$E244,3))</f>
+        <f>IF($N244="","",ROUNDUP(ROUNDUP($N244,2)*$E244,3))</f>
       </c>
       <c r="P244" s="121" t="str">
         <f>IF($L244="","",$I244*$L244)</f>
@@ -14390,10 +14391,10 @@
         <f>IF($L245="","",$C245*$L245)</f>
       </c>
       <c r="N245" s="119" t="str">
-        <f>IF($M245="","",ROUNDDOWN($C245+$M245,2))</f>
+        <f>IF($M245="","",ROUNDUP($C245+$M245,2))</f>
       </c>
       <c r="O245" s="120" t="str">
-        <f>IF($N245="","",ROUNDDOWN(ROUNDDOWN($N245,2)*$E245,3))</f>
+        <f>IF($N245="","",ROUNDUP(ROUNDUP($N245,2)*$E245,3))</f>
       </c>
       <c r="P245" s="121" t="str">
         <f>IF($L245="","",$I245*$L245)</f>
@@ -14444,10 +14445,10 @@
         <f>IF($L246="","",$C246*$L246)</f>
       </c>
       <c r="N246" s="119" t="str">
-        <f>IF($M246="","",ROUNDDOWN($C246+$M246,2))</f>
+        <f>IF($M246="","",ROUNDUP($C246+$M246,2))</f>
       </c>
       <c r="O246" s="120" t="str">
-        <f>IF($N246="","",ROUNDDOWN(ROUNDDOWN($N246,2)*$E246,3))</f>
+        <f>IF($N246="","",ROUNDUP(ROUNDUP($N246,2)*$E246,3))</f>
       </c>
       <c r="P246" s="121" t="str">
         <f>IF($L246="","",$I246*$L246)</f>
@@ -14498,10 +14499,10 @@
         <f>IF($L247="","",$C247*$L247)</f>
       </c>
       <c r="N247" s="119" t="str">
-        <f>IF($M247="","",ROUNDDOWN($C247+$M247,2))</f>
+        <f>IF($M247="","",ROUNDUP($C247+$M247,2))</f>
       </c>
       <c r="O247" s="120" t="str">
-        <f>IF($N247="","",ROUNDDOWN(ROUNDDOWN($N247,2)*$E247,3))</f>
+        <f>IF($N247="","",ROUNDUP(ROUNDUP($N247,2)*$E247,3))</f>
       </c>
       <c r="P247" s="121" t="str">
         <f>IF($L247="","",$I247*$L247)</f>
@@ -14552,10 +14553,10 @@
         <f>IF($L248="","",$C248*$L248)</f>
       </c>
       <c r="N248" s="119" t="str">
-        <f>IF($M248="","",ROUNDDOWN($C248+$M248,2))</f>
+        <f>IF($M248="","",ROUNDUP($C248+$M248,2))</f>
       </c>
       <c r="O248" s="120" t="str">
-        <f>IF($N248="","",ROUNDDOWN(ROUNDDOWN($N248,2)*$E248,3))</f>
+        <f>IF($N248="","",ROUNDUP(ROUNDUP($N248,2)*$E248,3))</f>
       </c>
       <c r="P248" s="121" t="str">
         <f>IF($L248="","",$I248*$L248)</f>
@@ -14606,10 +14607,10 @@
         <f>IF($L249="","",$C249*$L249)</f>
       </c>
       <c r="N249" s="119" t="str">
-        <f>IF($M249="","",ROUNDDOWN($C249+$M249,2))</f>
+        <f>IF($M249="","",ROUNDUP($C249+$M249,2))</f>
       </c>
       <c r="O249" s="120" t="str">
-        <f>IF($N249="","",ROUNDDOWN(ROUNDDOWN($N249,2)*$E249,3))</f>
+        <f>IF($N249="","",ROUNDUP(ROUNDUP($N249,2)*$E249,3))</f>
       </c>
       <c r="P249" s="121" t="str">
         <f>IF($L249="","",$I249*$L249)</f>
@@ -14660,10 +14661,10 @@
         <f>IF($L250="","",$C250*$L250)</f>
       </c>
       <c r="N250" s="119" t="str">
-        <f>IF($M250="","",ROUNDDOWN($C250+$M250,2))</f>
+        <f>IF($M250="","",ROUNDUP($C250+$M250,2))</f>
       </c>
       <c r="O250" s="120" t="str">
-        <f>IF($N250="","",ROUNDDOWN(ROUNDDOWN($N250,2)*$E250,3))</f>
+        <f>IF($N250="","",ROUNDUP(ROUNDUP($N250,2)*$E250,3))</f>
       </c>
       <c r="P250" s="121" t="str">
         <f>IF($L250="","",$I250*$L250)</f>
@@ -14714,10 +14715,10 @@
         <f>IF($L251="","",$C251*$L251)</f>
       </c>
       <c r="N251" s="119" t="str">
-        <f>IF($M251="","",ROUNDDOWN($C251+$M251,2))</f>
+        <f>IF($M251="","",ROUNDUP($C251+$M251,2))</f>
       </c>
       <c r="O251" s="120" t="str">
-        <f>IF($N251="","",ROUNDDOWN(ROUNDDOWN($N251,2)*$E251,3))</f>
+        <f>IF($N251="","",ROUNDUP(ROUNDUP($N251,2)*$E251,3))</f>
       </c>
       <c r="P251" s="121" t="str">
         <f>IF($L251="","",$I251*$L251)</f>
@@ -14768,10 +14769,10 @@
         <f>IF($L252="","",$C252*$L252)</f>
       </c>
       <c r="N252" s="119" t="str">
-        <f>IF($M252="","",ROUNDDOWN($C252+$M252,2))</f>
+        <f>IF($M252="","",ROUNDUP($C252+$M252,2))</f>
       </c>
       <c r="O252" s="120" t="str">
-        <f>IF($N252="","",ROUNDDOWN(ROUNDDOWN($N252,2)*$E252,3))</f>
+        <f>IF($N252="","",ROUNDUP(ROUNDUP($N252,2)*$E252,3))</f>
       </c>
       <c r="P252" s="121" t="str">
         <f>IF($L252="","",$I252*$L252)</f>
@@ -14822,10 +14823,10 @@
         <f>IF($L253="","",$C253*$L253)</f>
       </c>
       <c r="N253" s="119" t="str">
-        <f>IF($M253="","",ROUNDDOWN($C253+$M253,2))</f>
+        <f>IF($M253="","",ROUNDUP($C253+$M253,2))</f>
       </c>
       <c r="O253" s="120" t="str">
-        <f>IF($N253="","",ROUNDDOWN(ROUNDDOWN($N253,2)*$E253,3))</f>
+        <f>IF($N253="","",ROUNDUP(ROUNDUP($N253,2)*$E253,3))</f>
       </c>
       <c r="P253" s="121" t="str">
         <f>IF($L253="","",$I253*$L253)</f>
@@ -14876,10 +14877,10 @@
         <f>IF($L254="","",$C254*$L254)</f>
       </c>
       <c r="N254" s="119" t="str">
-        <f>IF($M254="","",ROUNDDOWN($C254+$M254,2))</f>
+        <f>IF($M254="","",ROUNDUP($C254+$M254,2))</f>
       </c>
       <c r="O254" s="120" t="str">
-        <f>IF($N254="","",ROUNDDOWN(ROUNDDOWN($N254,2)*$E254,3))</f>
+        <f>IF($N254="","",ROUNDUP(ROUNDUP($N254,2)*$E254,3))</f>
       </c>
       <c r="P254" s="121" t="str">
         <f>IF($L254="","",$I254*$L254)</f>
@@ -14930,10 +14931,10 @@
         <f>IF($L255="","",$C255*$L255)</f>
       </c>
       <c r="N255" s="119" t="str">
-        <f>IF($M255="","",ROUNDDOWN($C255+$M255,2))</f>
+        <f>IF($M255="","",ROUNDUP($C255+$M255,2))</f>
       </c>
       <c r="O255" s="120" t="str">
-        <f>IF($N255="","",ROUNDDOWN(ROUNDDOWN($N255,2)*$E255,3))</f>
+        <f>IF($N255="","",ROUNDUP(ROUNDUP($N255,2)*$E255,3))</f>
       </c>
       <c r="P255" s="121" t="str">
         <f>IF($L255="","",$I255*$L255)</f>
@@ -14984,10 +14985,10 @@
         <f>IF($L256="","",$C256*$L256)</f>
       </c>
       <c r="N256" s="119" t="str">
-        <f>IF($M256="","",ROUNDDOWN($C256+$M256,2))</f>
+        <f>IF($M256="","",ROUNDUP($C256+$M256,2))</f>
       </c>
       <c r="O256" s="120" t="str">
-        <f>IF($N256="","",ROUNDDOWN(ROUNDDOWN($N256,2)*$E256,3))</f>
+        <f>IF($N256="","",ROUNDUP(ROUNDUP($N256,2)*$E256,3))</f>
       </c>
       <c r="P256" s="121" t="str">
         <f>IF($L256="","",$I256*$L256)</f>
@@ -15038,10 +15039,10 @@
         <f>IF($L257="","",$C257*$L257)</f>
       </c>
       <c r="N257" s="119" t="str">
-        <f>IF($M257="","",ROUNDDOWN($C257+$M257,2))</f>
+        <f>IF($M257="","",ROUNDUP($C257+$M257,2))</f>
       </c>
       <c r="O257" s="120" t="str">
-        <f>IF($N257="","",ROUNDDOWN(ROUNDDOWN($N257,2)*$E257,3))</f>
+        <f>IF($N257="","",ROUNDUP(ROUNDUP($N257,2)*$E257,3))</f>
       </c>
       <c r="P257" s="121" t="str">
         <f>IF($L257="","",$I257*$L257)</f>
@@ -15092,10 +15093,10 @@
         <f>IF($L258="","",$C258*$L258)</f>
       </c>
       <c r="N258" s="119" t="str">
-        <f>IF($M258="","",ROUNDDOWN($C258+$M258,2))</f>
+        <f>IF($M258="","",ROUNDUP($C258+$M258,2))</f>
       </c>
       <c r="O258" s="120" t="str">
-        <f>IF($N258="","",ROUNDDOWN(ROUNDDOWN($N258,2)*$E258,3))</f>
+        <f>IF($N258="","",ROUNDUP(ROUNDUP($N258,2)*$E258,3))</f>
       </c>
       <c r="P258" s="121" t="str">
         <f>IF($L258="","",$I258*$L258)</f>
@@ -15146,10 +15147,10 @@
         <f>IF($L259="","",$C259*$L259)</f>
       </c>
       <c r="N259" s="119" t="str">
-        <f>IF($M259="","",ROUNDDOWN($C259+$M259,2))</f>
+        <f>IF($M259="","",ROUNDUP($C259+$M259,2))</f>
       </c>
       <c r="O259" s="120" t="str">
-        <f>IF($N259="","",ROUNDDOWN(ROUNDDOWN($N259,2)*$E259,3))</f>
+        <f>IF($N259="","",ROUNDUP(ROUNDUP($N259,2)*$E259,3))</f>
       </c>
       <c r="P259" s="121" t="str">
         <f>IF($L259="","",$I259*$L259)</f>
@@ -15200,10 +15201,10 @@
         <f>IF($L260="","",$C260*$L260)</f>
       </c>
       <c r="N260" s="119" t="str">
-        <f>IF($M260="","",ROUNDDOWN($C260+$M260,2))</f>
+        <f>IF($M260="","",ROUNDUP($C260+$M260,2))</f>
       </c>
       <c r="O260" s="120" t="str">
-        <f>IF($N260="","",ROUNDDOWN(ROUNDDOWN($N260,2)*$E260,3))</f>
+        <f>IF($N260="","",ROUNDUP(ROUNDUP($N260,2)*$E260,3))</f>
       </c>
       <c r="P260" s="121" t="str">
         <f>IF($L260="","",$I260*$L260)</f>
@@ -15254,10 +15255,10 @@
         <f>IF($L261="","",$C261*$L261)</f>
       </c>
       <c r="N261" s="119" t="str">
-        <f>IF($M261="","",ROUNDDOWN($C261+$M261,2))</f>
+        <f>IF($M261="","",ROUNDUP($C261+$M261,2))</f>
       </c>
       <c r="O261" s="120" t="str">
-        <f>IF($N261="","",ROUNDDOWN(ROUNDDOWN($N261,2)*$E261,3))</f>
+        <f>IF($N261="","",ROUNDUP(ROUNDUP($N261,2)*$E261,3))</f>
       </c>
       <c r="P261" s="121" t="str">
         <f>IF($L261="","",$I261*$L261)</f>
@@ -15308,10 +15309,10 @@
         <f>IF($L262="","",$C262*$L262)</f>
       </c>
       <c r="N262" s="119" t="str">
-        <f>IF($M262="","",ROUNDDOWN($C262+$M262,2))</f>
+        <f>IF($M262="","",ROUNDUP($C262+$M262,2))</f>
       </c>
       <c r="O262" s="120" t="str">
-        <f>IF($N262="","",ROUNDDOWN(ROUNDDOWN($N262,2)*$E262,3))</f>
+        <f>IF($N262="","",ROUNDUP(ROUNDUP($N262,2)*$E262,3))</f>
       </c>
       <c r="P262" s="121" t="str">
         <f>IF($L262="","",$I262*$L262)</f>
@@ -15362,10 +15363,10 @@
         <f>IF($L263="","",$C263*$L263)</f>
       </c>
       <c r="N263" s="119" t="str">
-        <f>IF($M263="","",ROUNDDOWN($C263+$M263,2))</f>
+        <f>IF($M263="","",ROUNDUP($C263+$M263,2))</f>
       </c>
       <c r="O263" s="120" t="str">
-        <f>IF($N263="","",ROUNDDOWN(ROUNDDOWN($N263,2)*$E263,3))</f>
+        <f>IF($N263="","",ROUNDUP(ROUNDUP($N263,2)*$E263,3))</f>
       </c>
       <c r="P263" s="121" t="str">
         <f>IF($L263="","",$I263*$L263)</f>
@@ -15416,10 +15417,10 @@
         <f>IF($L264="","",$C264*$L264)</f>
       </c>
       <c r="N264" s="119" t="str">
-        <f>IF($M264="","",ROUNDDOWN($C264+$M264,2))</f>
+        <f>IF($M264="","",ROUNDUP($C264+$M264,2))</f>
       </c>
       <c r="O264" s="120" t="str">
-        <f>IF($N264="","",ROUNDDOWN(ROUNDDOWN($N264,2)*$E264,3))</f>
+        <f>IF($N264="","",ROUNDUP(ROUNDUP($N264,2)*$E264,3))</f>
       </c>
       <c r="P264" s="121" t="str">
         <f>IF($L264="","",$I264*$L264)</f>
@@ -15470,10 +15471,10 @@
         <f>IF($L265="","",$C265*$L265)</f>
       </c>
       <c r="N265" s="119" t="str">
-        <f>IF($M265="","",ROUNDDOWN($C265+$M265,2))</f>
+        <f>IF($M265="","",ROUNDUP($C265+$M265,2))</f>
       </c>
       <c r="O265" s="120" t="str">
-        <f>IF($N265="","",ROUNDDOWN(ROUNDDOWN($N265,2)*$E265,3))</f>
+        <f>IF($N265="","",ROUNDUP(ROUNDUP($N265,2)*$E265,3))</f>
       </c>
       <c r="P265" s="121" t="str">
         <f>IF($L265="","",$I265*$L265)</f>
@@ -15524,10 +15525,10 @@
         <f>IF($L266="","",$C266*$L266)</f>
       </c>
       <c r="N266" s="119" t="str">
-        <f>IF($M266="","",ROUNDDOWN($C266+$M266,2))</f>
+        <f>IF($M266="","",ROUNDUP($C266+$M266,2))</f>
       </c>
       <c r="O266" s="120" t="str">
-        <f>IF($N266="","",ROUNDDOWN(ROUNDDOWN($N266,2)*$E266,3))</f>
+        <f>IF($N266="","",ROUNDUP(ROUNDUP($N266,2)*$E266,3))</f>
       </c>
       <c r="P266" s="121" t="str">
         <f>IF($L266="","",$I266*$L266)</f>
@@ -15578,10 +15579,10 @@
         <f>IF($L267="","",$C267*$L267)</f>
       </c>
       <c r="N267" s="119" t="str">
-        <f>IF($M267="","",ROUNDDOWN($C267+$M267,2))</f>
+        <f>IF($M267="","",ROUNDUP($C267+$M267,2))</f>
       </c>
       <c r="O267" s="120" t="str">
-        <f>IF($N267="","",ROUNDDOWN(ROUNDDOWN($N267,2)*$E267,3))</f>
+        <f>IF($N267="","",ROUNDUP(ROUNDUP($N267,2)*$E267,3))</f>
       </c>
       <c r="P267" s="121" t="str">
         <f>IF($L267="","",$I267*$L267)</f>
@@ -15632,10 +15633,10 @@
         <f>IF($L268="","",$C268*$L268)</f>
       </c>
       <c r="N268" s="119" t="str">
-        <f>IF($M268="","",ROUNDDOWN($C268+$M268,2))</f>
+        <f>IF($M268="","",ROUNDUP($C268+$M268,2))</f>
       </c>
       <c r="O268" s="120" t="str">
-        <f>IF($N268="","",ROUNDDOWN(ROUNDDOWN($N268,2)*$E268,3))</f>
+        <f>IF($N268="","",ROUNDUP(ROUNDUP($N268,2)*$E268,3))</f>
       </c>
       <c r="P268" s="121" t="str">
         <f>IF($L268="","",$I268*$L268)</f>
@@ -15686,10 +15687,10 @@
         <f>IF($L269="","",$C269*$L269)</f>
       </c>
       <c r="N269" s="119" t="str">
-        <f>IF($M269="","",ROUNDDOWN($C269+$M269,2))</f>
+        <f>IF($M269="","",ROUNDUP($C269+$M269,2))</f>
       </c>
       <c r="O269" s="120" t="str">
-        <f>IF($N269="","",ROUNDDOWN(ROUNDDOWN($N269,2)*$E269,3))</f>
+        <f>IF($N269="","",ROUNDUP(ROUNDUP($N269,2)*$E269,3))</f>
       </c>
       <c r="P269" s="121" t="str">
         <f>IF($L269="","",$I269*$L269)</f>
@@ -15740,10 +15741,10 @@
         <f>IF($L270="","",$C270*$L270)</f>
       </c>
       <c r="N270" s="119" t="str">
-        <f>IF($M270="","",ROUNDDOWN($C270+$M270,2))</f>
+        <f>IF($M270="","",ROUNDUP($C270+$M270,2))</f>
       </c>
       <c r="O270" s="120" t="str">
-        <f>IF($N270="","",ROUNDDOWN(ROUNDDOWN($N270,2)*$E270,3))</f>
+        <f>IF($N270="","",ROUNDUP(ROUNDUP($N270,2)*$E270,3))</f>
       </c>
       <c r="P270" s="121" t="str">
         <f>IF($L270="","",$I270*$L270)</f>
@@ -15794,10 +15795,10 @@
         <f>IF($L271="","",$C271*$L271)</f>
       </c>
       <c r="N271" s="119" t="str">
-        <f>IF($M271="","",ROUNDDOWN($C271+$M271,2))</f>
+        <f>IF($M271="","",ROUNDUP($C271+$M271,2))</f>
       </c>
       <c r="O271" s="120" t="str">
-        <f>IF($N271="","",ROUNDDOWN(ROUNDDOWN($N271,2)*$E271,3))</f>
+        <f>IF($N271="","",ROUNDUP(ROUNDUP($N271,2)*$E271,3))</f>
       </c>
       <c r="P271" s="121" t="str">
         <f>IF($L271="","",$I271*$L271)</f>
@@ -15848,10 +15849,10 @@
         <f>IF($L272="","",$C272*$L272)</f>
       </c>
       <c r="N272" s="119" t="str">
-        <f>IF($M272="","",ROUNDDOWN($C272+$M272,2))</f>
+        <f>IF($M272="","",ROUNDUP($C272+$M272,2))</f>
       </c>
       <c r="O272" s="120" t="str">
-        <f>IF($N272="","",ROUNDDOWN(ROUNDDOWN($N272,2)*$E272,3))</f>
+        <f>IF($N272="","",ROUNDUP(ROUNDUP($N272,2)*$E272,3))</f>
       </c>
       <c r="P272" s="121" t="str">
         <f>IF($L272="","",$I272*$L272)</f>
@@ -15902,10 +15903,10 @@
         <f>IF($L273="","",$C273*$L273)</f>
       </c>
       <c r="N273" s="119" t="str">
-        <f>IF($M273="","",ROUNDDOWN($C273+$M273,2))</f>
+        <f>IF($M273="","",ROUNDUP($C273+$M273,2))</f>
       </c>
       <c r="O273" s="120" t="str">
-        <f>IF($N273="","",ROUNDDOWN(ROUNDDOWN($N273,2)*$E273,3))</f>
+        <f>IF($N273="","",ROUNDUP(ROUNDUP($N273,2)*$E273,3))</f>
       </c>
       <c r="P273" s="121" t="str">
         <f>IF($L273="","",$I273*$L273)</f>
@@ -15956,10 +15957,10 @@
         <f>IF($L274="","",$C274*$L274)</f>
       </c>
       <c r="N274" s="119" t="str">
-        <f>IF($M274="","",ROUNDDOWN($C274+$M274,2))</f>
+        <f>IF($M274="","",ROUNDUP($C274+$M274,2))</f>
       </c>
       <c r="O274" s="120" t="str">
-        <f>IF($N274="","",ROUNDDOWN(ROUNDDOWN($N274,2)*$E274,3))</f>
+        <f>IF($N274="","",ROUNDUP(ROUNDUP($N274,2)*$E274,3))</f>
       </c>
       <c r="P274" s="121" t="str">
         <f>IF($L274="","",$I274*$L274)</f>
@@ -16010,10 +16011,10 @@
         <f>IF($L275="","",$C275*$L275)</f>
       </c>
       <c r="N275" s="119" t="str">
-        <f>IF($M275="","",ROUNDDOWN($C275+$M275,2))</f>
+        <f>IF($M275="","",ROUNDUP($C275+$M275,2))</f>
       </c>
       <c r="O275" s="120" t="str">
-        <f>IF($N275="","",ROUNDDOWN(ROUNDDOWN($N275,2)*$E275,3))</f>
+        <f>IF($N275="","",ROUNDUP(ROUNDUP($N275,2)*$E275,3))</f>
       </c>
       <c r="P275" s="121" t="str">
         <f>IF($L275="","",$I275*$L275)</f>
@@ -16064,10 +16065,10 @@
         <f>IF($L276="","",$C276*$L276)</f>
       </c>
       <c r="N276" s="119" t="str">
-        <f>IF($M276="","",ROUNDDOWN($C276+$M276,2))</f>
+        <f>IF($M276="","",ROUNDUP($C276+$M276,2))</f>
       </c>
       <c r="O276" s="120" t="str">
-        <f>IF($N276="","",ROUNDDOWN(ROUNDDOWN($N276,2)*$E276,3))</f>
+        <f>IF($N276="","",ROUNDUP(ROUNDUP($N276,2)*$E276,3))</f>
       </c>
       <c r="P276" s="121" t="str">
         <f>IF($L276="","",$I276*$L276)</f>
@@ -16118,10 +16119,10 @@
         <f>IF($L277="","",$C277*$L277)</f>
       </c>
       <c r="N277" s="119" t="str">
-        <f>IF($M277="","",ROUNDDOWN($C277+$M277,2))</f>
+        <f>IF($M277="","",ROUNDUP($C277+$M277,2))</f>
       </c>
       <c r="O277" s="120" t="str">
-        <f>IF($N277="","",ROUNDDOWN(ROUNDDOWN($N277,2)*$E277,3))</f>
+        <f>IF($N277="","",ROUNDUP(ROUNDUP($N277,2)*$E277,3))</f>
       </c>
       <c r="P277" s="121" t="str">
         <f>IF($L277="","",$I277*$L277)</f>
@@ -16172,10 +16173,10 @@
         <f>IF($L278="","",$C278*$L278)</f>
       </c>
       <c r="N278" s="119" t="str">
-        <f>IF($M278="","",ROUNDDOWN($C278+$M278,2))</f>
+        <f>IF($M278="","",ROUNDUP($C278+$M278,2))</f>
       </c>
       <c r="O278" s="120" t="str">
-        <f>IF($N278="","",ROUNDDOWN(ROUNDDOWN($N278,2)*$E278,3))</f>
+        <f>IF($N278="","",ROUNDUP(ROUNDUP($N278,2)*$E278,3))</f>
       </c>
       <c r="P278" s="121" t="str">
         <f>IF($L278="","",$I278*$L278)</f>
@@ -16226,10 +16227,10 @@
         <f>IF($L279="","",$C279*$L279)</f>
       </c>
       <c r="N279" s="119" t="str">
-        <f>IF($M279="","",ROUNDDOWN($C279+$M279,2))</f>
+        <f>IF($M279="","",ROUNDUP($C279+$M279,2))</f>
       </c>
       <c r="O279" s="120" t="str">
-        <f>IF($N279="","",ROUNDDOWN(ROUNDDOWN($N279,2)*$E279,3))</f>
+        <f>IF($N279="","",ROUNDUP(ROUNDUP($N279,2)*$E279,3))</f>
       </c>
       <c r="P279" s="121" t="str">
         <f>IF($L279="","",$I279*$L279)</f>
@@ -16280,10 +16281,10 @@
         <f>IF($L280="","",$C280*$L280)</f>
       </c>
       <c r="N280" s="119" t="str">
-        <f>IF($M280="","",ROUNDDOWN($C280+$M280,2))</f>
+        <f>IF($M280="","",ROUNDUP($C280+$M280,2))</f>
       </c>
       <c r="O280" s="120" t="str">
-        <f>IF($N280="","",ROUNDDOWN(ROUNDDOWN($N280,2)*$E280,3))</f>
+        <f>IF($N280="","",ROUNDUP(ROUNDUP($N280,2)*$E280,3))</f>
       </c>
       <c r="P280" s="121" t="str">
         <f>IF($L280="","",$I280*$L280)</f>
@@ -16334,10 +16335,10 @@
         <f>IF($L281="","",$C281*$L281)</f>
       </c>
       <c r="N281" s="119" t="str">
-        <f>IF($M281="","",ROUNDDOWN($C281+$M281,2))</f>
+        <f>IF($M281="","",ROUNDUP($C281+$M281,2))</f>
       </c>
       <c r="O281" s="120" t="str">
-        <f>IF($N281="","",ROUNDDOWN(ROUNDDOWN($N281,2)*$E281,3))</f>
+        <f>IF($N281="","",ROUNDUP(ROUNDUP($N281,2)*$E281,3))</f>
       </c>
       <c r="P281" s="121" t="str">
         <f>IF($L281="","",$I281*$L281)</f>
@@ -16388,10 +16389,10 @@
         <f>IF($L282="","",$C282*$L282)</f>
       </c>
       <c r="N282" s="119" t="str">
-        <f>IF($M282="","",ROUNDDOWN($C282+$M282,2))</f>
+        <f>IF($M282="","",ROUNDUP($C282+$M282,2))</f>
       </c>
       <c r="O282" s="120" t="str">
-        <f>IF($N282="","",ROUNDDOWN(ROUNDDOWN($N282,2)*$E282,3))</f>
+        <f>IF($N282="","",ROUNDUP(ROUNDUP($N282,2)*$E282,3))</f>
       </c>
       <c r="P282" s="121" t="str">
         <f>IF($L282="","",$I282*$L282)</f>
@@ -16442,10 +16443,10 @@
         <f>IF($L283="","",$C283*$L283)</f>
       </c>
       <c r="N283" s="119" t="str">
-        <f>IF($M283="","",ROUNDDOWN($C283+$M283,2))</f>
+        <f>IF($M283="","",ROUNDUP($C283+$M283,2))</f>
       </c>
       <c r="O283" s="120" t="str">
-        <f>IF($N283="","",ROUNDDOWN(ROUNDDOWN($N283,2)*$E283,3))</f>
+        <f>IF($N283="","",ROUNDUP(ROUNDUP($N283,2)*$E283,3))</f>
       </c>
       <c r="P283" s="121" t="str">
         <f>IF($L283="","",$I283*$L283)</f>
@@ -16496,10 +16497,10 @@
         <f>IF($L284="","",$C284*$L284)</f>
       </c>
       <c r="N284" s="119" t="str">
-        <f>IF($M284="","",ROUNDDOWN($C284+$M284,2))</f>
+        <f>IF($M284="","",ROUNDUP($C284+$M284,2))</f>
       </c>
       <c r="O284" s="120" t="str">
-        <f>IF($N284="","",ROUNDDOWN(ROUNDDOWN($N284,2)*$E284,3))</f>
+        <f>IF($N284="","",ROUNDUP(ROUNDUP($N284,2)*$E284,3))</f>
       </c>
       <c r="P284" s="121" t="str">
         <f>IF($L284="","",$I284*$L284)</f>
@@ -16550,10 +16551,10 @@
         <f>IF($L285="","",$C285*$L285)</f>
       </c>
       <c r="N285" s="119" t="str">
-        <f>IF($M285="","",ROUNDDOWN($C285+$M285,2))</f>
+        <f>IF($M285="","",ROUNDUP($C285+$M285,2))</f>
       </c>
       <c r="O285" s="120" t="str">
-        <f>IF($N285="","",ROUNDDOWN(ROUNDDOWN($N285,2)*$E285,3))</f>
+        <f>IF($N285="","",ROUNDUP(ROUNDUP($N285,2)*$E285,3))</f>
       </c>
       <c r="P285" s="121" t="str">
         <f>IF($L285="","",$I285*$L285)</f>
@@ -16604,10 +16605,10 @@
         <f>IF($L286="","",$C286*$L286)</f>
       </c>
       <c r="N286" s="119" t="str">
-        <f>IF($M286="","",ROUNDDOWN($C286+$M286,2))</f>
+        <f>IF($M286="","",ROUNDUP($C286+$M286,2))</f>
       </c>
       <c r="O286" s="120" t="str">
-        <f>IF($N286="","",ROUNDDOWN(ROUNDDOWN($N286,2)*$E286,3))</f>
+        <f>IF($N286="","",ROUNDUP(ROUNDUP($N286,2)*$E286,3))</f>
       </c>
       <c r="P286" s="121" t="str">
         <f>IF($L286="","",$I286*$L286)</f>
@@ -16658,10 +16659,10 @@
         <f>IF($L287="","",$C287*$L287)</f>
       </c>
       <c r="N287" s="119" t="str">
-        <f>IF($M287="","",ROUNDDOWN($C287+$M287,2))</f>
+        <f>IF($M287="","",ROUNDUP($C287+$M287,2))</f>
       </c>
       <c r="O287" s="120" t="str">
-        <f>IF($N287="","",ROUNDDOWN(ROUNDDOWN($N287,2)*$E287,3))</f>
+        <f>IF($N287="","",ROUNDUP(ROUNDUP($N287,2)*$E287,3))</f>
       </c>
       <c r="P287" s="121" t="str">
         <f>IF($L287="","",$I287*$L287)</f>
@@ -16712,10 +16713,10 @@
         <f>IF($L288="","",$C288*$L288)</f>
       </c>
       <c r="N288" s="119" t="str">
-        <f>IF($M288="","",ROUNDDOWN($C288+$M288,2))</f>
+        <f>IF($M288="","",ROUNDUP($C288+$M288,2))</f>
       </c>
       <c r="O288" s="120" t="str">
-        <f>IF($N288="","",ROUNDDOWN(ROUNDDOWN($N288,2)*$E288,3))</f>
+        <f>IF($N288="","",ROUNDUP(ROUNDUP($N288,2)*$E288,3))</f>
       </c>
       <c r="P288" s="121" t="str">
         <f>IF($L288="","",$I288*$L288)</f>
@@ -16766,10 +16767,10 @@
         <f>IF($L289="","",$C289*$L289)</f>
       </c>
       <c r="N289" s="119" t="str">
-        <f>IF($M289="","",ROUNDDOWN($C289+$M289,2))</f>
+        <f>IF($M289="","",ROUNDUP($C289+$M289,2))</f>
       </c>
       <c r="O289" s="120" t="str">
-        <f>IF($N289="","",ROUNDDOWN(ROUNDDOWN($N289,2)*$E289,3))</f>
+        <f>IF($N289="","",ROUNDUP(ROUNDUP($N289,2)*$E289,3))</f>
       </c>
       <c r="P289" s="121" t="str">
         <f>IF($L289="","",$I289*$L289)</f>
@@ -16820,10 +16821,10 @@
         <f>IF($L290="","",$C290*$L290)</f>
       </c>
       <c r="N290" s="119" t="str">
-        <f>IF($M290="","",ROUNDDOWN($C290+$M290,2))</f>
+        <f>IF($M290="","",ROUNDUP($C290+$M290,2))</f>
       </c>
       <c r="O290" s="120" t="str">
-        <f>IF($N290="","",ROUNDDOWN(ROUNDDOWN($N290,2)*$E290,3))</f>
+        <f>IF($N290="","",ROUNDUP(ROUNDUP($N290,2)*$E290,3))</f>
       </c>
       <c r="P290" s="121" t="str">
         <f>IF($L290="","",$I290*$L290)</f>
@@ -16874,10 +16875,10 @@
         <f>IF($L291="","",$C291*$L291)</f>
       </c>
       <c r="N291" s="119" t="str">
-        <f>IF($M291="","",ROUNDDOWN($C291+$M291,2))</f>
+        <f>IF($M291="","",ROUNDUP($C291+$M291,2))</f>
       </c>
       <c r="O291" s="120" t="str">
-        <f>IF($N291="","",ROUNDDOWN(ROUNDDOWN($N291,2)*$E291,3))</f>
+        <f>IF($N291="","",ROUNDUP(ROUNDUP($N291,2)*$E291,3))</f>
       </c>
       <c r="P291" s="121" t="str">
         <f>IF($L291="","",$I291*$L291)</f>
@@ -16928,10 +16929,10 @@
         <f>IF($L292="","",$C292*$L292)</f>
       </c>
       <c r="N292" s="119" t="str">
-        <f>IF($M292="","",ROUNDDOWN($C292+$M292,2))</f>
+        <f>IF($M292="","",ROUNDUP($C292+$M292,2))</f>
       </c>
       <c r="O292" s="120" t="str">
-        <f>IF($N292="","",ROUNDDOWN(ROUNDDOWN($N292,2)*$E292,3))</f>
+        <f>IF($N292="","",ROUNDUP(ROUNDUP($N292,2)*$E292,3))</f>
       </c>
       <c r="P292" s="121" t="str">
         <f>IF($L292="","",$I292*$L292)</f>
@@ -16982,10 +16983,10 @@
         <f>IF($L293="","",$C293*$L293)</f>
       </c>
       <c r="N293" s="119" t="str">
-        <f>IF($M293="","",ROUNDDOWN($C293+$M293,2))</f>
+        <f>IF($M293="","",ROUNDUP($C293+$M293,2))</f>
       </c>
       <c r="O293" s="120" t="str">
-        <f>IF($N293="","",ROUNDDOWN(ROUNDDOWN($N293,2)*$E293,3))</f>
+        <f>IF($N293="","",ROUNDUP(ROUNDUP($N293,2)*$E293,3))</f>
       </c>
       <c r="P293" s="121" t="str">
         <f>IF($L293="","",$I293*$L293)</f>
@@ -17036,10 +17037,10 @@
         <f>IF($L294="","",$C294*$L294)</f>
       </c>
       <c r="N294" s="119" t="str">
-        <f>IF($M294="","",ROUNDDOWN($C294+$M294,2))</f>
+        <f>IF($M294="","",ROUNDUP($C294+$M294,2))</f>
       </c>
       <c r="O294" s="120" t="str">
-        <f>IF($N294="","",ROUNDDOWN(ROUNDDOWN($N294,2)*$E294,3))</f>
+        <f>IF($N294="","",ROUNDUP(ROUNDUP($N294,2)*$E294,3))</f>
       </c>
       <c r="P294" s="121" t="str">
         <f>IF($L294="","",$I294*$L294)</f>
@@ -17090,10 +17091,10 @@
         <f>IF($L295="","",$C295*$L295)</f>
       </c>
       <c r="N295" s="119" t="str">
-        <f>IF($M295="","",ROUNDDOWN($C295+$M295,2))</f>
+        <f>IF($M295="","",ROUNDUP($C295+$M295,2))</f>
       </c>
       <c r="O295" s="120" t="str">
-        <f>IF($N295="","",ROUNDDOWN(ROUNDDOWN($N295,2)*$E295,3))</f>
+        <f>IF($N295="","",ROUNDUP(ROUNDUP($N295,2)*$E295,3))</f>
       </c>
       <c r="P295" s="121" t="str">
         <f>IF($L295="","",$I295*$L295)</f>
@@ -17144,10 +17145,10 @@
         <f>IF($L296="","",$C296*$L296)</f>
       </c>
       <c r="N296" s="119" t="str">
-        <f>IF($M296="","",ROUNDDOWN($C296+$M296,2))</f>
+        <f>IF($M296="","",ROUNDUP($C296+$M296,2))</f>
       </c>
       <c r="O296" s="120" t="str">
-        <f>IF($N296="","",ROUNDDOWN(ROUNDDOWN($N296,2)*$E296,3))</f>
+        <f>IF($N296="","",ROUNDUP(ROUNDUP($N296,2)*$E296,3))</f>
       </c>
       <c r="P296" s="121" t="str">
         <f>IF($L296="","",$I296*$L296)</f>
@@ -17198,10 +17199,10 @@
         <f>IF($L297="","",$C297*$L297)</f>
       </c>
       <c r="N297" s="119" t="str">
-        <f>IF($M297="","",ROUNDDOWN($C297+$M297,2))</f>
+        <f>IF($M297="","",ROUNDUP($C297+$M297,2))</f>
       </c>
       <c r="O297" s="120" t="str">
-        <f>IF($N297="","",ROUNDDOWN(ROUNDDOWN($N297,2)*$E297,3))</f>
+        <f>IF($N297="","",ROUNDUP(ROUNDUP($N297,2)*$E297,3))</f>
       </c>
       <c r="P297" s="121" t="str">
         <f>IF($L297="","",$I297*$L297)</f>
@@ -17252,10 +17253,10 @@
         <f>IF($L298="","",$C298*$L298)</f>
       </c>
       <c r="N298" s="119" t="str">
-        <f>IF($M298="","",ROUNDDOWN($C298+$M298,2))</f>
+        <f>IF($M298="","",ROUNDUP($C298+$M298,2))</f>
       </c>
       <c r="O298" s="120" t="str">
-        <f>IF($N298="","",ROUNDDOWN(ROUNDDOWN($N298,2)*$E298,3))</f>
+        <f>IF($N298="","",ROUNDUP(ROUNDUP($N298,2)*$E298,3))</f>
       </c>
       <c r="P298" s="121" t="str">
         <f>IF($L298="","",$I298*$L298)</f>
@@ -17306,10 +17307,10 @@
         <f>IF($L299="","",$C299*$L299)</f>
       </c>
       <c r="N299" s="119" t="str">
-        <f>IF($M299="","",ROUNDDOWN($C299+$M299,2))</f>
+        <f>IF($M299="","",ROUNDUP($C299+$M299,2))</f>
       </c>
       <c r="O299" s="120" t="str">
-        <f>IF($N299="","",ROUNDDOWN(ROUNDDOWN($N299,2)*$E299,3))</f>
+        <f>IF($N299="","",ROUNDUP(ROUNDUP($N299,2)*$E299,3))</f>
       </c>
       <c r="P299" s="121" t="str">
         <f>IF($L299="","",$I299*$L299)</f>
@@ -17360,10 +17361,10 @@
         <f>IF($L300="","",$C300*$L300)</f>
       </c>
       <c r="N300" s="119" t="str">
-        <f>IF($M300="","",ROUNDDOWN($C300+$M300,2))</f>
+        <f>IF($M300="","",ROUNDUP($C300+$M300,2))</f>
       </c>
       <c r="O300" s="120" t="str">
-        <f>IF($N300="","",ROUNDDOWN(ROUNDDOWN($N300,2)*$E300,3))</f>
+        <f>IF($N300="","",ROUNDUP(ROUNDUP($N300,2)*$E300,3))</f>
       </c>
       <c r="P300" s="121" t="str">
         <f>IF($L300="","",$I300*$L300)</f>
@@ -17414,10 +17415,10 @@
         <f>IF($L301="","",$C301*$L301)</f>
       </c>
       <c r="N301" s="119" t="str">
-        <f>IF($M301="","",ROUNDDOWN($C301+$M301,2))</f>
+        <f>IF($M301="","",ROUNDUP($C301+$M301,2))</f>
       </c>
       <c r="O301" s="120" t="str">
-        <f>IF($N301="","",ROUNDDOWN(ROUNDDOWN($N301,2)*$E301,3))</f>
+        <f>IF($N301="","",ROUNDUP(ROUNDUP($N301,2)*$E301,3))</f>
       </c>
       <c r="P301" s="121" t="str">
         <f>IF($L301="","",$I301*$L301)</f>
@@ -17468,10 +17469,10 @@
         <f>IF($L302="","",$C302*$L302)</f>
       </c>
       <c r="N302" s="119" t="str">
-        <f>IF($M302="","",ROUNDDOWN($C302+$M302,2))</f>
+        <f>IF($M302="","",ROUNDUP($C302+$M302,2))</f>
       </c>
       <c r="O302" s="120" t="str">
-        <f>IF($N302="","",ROUNDDOWN(ROUNDDOWN($N302,2)*$E302,3))</f>
+        <f>IF($N302="","",ROUNDUP(ROUNDUP($N302,2)*$E302,3))</f>
       </c>
       <c r="P302" s="121" t="str">
         <f>IF($L302="","",$I302*$L302)</f>
@@ -17522,10 +17523,10 @@
         <f>IF($L303="","",$C303*$L303)</f>
       </c>
       <c r="N303" s="119" t="str">
-        <f>IF($M303="","",ROUNDDOWN($C303+$M303,2))</f>
+        <f>IF($M303="","",ROUNDUP($C303+$M303,2))</f>
       </c>
       <c r="O303" s="120" t="str">
-        <f>IF($N303="","",ROUNDDOWN(ROUNDDOWN($N303,2)*$E303,3))</f>
+        <f>IF($N303="","",ROUNDUP(ROUNDUP($N303,2)*$E303,3))</f>
       </c>
       <c r="P303" s="121" t="str">
         <f>IF($L303="","",$I303*$L303)</f>
@@ -17576,10 +17577,10 @@
         <f>IF($L304="","",$C304*$L304)</f>
       </c>
       <c r="N304" s="119" t="str">
-        <f>IF($M304="","",ROUNDDOWN($C304+$M304,2))</f>
+        <f>IF($M304="","",ROUNDUP($C304+$M304,2))</f>
       </c>
       <c r="O304" s="120" t="str">
-        <f>IF($N304="","",ROUNDDOWN(ROUNDDOWN($N304,2)*$E304,3))</f>
+        <f>IF($N304="","",ROUNDUP(ROUNDUP($N304,2)*$E304,3))</f>
       </c>
       <c r="P304" s="121" t="str">
         <f>IF($L304="","",$I304*$L304)</f>
@@ -17630,10 +17631,10 @@
         <f>IF($L305="","",$C305*$L305)</f>
       </c>
       <c r="N305" s="119" t="str">
-        <f>IF($M305="","",ROUNDDOWN($C305+$M305,2))</f>
+        <f>IF($M305="","",ROUNDUP($C305+$M305,2))</f>
       </c>
       <c r="O305" s="120" t="str">
-        <f>IF($N305="","",ROUNDDOWN(ROUNDDOWN($N305,2)*$E305,3))</f>
+        <f>IF($N305="","",ROUNDUP(ROUNDUP($N305,2)*$E305,3))</f>
       </c>
       <c r="P305" s="121" t="str">
         <f>IF($L305="","",$I305*$L305)</f>
@@ -17684,10 +17685,10 @@
         <f>IF($L306="","",$C306*$L306)</f>
       </c>
       <c r="N306" s="119" t="str">
-        <f>IF($M306="","",ROUNDDOWN($C306+$M306,2))</f>
+        <f>IF($M306="","",ROUNDUP($C306+$M306,2))</f>
       </c>
       <c r="O306" s="120" t="str">
-        <f>IF($N306="","",ROUNDDOWN(ROUNDDOWN($N306,2)*$E306,3))</f>
+        <f>IF($N306="","",ROUNDUP(ROUNDUP($N306,2)*$E306,3))</f>
       </c>
       <c r="P306" s="121" t="str">
         <f>IF($L306="","",$I306*$L306)</f>
@@ -17738,10 +17739,10 @@
         <f>IF($L307="","",$C307*$L307)</f>
       </c>
       <c r="N307" s="119" t="str">
-        <f>IF($M307="","",ROUNDDOWN($C307+$M307,2))</f>
+        <f>IF($M307="","",ROUNDUP($C307+$M307,2))</f>
       </c>
       <c r="O307" s="120" t="str">
-        <f>IF($N307="","",ROUNDDOWN(ROUNDDOWN($N307,2)*$E307,3))</f>
+        <f>IF($N307="","",ROUNDUP(ROUNDUP($N307,2)*$E307,3))</f>
       </c>
       <c r="P307" s="121" t="str">
         <f>IF($L307="","",$I307*$L307)</f>
@@ -17792,10 +17793,10 @@
         <f>IF($L308="","",$C308*$L308)</f>
       </c>
       <c r="N308" s="119" t="str">
-        <f>IF($M308="","",ROUNDDOWN($C308+$M308,2))</f>
+        <f>IF($M308="","",ROUNDUP($C308+$M308,2))</f>
       </c>
       <c r="O308" s="120" t="str">
-        <f>IF($N308="","",ROUNDDOWN(ROUNDDOWN($N308,2)*$E308,3))</f>
+        <f>IF($N308="","",ROUNDUP(ROUNDUP($N308,2)*$E308,3))</f>
       </c>
       <c r="P308" s="121" t="str">
         <f>IF($L308="","",$I308*$L308)</f>
@@ -17846,10 +17847,10 @@
         <f>IF($L309="","",$C309*$L309)</f>
       </c>
       <c r="N309" s="119" t="str">
-        <f>IF($M309="","",ROUNDDOWN($C309+$M309,2))</f>
+        <f>IF($M309="","",ROUNDUP($C309+$M309,2))</f>
       </c>
       <c r="O309" s="120" t="str">
-        <f>IF($N309="","",ROUNDDOWN(ROUNDDOWN($N309,2)*$E309,3))</f>
+        <f>IF($N309="","",ROUNDUP(ROUNDUP($N309,2)*$E309,3))</f>
       </c>
       <c r="P309" s="121" t="str">
         <f>IF($L309="","",$I309*$L309)</f>
@@ -17900,10 +17901,10 @@
         <f>IF($L310="","",$C310*$L310)</f>
       </c>
       <c r="N310" s="119" t="str">
-        <f>IF($M310="","",ROUNDDOWN($C310+$M310,2))</f>
+        <f>IF($M310="","",ROUNDUP($C310+$M310,2))</f>
       </c>
       <c r="O310" s="120" t="str">
-        <f>IF($N310="","",ROUNDDOWN(ROUNDDOWN($N310,2)*$E310,3))</f>
+        <f>IF($N310="","",ROUNDUP(ROUNDUP($N310,2)*$E310,3))</f>
       </c>
       <c r="P310" s="121" t="str">
         <f>IF($L310="","",$I310*$L310)</f>
@@ -17954,10 +17955,10 @@
         <f>IF($L311="","",$C311*$L311)</f>
       </c>
       <c r="N311" s="119" t="str">
-        <f>IF($M311="","",ROUNDDOWN($C311+$M311,2))</f>
+        <f>IF($M311="","",ROUNDUP($C311+$M311,2))</f>
       </c>
       <c r="O311" s="120" t="str">
-        <f>IF($N311="","",ROUNDDOWN(ROUNDDOWN($N311,2)*$E311,3))</f>
+        <f>IF($N311="","",ROUNDUP(ROUNDUP($N311,2)*$E311,3))</f>
       </c>
       <c r="P311" s="121" t="str">
         <f>IF($L311="","",$I311*$L311)</f>
@@ -18008,10 +18009,10 @@
         <f>IF($L312="","",$C312*$L312)</f>
       </c>
       <c r="N312" s="119" t="str">
-        <f>IF($M312="","",ROUNDDOWN($C312+$M312,2))</f>
+        <f>IF($M312="","",ROUNDUP($C312+$M312,2))</f>
       </c>
       <c r="O312" s="120" t="str">
-        <f>IF($N312="","",ROUNDDOWN(ROUNDDOWN($N312,2)*$E312,3))</f>
+        <f>IF($N312="","",ROUNDUP(ROUNDUP($N312,2)*$E312,3))</f>
       </c>
       <c r="P312" s="121" t="str">
         <f>IF($L312="","",$I312*$L312)</f>
@@ -18062,10 +18063,10 @@
         <f>IF($L313="","",$C313*$L313)</f>
       </c>
       <c r="N313" s="119" t="str">
-        <f>IF($M313="","",ROUNDDOWN($C313+$M313,2))</f>
+        <f>IF($M313="","",ROUNDUP($C313+$M313,2))</f>
       </c>
       <c r="O313" s="120" t="str">
-        <f>IF($N313="","",ROUNDDOWN(ROUNDDOWN($N313,2)*$E313,3))</f>
+        <f>IF($N313="","",ROUNDUP(ROUNDUP($N313,2)*$E313,3))</f>
       </c>
       <c r="P313" s="121" t="str">
         <f>IF($L313="","",$I313*$L313)</f>
@@ -18116,10 +18117,10 @@
         <f>IF($L314="","",$C314*$L314)</f>
       </c>
       <c r="N314" s="119" t="str">
-        <f>IF($M314="","",ROUNDDOWN($C314+$M314,2))</f>
+        <f>IF($M314="","",ROUNDUP($C314+$M314,2))</f>
       </c>
       <c r="O314" s="120" t="str">
-        <f>IF($N314="","",ROUNDDOWN(ROUNDDOWN($N314,2)*$E314,3))</f>
+        <f>IF($N314="","",ROUNDUP(ROUNDUP($N314,2)*$E314,3))</f>
       </c>
       <c r="P314" s="121" t="str">
         <f>IF($L314="","",$I314*$L314)</f>
@@ -18170,10 +18171,10 @@
         <f>IF($L315="","",$C315*$L315)</f>
       </c>
       <c r="N315" s="119" t="str">
-        <f>IF($M315="","",ROUNDDOWN($C315+$M315,2))</f>
+        <f>IF($M315="","",ROUNDUP($C315+$M315,2))</f>
       </c>
       <c r="O315" s="120" t="str">
-        <f>IF($N315="","",ROUNDDOWN(ROUNDDOWN($N315,2)*$E315,3))</f>
+        <f>IF($N315="","",ROUNDUP(ROUNDUP($N315,2)*$E315,3))</f>
       </c>
       <c r="P315" s="121" t="str">
         <f>IF($L315="","",$I315*$L315)</f>
@@ -18224,10 +18225,10 @@
         <f>IF($L316="","",$C316*$L316)</f>
       </c>
       <c r="N316" s="119" t="str">
-        <f>IF($M316="","",ROUNDDOWN($C316+$M316,2))</f>
+        <f>IF($M316="","",ROUNDUP($C316+$M316,2))</f>
       </c>
       <c r="O316" s="120" t="str">
-        <f>IF($N316="","",ROUNDDOWN(ROUNDDOWN($N316,2)*$E316,3))</f>
+        <f>IF($N316="","",ROUNDUP(ROUNDUP($N316,2)*$E316,3))</f>
       </c>
       <c r="P316" s="121" t="str">
         <f>IF($L316="","",$I316*$L316)</f>
@@ -18278,10 +18279,10 @@
         <f>IF($L317="","",$C317*$L317)</f>
       </c>
       <c r="N317" s="119" t="str">
-        <f>IF($M317="","",ROUNDDOWN($C317+$M317,2))</f>
+        <f>IF($M317="","",ROUNDUP($C317+$M317,2))</f>
       </c>
       <c r="O317" s="120" t="str">
-        <f>IF($N317="","",ROUNDDOWN(ROUNDDOWN($N317,2)*$E317,3))</f>
+        <f>IF($N317="","",ROUNDUP(ROUNDUP($N317,2)*$E317,3))</f>
       </c>
       <c r="P317" s="121" t="str">
         <f>IF($L317="","",$I317*$L317)</f>
@@ -18332,10 +18333,10 @@
         <f>IF($L318="","",$C318*$L318)</f>
       </c>
       <c r="N318" s="119" t="str">
-        <f>IF($M318="","",ROUNDDOWN($C318+$M318,2))</f>
+        <f>IF($M318="","",ROUNDUP($C318+$M318,2))</f>
       </c>
       <c r="O318" s="120" t="str">
-        <f>IF($N318="","",ROUNDDOWN(ROUNDDOWN($N318,2)*$E318,3))</f>
+        <f>IF($N318="","",ROUNDUP(ROUNDUP($N318,2)*$E318,3))</f>
       </c>
       <c r="P318" s="121" t="str">
         <f>IF($L318="","",$I318*$L318)</f>
@@ -18386,10 +18387,10 @@
         <f>IF($L319="","",$C319*$L319)</f>
       </c>
       <c r="N319" s="119" t="str">
-        <f>IF($M319="","",ROUNDDOWN($C319+$M319,2))</f>
+        <f>IF($M319="","",ROUNDUP($C319+$M319,2))</f>
       </c>
       <c r="O319" s="120" t="str">
-        <f>IF($N319="","",ROUNDDOWN(ROUNDDOWN($N319,2)*$E319,3))</f>
+        <f>IF($N319="","",ROUNDUP(ROUNDUP($N319,2)*$E319,3))</f>
       </c>
       <c r="P319" s="121" t="str">
         <f>IF($L319="","",$I319*$L319)</f>
@@ -18440,10 +18441,10 @@
         <f>IF($L320="","",$C320*$L320)</f>
       </c>
       <c r="N320" s="119" t="str">
-        <f>IF($M320="","",ROUNDDOWN($C320+$M320,2))</f>
+        <f>IF($M320="","",ROUNDUP($C320+$M320,2))</f>
       </c>
       <c r="O320" s="120" t="str">
-        <f>IF($N320="","",ROUNDDOWN(ROUNDDOWN($N320,2)*$E320,3))</f>
+        <f>IF($N320="","",ROUNDUP(ROUNDUP($N320,2)*$E320,3))</f>
       </c>
       <c r="P320" s="121" t="str">
         <f>IF($L320="","",$I320*$L320)</f>
@@ -18494,10 +18495,10 @@
         <f>IF($L321="","",$C321*$L321)</f>
       </c>
       <c r="N321" s="119" t="str">
-        <f>IF($M321="","",ROUNDDOWN($C321+$M321,2))</f>
+        <f>IF($M321="","",ROUNDUP($C321+$M321,2))</f>
       </c>
       <c r="O321" s="120" t="str">
-        <f>IF($N321="","",ROUNDDOWN(ROUNDDOWN($N321,2)*$E321,3))</f>
+        <f>IF($N321="","",ROUNDUP(ROUNDUP($N321,2)*$E321,3))</f>
       </c>
       <c r="P321" s="121" t="str">
         <f>IF($L321="","",$I321*$L321)</f>
@@ -18548,10 +18549,10 @@
         <f>IF($L322="","",$C322*$L322)</f>
       </c>
       <c r="N322" s="119" t="str">
-        <f>IF($M322="","",ROUNDDOWN($C322+$M322,2))</f>
+        <f>IF($M322="","",ROUNDUP($C322+$M322,2))</f>
       </c>
       <c r="O322" s="120" t="str">
-        <f>IF($N322="","",ROUNDDOWN(ROUNDDOWN($N322,2)*$E322,3))</f>
+        <f>IF($N322="","",ROUNDUP(ROUNDUP($N322,2)*$E322,3))</f>
       </c>
       <c r="P322" s="121" t="str">
         <f>IF($L322="","",$I322*$L322)</f>
@@ -18602,10 +18603,10 @@
         <f>IF($L323="","",$C323*$L323)</f>
       </c>
       <c r="N323" s="119" t="str">
-        <f>IF($M323="","",ROUNDDOWN($C323+$M323,2))</f>
+        <f>IF($M323="","",ROUNDUP($C323+$M323,2))</f>
       </c>
       <c r="O323" s="120" t="str">
-        <f>IF($N323="","",ROUNDDOWN(ROUNDDOWN($N323,2)*$E323,3))</f>
+        <f>IF($N323="","",ROUNDUP(ROUNDUP($N323,2)*$E323,3))</f>
       </c>
       <c r="P323" s="121" t="str">
         <f>IF($L323="","",$I323*$L323)</f>
@@ -18656,10 +18657,10 @@
         <f>IF($L324="","",$C324*$L324)</f>
       </c>
       <c r="N324" s="119" t="str">
-        <f>IF($M324="","",ROUNDDOWN($C324+$M324,2))</f>
+        <f>IF($M324="","",ROUNDUP($C324+$M324,2))</f>
       </c>
       <c r="O324" s="120" t="str">
-        <f>IF($N324="","",ROUNDDOWN(ROUNDDOWN($N324,2)*$E324,3))</f>
+        <f>IF($N324="","",ROUNDUP(ROUNDUP($N324,2)*$E324,3))</f>
       </c>
       <c r="P324" s="121" t="str">
         <f>IF($L324="","",$I324*$L324)</f>
@@ -18710,10 +18711,10 @@
         <f>IF($L325="","",$C325*$L325)</f>
       </c>
       <c r="N325" s="119" t="str">
-        <f>IF($M325="","",ROUNDDOWN($C325+$M325,2))</f>
+        <f>IF($M325="","",ROUNDUP($C325+$M325,2))</f>
       </c>
       <c r="O325" s="120" t="str">
-        <f>IF($N325="","",ROUNDDOWN(ROUNDDOWN($N325,2)*$E325,3))</f>
+        <f>IF($N325="","",ROUNDUP(ROUNDUP($N325,2)*$E325,3))</f>
       </c>
       <c r="P325" s="121" t="str">
         <f>IF($L325="","",$I325*$L325)</f>
@@ -18764,10 +18765,10 @@
         <f>IF($L326="","",$C326*$L326)</f>
       </c>
       <c r="N326" s="119" t="str">
-        <f>IF($M326="","",ROUNDDOWN($C326+$M326,2))</f>
+        <f>IF($M326="","",ROUNDUP($C326+$M326,2))</f>
       </c>
       <c r="O326" s="120" t="str">
-        <f>IF($N326="","",ROUNDDOWN(ROUNDDOWN($N326,2)*$E326,3))</f>
+        <f>IF($N326="","",ROUNDUP(ROUNDUP($N326,2)*$E326,3))</f>
       </c>
       <c r="P326" s="121" t="str">
         <f>IF($L326="","",$I326*$L326)</f>
@@ -18818,10 +18819,10 @@
         <f>IF($L327="","",$C327*$L327)</f>
       </c>
       <c r="N327" s="119" t="str">
-        <f>IF($M327="","",ROUNDDOWN($C327+$M327,2))</f>
+        <f>IF($M327="","",ROUNDUP($C327+$M327,2))</f>
       </c>
       <c r="O327" s="120" t="str">
-        <f>IF($N327="","",ROUNDDOWN(ROUNDDOWN($N327,2)*$E327,3))</f>
+        <f>IF($N327="","",ROUNDUP(ROUNDUP($N327,2)*$E327,3))</f>
       </c>
       <c r="P327" s="121" t="str">
         <f>IF($L327="","",$I327*$L327)</f>
@@ -18872,10 +18873,10 @@
         <f>IF($L328="","",$C328*$L328)</f>
       </c>
       <c r="N328" s="119" t="str">
-        <f>IF($M328="","",ROUNDDOWN($C328+$M328,2))</f>
+        <f>IF($M328="","",ROUNDUP($C328+$M328,2))</f>
       </c>
       <c r="O328" s="120" t="str">
-        <f>IF($N328="","",ROUNDDOWN(ROUNDDOWN($N328,2)*$E328,3))</f>
+        <f>IF($N328="","",ROUNDUP(ROUNDUP($N328,2)*$E328,3))</f>
       </c>
       <c r="P328" s="121" t="str">
         <f>IF($L328="","",$I328*$L328)</f>
@@ -18926,10 +18927,10 @@
         <f>IF($L329="","",$C329*$L329)</f>
       </c>
       <c r="N329" s="119" t="str">
-        <f>IF($M329="","",ROUNDDOWN($C329+$M329,2))</f>
+        <f>IF($M329="","",ROUNDUP($C329+$M329,2))</f>
       </c>
       <c r="O329" s="120" t="str">
-        <f>IF($N329="","",ROUNDDOWN(ROUNDDOWN($N329,2)*$E329,3))</f>
+        <f>IF($N329="","",ROUNDUP(ROUNDUP($N329,2)*$E329,3))</f>
       </c>
       <c r="P329" s="121" t="str">
         <f>IF($L329="","",$I329*$L329)</f>
@@ -18980,10 +18981,10 @@
         <f>IF($L330="","",$C330*$L330)</f>
       </c>
       <c r="N330" s="119" t="str">
-        <f>IF($M330="","",ROUNDDOWN($C330+$M330,2))</f>
+        <f>IF($M330="","",ROUNDUP($C330+$M330,2))</f>
       </c>
       <c r="O330" s="120" t="str">
-        <f>IF($N330="","",ROUNDDOWN(ROUNDDOWN($N330,2)*$E330,3))</f>
+        <f>IF($N330="","",ROUNDUP(ROUNDUP($N330,2)*$E330,3))</f>
       </c>
       <c r="P330" s="121" t="str">
         <f>IF($L330="","",$I330*$L330)</f>
@@ -19034,10 +19035,10 @@
         <f>IF($L331="","",$C331*$L331)</f>
       </c>
       <c r="N331" s="119" t="str">
-        <f>IF($M331="","",ROUNDDOWN($C331+$M331,2))</f>
+        <f>IF($M331="","",ROUNDUP($C331+$M331,2))</f>
       </c>
       <c r="O331" s="120" t="str">
-        <f>IF($N331="","",ROUNDDOWN(ROUNDDOWN($N331,2)*$E331,3))</f>
+        <f>IF($N331="","",ROUNDUP(ROUNDUP($N331,2)*$E331,3))</f>
       </c>
       <c r="P331" s="121" t="str">
         <f>IF($L331="","",$I331*$L331)</f>
@@ -19088,10 +19089,10 @@
         <f>IF($L332="","",$C332*$L332)</f>
       </c>
       <c r="N332" s="119" t="str">
-        <f>IF($M332="","",ROUNDDOWN($C332+$M332,2))</f>
+        <f>IF($M332="","",ROUNDUP($C332+$M332,2))</f>
       </c>
       <c r="O332" s="120" t="str">
-        <f>IF($N332="","",ROUNDDOWN(ROUNDDOWN($N332,2)*$E332,3))</f>
+        <f>IF($N332="","",ROUNDUP(ROUNDUP($N332,2)*$E332,3))</f>
       </c>
       <c r="P332" s="121" t="str">
         <f>IF($L332="","",$I332*$L332)</f>
@@ -19142,10 +19143,10 @@
         <f>IF($L333="","",$C333*$L333)</f>
       </c>
       <c r="N333" s="119" t="str">
-        <f>IF($M333="","",ROUNDDOWN($C333+$M333,2))</f>
+        <f>IF($M333="","",ROUNDUP($C333+$M333,2))</f>
       </c>
       <c r="O333" s="120" t="str">
-        <f>IF($N333="","",ROUNDDOWN(ROUNDDOWN($N333,2)*$E333,3))</f>
+        <f>IF($N333="","",ROUNDUP(ROUNDUP($N333,2)*$E333,3))</f>
       </c>
       <c r="P333" s="121" t="str">
         <f>IF($L333="","",$I333*$L333)</f>
@@ -19196,10 +19197,10 @@
         <f>IF($L334="","",$C334*$L334)</f>
       </c>
       <c r="N334" s="119" t="str">
-        <f>IF($M334="","",ROUNDDOWN($C334+$M334,2))</f>
+        <f>IF($M334="","",ROUNDUP($C334+$M334,2))</f>
       </c>
       <c r="O334" s="120" t="str">
-        <f>IF($N334="","",ROUNDDOWN(ROUNDDOWN($N334,2)*$E334,3))</f>
+        <f>IF($N334="","",ROUNDUP(ROUNDUP($N334,2)*$E334,3))</f>
       </c>
       <c r="P334" s="121" t="str">
         <f>IF($L334="","",$I334*$L334)</f>
@@ -19250,10 +19251,10 @@
         <f>IF($L335="","",$C335*$L335)</f>
       </c>
       <c r="N335" s="119" t="str">
-        <f>IF($M335="","",ROUNDDOWN($C335+$M335,2))</f>
+        <f>IF($M335="","",ROUNDUP($C335+$M335,2))</f>
       </c>
       <c r="O335" s="120" t="str">
-        <f>IF($N335="","",ROUNDDOWN(ROUNDDOWN($N335,2)*$E335,3))</f>
+        <f>IF($N335="","",ROUNDUP(ROUNDUP($N335,2)*$E335,3))</f>
       </c>
       <c r="P335" s="121" t="str">
         <f>IF($L335="","",$I335*$L335)</f>
@@ -19304,10 +19305,10 @@
         <f>IF($L336="","",$C336*$L336)</f>
       </c>
       <c r="N336" s="119" t="str">
-        <f>IF($M336="","",ROUNDDOWN($C336+$M336,2))</f>
+        <f>IF($M336="","",ROUNDUP($C336+$M336,2))</f>
       </c>
       <c r="O336" s="120" t="str">
-        <f>IF($N336="","",ROUNDDOWN(ROUNDDOWN($N336,2)*$E336,3))</f>
+        <f>IF($N336="","",ROUNDUP(ROUNDUP($N336,2)*$E336,3))</f>
       </c>
       <c r="P336" s="121" t="str">
         <f>IF($L336="","",$I336*$L336)</f>
@@ -19358,10 +19359,10 @@
         <f>IF($L337="","",$C337*$L337)</f>
       </c>
       <c r="N337" s="119" t="str">
-        <f>IF($M337="","",ROUNDDOWN($C337+$M337,2))</f>
+        <f>IF($M337="","",ROUNDUP($C337+$M337,2))</f>
       </c>
       <c r="O337" s="120" t="str">
-        <f>IF($N337="","",ROUNDDOWN(ROUNDDOWN($N337,2)*$E337,3))</f>
+        <f>IF($N337="","",ROUNDUP(ROUNDUP($N337,2)*$E337,3))</f>
       </c>
       <c r="P337" s="121" t="str">
         <f>IF($L337="","",$I337*$L337)</f>
@@ -19412,10 +19413,10 @@
         <f>IF($L338="","",$C338*$L338)</f>
       </c>
       <c r="N338" s="119" t="str">
-        <f>IF($M338="","",ROUNDDOWN($C338+$M338,2))</f>
+        <f>IF($M338="","",ROUNDUP($C338+$M338,2))</f>
       </c>
       <c r="O338" s="120" t="str">
-        <f>IF($N338="","",ROUNDDOWN(ROUNDDOWN($N338,2)*$E338,3))</f>
+        <f>IF($N338="","",ROUNDUP(ROUNDUP($N338,2)*$E338,3))</f>
       </c>
       <c r="P338" s="121" t="str">
         <f>IF($L338="","",$I338*$L338)</f>
@@ -19466,10 +19467,10 @@
         <f>IF($L339="","",$C339*$L339)</f>
       </c>
       <c r="N339" s="119" t="str">
-        <f>IF($M339="","",ROUNDDOWN($C339+$M339,2))</f>
+        <f>IF($M339="","",ROUNDUP($C339+$M339,2))</f>
       </c>
       <c r="O339" s="120" t="str">
-        <f>IF($N339="","",ROUNDDOWN(ROUNDDOWN($N339,2)*$E339,3))</f>
+        <f>IF($N339="","",ROUNDUP(ROUNDUP($N339,2)*$E339,3))</f>
       </c>
       <c r="P339" s="121" t="str">
         <f>IF($L339="","",$I339*$L339)</f>
@@ -19520,10 +19521,10 @@
         <f>IF($L340="","",$C340*$L340)</f>
       </c>
       <c r="N340" s="119" t="str">
-        <f>IF($M340="","",ROUNDDOWN($C340+$M340,2))</f>
+        <f>IF($M340="","",ROUNDUP($C340+$M340,2))</f>
       </c>
       <c r="O340" s="120" t="str">
-        <f>IF($N340="","",ROUNDDOWN(ROUNDDOWN($N340,2)*$E340,3))</f>
+        <f>IF($N340="","",ROUNDUP(ROUNDUP($N340,2)*$E340,3))</f>
       </c>
       <c r="P340" s="121" t="str">
         <f>IF($L340="","",$I340*$L340)</f>
@@ -19574,10 +19575,10 @@
         <f>IF($L341="","",$C341*$L341)</f>
       </c>
       <c r="N341" s="119" t="str">
-        <f>IF($M341="","",ROUNDDOWN($C341+$M341,2))</f>
+        <f>IF($M341="","",ROUNDUP($C341+$M341,2))</f>
       </c>
       <c r="O341" s="120" t="str">
-        <f>IF($N341="","",ROUNDDOWN(ROUNDDOWN($N341,2)*$E341,3))</f>
+        <f>IF($N341="","",ROUNDUP(ROUNDUP($N341,2)*$E341,3))</f>
       </c>
       <c r="P341" s="121" t="str">
         <f>IF($L341="","",$I341*$L341)</f>
@@ -19628,10 +19629,10 @@
         <f>IF($L342="","",$C342*$L342)</f>
       </c>
       <c r="N342" s="119" t="str">
-        <f>IF($M342="","",ROUNDDOWN($C342+$M342,2))</f>
+        <f>IF($M342="","",ROUNDUP($C342+$M342,2))</f>
       </c>
       <c r="O342" s="120" t="str">
-        <f>IF($N342="","",ROUNDDOWN(ROUNDDOWN($N342,2)*$E342,3))</f>
+        <f>IF($N342="","",ROUNDUP(ROUNDUP($N342,2)*$E342,3))</f>
       </c>
       <c r="P342" s="121" t="str">
         <f>IF($L342="","",$I342*$L342)</f>
@@ -19682,10 +19683,10 @@
         <f>IF($L343="","",$C343*$L343)</f>
       </c>
       <c r="N343" s="119" t="str">
-        <f>IF($M343="","",ROUNDDOWN($C343+$M343,2))</f>
+        <f>IF($M343="","",ROUNDUP($C343+$M343,2))</f>
       </c>
       <c r="O343" s="120" t="str">
-        <f>IF($N343="","",ROUNDDOWN(ROUNDDOWN($N343,2)*$E343,3))</f>
+        <f>IF($N343="","",ROUNDUP(ROUNDUP($N343,2)*$E343,3))</f>
       </c>
       <c r="P343" s="121" t="str">
         <f>IF($L343="","",$I343*$L343)</f>
@@ -19736,10 +19737,10 @@
         <f>IF($L344="","",$C344*$L344)</f>
       </c>
       <c r="N344" s="119" t="str">
-        <f>IF($M344="","",ROUNDDOWN($C344+$M344,2))</f>
+        <f>IF($M344="","",ROUNDUP($C344+$M344,2))</f>
       </c>
       <c r="O344" s="120" t="str">
-        <f>IF($N344="","",ROUNDDOWN(ROUNDDOWN($N344,2)*$E344,3))</f>
+        <f>IF($N344="","",ROUNDUP(ROUNDUP($N344,2)*$E344,3))</f>
       </c>
       <c r="P344" s="121" t="str">
         <f>IF($L344="","",$I344*$L344)</f>
@@ -19790,10 +19791,10 @@
         <f>IF($L345="","",$C345*$L345)</f>
       </c>
       <c r="N345" s="119" t="str">
-        <f>IF($M345="","",ROUNDDOWN($C345+$M345,2))</f>
+        <f>IF($M345="","",ROUNDUP($C345+$M345,2))</f>
       </c>
       <c r="O345" s="120" t="str">
-        <f>IF($N345="","",ROUNDDOWN(ROUNDDOWN($N345,2)*$E345,3))</f>
+        <f>IF($N345="","",ROUNDUP(ROUNDUP($N345,2)*$E345,3))</f>
       </c>
       <c r="P345" s="121" t="str">
         <f>IF($L345="","",$I345*$L345)</f>
@@ -19844,10 +19845,10 @@
         <f>IF($L346="","",$C346*$L346)</f>
       </c>
       <c r="N346" s="119" t="str">
-        <f>IF($M346="","",ROUNDDOWN($C346+$M346,2))</f>
+        <f>IF($M346="","",ROUNDUP($C346+$M346,2))</f>
       </c>
       <c r="O346" s="120" t="str">
-        <f>IF($N346="","",ROUNDDOWN(ROUNDDOWN($N346,2)*$E346,3))</f>
+        <f>IF($N346="","",ROUNDUP(ROUNDUP($N346,2)*$E346,3))</f>
       </c>
       <c r="P346" s="121" t="str">
         <f>IF($L346="","",$I346*$L346)</f>
@@ -19898,10 +19899,10 @@
         <f>IF($L347="","",$C347*$L347)</f>
       </c>
       <c r="N347" s="119" t="str">
-        <f>IF($M347="","",ROUNDDOWN($C347+$M347,2))</f>
+        <f>IF($M347="","",ROUNDUP($C347+$M347,2))</f>
       </c>
       <c r="O347" s="120" t="str">
-        <f>IF($N347="","",ROUNDDOWN(ROUNDDOWN($N347,2)*$E347,3))</f>
+        <f>IF($N347="","",ROUNDUP(ROUNDUP($N347,2)*$E347,3))</f>
       </c>
       <c r="P347" s="121" t="str">
         <f>IF($L347="","",$I347*$L347)</f>
@@ -19952,10 +19953,10 @@
         <f>IF($L348="","",$C348*$L348)</f>
       </c>
       <c r="N348" s="119" t="str">
-        <f>IF($M348="","",ROUNDDOWN($C348+$M348,2))</f>
+        <f>IF($M348="","",ROUNDUP($C348+$M348,2))</f>
       </c>
       <c r="O348" s="120" t="str">
-        <f>IF($N348="","",ROUNDDOWN(ROUNDDOWN($N348,2)*$E348,3))</f>
+        <f>IF($N348="","",ROUNDUP(ROUNDUP($N348,2)*$E348,3))</f>
       </c>
       <c r="P348" s="121" t="str">
         <f>IF($L348="","",$I348*$L348)</f>
@@ -20006,10 +20007,10 @@
         <f>IF($L349="","",$C349*$L349)</f>
       </c>
       <c r="N349" s="119" t="str">
-        <f>IF($M349="","",ROUNDDOWN($C349+$M349,2))</f>
+        <f>IF($M349="","",ROUNDUP($C349+$M349,2))</f>
       </c>
       <c r="O349" s="120" t="str">
-        <f>IF($N349="","",ROUNDDOWN(ROUNDDOWN($N349,2)*$E349,3))</f>
+        <f>IF($N349="","",ROUNDUP(ROUNDUP($N349,2)*$E349,3))</f>
       </c>
       <c r="P349" s="121" t="str">
         <f>IF($L349="","",$I349*$L349)</f>
@@ -20060,10 +20061,10 @@
         <f>IF($L350="","",$C350*$L350)</f>
       </c>
       <c r="N350" s="119" t="str">
-        <f>IF($M350="","",ROUNDDOWN($C350+$M350,2))</f>
+        <f>IF($M350="","",ROUNDUP($C350+$M350,2))</f>
       </c>
       <c r="O350" s="120" t="str">
-        <f>IF($N350="","",ROUNDDOWN(ROUNDDOWN($N350,2)*$E350,3))</f>
+        <f>IF($N350="","",ROUNDUP(ROUNDUP($N350,2)*$E350,3))</f>
       </c>
       <c r="P350" s="121" t="str">
         <f>IF($L350="","",$I350*$L350)</f>
@@ -20114,10 +20115,10 @@
         <f>IF($L351="","",$C351*$L351)</f>
       </c>
       <c r="N351" s="119" t="str">
-        <f>IF($M351="","",ROUNDDOWN($C351+$M351,2))</f>
+        <f>IF($M351="","",ROUNDUP($C351+$M351,2))</f>
       </c>
       <c r="O351" s="120" t="str">
-        <f>IF($N351="","",ROUNDDOWN(ROUNDDOWN($N351,2)*$E351,3))</f>
+        <f>IF($N351="","",ROUNDUP(ROUNDUP($N351,2)*$E351,3))</f>
       </c>
       <c r="P351" s="121" t="str">
         <f>IF($L351="","",$I351*$L351)</f>
@@ -20168,10 +20169,10 @@
         <f>IF($L352="","",$C352*$L352)</f>
       </c>
       <c r="N352" s="119" t="str">
-        <f>IF($M352="","",ROUNDDOWN($C352+$M352,2))</f>
+        <f>IF($M352="","",ROUNDUP($C352+$M352,2))</f>
       </c>
       <c r="O352" s="120" t="str">
-        <f>IF($N352="","",ROUNDDOWN(ROUNDDOWN($N352,2)*$E352,3))</f>
+        <f>IF($N352="","",ROUNDUP(ROUNDUP($N352,2)*$E352,3))</f>
       </c>
       <c r="P352" s="121" t="str">
         <f>IF($L352="","",$I352*$L352)</f>
@@ -20222,10 +20223,10 @@
         <f>IF($L353="","",$C353*$L353)</f>
       </c>
       <c r="N353" s="119" t="str">
-        <f>IF($M353="","",ROUNDDOWN($C353+$M353,2))</f>
+        <f>IF($M353="","",ROUNDUP($C353+$M353,2))</f>
       </c>
       <c r="O353" s="120" t="str">
-        <f>IF($N353="","",ROUNDDOWN(ROUNDDOWN($N353,2)*$E353,3))</f>
+        <f>IF($N353="","",ROUNDUP(ROUNDUP($N353,2)*$E353,3))</f>
       </c>
       <c r="P353" s="121" t="str">
         <f>IF($L353="","",$I353*$L353)</f>
@@ -20276,10 +20277,10 @@
         <f>IF($L354="","",$C354*$L354)</f>
       </c>
       <c r="N354" s="132" t="str">
-        <f>IF($M354="","",ROUNDDOWN($C354+$M354,2))</f>
+        <f>IF($M354="","",ROUNDUP($C354+$M354,2))</f>
       </c>
       <c r="O354" s="133" t="str">
-        <f>IF($N354="","",ROUNDDOWN(ROUNDDOWN($N354,2)*$E354,3))</f>
+        <f>IF($N354="","",ROUNDUP(ROUNDUP($N354,2)*$E354,3))</f>
       </c>
       <c r="P354" s="134" t="str">
         <f>IF($L354="","",$I354*$L354)</f>
@@ -21255,8 +21256,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="90" t="str">
-        <v>Accountant - II - Finance &amp; Legal (B Support / Professional) - P2</v>
+      <c r="A2" s="90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accountant - II - Finance &amp; Legal (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B2" s="90" t="str">
         <v>H</v>
@@ -21296,8 +21299,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="91" t="str">
-        <v>Accountant - III - Finance &amp; Legal (B Support / Professional) - P3</v>
+      <c r="A3" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accountant - III - Finance &amp; Legal (B Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B3" s="91" t="str">
         <v>J</v>
@@ -21337,8 +21342,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="91" t="str">
-        <v>Administrative Assistant - II - Business Support (A) Admin/Finance/HR - B2</v>
+      <c r="A4" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrative Assistant - II - Business Support (A) Admin/Finance/HR - B2</t>
+        </is>
       </c>
       <c r="B4" s="91" t="str">
         <v>C</v>
@@ -21378,8 +21385,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="91" t="str">
-        <v>Administrative Assistant - III - Business Support (A) Admin/Finance/HR - B3</v>
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrative Assistant - III - Business Support (A) Admin/Finance/HR - B3</t>
+        </is>
       </c>
       <c r="B5" s="91" t="str">
         <v>D</v>
@@ -21419,8 +21428,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="str">
-        <v>Analytical Chemist - I - LAB (B Support / Research) - R1</v>
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analytical Chemist - I - LAB (B Support / Research) - R1</t>
+        </is>
       </c>
       <c r="B6" s="91" t="str">
         <v>E</v>
@@ -21454,8 +21465,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="str">
-        <v>Assembler - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</v>
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assembler - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</t>
+        </is>
       </c>
       <c r="B7" s="91" t="str">
         <v>B</v>
@@ -21477,8 +21490,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="str">
-        <v>Automation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B8" s="91" t="str">
         <v>J</v>
@@ -21500,8 +21515,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="str">
-        <v>Biochemical Operator – ll - Production &amp; Operations Support (T): Industrial – O2 (Mid)</v>
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biochemical Operator – ll - Production &amp; Operations Support (T): Industrial – O2 (Mid)</t>
+        </is>
       </c>
       <c r="B9" s="91" t="str">
         <v>C</v>
@@ -21523,8 +21540,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="str">
-        <v>Biochemist - I - LAB (B Support / Research) - R1</v>
+      <c r="A10" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biochemist - I - LAB (B Support / Research) - R1</t>
+        </is>
       </c>
       <c r="B10" s="91" t="str">
         <v>E</v>
@@ -21546,8 +21565,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="str">
-        <v>Biologist - I - LAB (B Support / Research) - R1</v>
+      <c r="A11" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biologist - I - LAB (B Support / Research) - R1</t>
+        </is>
       </c>
       <c r="B11" s="91" t="str">
         <v>E</v>
@@ -21569,8 +21590,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="str">
-        <v>Business Analyst - II - Information Communications Technology (B Support / Professional) - P2</v>
+      <c r="A12" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Analyst - II - Information Communications Technology (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B12" s="91" t="str">
         <v>H</v>
@@ -21592,8 +21615,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="91" t="str">
-        <v>Business Analyst - III - Information Communications Technology (B Support / Professional) - P3</v>
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Analyst - III - Information Communications Technology (B Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B13" s="91" t="str">
         <v>J</v>
@@ -21615,8 +21640,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="91" t="str">
-        <v>Business Analyst - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      <c r="A14" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Analyst - IV - Information Communications Technology (B Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B14" s="91" t="str">
         <v>L</v>
@@ -21638,8 +21665,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="91" t="str">
-        <v>Business Consultant - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business Consultant - IV - Information Communications Technology (B Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B15" s="91" t="str">
         <v>L</v>
@@ -21649,8 +21678,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="91" t="str">
-        <v>Chemical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B16" s="91" t="str">
         <v>J</v>
@@ -21660,8 +21691,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="91" t="str">
-        <v>Civil Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B17" s="91" t="str">
         <v>H</v>
@@ -21671,8 +21704,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="91" t="str">
-        <v>Civil Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Civil Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B18" s="91" t="str">
         <v>J</v>
@@ -21682,8 +21717,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="91" t="str">
-        <v>Compliance Specialist - I - Administrative (B Support / Professional) - P1</v>
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compliance Specialist - I - Administrative (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B19" s="91" t="str">
         <v>F</v>
@@ -21693,8 +21730,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="91" t="str">
-        <v>Data Analyst - II - Information Communications Technology (B Support / Professional) - P2</v>
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Analyst - II - Information Communications Technology (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B20" s="91" t="str">
         <v>H</v>
@@ -21704,8 +21743,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="91" t="str">
-        <v>Data Entry Clerk - III - Business Support (A) Admin/Finance/HR - B3</v>
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Entry Clerk - III - Business Support (A) Admin/Finance/HR - B3</t>
+        </is>
       </c>
       <c r="B21" s="91" t="str">
         <v>D</v>
@@ -21715,8 +21756,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="91" t="str">
-        <v>Documentation Specialist - I - Administrative (B Support / Professional) - P1</v>
+      <c r="A22" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation Specialist - I - Administrative (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B22" s="91" t="str">
         <v>F</v>
@@ -21726,8 +21769,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="91" t="str">
-        <v>Documentation Specialist - III - Administrative (B Support / Professional) - B3</v>
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation Specialist - III - Administrative (B Support / Professional) - B3</t>
+        </is>
       </c>
       <c r="B23" s="91" t="str">
         <v>D</v>
@@ -21737,8 +21782,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="91" t="str">
-        <v>Electrical Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical Engineer - I - Engineering (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B24" s="91" t="str">
         <v>F</v>
@@ -21748,8 +21795,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="91" t="str">
-        <v>Electrical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B25" s="91" t="str">
         <v>J</v>
@@ -21759,8 +21808,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="91" t="str">
-        <v>Environmental Monitoring Specialist II - Environment Health &amp; Safety P&amp;O Support / Professional P2</v>
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environmental Monitoring Specialist II - Environment Health &amp; Safety P&amp;O Support / Professional P2</t>
+        </is>
       </c>
       <c r="B26" s="91" t="str">
         <v>H</v>
@@ -21770,8 +21821,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="91" t="str">
-        <v>Executive Assistant - II - Business Support (A) Admin/Finance/HR - B2</v>
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Executive Assistant - II - Business Support (A) Admin/Finance/HR - B2</t>
+        </is>
       </c>
       <c r="B27" s="91" t="str">
         <v>C</v>
@@ -21781,8 +21834,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="91" t="str">
-        <v>Health/Safety Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</v>
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health/Safety Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B28" s="91" t="str">
         <v>H</v>
@@ -21792,8 +21847,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="91" t="str">
-        <v>Health/Safety Specialist - III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</v>
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health/Safety Specialist - III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B29" s="91" t="str">
         <v>J</v>
@@ -21803,8 +21860,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="91" t="str">
-        <v>Health/Safety Specialist - IV - Environment Health &amp; Safety (P &amp; O Support / Professional) - P4</v>
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health/Safety Specialist - IV - Environment Health &amp; Safety (P &amp; O Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B30" s="91" t="str">
         <v>M</v>
@@ -21814,8 +21873,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="91" t="str">
-        <v>HR Analyst - I - Human Resources (B Support / Professional) - P1</v>
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR Analyst - I - Human Resources (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B31" s="91" t="str">
         <v>F</v>
@@ -21825,8 +21886,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="91" t="str">
-        <v>HR Analyst - II - Human Resources (B Support / Professional) - P2</v>
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HR Analyst - II - Human Resources (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B32" s="91" t="str">
         <v>H</v>
@@ -21836,8 +21899,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="91" t="str">
-        <v>Industrial Hygienist - I - Environment Health  &amp; Safety P&amp;O Support / Professional - P1</v>
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial Hygienist - I - Environment Health  &amp; Safety P&amp;O Support / Professional - P1</t>
+        </is>
       </c>
       <c r="B33" s="91" t="str">
         <v>G</v>
@@ -21847,8 +21912,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="91" t="str">
-        <v>Industrial Hygienist - II - Environment  Health &amp; Safety P&amp;O Support / Professional - P2</v>
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial Hygienist - II - Environment  Health &amp; Safety P&amp;O Support / Professional - P2</t>
+        </is>
       </c>
       <c r="B34" s="91" t="str">
         <v>H</v>
@@ -21858,8 +21925,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="91" t="str">
-        <v>Inspector Operator - III - Industrial (P &amp; O Support / Professional) - O3</v>
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspector Operator - III - Industrial (P &amp; O Support / Professional) - O3</t>
+        </is>
       </c>
       <c r="B35" s="91" t="str">
         <v>E</v>
@@ -21869,8 +21938,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="91" t="str">
-        <v>Lab Assistant - III - Business Support (T) Science/Medical/Clinical - B3</v>
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab Assistant - III - Business Support (T) Science/Medical/Clinical - B3</t>
+        </is>
       </c>
       <c r="B36" s="91" t="str">
         <v>D</v>
@@ -21880,8 +21951,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="91" t="str">
-        <v>Lab Technician - Animal - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mi</v>
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab Technician - Animal - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mi</t>
+        </is>
       </c>
       <c r="B37" s="91" t="str">
         <v>C</v>
@@ -21891,8 +21964,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="91" t="str">
-        <v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (High)</v>
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (High)</t>
+        </is>
       </c>
       <c r="B38" s="91" t="str">
         <v>D</v>
@@ -21902,8 +21977,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="91" t="str">
-        <v>Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mid)</v>
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab Technician - II - Production &amp; Operations Support (T) Science/Medical/Clinical - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B39" s="91" t="str">
         <v>C</v>
@@ -21913,8 +21990,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="91" t="str">
-        <v>Lab Technician - III - Production &amp; Operations Support (T) Science/Medical/Clinical - O3</v>
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lab Technician - III - Production &amp; Operations Support (T) Science/Medical/Clinical - O3</t>
+        </is>
       </c>
       <c r="B40" s="91" t="str">
         <v>D</v>
@@ -21924,8 +22003,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="91" t="str">
-        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Technician - II - Production &amp; Operations Support (T): Industrial - O2 (High)</t>
+        </is>
       </c>
       <c r="B41" s="91" t="str">
         <v>D</v>
@@ -21935,8 +22016,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="91" t="str">
-        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O2 High – PS</v>
+      <c r="A42" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O2 High – PS</t>
+        </is>
       </c>
       <c r="B42" s="91" t="str">
         <v>D</v>
@@ -21946,8 +22029,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="91" t="str">
-        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O3 – PS</v>
+      <c r="A43" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O3 – PS</t>
+        </is>
       </c>
       <c r="B43" s="91" t="str">
         <v>E</v>
@@ -21957,8 +22042,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="91" t="str">
-        <v>Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O4 – PS</v>
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Technician - II - Production &amp; Operations Support (T): Industrial O4 – PS</t>
+        </is>
       </c>
       <c r="B44" s="91" t="str">
         <v>F</v>
@@ -21968,8 +22055,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="91" t="str">
-        <v>Maintenance Technician - IV - Production &amp; Operations Support (T): Industrial - O4</v>
+      <c r="A45" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintenance Technician - IV - Production &amp; Operations Support (T): Industrial - O4</t>
+        </is>
       </c>
       <c r="B45" s="91" t="str">
         <v>F</v>
@@ -21979,8 +22068,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="91" t="str">
-        <v>Marketing Research Specialist - II - Creative (B Support / Professional) - P2</v>
+      <c r="A46" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing Research Specialist - II - Creative (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B46" s="91" t="str">
         <v>H</v>
@@ -21990,8 +22081,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="91" t="str">
-        <v>Mechanical Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A47" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B47" s="91" t="str">
         <v>H</v>
@@ -22001,8 +22094,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="91" t="str">
-        <v>Mechanical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A48" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B48" s="91" t="str">
         <v>J</v>
@@ -22012,8 +22107,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="91" t="str">
-        <v>Operations Manager - I - Industrial (P &amp; O Support / Professional) - P1</v>
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operations Manager - I - Industrial (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B49" s="91" t="str">
         <v>G</v>
@@ -22023,8 +22120,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="91" t="str">
-        <v>Operations Manager - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      <c r="A50" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operations Manager - II - Industrial (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B50" s="91" t="str">
         <v>H</v>
@@ -22034,8 +22133,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="91" t="str">
-        <v>Operations Manager - IV - Industrial (P &amp; O Support / Professional) - P4</v>
+      <c r="A51" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operations Manager - IV - Industrial (P &amp; O Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B51" s="91" t="str">
         <v>L</v>
@@ -22045,8 +22146,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="91" t="str">
-        <v>Packaging Engineer - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      <c r="A52" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Packaging Engineer - II - Industrial (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B52" s="91" t="str">
         <v>H</v>
@@ -22056,8 +22159,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="91" t="str">
-        <v>Packaging Operator - I - Production &amp; Operations Support (T): Industrial - O1</v>
+      <c r="A53" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Packaging Operator - I - Production &amp; Operations Support (T): Industrial - O1</t>
+        </is>
       </c>
       <c r="B53" s="91" t="str">
         <v>B</v>
@@ -22067,8 +22172,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="91" t="str">
-        <v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</v>
+      <c r="A54" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Low)</t>
+        </is>
       </c>
       <c r="B54" s="91" t="str">
         <v>B</v>
@@ -22078,8 +22185,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="91" t="str">
-        <v>Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      <c r="A55" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Packaging Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B55" s="91" t="str">
         <v>C</v>
@@ -22089,8 +22198,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="91" t="str">
-        <v>Packaging Operator - III - Production &amp; Operations Support (T): Industrial - O3</v>
+      <c r="A56" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Packaging Operator - III - Production &amp; Operations Support (T): Industrial - O3</t>
+        </is>
       </c>
       <c r="B56" s="91" t="str">
         <v>E</v>
@@ -22100,8 +22211,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="91" t="str">
-        <v>Pharmaceutical Specialist - I - Engineering (P &amp; O  Support / Professional) - P1</v>
+      <c r="A57" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmaceutical Specialist - I - Engineering (P &amp; O  Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B57" s="91" t="str">
         <v>F</v>
@@ -22111,8 +22224,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="91" t="str">
-        <v>Pharmaceutical Specialist - Ill - Engineering (P &amp; O  Support / Professional) - P3</v>
+      <c r="A58" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmaceutical Specialist - Ill - Engineering (P &amp; O  Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B58" s="91" t="str">
         <v>J</v>
@@ -22122,8 +22237,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="91" t="str">
-        <v>Process Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A59" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B59" s="91" t="str">
         <v>H</v>
@@ -22133,8 +22250,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="91" t="str">
-        <v>Process Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A60" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B60" s="91" t="str">
         <v>J</v>
@@ -22144,8 +22263,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="91" t="str">
-        <v>Process Engineer - IV - Engineering (P &amp; O Support / Professional) - P4</v>
+      <c r="A61" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process Engineer - IV - Engineering (P &amp; O Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B61" s="91" t="str">
         <v>L</v>
@@ -22155,8 +22276,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="91" t="str">
-        <v>Procurement Specialist - llI - Administrative (B Support /  Professional) - P3</v>
+      <c r="A62" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procurement Specialist - llI - Administrative (B Support /  Professional) - P3</t>
+        </is>
       </c>
       <c r="B62" s="91" t="str">
         <v>J</v>
@@ -22166,8 +22289,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="91" t="str">
-        <v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      <c r="A63" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (High)</t>
+        </is>
       </c>
       <c r="B63" s="91" t="str">
         <v>D</v>
@@ -22177,8 +22302,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="91" t="str">
-        <v>Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      <c r="A64" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production Operator - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B64" s="91" t="str">
         <v>C</v>
@@ -22188,8 +22315,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="91" t="str">
-        <v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (High)</v>
+      <c r="A65" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (High)</t>
+        </is>
       </c>
       <c r="B65" s="91" t="str">
         <v>D</v>
@@ -22199,8 +22328,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="91" t="str">
-        <v>Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      <c r="A66" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production Tech - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B66" s="91" t="str">
         <v>C</v>
@@ -22210,8 +22341,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="91" t="str">
-        <v>Project Coordinator - I - Administrative (B Support / Professional) - P1</v>
+      <c r="A67" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Coordinator - I - Administrative (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B67" s="91" t="str">
         <v>F</v>
@@ -22221,8 +22354,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="91" t="str">
-        <v>Project Coordinator - II - Administrative (B Support / Professional) - P2</v>
+      <c r="A68" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Coordinator - II - Administrative (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B68" s="91" t="str">
         <v>H</v>
@@ -22232,8 +22367,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="91" t="str">
-        <v>Project Manager - Il - Engineering (P &amp; O Support /  Professional) - P2</v>
+      <c r="A69" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - Il - Engineering (P &amp; O Support /  Professional) - P2</t>
+        </is>
       </c>
       <c r="B69" s="91" t="str">
         <v>H</v>
@@ -22243,8 +22380,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="91" t="str">
-        <v>Project Manager - Ill - Engineering (P &amp; O Support /  Professional) - P3</v>
+      <c r="A70" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - Ill - Engineering (P &amp; O Support /  Professional) - P3</t>
+        </is>
       </c>
       <c r="B70" s="91" t="str">
         <v>J</v>
@@ -22254,8 +22393,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="91" t="str">
-        <v>Project Manager - IT - II - Information Communications Technology (B Support / Professional) - P2</v>
+      <c r="A71" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - IT - II - Information Communications Technology (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B71" s="91" t="str">
         <v>H</v>
@@ -22265,8 +22406,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="91" t="str">
-        <v>Project Manager - IT - III - Information Communications Technology (B Support / Professional) - P3</v>
+      <c r="A72" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - IT - III - Information Communications Technology (B Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B72" s="91" t="str">
         <v>J</v>
@@ -22276,8 +22419,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="91" t="str">
-        <v>Project Manager - IT - IV - Information Communications Technology (B Support / Professional) - P4</v>
+      <c r="A73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - IT - IV - Information Communications Technology (B Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B73" s="91" t="str">
         <v>M</v>
@@ -22287,8 +22432,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="91" t="str">
-        <v>Project Manager - IV - Engineering (P &amp; O Support /  Professional) - P4</v>
+      <c r="A74" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - IV - Engineering (P &amp; O Support /  Professional) - P4</t>
+        </is>
       </c>
       <c r="B74" s="91" t="str">
         <v>L</v>
@@ -22298,8 +22445,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="91" t="str">
-        <v>Project Manager - Non IT - II - Administrative (B Support / Professional) - P2</v>
+      <c r="A75" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - Non IT - II - Administrative (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B75" s="91" t="str">
         <v>H</v>
@@ -22309,8 +22458,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="91" t="str">
-        <v>Project Manager - Non IT - III - Administrative (B Support / Professional) - P3</v>
+      <c r="A76" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - Non IT - III - Administrative (B Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B76" s="91" t="str">
         <v>J</v>
@@ -22320,8 +22471,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="91" t="str">
-        <v>Project Manager - Non IT - IV - Administrative (B Support / Professional) - P4</v>
+      <c r="A77" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Manager - Non IT - IV - Administrative (B Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B77" s="91" t="str">
         <v>L</v>
@@ -22331,8 +22484,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="91" t="str">
-        <v>Qualified Person - III - Administrative (B Support /  Professional) - P3</v>
+      <c r="A78" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qualified Person - III - Administrative (B Support /  Professional) - P3</t>
+        </is>
       </c>
       <c r="B78" s="91" t="str">
         <v>J</v>
@@ -22342,8 +22497,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="91" t="str">
-        <v>Quality Assurance - Packaging - I - Industrial (P &amp; O Support / Professional) - P1</v>
+      <c r="A79" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Assurance - Packaging - I - Industrial (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B79" s="91" t="str">
         <v>G</v>
@@ -22353,8 +22510,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="91" t="str">
-        <v>Quality Assurance - Packaging - II - Industrial (P &amp; O Support / Professional) - P2</v>
+      <c r="A80" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Assurance - Packaging - II - Industrial (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B80" s="91" t="str">
         <v>H</v>
@@ -22364,8 +22523,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="91" t="str">
-        <v>Quality Assurance - Packaging - IV - Industrial (P &amp; O Support / Professional) - P4</v>
+      <c r="A81" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Assurance - Packaging - IV - Industrial (P &amp; O Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B81" s="91" t="str">
         <v>L</v>
@@ -22375,8 +22536,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="91" t="str">
-        <v>Quality Auditor - I - Administrative (B Support / Professional) - P1</v>
+      <c r="A82" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Auditor - I - Administrative (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B82" s="91" t="str">
         <v>F</v>
@@ -22386,8 +22549,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="91" t="str">
-        <v>Quality Auditor - II - Administrative (B Support / Professional) - P2</v>
+      <c r="A83" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Auditor - II - Administrative (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B83" s="91" t="str">
         <v>H</v>
@@ -22397,8 +22562,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="91" t="str">
-        <v>Quality Auditor - III - Administrative (B Support / Professional) - P3</v>
+      <c r="A84" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Auditor - III - Administrative (B Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B84" s="91" t="str">
         <v>J</v>
@@ -22408,8 +22575,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="91" t="str">
-        <v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (High)</v>
+      <c r="A85" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Control Specialist - II - LAB (O Support / Research) - O2 (High)</t>
+        </is>
       </c>
       <c r="B85" s="91" t="str">
         <v>D</v>
@@ -22419,8 +22588,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="91" t="str">
-        <v>Quality Control Specialist - II - LAB (O Support / Research) - O2 (Mid)</v>
+      <c r="A86" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Control Specialist - II - LAB (O Support / Research) - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B86" s="91" t="str">
         <v>C</v>
@@ -22430,8 +22601,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="91" t="str">
-        <v>Quality Control Specialist - III - LAB (O Support / Research) - O3</v>
+      <c r="A87" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Control Specialist - III - LAB (O Support / Research) - O3</t>
+        </is>
       </c>
       <c r="B87" s="91" t="str">
         <v>E</v>
@@ -22441,8 +22614,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="91" t="str">
-        <v>Quality Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A88" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B88" s="91" t="str">
         <v>H</v>
@@ -22452,8 +22627,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="91" t="str">
-        <v>Regulatory Affairs Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</v>
+      <c r="A89" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulatory Affairs Specialist - II - Environment Health &amp; Safety (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B89" s="91" t="str">
         <v>H</v>
@@ -22463,8 +22640,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="91" t="str">
-        <v>Regulatory Affairs Specialist III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</v>
+      <c r="A90" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulatory Affairs Specialist III - Environment Health &amp; Safety (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B90" s="91" t="str">
         <v>J</v>
@@ -22474,8 +22653,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="91" t="str">
-        <v>Reliability Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      <c r="A91" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability Engineer - I - Engineering (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B91" s="91" t="str">
         <v>F</v>
@@ -22485,8 +22666,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="91" t="str">
-        <v>Reliability Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A92" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B92" s="91" t="str">
         <v>H</v>
@@ -22496,8 +22679,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="91" t="str">
-        <v>Reliability Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A93" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B93" s="91" t="str">
         <v>J</v>
@@ -22507,8 +22692,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="91" t="str">
-        <v>Reliability Engineer - IV - Engineering (P &amp; O Support / Professional) - O4</v>
+      <c r="A94" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reliability Engineer - IV - Engineering (P &amp; O Support / Professional) - O4</t>
+        </is>
       </c>
       <c r="B94" s="91" t="str">
         <v>G</v>
@@ -22518,8 +22705,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="91" t="str">
-        <v>Sales Assistant - I - Administrative (B Support / Professional) - P1</v>
+      <c r="A95" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sales Assistant - I - Administrative (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B95" s="91" t="str">
         <v>G</v>
@@ -22529,8 +22718,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="91" t="str">
-        <v>Scientific Technical Specialist - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      <c r="A96" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientific Technical Specialist - I - Engineering (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B96" s="91" t="str">
         <v>F</v>
@@ -22540,8 +22731,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="91" t="str">
-        <v>Scientific Technical Specialist - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A97" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientific Technical Specialist - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B97" s="91" t="str">
         <v>H</v>
@@ -22551,8 +22744,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="91" t="str">
-        <v>Scientific Technical Specialist - III - Engineering (P &amp; O Support / Professional) - O3</v>
+      <c r="A98" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientific Technical Specialist - III - Engineering (P &amp; O Support / Professional) - O3</t>
+        </is>
       </c>
       <c r="B98" s="91" t="str">
         <v>E</v>
@@ -22562,8 +22757,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="91" t="str">
-        <v>Scientist - I - Science (P &amp; O / Research) - R1</v>
+      <c r="A99" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientist - I - Science (P &amp; O / Research) - R1</t>
+        </is>
       </c>
       <c r="B99" s="91" t="str">
         <v>E</v>
@@ -22573,8 +22770,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="91" t="str">
-        <v>Scientist - I - Science (P &amp; O / Research) - R1 - GS</v>
+      <c r="A100" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientist - I - Science (P &amp; O / Research) - R1 - GS</t>
+        </is>
       </c>
       <c r="B100" s="91" t="str">
         <v>E</v>
@@ -22584,8 +22783,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="91" t="str">
-        <v>Scientist - II - Science (P &amp; O / Research) - R2</v>
+      <c r="A101" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientist - II - Science (P &amp; O / Research) - R2</t>
+        </is>
       </c>
       <c r="B101" s="91" t="str">
         <v>G</v>
@@ -22595,8 +22796,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="91" t="str">
-        <v>Scientist - III - Science (P &amp; O / Research) - R3</v>
+      <c r="A102" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientist - III - Science (P &amp; O / Research) - R3</t>
+        </is>
       </c>
       <c r="B102" s="91" t="str">
         <v>J</v>
@@ -22606,8 +22809,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="91" t="str">
-        <v>Shipping/Receiving Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      <c r="A103" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shipping/Receiving Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B103" s="91" t="str">
         <v>C</v>
@@ -22617,8 +22822,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="91" t="str">
-        <v>Supply Chain Specialist - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A104" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supply Chain Specialist - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B104" s="91" t="str">
         <v>H</v>
@@ -22628,8 +22835,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="91" t="str">
-        <v>Supply Chain Specialist - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A105" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supply Chain Specialist - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B105" s="91" t="str">
         <v>J</v>
@@ -22639,8 +22848,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="91" t="str">
-        <v>Supply Chain Specialist - IV - Engineering (P &amp; O Support / Professional) - P4</v>
+      <c r="A106" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supply Chain Specialist - IV - Engineering (P &amp; O Support / Professional) - P4</t>
+        </is>
       </c>
       <c r="B106" s="91" t="str">
         <v>L</v>
@@ -22650,8 +22861,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="91" t="str">
-        <v>Technical Support Analyst - I - Information Communications Tech (B Support / Professional) - P1</v>
+      <c r="A107" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Support Analyst - I - Information Communications Tech (B Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B107" s="91" t="str">
         <v>G</v>
@@ -22661,8 +22874,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="91" t="str">
-        <v>Technical Support Analyst - II - Information Communications Tech (B Support / Professional) - P2</v>
+      <c r="A108" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Support Analyst - II - Information Communications Tech (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B108" s="91" t="str">
         <v>H</v>
@@ -22672,8 +22887,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="91" t="str">
-        <v>Technical Writer - II - Information Communications Technology (B Support / Professional) - P2</v>
+      <c r="A109" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Writer - II - Information Communications Technology (B Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B109" s="91" t="str">
         <v>H</v>
@@ -22683,8 +22900,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="91" t="str">
-        <v>Validation Engineer - I - Engineering (P &amp; O Support / Professional) - P1</v>
+      <c r="A110" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validation Engineer - I - Engineering (P &amp; O Support / Professional) - P1</t>
+        </is>
       </c>
       <c r="B110" s="91" t="str">
         <v>G</v>
@@ -22694,8 +22913,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="91" t="str">
-        <v>Validation Engineer - II - Engineering (P &amp; O Support / Professional) - P2</v>
+      <c r="A111" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validation Engineer - II - Engineering (P &amp; O Support / Professional) - P2</t>
+        </is>
       </c>
       <c r="B111" s="91" t="str">
         <v>H</v>
@@ -22705,8 +22926,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="91" t="str">
-        <v>Validation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</v>
+      <c r="A112" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validation Engineer - III - Engineering (P &amp; O Support / Professional) - P3</t>
+        </is>
       </c>
       <c r="B112" s="91" t="str">
         <v>J</v>
@@ -22716,8 +22939,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="92" t="str">
-        <v>Warehouse Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</v>
+      <c r="A113" s="92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warehouse Clerk - II - Production &amp; Operations Support (T): Industrial - O2 (Mid)</t>
+        </is>
       </c>
       <c r="B113" s="92" t="str">
         <v>C</v>
@@ -22729,7 +22954,8 @@
     <row r="114">
       <c r="A114" s="92" t="inlineStr">
         <is>
-          <t xml:space="preserve">CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)</t>
+          <t xml:space="preserve">CQ engineer  Site Engineering P1-G midpoint   (CQ=Commissioning&amp;Qualification)
+1 stap boven mid</t>
         </is>
       </c>
       <c r="B114" s="92" t="inlineStr">
@@ -22780,7 +23006,8 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.</t>
+          <t xml:space="preserve">SPOC=Programma-manager Site Engineering  P3-J  Tussen midpoint en max.
+2 stappen boven mid 1 stap  onder max</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -22797,7 +23024,8 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Projectmanager Site Engineering P2-H Tussen midpoint en max.</t>
+          <t xml:space="preserve">Projectmanager Site Engineering P2-H Tussen midpoint en max.
+2 stappen boven mid 1 stap onder max</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -22814,7 +23042,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Civil engineer Site Engineering P1-G midpoint 1 stap boven</t>
+          <t xml:space="preserve">Civil engineer Site Engineering P1-G midpoint 1 stap boven</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
